--- a/jogos_2026-05-04.xlsx
+++ b/jogos_2026-05-04.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>7.41</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.55</v>
+        <v>3.25</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.28</v>
+        <v>2.95</v>
       </c>
       <c r="R38" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G73" t="n">

--- a/jogos_2026-05-04.xlsx
+++ b/jogos_2026-05-04.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI75"/>
+  <dimension ref="A1:BI77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>7.41</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>7.41</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4482,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="BI20" s="3" t="n">
-        <v>46146.51041666666</v>
+        <v>46146.5</v>
       </c>
     </row>
     <row r="21">
@@ -4491,12 +4491,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4679,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
-        <v>46146.52083333334</v>
+        <v>46146.51041666666</v>
       </c>
     </row>
     <row r="22">
@@ -4688,27 +4688,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
-        <v>46146.54166666666</v>
+        <v>46146.52083333334</v>
       </c>
     </row>
     <row r="23">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7052,27 +7052,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7240,7 +7240,7 @@
         <v>0</v>
       </c>
       <c r="BI34" s="3" t="n">
-        <v>46146.54861111111</v>
+        <v>46146.54166666666</v>
       </c>
     </row>
     <row r="35">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7437,7 +7437,7 @@
         <v>0</v>
       </c>
       <c r="BI35" s="3" t="n">
-        <v>46146.55555555555</v>
+        <v>46146.54861111111</v>
       </c>
     </row>
     <row r="36">
@@ -7446,12 +7446,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7634,7 +7634,7 @@
         <v>0</v>
       </c>
       <c r="BI36" s="3" t="n">
-        <v>46146.5625</v>
+        <v>46146.55555555555</v>
       </c>
     </row>
     <row r="37">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>3.25</v>
+        <v>2.55</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.95</v>
+        <v>3.28</v>
       </c>
       <c r="R38" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8234,12 +8234,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8422,7 +8422,7 @@
         <v>0</v>
       </c>
       <c r="BI40" s="3" t="n">
-        <v>46146.58333333334</v>
+        <v>46146.5625</v>
       </c>
     </row>
     <row r="41">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10401,27 +10401,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10589,7 +10589,7 @@
         <v>0</v>
       </c>
       <c r="BI51" s="3" t="n">
-        <v>46146.58680555555</v>
+        <v>46146.58333333334</v>
       </c>
     </row>
     <row r="52">
@@ -10598,12 +10598,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10786,7 +10786,7 @@
         <v>0</v>
       </c>
       <c r="BI52" s="3" t="n">
-        <v>46146.60416666666</v>
+        <v>46146.58333333334</v>
       </c>
     </row>
     <row r="53">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10983,7 +10983,7 @@
         <v>0</v>
       </c>
       <c r="BI53" s="3" t="n">
-        <v>46146.60416666666</v>
+        <v>46146.58680555555</v>
       </c>
     </row>
     <row r="54">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11189,27 +11189,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11377,7 +11377,7 @@
         <v>0</v>
       </c>
       <c r="BI55" s="3" t="n">
-        <v>46146.625</v>
+        <v>46146.60416666666</v>
       </c>
     </row>
     <row r="56">
@@ -11386,12 +11386,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11574,7 +11574,7 @@
         <v>0</v>
       </c>
       <c r="BI56" s="3" t="n">
-        <v>46146.625</v>
+        <v>46146.60416666666</v>
       </c>
     </row>
     <row r="57">
@@ -11780,12 +11780,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11968,7 +11968,7 @@
         <v>0</v>
       </c>
       <c r="BI58" s="3" t="n">
-        <v>46146.64583333334</v>
+        <v>46146.625</v>
       </c>
     </row>
     <row r="59">
@@ -11977,12 +11977,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12165,7 +12165,7 @@
         <v>0</v>
       </c>
       <c r="BI59" s="3" t="n">
-        <v>46146.64583333334</v>
+        <v>46146.625</v>
       </c>
     </row>
     <row r="60">
@@ -12174,12 +12174,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12362,7 +12362,7 @@
         <v>0</v>
       </c>
       <c r="BI60" s="3" t="n">
-        <v>46146.65625</v>
+        <v>46146.64583333334</v>
       </c>
     </row>
     <row r="61">
@@ -12371,12 +12371,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF61" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12559,7 +12559,7 @@
         <v>0</v>
       </c>
       <c r="BI61" s="3" t="n">
-        <v>46146.66666666666</v>
+        <v>46146.64583333334</v>
       </c>
     </row>
     <row r="62">
@@ -12568,12 +12568,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12756,7 +12756,7 @@
         <v>0</v>
       </c>
       <c r="BI62" s="3" t="n">
-        <v>46146.66666666666</v>
+        <v>46146.65625</v>
       </c>
     </row>
     <row r="63">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12953,7 +12953,7 @@
         <v>0</v>
       </c>
       <c r="BI63" s="3" t="n">
-        <v>46146.67708333334</v>
+        <v>46146.66666666666</v>
       </c>
     </row>
     <row r="64">
@@ -12962,27 +12962,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13150,7 +13150,7 @@
         <v>0</v>
       </c>
       <c r="BI64" s="3" t="n">
-        <v>46146.79166666666</v>
+        <v>46146.66666666666</v>
       </c>
     </row>
     <row r="65">
@@ -13159,27 +13159,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13347,7 +13347,7 @@
         <v>0</v>
       </c>
       <c r="BI65" s="3" t="n">
-        <v>46146.79166666666</v>
+        <v>46146.67708333334</v>
       </c>
     </row>
     <row r="66">
@@ -13356,12 +13356,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13544,7 +13544,7 @@
         <v>0</v>
       </c>
       <c r="BI66" s="3" t="n">
-        <v>46146.83333333334</v>
+        <v>46146.79166666666</v>
       </c>
     </row>
     <row r="67">
@@ -13553,12 +13553,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13741,7 +13741,7 @@
         <v>0</v>
       </c>
       <c r="BI67" s="3" t="n">
-        <v>46146.83333333334</v>
+        <v>46146.79166666666</v>
       </c>
     </row>
     <row r="68">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14144,12 +14144,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14332,7 +14332,7 @@
         <v>0</v>
       </c>
       <c r="BI70" s="3" t="n">
-        <v>46146.875</v>
+        <v>46146.83333333334</v>
       </c>
     </row>
     <row r="71">
@@ -14341,27 +14341,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14529,7 +14529,7 @@
         <v>0</v>
       </c>
       <c r="BI71" s="3" t="n">
-        <v>46146.875</v>
+        <v>46146.83333333334</v>
       </c>
     </row>
     <row r="72">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14932,27 +14932,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15120,7 +15120,7 @@
         <v>0</v>
       </c>
       <c r="BI74" s="3" t="n">
-        <v>46146.89583333334</v>
+        <v>46146.875</v>
       </c>
     </row>
     <row r="75">
@@ -15129,12 +15129,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15317,6 +15317,400 @@
         <v>0</v>
       </c>
       <c r="BI75" s="3" t="n">
+        <v>46146.875</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>San Marcos</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N76" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>0</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
+      </c>
+      <c r="V76" t="n">
+        <v>0</v>
+      </c>
+      <c r="W76" t="n">
+        <v>0</v>
+      </c>
+      <c r="X76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI76" s="3" t="n">
+        <v>46146.89583333334</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Gimnasia y Tiro</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Agropecuario</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N77" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
+      </c>
+      <c r="V77" t="n">
+        <v>0</v>
+      </c>
+      <c r="W77" t="n">
+        <v>0</v>
+      </c>
+      <c r="X77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI77" s="3" t="n">
         <v>46146.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-05-04.xlsx
+++ b/jogos_2026-05-04.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>7.41</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="R13" t="n">
-        <v>7.41</v>
+        <v>4.57</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="R37" t="n">
-        <v>2.4</v>
+        <v>2.67</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="R38" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF63" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G77" t="n">

--- a/jogos_2026-05-04.xlsx
+++ b/jogos_2026-05-04.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="R11" t="n">
-        <v>7.41</v>
+        <v>4.57</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>7.41</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.55</v>
+        <v>3.25</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.28</v>
+        <v>2.95</v>
       </c>
       <c r="R37" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="R38" t="n">
-        <v>2.4</v>
+        <v>2.67</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="R39" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF64" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G75" t="n">

--- a/jogos_2026-05-04.xlsx
+++ b/jogos_2026-05-04.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>7.41</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>7.41</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="R37" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="R39" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>7.06</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G75" t="n">

--- a/jogos_2026-05-04.xlsx
+++ b/jogos_2026-05-04.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>7.41</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>7.41</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>3.25</v>
+        <v>2.55</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.95</v>
+        <v>3.28</v>
       </c>
       <c r="R39" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.55</v>
+        <v>3.25</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.28</v>
+        <v>2.95</v>
       </c>
       <c r="R40" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>4.92</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>7.06</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="Q48" t="n">
-        <v>5.48</v>
+        <v>4.33</v>
       </c>
       <c r="R48" t="n">
-        <v>7.06</v>
+        <v>4.92</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1.35</v>
+        <v>1.99</v>
       </c>
       <c r="Q60" t="n">
-        <v>5.41</v>
+        <v>3.6</v>
       </c>
       <c r="R60" t="n">
-        <v>8.5</v>
+        <v>3.58</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>1.99</v>
+        <v>1.35</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.6</v>
+        <v>5.41</v>
       </c>
       <c r="R61" t="n">
-        <v>3.58</v>
+        <v>8.5</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF63" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G75" t="n">

--- a/jogos_2026-05-04.xlsx
+++ b/jogos_2026-05-04.xlsx
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>7.41</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>7.41</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="R38" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="R40" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>5.48</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>7.06</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>4.92</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>7.06</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1.99</v>
+        <v>1.35</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.6</v>
+        <v>5.41</v>
       </c>
       <c r="R60" t="n">
-        <v>3.58</v>
+        <v>8.5</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>1.35</v>
+        <v>1.99</v>
       </c>
       <c r="Q61" t="n">
-        <v>5.41</v>
+        <v>3.6</v>
       </c>
       <c r="R61" t="n">
-        <v>8.5</v>
+        <v>3.58</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>

--- a/jogos_2026-05-04.xlsx
+++ b/jogos_2026-05-04.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>7.41</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>7.41</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.55</v>
+        <v>3.25</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.28</v>
+        <v>2.95</v>
       </c>
       <c r="R37" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>3.25</v>
+        <v>2.55</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.95</v>
+        <v>3.28</v>
       </c>
       <c r="R38" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>4.92</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>7.06</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>5.48</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>7.06</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF64" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>

--- a/jogos_2026-05-04.xlsx
+++ b/jogos_2026-05-04.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>7.41</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>7.41</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="R37" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="R39" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>7.06</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>5.48</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>7.06</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.58</v>
+        <v>1.79</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="R50" t="n">
-        <v>4.92</v>
+        <v>4.22</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1.35</v>
+        <v>1.99</v>
       </c>
       <c r="Q60" t="n">
-        <v>5.41</v>
+        <v>3.6</v>
       </c>
       <c r="R60" t="n">
-        <v>8.5</v>
+        <v>3.58</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>1.99</v>
+        <v>1.35</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.6</v>
+        <v>5.41</v>
       </c>
       <c r="R61" t="n">
-        <v>3.58</v>
+        <v>8.5</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G75" t="n">

--- a/jogos_2026-05-04.xlsx
+++ b/jogos_2026-05-04.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>7.41</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>7.41</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.6</v>
+        <v>1.58</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="R42" t="n">
-        <v>2.54</v>
+        <v>4.92</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>4.92</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>5.48</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>7.06</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.61</v>
+        <v>1.38</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.34</v>
+        <v>5.48</v>
       </c>
       <c r="R45" t="n">
-        <v>2.52</v>
+        <v>7.06</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>

--- a/jogos_2026-05-04.xlsx
+++ b/jogos_2026-05-04.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI77"/>
+  <dimension ref="A1:BI82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>7.41</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="R14" t="n">
-        <v>4.57</v>
+        <v>7.41</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3900,27 +3900,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4088,7 +4088,7 @@
         <v>0</v>
       </c>
       <c r="BI18" s="3" t="n">
-        <v>46146.47916666666</v>
+        <v>46146.45833333334</v>
       </c>
     </row>
     <row r="19">
@@ -4097,27 +4097,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4285,7 +4285,7 @@
         <v>0</v>
       </c>
       <c r="BI19" s="3" t="n">
-        <v>46146.5</v>
+        <v>46146.45833333334</v>
       </c>
     </row>
     <row r="20">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4482,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="BI20" s="3" t="n">
-        <v>46146.5</v>
+        <v>46146.47916666666</v>
       </c>
     </row>
     <row r="21">
@@ -4491,12 +4491,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4679,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
-        <v>46146.51041666666</v>
+        <v>46146.5</v>
       </c>
     </row>
     <row r="22">
@@ -4688,27 +4688,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
-        <v>46146.52083333334</v>
+        <v>46146.5</v>
       </c>
     </row>
     <row r="23">
@@ -4885,27 +4885,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5073,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="BI23" s="3" t="n">
-        <v>46146.54166666666</v>
+        <v>46146.5</v>
       </c>
     </row>
     <row r="24">
@@ -5082,27 +5082,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5270,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="BI24" s="3" t="n">
-        <v>46146.54166666666</v>
+        <v>46146.5</v>
       </c>
     </row>
     <row r="25">
@@ -5279,27 +5279,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="BI25" s="3" t="n">
-        <v>46146.54166666666</v>
+        <v>46146.5</v>
       </c>
     </row>
     <row r="26">
@@ -5476,27 +5476,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5664,7 +5664,7 @@
         <v>0</v>
       </c>
       <c r="BI26" s="3" t="n">
-        <v>46146.54166666666</v>
+        <v>46146.5</v>
       </c>
     </row>
     <row r="27">
@@ -5673,27 +5673,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5861,7 +5861,7 @@
         <v>0</v>
       </c>
       <c r="BI27" s="3" t="n">
-        <v>46146.54166666666</v>
+        <v>46146.51041666666</v>
       </c>
     </row>
     <row r="28">
@@ -5870,27 +5870,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6058,7 +6058,7 @@
         <v>0</v>
       </c>
       <c r="BI28" s="3" t="n">
-        <v>46146.54166666666</v>
+        <v>46146.52083333334</v>
       </c>
     </row>
     <row r="29">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7249,27 +7249,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7437,7 +7437,7 @@
         <v>0</v>
       </c>
       <c r="BI35" s="3" t="n">
-        <v>46146.54861111111</v>
+        <v>46146.54166666666</v>
       </c>
     </row>
     <row r="36">
@@ -7446,27 +7446,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7634,7 +7634,7 @@
         <v>0</v>
       </c>
       <c r="BI36" s="3" t="n">
-        <v>46146.55555555555</v>
+        <v>46146.54166666666</v>
       </c>
     </row>
     <row r="37">
@@ -7643,27 +7643,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -7831,7 +7831,7 @@
         <v>0</v>
       </c>
       <c r="BI37" s="3" t="n">
-        <v>46146.5625</v>
+        <v>46146.54166666666</v>
       </c>
     </row>
     <row r="38">
@@ -7840,27 +7840,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8028,7 +8028,7 @@
         <v>0</v>
       </c>
       <c r="BI38" s="3" t="n">
-        <v>46146.5625</v>
+        <v>46146.54166666666</v>
       </c>
     </row>
     <row r="39">
@@ -8037,27 +8037,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8225,7 +8225,7 @@
         <v>0</v>
       </c>
       <c r="BI39" s="3" t="n">
-        <v>46146.5625</v>
+        <v>46146.54166666666</v>
       </c>
     </row>
     <row r="40">
@@ -8234,27 +8234,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8422,7 +8422,7 @@
         <v>0</v>
       </c>
       <c r="BI40" s="3" t="n">
-        <v>46146.5625</v>
+        <v>46146.54166666666</v>
       </c>
     </row>
     <row r="41">
@@ -8431,12 +8431,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8619,7 +8619,7 @@
         <v>0</v>
       </c>
       <c r="BI41" s="3" t="n">
-        <v>46146.58333333334</v>
+        <v>46146.54861111111</v>
       </c>
     </row>
     <row r="42">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>4.92</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8816,7 +8816,7 @@
         <v>0</v>
       </c>
       <c r="BI42" s="3" t="n">
-        <v>46146.58333333334</v>
+        <v>46146.55555555555</v>
       </c>
     </row>
     <row r="43">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9013,7 +9013,7 @@
         <v>0</v>
       </c>
       <c r="BI43" s="3" t="n">
-        <v>46146.58333333334</v>
+        <v>46146.5625</v>
       </c>
     </row>
     <row r="44">
@@ -9022,12 +9022,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9210,7 +9210,7 @@
         <v>0</v>
       </c>
       <c r="BI44" s="3" t="n">
-        <v>46146.58333333334</v>
+        <v>46146.5625</v>
       </c>
     </row>
     <row r="45">
@@ -9219,27 +9219,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.38</v>
+        <v>3.25</v>
       </c>
       <c r="Q45" t="n">
-        <v>5.48</v>
+        <v>2.95</v>
       </c>
       <c r="R45" t="n">
-        <v>7.06</v>
+        <v>2.5</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="BI45" s="3" t="n">
-        <v>46146.58333333334</v>
+        <v>46146.5625</v>
       </c>
     </row>
     <row r="46">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9604,7 +9604,7 @@
         <v>0</v>
       </c>
       <c r="BI46" s="3" t="n">
-        <v>46146.58333333334</v>
+        <v>46146.5625</v>
       </c>
     </row>
     <row r="47">
@@ -9613,27 +9613,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9801,7 +9801,7 @@
         <v>0</v>
       </c>
       <c r="BI47" s="3" t="n">
-        <v>46146.58333333334</v>
+        <v>46146.57291666666</v>
       </c>
     </row>
     <row r="48">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.79</v>
+        <v>1.38</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.7</v>
+        <v>5.48</v>
       </c>
       <c r="R52" t="n">
-        <v>4.22</v>
+        <v>7.06</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10795,27 +10795,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10983,7 +10983,7 @@
         <v>0</v>
       </c>
       <c r="BI53" s="3" t="n">
-        <v>46146.58680555555</v>
+        <v>46146.58333333334</v>
       </c>
     </row>
     <row r="54">
@@ -10992,27 +10992,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11180,7 +11180,7 @@
         <v>0</v>
       </c>
       <c r="BI54" s="3" t="n">
-        <v>46146.60416666666</v>
+        <v>46146.58333333334</v>
       </c>
     </row>
     <row r="55">
@@ -11189,27 +11189,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11377,7 +11377,7 @@
         <v>0</v>
       </c>
       <c r="BI55" s="3" t="n">
-        <v>46146.60416666666</v>
+        <v>46146.58333333334</v>
       </c>
     </row>
     <row r="56">
@@ -11386,12 +11386,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.65</v>
+        <v>1.58</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="R56" t="n">
-        <v>2.65</v>
+        <v>4.92</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11574,7 +11574,7 @@
         <v>0</v>
       </c>
       <c r="BI56" s="3" t="n">
-        <v>46146.60416666666</v>
+        <v>46146.58333333334</v>
       </c>
     </row>
     <row r="57">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11771,7 +11771,7 @@
         <v>0</v>
       </c>
       <c r="BI57" s="3" t="n">
-        <v>46146.625</v>
+        <v>46146.58333333334</v>
       </c>
     </row>
     <row r="58">
@@ -11780,12 +11780,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11968,7 +11968,7 @@
         <v>0</v>
       </c>
       <c r="BI58" s="3" t="n">
-        <v>46146.625</v>
+        <v>46146.58333333334</v>
       </c>
     </row>
     <row r="59">
@@ -11977,12 +11977,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12165,7 +12165,7 @@
         <v>0</v>
       </c>
       <c r="BI59" s="3" t="n">
-        <v>46146.625</v>
+        <v>46146.58333333334</v>
       </c>
     </row>
     <row r="60">
@@ -12174,27 +12174,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1.99</v>
+        <v>2.93</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R60" t="n">
-        <v>3.58</v>
+        <v>2.29</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AF60" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12362,7 +12362,7 @@
         <v>0</v>
       </c>
       <c r="BI60" s="3" t="n">
-        <v>46146.64583333334</v>
+        <v>46146.58680555555</v>
       </c>
     </row>
     <row r="61">
@@ -12371,27 +12371,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>5.41</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12559,7 +12559,7 @@
         <v>0</v>
       </c>
       <c r="BI61" s="3" t="n">
-        <v>46146.64583333334</v>
+        <v>46146.60416666666</v>
       </c>
     </row>
     <row r="62">
@@ -12568,27 +12568,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12756,7 +12756,7 @@
         <v>0</v>
       </c>
       <c r="BI62" s="3" t="n">
-        <v>46146.65625</v>
+        <v>46146.60416666666</v>
       </c>
     </row>
     <row r="63">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>5.63</v>
+        <v>2.65</v>
       </c>
       <c r="Q63" t="n">
-        <v>4.21</v>
+        <v>3.1</v>
       </c>
       <c r="R63" t="n">
-        <v>1.67</v>
+        <v>2.65</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF63" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12953,7 +12953,7 @@
         <v>0</v>
       </c>
       <c r="BI63" s="3" t="n">
-        <v>46146.66666666666</v>
+        <v>46146.60416666666</v>
       </c>
     </row>
     <row r="64">
@@ -12962,12 +12962,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13150,7 +13150,7 @@
         <v>0</v>
       </c>
       <c r="BI64" s="3" t="n">
-        <v>46146.66666666666</v>
+        <v>46146.625</v>
       </c>
     </row>
     <row r="65">
@@ -13159,12 +13159,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13347,7 +13347,7 @@
         <v>0</v>
       </c>
       <c r="BI65" s="3" t="n">
-        <v>46146.67708333334</v>
+        <v>46146.625</v>
       </c>
     </row>
     <row r="66">
@@ -13356,27 +13356,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13544,7 +13544,7 @@
         <v>0</v>
       </c>
       <c r="BI66" s="3" t="n">
-        <v>46146.79166666666</v>
+        <v>46146.625</v>
       </c>
     </row>
     <row r="67">
@@ -13553,27 +13553,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.24</v>
+        <v>3.6</v>
       </c>
       <c r="R67" t="n">
-        <v>3.67</v>
+        <v>3.58</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13741,7 +13741,7 @@
         <v>0</v>
       </c>
       <c r="BI67" s="3" t="n">
-        <v>46146.79166666666</v>
+        <v>46146.64583333334</v>
       </c>
     </row>
     <row r="68">
@@ -13750,27 +13750,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13938,7 +13938,7 @@
         <v>0</v>
       </c>
       <c r="BI68" s="3" t="n">
-        <v>46146.83333333334</v>
+        <v>46146.64583333334</v>
       </c>
     </row>
     <row r="69">
@@ -13947,27 +13947,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14135,7 +14135,7 @@
         <v>0</v>
       </c>
       <c r="BI69" s="3" t="n">
-        <v>46146.83333333334</v>
+        <v>46146.65625</v>
       </c>
     </row>
     <row r="70">
@@ -14144,27 +14144,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14332,7 +14332,7 @@
         <v>0</v>
       </c>
       <c r="BI70" s="3" t="n">
-        <v>46146.83333333334</v>
+        <v>46146.66666666666</v>
       </c>
     </row>
     <row r="71">
@@ -14341,27 +14341,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14529,7 +14529,7 @@
         <v>0</v>
       </c>
       <c r="BI71" s="3" t="n">
-        <v>46146.83333333334</v>
+        <v>46146.66666666666</v>
       </c>
     </row>
     <row r="72">
@@ -14538,12 +14538,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14726,7 +14726,7 @@
         <v>0</v>
       </c>
       <c r="BI72" s="3" t="n">
-        <v>46146.875</v>
+        <v>46146.66666666666</v>
       </c>
     </row>
     <row r="73">
@@ -14735,12 +14735,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>6.46</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>12.8</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14923,7 +14923,7 @@
         <v>0</v>
       </c>
       <c r="BI73" s="3" t="n">
-        <v>46146.875</v>
+        <v>46146.67708333334</v>
       </c>
     </row>
     <row r="74">
@@ -14932,12 +14932,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15120,7 +15120,7 @@
         <v>0</v>
       </c>
       <c r="BI74" s="3" t="n">
-        <v>46146.875</v>
+        <v>46146.79166666666</v>
       </c>
     </row>
     <row r="75">
@@ -15129,27 +15129,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15317,7 +15317,7 @@
         <v>0</v>
       </c>
       <c r="BI75" s="3" t="n">
-        <v>46146.875</v>
+        <v>46146.79166666666</v>
       </c>
     </row>
     <row r="76">
@@ -15326,12 +15326,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15514,7 +15514,7 @@
         <v>0</v>
       </c>
       <c r="BI76" s="3" t="n">
-        <v>46146.89583333334</v>
+        <v>46146.83333333334</v>
       </c>
     </row>
     <row r="77">
@@ -15523,7 +15523,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,141 +15576,1126 @@
         </is>
       </c>
       <c r="P77" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R77" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
+      </c>
+      <c r="V77" t="n">
+        <v>0</v>
+      </c>
+      <c r="W77" t="n">
+        <v>0</v>
+      </c>
+      <c r="X77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI77" s="3" t="n">
+        <v>46146.83333333334</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Floresta</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Maranhão</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N78" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>0</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0</v>
+      </c>
+      <c r="V78" t="n">
+        <v>0</v>
+      </c>
+      <c r="W78" t="n">
+        <v>0</v>
+      </c>
+      <c r="X78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI78" s="3" t="n">
+        <v>46146.83333333334</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Figueirense</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Barra do Garcas</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N79" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0</v>
+      </c>
+      <c r="V79" t="n">
+        <v>0</v>
+      </c>
+      <c r="W79" t="n">
+        <v>0</v>
+      </c>
+      <c r="X79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI79" s="3" t="n">
+        <v>46146.83333333334</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Universitario de Vinto</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Blooming</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N80" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>0</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0</v>
+      </c>
+      <c r="V80" t="n">
+        <v>0</v>
+      </c>
+      <c r="W80" t="n">
+        <v>0</v>
+      </c>
+      <c r="X80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI80" s="3" t="n">
+        <v>46146.875</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>San Marcos</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N81" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" t="n">
+        <v>0</v>
+      </c>
+      <c r="U81" t="n">
+        <v>0</v>
+      </c>
+      <c r="V81" t="n">
+        <v>0</v>
+      </c>
+      <c r="W81" t="n">
+        <v>0</v>
+      </c>
+      <c r="X81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI81" s="3" t="n">
+        <v>46146.89583333334</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Gimnasia y Tiro</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Agropecuario</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N82" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q77" t="n">
+      <c r="Q82" t="n">
         <v>2.8</v>
       </c>
-      <c r="R77" t="n">
+      <c r="R82" t="n">
         <v>3.8</v>
       </c>
-      <c r="S77" t="n">
-        <v>0</v>
-      </c>
-      <c r="T77" t="n">
-        <v>0</v>
-      </c>
-      <c r="U77" t="n">
-        <v>0</v>
-      </c>
-      <c r="V77" t="n">
-        <v>0</v>
-      </c>
-      <c r="W77" t="n">
-        <v>0</v>
-      </c>
-      <c r="X77" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y77" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ77" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA77" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB77" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC77" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD77" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE77" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF77" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG77" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH77" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI77" s="3" t="n">
+      <c r="S82" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" t="n">
+        <v>0</v>
+      </c>
+      <c r="U82" t="n">
+        <v>0</v>
+      </c>
+      <c r="V82" t="n">
+        <v>0</v>
+      </c>
+      <c r="W82" t="n">
+        <v>0</v>
+      </c>
+      <c r="X82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI82" s="3" t="n">
         <v>46146.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-05-04.xlsx
+++ b/jogos_2026-05-04.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>7.41</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>7.41</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="R43" t="n">
-        <v>2.4</v>
+        <v>2.67</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="R45" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.58</v>
+        <v>2.17</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.33</v>
+        <v>3.54</v>
       </c>
       <c r="R56" t="n">
-        <v>4.92</v>
+        <v>3.03</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.17</v>
+        <v>1.58</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.54</v>
+        <v>4.33</v>
       </c>
       <c r="R59" t="n">
-        <v>3.03</v>
+        <v>4.92</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.99</v>
+        <v>1.35</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.6</v>
+        <v>5.41</v>
       </c>
       <c r="R67" t="n">
-        <v>3.58</v>
+        <v>8.5</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1.35</v>
+        <v>1.99</v>
       </c>
       <c r="Q68" t="n">
-        <v>5.41</v>
+        <v>3.6</v>
       </c>
       <c r="R68" t="n">
-        <v>8.5</v>
+        <v>3.58</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G79" t="n">

--- a/jogos_2026-05-04.xlsx
+++ b/jogos_2026-05-04.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="R43" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="R45" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>7.06</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.38</v>
+        <v>2.6</v>
       </c>
       <c r="Q52" t="n">
-        <v>5.48</v>
+        <v>3.4</v>
       </c>
       <c r="R52" t="n">
-        <v>7.06</v>
+        <v>2.54</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.17</v>
+        <v>1.58</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.54</v>
+        <v>4.33</v>
       </c>
       <c r="R56" t="n">
-        <v>3.03</v>
+        <v>4.92</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>4.92</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF70" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G79" t="n">

--- a/jogos_2026-05-04.xlsx
+++ b/jogos_2026-05-04.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI82"/>
+  <dimension ref="A1:BI84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.83</v>
+        <v>3.43</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>2.64</v>
       </c>
       <c r="R12" t="n">
-        <v>4.57</v>
+        <v>2.33</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>7.41</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>7.41</v>
+        <v>4.57</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4195,10 +4195,10 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8431,27 +8431,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8619,7 +8619,7 @@
         <v>0</v>
       </c>
       <c r="BI41" s="3" t="n">
-        <v>46146.54861111111</v>
+        <v>46146.54166666666</v>
       </c>
     </row>
     <row r="42">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8816,7 +8816,7 @@
         <v>0</v>
       </c>
       <c r="BI42" s="3" t="n">
-        <v>46146.55555555555</v>
+        <v>46146.54166666666</v>
       </c>
     </row>
     <row r="43">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9013,7 +9013,7 @@
         <v>0</v>
       </c>
       <c r="BI43" s="3" t="n">
-        <v>46146.5625</v>
+        <v>46146.54861111111</v>
       </c>
     </row>
     <row r="44">
@@ -9022,12 +9022,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9210,7 +9210,7 @@
         <v>0</v>
       </c>
       <c r="BI44" s="3" t="n">
-        <v>46146.5625</v>
+        <v>46146.55555555555</v>
       </c>
     </row>
     <row r="45">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>3.25</v>
+        <v>2.55</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.95</v>
+        <v>3.28</v>
       </c>
       <c r="R45" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9613,12 +9613,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9801,7 +9801,7 @@
         <v>0</v>
       </c>
       <c r="BI47" s="3" t="n">
-        <v>46146.57291666666</v>
+        <v>46146.5625</v>
       </c>
     </row>
     <row r="48">
@@ -9810,12 +9810,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9998,7 +9998,7 @@
         <v>0</v>
       </c>
       <c r="BI48" s="3" t="n">
-        <v>46146.58333333334</v>
+        <v>46146.5625</v>
       </c>
     </row>
     <row r="49">
@@ -10007,27 +10007,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10195,7 +10195,7 @@
         <v>0</v>
       </c>
       <c r="BI49" s="3" t="n">
-        <v>46146.58333333334</v>
+        <v>46146.57291666666</v>
       </c>
     </row>
     <row r="50">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.38</v>
+        <v>1.79</v>
       </c>
       <c r="Q50" t="n">
-        <v>5.48</v>
+        <v>3.7</v>
       </c>
       <c r="R50" t="n">
-        <v>7.06</v>
+        <v>4.22</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.17</v>
+        <v>2.6</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="R51" t="n">
-        <v>3.03</v>
+        <v>2.54</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>7.06</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.61</v>
+        <v>1.8</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.34</v>
+        <v>3.54</v>
       </c>
       <c r="R55" t="n">
-        <v>2.52</v>
+        <v>4.24</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.58</v>
+        <v>2.61</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.33</v>
+        <v>3.34</v>
       </c>
       <c r="R56" t="n">
-        <v>4.92</v>
+        <v>2.52</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12174,27 +12174,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.93</v>
+        <v>1.58</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="R60" t="n">
-        <v>2.29</v>
+        <v>4.92</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12362,7 +12362,7 @@
         <v>0</v>
       </c>
       <c r="BI60" s="3" t="n">
-        <v>46146.58680555555</v>
+        <v>46146.58333333334</v>
       </c>
     </row>
     <row r="61">
@@ -12371,12 +12371,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12559,7 +12559,7 @@
         <v>0</v>
       </c>
       <c r="BI61" s="3" t="n">
-        <v>46146.60416666666</v>
+        <v>46146.58333333334</v>
       </c>
     </row>
     <row r="62">
@@ -12568,12 +12568,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12756,7 +12756,7 @@
         <v>0</v>
       </c>
       <c r="BI62" s="3" t="n">
-        <v>46146.60416666666</v>
+        <v>46146.58680555555</v>
       </c>
     </row>
     <row r="63">
@@ -12962,12 +12962,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13150,7 +13150,7 @@
         <v>0</v>
       </c>
       <c r="BI64" s="3" t="n">
-        <v>46146.625</v>
+        <v>46146.60416666666</v>
       </c>
     </row>
     <row r="65">
@@ -13159,27 +13159,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13347,7 +13347,7 @@
         <v>0</v>
       </c>
       <c r="BI65" s="3" t="n">
-        <v>46146.625</v>
+        <v>46146.60416666666</v>
       </c>
     </row>
     <row r="66">
@@ -13553,12 +13553,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>5.41</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13741,7 +13741,7 @@
         <v>0</v>
       </c>
       <c r="BI67" s="3" t="n">
-        <v>46146.64583333334</v>
+        <v>46146.625</v>
       </c>
     </row>
     <row r="68">
@@ -13750,12 +13750,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13938,7 +13938,7 @@
         <v>0</v>
       </c>
       <c r="BI68" s="3" t="n">
-        <v>46146.64583333334</v>
+        <v>46146.625</v>
       </c>
     </row>
     <row r="69">
@@ -13947,12 +13947,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14135,7 +14135,7 @@
         <v>0</v>
       </c>
       <c r="BI69" s="3" t="n">
-        <v>46146.65625</v>
+        <v>46146.64583333334</v>
       </c>
     </row>
     <row r="70">
@@ -14144,12 +14144,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>5.63</v>
+        <v>1.99</v>
       </c>
       <c r="Q70" t="n">
-        <v>4.21</v>
+        <v>3.6</v>
       </c>
       <c r="R70" t="n">
-        <v>1.67</v>
+        <v>3.58</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AF70" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14332,7 +14332,7 @@
         <v>0</v>
       </c>
       <c r="BI70" s="3" t="n">
-        <v>46146.66666666666</v>
+        <v>46146.64583333334</v>
       </c>
     </row>
     <row r="71">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14529,7 +14529,7 @@
         <v>0</v>
       </c>
       <c r="BI71" s="3" t="n">
-        <v>46146.66666666666</v>
+        <v>46146.65625</v>
       </c>
     </row>
     <row r="72">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14735,12 +14735,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>6.46</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>12.8</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14923,7 +14923,7 @@
         <v>0</v>
       </c>
       <c r="BI73" s="3" t="n">
-        <v>46146.67708333334</v>
+        <v>46146.66666666666</v>
       </c>
     </row>
     <row r="74">
@@ -14932,27 +14932,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15120,7 +15120,7 @@
         <v>0</v>
       </c>
       <c r="BI74" s="3" t="n">
-        <v>46146.79166666666</v>
+        <v>46146.66666666666</v>
       </c>
     </row>
     <row r="75">
@@ -15129,27 +15129,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.03</v>
+        <v>1.25</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.24</v>
+        <v>6.46</v>
       </c>
       <c r="R75" t="n">
-        <v>3.67</v>
+        <v>12.8</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15317,7 +15317,7 @@
         <v>0</v>
       </c>
       <c r="BI75" s="3" t="n">
-        <v>46146.79166666666</v>
+        <v>46146.67708333334</v>
       </c>
     </row>
     <row r="76">
@@ -15326,12 +15326,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15514,7 +15514,7 @@
         <v>0</v>
       </c>
       <c r="BI76" s="3" t="n">
-        <v>46146.83333333334</v>
+        <v>46146.79166666666</v>
       </c>
     </row>
     <row r="77">
@@ -15523,12 +15523,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15711,7 +15711,7 @@
         <v>0</v>
       </c>
       <c r="BI77" s="3" t="n">
-        <v>46146.83333333334</v>
+        <v>46146.79166666666</v>
       </c>
     </row>
     <row r="78">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16114,12 +16114,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16302,7 +16302,7 @@
         <v>0</v>
       </c>
       <c r="BI80" s="3" t="n">
-        <v>46146.875</v>
+        <v>46146.83333333334</v>
       </c>
     </row>
     <row r="81">
@@ -16311,12 +16311,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16499,7 +16499,7 @@
         <v>0</v>
       </c>
       <c r="BI81" s="3" t="n">
-        <v>46146.89583333334</v>
+        <v>46146.83333333334</v>
       </c>
     </row>
     <row r="82">
@@ -16508,12 +16508,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,141 +16561,535 @@
         </is>
       </c>
       <c r="P82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" t="n">
+        <v>0</v>
+      </c>
+      <c r="U82" t="n">
+        <v>0</v>
+      </c>
+      <c r="V82" t="n">
+        <v>0</v>
+      </c>
+      <c r="W82" t="n">
+        <v>0</v>
+      </c>
+      <c r="X82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI82" s="3" t="n">
+        <v>46146.875</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Gimnasia y Tiro</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Agropecuario</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N83" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q82" t="n">
+      <c r="Q83" t="n">
         <v>2.8</v>
       </c>
-      <c r="R82" t="n">
+      <c r="R83" t="n">
         <v>3.8</v>
       </c>
-      <c r="S82" t="n">
-        <v>0</v>
-      </c>
-      <c r="T82" t="n">
-        <v>0</v>
-      </c>
-      <c r="U82" t="n">
-        <v>0</v>
-      </c>
-      <c r="V82" t="n">
-        <v>0</v>
-      </c>
-      <c r="W82" t="n">
-        <v>0</v>
-      </c>
-      <c r="X82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ82" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA82" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB82" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC82" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD82" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE82" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF82" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG82" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH82" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI82" s="3" t="n">
+      <c r="S83" t="n">
+        <v>0</v>
+      </c>
+      <c r="T83" t="n">
+        <v>0</v>
+      </c>
+      <c r="U83" t="n">
+        <v>0</v>
+      </c>
+      <c r="V83" t="n">
+        <v>0</v>
+      </c>
+      <c r="W83" t="n">
+        <v>0</v>
+      </c>
+      <c r="X83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI83" s="3" t="n">
+        <v>46146.89583333334</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>San Marcos</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N84" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>0</v>
+      </c>
+      <c r="R84" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" t="n">
+        <v>0</v>
+      </c>
+      <c r="T84" t="n">
+        <v>0</v>
+      </c>
+      <c r="U84" t="n">
+        <v>0</v>
+      </c>
+      <c r="V84" t="n">
+        <v>0</v>
+      </c>
+      <c r="W84" t="n">
+        <v>0</v>
+      </c>
+      <c r="X84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI84" s="3" t="n">
         <v>46146.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-05-04.xlsx
+++ b/jogos_2026-05-04.xlsx
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>3.43</v>
+        <v>1.66</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.64</v>
+        <v>3.25</v>
       </c>
       <c r="R12" t="n">
-        <v>2.33</v>
+        <v>7.41</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="R15" t="n">
-        <v>7.41</v>
+        <v>4.57</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4195,10 +4195,10 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="R46" t="n">
-        <v>2.4</v>
+        <v>2.67</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>7.06</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.38</v>
+        <v>2.17</v>
       </c>
       <c r="Q54" t="n">
-        <v>5.48</v>
+        <v>3.54</v>
       </c>
       <c r="R54" t="n">
-        <v>7.06</v>
+        <v>3.03</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="R56" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.17</v>
+        <v>1.8</v>
       </c>
       <c r="Q57" t="n">
         <v>3.54</v>
       </c>
       <c r="R57" t="n">
-        <v>3.03</v>
+        <v>4.24</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>4.92</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.35</v>
+        <v>1.99</v>
       </c>
       <c r="Q69" t="n">
-        <v>5.41</v>
+        <v>3.6</v>
       </c>
       <c r="R69" t="n">
-        <v>8.5</v>
+        <v>3.58</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.99</v>
+        <v>1.35</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.6</v>
+        <v>5.41</v>
       </c>
       <c r="R70" t="n">
-        <v>3.58</v>
+        <v>8.5</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>

--- a/jogos_2026-05-04.xlsx
+++ b/jogos_2026-05-04.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>7.41</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>3.43</v>
+        <v>1.83</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.64</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>2.33</v>
+        <v>4.57</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>7.41</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="R46" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>3.25</v>
+        <v>2.55</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.95</v>
+        <v>3.28</v>
       </c>
       <c r="R48" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>7.06</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.38</v>
+        <v>2.6</v>
       </c>
       <c r="Q52" t="n">
-        <v>5.48</v>
+        <v>3.4</v>
       </c>
       <c r="R52" t="n">
-        <v>7.06</v>
+        <v>2.54</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.61</v>
+        <v>1.79</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.34</v>
+        <v>3.7</v>
       </c>
       <c r="R53" t="n">
-        <v>2.52</v>
+        <v>4.22</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="R56" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="Q57" t="n">
         <v>3.54</v>
       </c>
       <c r="R57" t="n">
-        <v>4.24</v>
+        <v>3.03</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>4.92</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G81" t="n">

--- a/jogos_2026-05-04.xlsx
+++ b/jogos_2026-05-04.xlsx
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>7.41</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>7.41</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>3.25</v>
+        <v>3.89</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.95</v>
+        <v>3.67</v>
       </c>
       <c r="R45" t="n">
-        <v>2.5</v>
+        <v>2.06</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.58</v>
+        <v>1.38</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.33</v>
+        <v>5.48</v>
       </c>
       <c r="R50" t="n">
-        <v>4.92</v>
+        <v>7.06</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>5.48</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>7.06</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="R52" t="n">
-        <v>2.54</v>
+        <v>4.24</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.79</v>
+        <v>2.17</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.7</v>
+        <v>3.54</v>
       </c>
       <c r="R53" t="n">
-        <v>4.22</v>
+        <v>3.03</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.17</v>
+        <v>1.58</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.54</v>
+        <v>4.33</v>
       </c>
       <c r="R57" t="n">
-        <v>3.03</v>
+        <v>4.92</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.99</v>
+        <v>1.35</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.6</v>
+        <v>5.41</v>
       </c>
       <c r="R69" t="n">
-        <v>3.58</v>
+        <v>8.5</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.35</v>
+        <v>1.99</v>
       </c>
       <c r="Q70" t="n">
-        <v>5.41</v>
+        <v>3.6</v>
       </c>
       <c r="R70" t="n">
-        <v>8.5</v>
+        <v>3.58</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF71" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF74" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G81" t="n">

--- a/jogos_2026-05-04.xlsx
+++ b/jogos_2026-05-04.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="R14" t="n">
-        <v>4.57</v>
+        <v>7.41</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>7.41</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>3.89</v>
+        <v>2.7</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.67</v>
+        <v>3.3</v>
       </c>
       <c r="R45" t="n">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.68</v>
+        <v>1.93</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.7</v>
+        <v>3.89</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.3</v>
+        <v>3.67</v>
       </c>
       <c r="R46" t="n">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.93</v>
+        <v>1.68</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>3.25</v>
+        <v>2.55</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.95</v>
+        <v>3.28</v>
       </c>
       <c r="R47" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.55</v>
+        <v>3.25</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.28</v>
+        <v>2.95</v>
       </c>
       <c r="R48" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>5.48</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>7.06</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="R52" t="n">
-        <v>4.24</v>
+        <v>2.54</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.61</v>
+        <v>1.38</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.34</v>
+        <v>5.48</v>
       </c>
       <c r="R56" t="n">
-        <v>2.52</v>
+        <v>7.06</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.58</v>
+        <v>2.61</v>
       </c>
       <c r="Q57" t="n">
-        <v>4.33</v>
+        <v>3.34</v>
       </c>
       <c r="R57" t="n">
-        <v>4.92</v>
+        <v>2.52</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.7</v>
+        <v>3.54</v>
       </c>
       <c r="R58" t="n">
-        <v>4.22</v>
+        <v>4.24</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.6</v>
+        <v>1.79</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="R59" t="n">
-        <v>2.54</v>
+        <v>4.22</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.35</v>
+        <v>1.99</v>
       </c>
       <c r="Q69" t="n">
-        <v>5.41</v>
+        <v>3.6</v>
       </c>
       <c r="R69" t="n">
-        <v>8.5</v>
+        <v>3.58</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.99</v>
+        <v>1.35</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.6</v>
+        <v>5.41</v>
       </c>
       <c r="R70" t="n">
-        <v>3.58</v>
+        <v>8.5</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF74" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>

--- a/jogos_2026-05-04.xlsx
+++ b/jogos_2026-05-04.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>7.41</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>7.41</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.83</v>
+        <v>3.43</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>2.64</v>
       </c>
       <c r="R16" t="n">
-        <v>4.57</v>
+        <v>2.33</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4195,10 +4195,10 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>5.42</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="R45" t="n">
-        <v>2.4</v>
+        <v>2.67</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>3.89</v>
+        <v>3.25</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.67</v>
+        <v>2.95</v>
       </c>
       <c r="R46" t="n">
-        <v>2.06</v>
+        <v>2.5</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="R47" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>3.25</v>
+        <v>3.89</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.95</v>
+        <v>3.67</v>
       </c>
       <c r="R48" t="n">
-        <v>2.5</v>
+        <v>2.06</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.61</v>
+        <v>1.8</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.34</v>
+        <v>3.54</v>
       </c>
       <c r="R57" t="n">
-        <v>2.52</v>
+        <v>4.24</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>4.92</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF74" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>

--- a/jogos_2026-05-04.xlsx
+++ b/jogos_2026-05-04.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>7.41</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="R19" t="n">
-        <v>4.57</v>
+        <v>7.41</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4195,10 +4195,10 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>5.42</v>
+        <v>2.6</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="R34" t="n">
-        <v>1.56</v>
+        <v>2.43</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>5.42</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.55</v>
+        <v>3.89</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.28</v>
+        <v>3.67</v>
       </c>
       <c r="R45" t="n">
-        <v>2.67</v>
+        <v>2.06</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="R46" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="R47" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>3.89</v>
+        <v>2.55</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.67</v>
+        <v>3.28</v>
       </c>
       <c r="R48" t="n">
-        <v>2.06</v>
+        <v>2.67</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.17</v>
+        <v>1.58</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.54</v>
+        <v>4.33</v>
       </c>
       <c r="R50" t="n">
-        <v>3.03</v>
+        <v>4.92</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="R51" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.6</v>
+        <v>1.79</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="R52" t="n">
-        <v>2.54</v>
+        <v>4.22</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.38</v>
+        <v>2.61</v>
       </c>
       <c r="Q56" t="n">
-        <v>5.48</v>
+        <v>3.34</v>
       </c>
       <c r="R56" t="n">
-        <v>7.06</v>
+        <v>2.52</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1.79</v>
+        <v>1.38</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.7</v>
+        <v>5.48</v>
       </c>
       <c r="R59" t="n">
-        <v>4.22</v>
+        <v>7.06</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="Q60" t="n">
-        <v>4.33</v>
+        <v>3.54</v>
       </c>
       <c r="R60" t="n">
-        <v>4.92</v>
+        <v>4.24</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.99</v>
+        <v>1.35</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.6</v>
+        <v>5.41</v>
       </c>
       <c r="R69" t="n">
-        <v>3.58</v>
+        <v>8.5</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.35</v>
+        <v>1.99</v>
       </c>
       <c r="Q70" t="n">
-        <v>5.41</v>
+        <v>3.6</v>
       </c>
       <c r="R70" t="n">
-        <v>8.5</v>
+        <v>3.58</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G81" t="n">

--- a/jogos_2026-05-04.xlsx
+++ b/jogos_2026-05-04.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>3.43</v>
+        <v>1.66</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.64</v>
+        <v>3.25</v>
       </c>
       <c r="R17" t="n">
-        <v>2.33</v>
+        <v>7.41</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>7.41</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.65</v>
+        <v>5.42</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="R37" t="n">
-        <v>2.44</v>
+        <v>1.56</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>5.42</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="R46" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="R47" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.58</v>
+        <v>1.38</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.33</v>
+        <v>5.48</v>
       </c>
       <c r="R50" t="n">
-        <v>4.92</v>
+        <v>7.06</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="R51" t="n">
-        <v>2.54</v>
+        <v>3.23</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.79</v>
+        <v>7.95</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="R52" t="n">
-        <v>4.22</v>
+        <v>1.33</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.17</v>
+        <v>2.04</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.54</v>
+        <v>3.42</v>
       </c>
       <c r="R54" t="n">
-        <v>3.03</v>
+        <v>3.43</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.61</v>
+        <v>1.58</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.34</v>
+        <v>4.33</v>
       </c>
       <c r="R56" t="n">
-        <v>2.52</v>
+        <v>4.92</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1.38</v>
+        <v>2.61</v>
       </c>
       <c r="Q59" t="n">
-        <v>5.48</v>
+        <v>3.34</v>
       </c>
       <c r="R59" t="n">
-        <v>7.06</v>
+        <v>2.52</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="Q60" t="n">
         <v>3.54</v>
       </c>
       <c r="R60" t="n">
-        <v>4.24</v>
+        <v>3.03</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.35</v>
+        <v>1.99</v>
       </c>
       <c r="Q69" t="n">
-        <v>5.41</v>
+        <v>3.6</v>
       </c>
       <c r="R69" t="n">
-        <v>8.5</v>
+        <v>3.58</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.99</v>
+        <v>1.35</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.6</v>
+        <v>5.41</v>
       </c>
       <c r="R70" t="n">
-        <v>3.58</v>
+        <v>8.5</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF74" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>

--- a/jogos_2026-05-04.xlsx
+++ b/jogos_2026-05-04.xlsx
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.36</v>
+        <v>2.14</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R33" t="n">
-        <v>2.75</v>
+        <v>3.14</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>5.42</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>5.42</v>
+        <v>2.09</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="R37" t="n">
-        <v>1.56</v>
+        <v>3.24</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.09</v>
+        <v>2.36</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R42" t="n">
-        <v>3.24</v>
+        <v>2.75</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>3.25</v>
+        <v>2.55</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.95</v>
+        <v>3.28</v>
       </c>
       <c r="R46" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.55</v>
+        <v>3.25</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.28</v>
+        <v>2.95</v>
       </c>
       <c r="R48" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.38</v>
+        <v>2.04</v>
       </c>
       <c r="Q50" t="n">
-        <v>5.48</v>
+        <v>3.42</v>
       </c>
       <c r="R50" t="n">
-        <v>7.06</v>
+        <v>3.43</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="R51" t="n">
-        <v>3.23</v>
+        <v>2.54</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>7.95</v>
+        <v>2</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="R52" t="n">
-        <v>1.33</v>
+        <v>3.23</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.73</v>
+        <v>7.95</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="R53" t="n">
-        <v>4.59</v>
+        <v>1.33</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.42</v>
+        <v>2.76</v>
       </c>
       <c r="R54" t="n">
-        <v>3.43</v>
+        <v>3.48</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.22</v>
+        <v>1.79</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.76</v>
+        <v>3.7</v>
       </c>
       <c r="R55" t="n">
-        <v>3.48</v>
+        <v>4.22</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="R56" t="n">
-        <v>4.92</v>
+        <v>4.59</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.7</v>
+        <v>3.54</v>
       </c>
       <c r="R57" t="n">
-        <v>4.22</v>
+        <v>4.24</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="R58" t="n">
-        <v>2.54</v>
+        <v>3.03</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.61</v>
+        <v>1.58</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.34</v>
+        <v>4.33</v>
       </c>
       <c r="R59" t="n">
-        <v>2.52</v>
+        <v>4.92</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.17</v>
+        <v>1.38</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.54</v>
+        <v>5.48</v>
       </c>
       <c r="R60" t="n">
-        <v>3.03</v>
+        <v>7.06</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>1.8</v>
+        <v>2.61</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="R61" t="n">
-        <v>4.24</v>
+        <v>2.52</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF61" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.65</v>
+        <v>2.94</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R64" t="n">
-        <v>2.65</v>
+        <v>2.21</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.94</v>
+        <v>2.65</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R65" t="n">
-        <v>2.21</v>
+        <v>2.65</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>

--- a/jogos_2026-05-04.xlsx
+++ b/jogos_2026-05-04.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI84"/>
+  <dimension ref="A1:BI87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>7.41</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.66</v>
+        <v>3.43</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.25</v>
+        <v>2.64</v>
       </c>
       <c r="R17" t="n">
-        <v>7.41</v>
+        <v>2.33</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.6</v>
+        <v>2.14</v>
       </c>
       <c r="Q34" t="n">
         <v>3.3</v>
       </c>
       <c r="R34" t="n">
-        <v>2.43</v>
+        <v>3.14</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>5.42</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>5.42</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8825,12 +8825,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9013,7 +9013,7 @@
         <v>0</v>
       </c>
       <c r="BI43" s="3" t="n">
-        <v>46146.54861111111</v>
+        <v>46146.54166666666</v>
       </c>
     </row>
     <row r="44">
@@ -9022,12 +9022,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9210,7 +9210,7 @@
         <v>0</v>
       </c>
       <c r="BI44" s="3" t="n">
-        <v>46146.55555555555</v>
+        <v>46146.54861111111</v>
       </c>
     </row>
     <row r="45">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="BI45" s="3" t="n">
-        <v>46146.5625</v>
+        <v>46146.55555555555</v>
       </c>
     </row>
     <row r="46">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="R46" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="R47" t="n">
-        <v>2.4</v>
+        <v>2.67</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>3.25</v>
+        <v>3.89</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.95</v>
+        <v>3.67</v>
       </c>
       <c r="R48" t="n">
-        <v>2.5</v>
+        <v>2.06</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10007,12 +10007,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10195,7 +10195,7 @@
         <v>0</v>
       </c>
       <c r="BI49" s="3" t="n">
-        <v>46146.57291666666</v>
+        <v>46146.5625</v>
       </c>
     </row>
     <row r="50">
@@ -10204,12 +10204,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10392,7 +10392,7 @@
         <v>0</v>
       </c>
       <c r="BI50" s="3" t="n">
-        <v>46146.58333333334</v>
+        <v>46146.57291666666</v>
       </c>
     </row>
     <row r="51">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="R51" t="n">
-        <v>2.54</v>
+        <v>3.23</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="R52" t="n">
-        <v>3.23</v>
+        <v>4.59</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>7.95</v>
+        <v>2.04</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.7</v>
+        <v>3.42</v>
       </c>
       <c r="R53" t="n">
-        <v>1.33</v>
+        <v>3.43</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.79</v>
+        <v>1.58</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="R55" t="n">
-        <v>4.22</v>
+        <v>4.92</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.73</v>
+        <v>2.61</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="R56" t="n">
-        <v>4.59</v>
+        <v>2.52</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="Q57" t="n">
         <v>3.54</v>
       </c>
       <c r="R57" t="n">
-        <v>4.24</v>
+        <v>3.03</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.17</v>
+        <v>1.79</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.54</v>
+        <v>3.7</v>
       </c>
       <c r="R58" t="n">
-        <v>3.03</v>
+        <v>4.22</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="Q59" t="n">
-        <v>4.33</v>
+        <v>3.54</v>
       </c>
       <c r="R59" t="n">
-        <v>4.92</v>
+        <v>4.24</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.61</v>
+        <v>7.95</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.34</v>
+        <v>4.7</v>
       </c>
       <c r="R61" t="n">
-        <v>2.52</v>
+        <v>1.33</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12568,12 +12568,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.93</v>
+        <v>2.6</v>
       </c>
       <c r="Q62" t="n">
         <v>3.4</v>
       </c>
       <c r="R62" t="n">
-        <v>2.29</v>
+        <v>2.54</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12756,7 +12756,7 @@
         <v>0</v>
       </c>
       <c r="BI62" s="3" t="n">
-        <v>46146.58680555555</v>
+        <v>46146.58333333334</v>
       </c>
     </row>
     <row r="63">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12953,7 +12953,7 @@
         <v>0</v>
       </c>
       <c r="BI63" s="3" t="n">
-        <v>46146.60416666666</v>
+        <v>46146.58680555555</v>
       </c>
     </row>
     <row r="64">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13356,27 +13356,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13544,7 +13544,7 @@
         <v>0</v>
       </c>
       <c r="BI66" s="3" t="n">
-        <v>46146.625</v>
+        <v>46146.60416666666</v>
       </c>
     </row>
     <row r="67">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13947,12 +13947,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14135,7 +14135,7 @@
         <v>0</v>
       </c>
       <c r="BI69" s="3" t="n">
-        <v>46146.64583333334</v>
+        <v>46146.625</v>
       </c>
     </row>
     <row r="70">
@@ -14144,12 +14144,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>5.41</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14332,7 +14332,7 @@
         <v>0</v>
       </c>
       <c r="BI70" s="3" t="n">
-        <v>46146.64583333334</v>
+        <v>46146.625</v>
       </c>
     </row>
     <row r="71">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.83</v>
+        <v>1.35</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.93</v>
+        <v>5.41</v>
       </c>
       <c r="R71" t="n">
-        <v>4.66</v>
+        <v>8.5</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF71" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14529,7 +14529,7 @@
         <v>0</v>
       </c>
       <c r="BI71" s="3" t="n">
-        <v>46146.65625</v>
+        <v>46146.64583333334</v>
       </c>
     </row>
     <row r="72">
@@ -14538,12 +14538,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>5.63</v>
+        <v>1.99</v>
       </c>
       <c r="Q72" t="n">
-        <v>4.21</v>
+        <v>3.6</v>
       </c>
       <c r="R72" t="n">
-        <v>1.67</v>
+        <v>3.58</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AF72" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14726,7 +14726,7 @@
         <v>0</v>
       </c>
       <c r="BI72" s="3" t="n">
-        <v>46146.66666666666</v>
+        <v>46146.64583333334</v>
       </c>
     </row>
     <row r="73">
@@ -14735,12 +14735,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF73" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -14923,7 +14923,7 @@
         <v>0</v>
       </c>
       <c r="BI73" s="3" t="n">
-        <v>46146.66666666666</v>
+        <v>46146.65625</v>
       </c>
     </row>
     <row r="74">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15129,12 +15129,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.25</v>
+        <v>5.63</v>
       </c>
       <c r="Q75" t="n">
-        <v>6.46</v>
+        <v>4.21</v>
       </c>
       <c r="R75" t="n">
-        <v>12.8</v>
+        <v>1.67</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF75" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15317,7 +15317,7 @@
         <v>0</v>
       </c>
       <c r="BI75" s="3" t="n">
-        <v>46146.67708333334</v>
+        <v>46146.66666666666</v>
       </c>
     </row>
     <row r="76">
@@ -15326,27 +15326,27 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15514,7 +15514,7 @@
         <v>0</v>
       </c>
       <c r="BI76" s="3" t="n">
-        <v>46146.79166666666</v>
+        <v>46146.66666666666</v>
       </c>
     </row>
     <row r="77">
@@ -15523,27 +15523,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>6.46</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>12.8</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15711,7 +15711,7 @@
         <v>0</v>
       </c>
       <c r="BI77" s="3" t="n">
-        <v>46146.79166666666</v>
+        <v>46146.67708333334</v>
       </c>
     </row>
     <row r="78">
@@ -15720,27 +15720,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15908,7 +15908,7 @@
         <v>0</v>
       </c>
       <c r="BI78" s="3" t="n">
-        <v>46146.83333333334</v>
+        <v>46146.70833333334</v>
       </c>
     </row>
     <row r="79">
@@ -15917,12 +15917,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16105,7 +16105,7 @@
         <v>0</v>
       </c>
       <c r="BI79" s="3" t="n">
-        <v>46146.83333333334</v>
+        <v>46146.79166666666</v>
       </c>
     </row>
     <row r="80">
@@ -16114,12 +16114,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16302,7 +16302,7 @@
         <v>0</v>
       </c>
       <c r="BI80" s="3" t="n">
-        <v>46146.83333333334</v>
+        <v>46146.79166666666</v>
       </c>
     </row>
     <row r="81">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16508,12 +16508,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16696,7 +16696,7 @@
         <v>0</v>
       </c>
       <c r="BI82" s="3" t="n">
-        <v>46146.875</v>
+        <v>46146.83333333334</v>
       </c>
     </row>
     <row r="83">
@@ -16705,12 +16705,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16893,7 +16893,7 @@
         <v>0</v>
       </c>
       <c r="BI83" s="3" t="n">
-        <v>46146.89583333334</v>
+        <v>46146.83333333334</v>
       </c>
     </row>
     <row r="84">
@@ -16902,7 +16902,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,141 +16955,732 @@
         </is>
       </c>
       <c r="P84" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R84" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="S84" t="n">
+        <v>0</v>
+      </c>
+      <c r="T84" t="n">
+        <v>0</v>
+      </c>
+      <c r="U84" t="n">
+        <v>0</v>
+      </c>
+      <c r="V84" t="n">
+        <v>0</v>
+      </c>
+      <c r="W84" t="n">
+        <v>0</v>
+      </c>
+      <c r="X84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI84" s="3" t="n">
+        <v>46146.83333333334</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Universitario de Vinto</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Blooming</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N85" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" t="n">
+        <v>0</v>
+      </c>
+      <c r="T85" t="n">
+        <v>0</v>
+      </c>
+      <c r="U85" t="n">
+        <v>0</v>
+      </c>
+      <c r="V85" t="n">
+        <v>0</v>
+      </c>
+      <c r="W85" t="n">
+        <v>0</v>
+      </c>
+      <c r="X85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI85" s="3" t="n">
+        <v>46146.875</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Gimnasia y Tiro</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Agropecuario</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N86" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q84" t="n">
+      <c r="Q86" t="n">
         <v>2.8</v>
       </c>
-      <c r="R84" t="n">
+      <c r="R86" t="n">
         <v>3.8</v>
       </c>
-      <c r="S84" t="n">
-        <v>0</v>
-      </c>
-      <c r="T84" t="n">
-        <v>0</v>
-      </c>
-      <c r="U84" t="n">
-        <v>0</v>
-      </c>
-      <c r="V84" t="n">
-        <v>0</v>
-      </c>
-      <c r="W84" t="n">
-        <v>0</v>
-      </c>
-      <c r="X84" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y84" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI84" s="3" t="n">
+      <c r="S86" t="n">
+        <v>0</v>
+      </c>
+      <c r="T86" t="n">
+        <v>0</v>
+      </c>
+      <c r="U86" t="n">
+        <v>0</v>
+      </c>
+      <c r="V86" t="n">
+        <v>0</v>
+      </c>
+      <c r="W86" t="n">
+        <v>0</v>
+      </c>
+      <c r="X86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI86" s="3" t="n">
+        <v>46146.89583333334</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>San Marcos</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N87" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="n">
+        <v>0</v>
+      </c>
+      <c r="T87" t="n">
+        <v>0</v>
+      </c>
+      <c r="U87" t="n">
+        <v>0</v>
+      </c>
+      <c r="V87" t="n">
+        <v>0</v>
+      </c>
+      <c r="W87" t="n">
+        <v>0</v>
+      </c>
+      <c r="X87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI87" s="3" t="n">
         <v>46146.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-05-04.xlsx
+++ b/jogos_2026-05-04.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>7.41</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="R15" t="n">
-        <v>4.57</v>
+        <v>7.41</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4195,10 +4195,10 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.6</v>
+        <v>2.14</v>
       </c>
       <c r="Q29" t="n">
         <v>3.3</v>
       </c>
       <c r="R29" t="n">
-        <v>2.43</v>
+        <v>3.14</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.55</v>
+        <v>3.89</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.28</v>
+        <v>3.67</v>
       </c>
       <c r="R47" t="n">
-        <v>2.67</v>
+        <v>2.06</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>3.89</v>
+        <v>2.55</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.67</v>
+        <v>3.28</v>
       </c>
       <c r="R48" t="n">
-        <v>2.06</v>
+        <v>2.67</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2</v>
+        <v>2.61</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.8</v>
+        <v>3.34</v>
       </c>
       <c r="R51" t="n">
-        <v>3.23</v>
+        <v>2.52</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.73</v>
+        <v>1.38</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.3</v>
+        <v>5.48</v>
       </c>
       <c r="R52" t="n">
-        <v>4.59</v>
+        <v>7.06</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.42</v>
+        <v>3.8</v>
       </c>
       <c r="R53" t="n">
-        <v>3.43</v>
+        <v>3.23</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.22</v>
+        <v>1.79</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.76</v>
+        <v>3.7</v>
       </c>
       <c r="R54" t="n">
-        <v>3.48</v>
+        <v>4.22</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.58</v>
+        <v>2.22</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.33</v>
+        <v>2.76</v>
       </c>
       <c r="R55" t="n">
-        <v>4.92</v>
+        <v>3.48</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.61</v>
+        <v>2.17</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.34</v>
+        <v>3.54</v>
       </c>
       <c r="R56" t="n">
-        <v>2.52</v>
+        <v>3.03</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.17</v>
+        <v>2.04</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.54</v>
+        <v>3.42</v>
       </c>
       <c r="R57" t="n">
-        <v>3.03</v>
+        <v>3.43</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="R58" t="n">
-        <v>4.22</v>
+        <v>4.59</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1.8</v>
+        <v>7.95</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.54</v>
+        <v>4.7</v>
       </c>
       <c r="R59" t="n">
-        <v>4.24</v>
+        <v>1.33</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="Q60" t="n">
-        <v>5.48</v>
+        <v>4.33</v>
       </c>
       <c r="R60" t="n">
-        <v>7.06</v>
+        <v>4.92</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>7.95</v>
+        <v>2.6</v>
       </c>
       <c r="Q61" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="R61" t="n">
-        <v>1.33</v>
+        <v>2.54</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="R62" t="n">
-        <v>2.54</v>
+        <v>4.24</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.65</v>
+        <v>2.94</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R65" t="n">
-        <v>2.65</v>
+        <v>2.21</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.35</v>
+        <v>1.99</v>
       </c>
       <c r="Q71" t="n">
-        <v>5.41</v>
+        <v>3.6</v>
       </c>
       <c r="R71" t="n">
-        <v>8.5</v>
+        <v>3.58</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.99</v>
+        <v>1.35</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.6</v>
+        <v>5.41</v>
       </c>
       <c r="R72" t="n">
-        <v>3.58</v>
+        <v>8.5</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF74" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF75" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>

--- a/jogos_2026-05-04.xlsx
+++ b/jogos_2026-05-04.xlsx
@@ -301,36 +301,36 @@
     <t>Croatia Druga HNL</t>
   </si>
   <si>
+    <t>India Indian Super League</t>
+  </si>
+  <si>
+    <t>England Premier League</t>
+  </si>
+  <si>
+    <t>Uzbekistan Uzbekistan Super League</t>
+  </si>
+  <si>
     <t>Egypt Egyptian Premier League</t>
   </si>
   <si>
+    <t>Serbia Prva Liga</t>
+  </si>
+  <si>
     <t>Russia FNL</t>
   </si>
   <si>
-    <t>Uzbekistan Uzbekistan Super League</t>
-  </si>
-  <si>
-    <t>England Premier League</t>
-  </si>
-  <si>
-    <t>Serbia Prva Liga</t>
-  </si>
-  <si>
-    <t>India Indian Super League</t>
-  </si>
-  <si>
     <t>Oman Professional League</t>
   </si>
   <si>
     <t>Romania Liga I</t>
   </si>
   <si>
+    <t>Serbia SuperLiga</t>
+  </si>
+  <si>
     <t>Tunisia Ligue 1</t>
   </si>
   <si>
-    <t>Serbia SuperLiga</t>
-  </si>
-  <si>
     <t>Azerbaijan Premyer Liqası</t>
   </si>
   <si>
@@ -340,51 +340,51 @@
     <t>Republic of Ireland Premier Division</t>
   </si>
   <si>
+    <t>Croatia Prva HNL</t>
+  </si>
+  <si>
+    <t>Jordan Jordanian Pro League</t>
+  </si>
+  <si>
     <t>Poland 1. Liga</t>
   </si>
   <si>
     <t>Morocco Botola Pro</t>
   </si>
   <si>
-    <t>Jordan Jordanian Pro League</t>
-  </si>
-  <si>
-    <t>Croatia Prva HNL</t>
-  </si>
-  <si>
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
     <t>Austria Bundesliga</t>
   </si>
   <si>
+    <t>Italy Serie A</t>
+  </si>
+  <si>
     <t>Scotland Premiership</t>
   </si>
   <si>
-    <t>Italy Serie A</t>
-  </si>
-  <si>
     <t>Algeria Ligue 1</t>
   </si>
   <si>
+    <t>Norway Eliteserien</t>
+  </si>
+  <si>
     <t>Israel Israeli Premier League</t>
   </si>
   <si>
-    <t>Norway Eliteserien</t>
+    <t>Denmark Superliga</t>
+  </si>
+  <si>
+    <t>Portugal LigaPro</t>
+  </si>
+  <si>
+    <t>Sweden Allsvenskan</t>
   </si>
   <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
-    <t>Portugal LigaPro</t>
-  </si>
-  <si>
-    <t>Denmark Superliga</t>
-  </si>
-  <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
@@ -409,12 +409,12 @@
     <t>Brazil Serie B</t>
   </si>
   <si>
+    <t>Brazil Serie C</t>
+  </si>
+  <si>
     <t>Argentina Prim B Nacional</t>
   </si>
   <si>
-    <t>Brazil Serie C</t>
-  </si>
-  <si>
     <t>Bolivia LFPB</t>
   </si>
   <si>
@@ -427,12 +427,12 @@
     <t>2026</t>
   </si>
   <si>
+    <t>Persib</t>
+  </si>
+  <si>
     <t>PSM</t>
   </si>
   <si>
-    <t>Persib</t>
-  </si>
-  <si>
     <t>Welayta Dicha</t>
   </si>
   <si>
@@ -445,114 +445,114 @@
     <t>Aston Villa Ladies</t>
   </si>
   <si>
+    <t>Mekelakeya</t>
+  </si>
+  <si>
     <t>Awassa Kenema</t>
   </si>
   <si>
-    <t>Mekelakeya</t>
-  </si>
-  <si>
     <t>Dugopolje</t>
   </si>
   <si>
+    <t>Odisha FC</t>
+  </si>
+  <si>
+    <t>Chelsea</t>
+  </si>
+  <si>
+    <t>Xorazm</t>
+  </si>
+  <si>
+    <t>Lokomotiv</t>
+  </si>
+  <si>
     <t>Pharco</t>
   </si>
   <si>
+    <t>Stepojevac Vaga</t>
+  </si>
+  <si>
+    <t>OFK Vršac</t>
+  </si>
+  <si>
     <t>Ural</t>
   </si>
   <si>
-    <t>Xorazm</t>
-  </si>
-  <si>
-    <t>Chelsea</t>
-  </si>
-  <si>
-    <t>OFK Vršac</t>
-  </si>
-  <si>
-    <t>Odisha FC</t>
-  </si>
-  <si>
-    <t>Lokomotiv</t>
-  </si>
-  <si>
-    <t>Stepojevac Vaga</t>
-  </si>
-  <si>
     <t>Al Khabourah</t>
   </si>
   <si>
     <t>Unirea Slobozia</t>
   </si>
   <si>
+    <t>Radnik Surdulica</t>
+  </si>
+  <si>
+    <t>Zarzis</t>
+  </si>
+  <si>
     <t>Monastir</t>
   </si>
   <si>
     <t>Nasaf</t>
   </si>
   <si>
+    <t>Jeunesse Sportive Omrane</t>
+  </si>
+  <si>
     <t>CA Bizertin</t>
   </si>
   <si>
-    <t>Zarzis</t>
-  </si>
-  <si>
-    <t>Radnik Surdulica</t>
-  </si>
-  <si>
-    <t>Jeunesse Sportive Omrane</t>
-  </si>
-  <si>
     <t>Al Nasr</t>
   </si>
   <si>
     <t>Qarabağ</t>
   </si>
   <si>
+    <t>Kerry</t>
+  </si>
+  <si>
+    <t>Sligo Rovers</t>
+  </si>
+  <si>
+    <t>Istra 1961</t>
+  </si>
+  <si>
+    <t>Waterford</t>
+  </si>
+  <si>
+    <t>Derry City</t>
+  </si>
+  <si>
+    <t>Bohemians</t>
+  </si>
+  <si>
     <t>Longford Town</t>
   </si>
   <si>
+    <t>Treaty United</t>
+  </si>
+  <si>
+    <t>Cobh Ramblers</t>
+  </si>
+  <si>
+    <t>Al Jazeera</t>
+  </si>
+  <si>
+    <t>Al Ahli</t>
+  </si>
+  <si>
+    <t>Finn Harps</t>
+  </si>
+  <si>
     <t>Shamrock Rovers</t>
   </si>
   <si>
-    <t>Sligo Rovers</t>
-  </si>
-  <si>
-    <t>Kerry</t>
-  </si>
-  <si>
     <t>Polonia Bytom</t>
   </si>
   <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
-    <t>Waterford</t>
-  </si>
-  <si>
-    <t>Derry City</t>
-  </si>
-  <si>
     <t>Hassania Agadir</t>
   </si>
   <si>
-    <t>Cobh Ramblers</t>
-  </si>
-  <si>
-    <t>Al Jazeera</t>
-  </si>
-  <si>
-    <t>Bohemians</t>
-  </si>
-  <si>
-    <t>Istra 1961</t>
-  </si>
-  <si>
-    <t>Treaty United</t>
-  </si>
-  <si>
-    <t>Al Ahli</t>
-  </si>
-  <si>
     <t>Al Feiha</t>
   </si>
   <si>
@@ -562,54 +562,54 @@
     <t>Rheindorf Altach</t>
   </si>
   <si>
+    <t>Arsenal Tula</t>
+  </si>
+  <si>
+    <t>Cremonese</t>
+  </si>
+  <si>
     <t>Hearts</t>
   </si>
   <si>
-    <t>Cremonese</t>
-  </si>
-  <si>
-    <t>Arsenal Tula</t>
-  </si>
-  <si>
     <t>CR Belouizdad</t>
   </si>
   <si>
+    <t>Al Ittihad</t>
+  </si>
+  <si>
+    <t>Wadi Degla</t>
+  </si>
+  <si>
+    <t>FK Bodo - Glimt</t>
+  </si>
+  <si>
+    <t>Bnei Sakhnin</t>
+  </si>
+  <si>
     <t>Maccabi Netanya</t>
   </si>
   <si>
-    <t>Bnei Sakhnin</t>
-  </si>
-  <si>
-    <t>FK Bodo - Glimt</t>
+    <t>Midtjylland</t>
+  </si>
+  <si>
+    <t>Porto II</t>
+  </si>
+  <si>
+    <t>Torreense</t>
+  </si>
+  <si>
+    <t>Halmstad</t>
+  </si>
+  <si>
+    <t>Djurgården</t>
+  </si>
+  <si>
+    <t>Čukarički</t>
   </si>
   <si>
     <t>Radomiak Radom</t>
   </si>
   <si>
-    <t>Al Ittihad</t>
-  </si>
-  <si>
-    <t>Djurgården</t>
-  </si>
-  <si>
-    <t>Torreense</t>
-  </si>
-  <si>
-    <t>Halmstad</t>
-  </si>
-  <si>
-    <t>Porto II</t>
-  </si>
-  <si>
-    <t>Čukarički</t>
-  </si>
-  <si>
-    <t>Midtjylland</t>
-  </si>
-  <si>
-    <t>Wadi Degla</t>
-  </si>
-  <si>
     <t>Landskrona</t>
   </si>
   <si>
@@ -622,33 +622,33 @@
     <t>B36</t>
   </si>
   <si>
+    <t>Al Ittifaq</t>
+  </si>
+  <si>
     <t>Vasas</t>
   </si>
   <si>
     <t>Yacoub El Mansour</t>
   </si>
   <si>
-    <t>Al Ittifaq</t>
+    <t>LASK Linz</t>
   </si>
   <si>
     <t>Almería</t>
   </si>
   <si>
-    <t>LASK Linz</t>
-  </si>
-  <si>
     <t>Roma</t>
   </si>
   <si>
+    <t>USM Alger</t>
+  </si>
+  <si>
     <t>Everton</t>
   </si>
   <si>
     <t>Sevilla FC</t>
   </si>
   <si>
-    <t>USM Alger</t>
-  </si>
-  <si>
     <t>Sporting CP</t>
   </si>
   <si>
@@ -661,18 +661,18 @@
     <t>Vila Nova</t>
   </si>
   <si>
+    <t>Ypiranga Erechim</t>
+  </si>
+  <si>
+    <t>Floresta</t>
+  </si>
+  <si>
     <t>Quilmes</t>
   </si>
   <si>
     <t>Figueirense</t>
   </si>
   <si>
-    <t>Ypiranga Erechim</t>
-  </si>
-  <si>
-    <t>Floresta</t>
-  </si>
-  <si>
     <t>Universitario de Vinto</t>
   </si>
   <si>
@@ -682,12 +682,12 @@
     <t>Gimnasia y Tiro</t>
   </si>
   <si>
+    <t>PSIM Yogyakarta</t>
+  </si>
+  <si>
     <t>Bhayangkara</t>
   </si>
   <si>
-    <t>PSIM Yogyakarta</t>
-  </si>
-  <si>
     <t>Hadiya Hosaena</t>
   </si>
   <si>
@@ -700,114 +700,114 @@
     <t>West Ham United Women</t>
   </si>
   <si>
+    <t>Adama Kenema</t>
+  </si>
+  <si>
     <t>Sheger Ketema</t>
   </si>
   <si>
-    <t>Adama Kenema</t>
-  </si>
-  <si>
     <t>Cibalia</t>
   </si>
   <si>
+    <t>Bengaluru</t>
+  </si>
+  <si>
+    <t>Nottingham Forest</t>
+  </si>
+  <si>
+    <t>Andijan</t>
+  </si>
+  <si>
+    <t>Qizilqum</t>
+  </si>
+  <si>
     <t>Al Mokawloon</t>
   </si>
   <si>
+    <t>Kabel Novi Sad</t>
+  </si>
+  <si>
+    <t>Jedinstvo Ub</t>
+  </si>
+  <si>
     <t>Shinnik</t>
   </si>
   <si>
-    <t>Andijan</t>
-  </si>
-  <si>
-    <t>Nottingham Forest</t>
-  </si>
-  <si>
-    <t>Jedinstvo Ub</t>
-  </si>
-  <si>
-    <t>Bengaluru</t>
-  </si>
-  <si>
-    <t>Qizilqum</t>
-  </si>
-  <si>
-    <t>Kabel Novi Sad</t>
-  </si>
-  <si>
     <t>Saham</t>
   </si>
   <si>
     <t>Hermannstadt</t>
   </si>
   <si>
+    <t>Vojvodina</t>
+  </si>
+  <si>
+    <t>Etoile du Sahel</t>
+  </si>
+  <si>
     <t>Métlaoui</t>
   </si>
   <si>
     <t>Navbahor</t>
   </si>
   <si>
+    <t>ES Tunis</t>
+  </si>
+  <si>
     <t>Marsa</t>
   </si>
   <si>
-    <t>Etoile du Sahel</t>
-  </si>
-  <si>
-    <t>Vojvodina</t>
-  </si>
-  <si>
-    <t>ES Tunis</t>
-  </si>
-  <si>
     <t>Al-Nahda</t>
   </si>
   <si>
     <t>Turan</t>
   </si>
   <si>
+    <t>Cork City</t>
+  </si>
+  <si>
+    <t>St Patrick's Athl.</t>
+  </si>
+  <si>
+    <t>Slaven Koprivnica</t>
+  </si>
+  <si>
+    <t>Dundalk</t>
+  </si>
+  <si>
+    <t>Galway United</t>
+  </si>
+  <si>
+    <t>Shelbourne</t>
+  </si>
+  <si>
     <t>Athlone Town</t>
   </si>
   <si>
+    <t>Wexford</t>
+  </si>
+  <si>
+    <t>UCD</t>
+  </si>
+  <si>
+    <t>Shabab Al Ordon</t>
+  </si>
+  <si>
+    <t>Al Buqa'a</t>
+  </si>
+  <si>
+    <t>Bray Wanderers</t>
+  </si>
+  <si>
     <t>Drogheda United</t>
   </si>
   <si>
-    <t>St Patrick's Athl.</t>
-  </si>
-  <si>
-    <t>Cork City</t>
-  </si>
-  <si>
     <t>Polonia Warszawa</t>
   </si>
   <si>
-    <t>Bray Wanderers</t>
-  </si>
-  <si>
-    <t>Dundalk</t>
-  </si>
-  <si>
-    <t>Galway United</t>
-  </si>
-  <si>
     <t>Olympic Safi</t>
   </si>
   <si>
-    <t>UCD</t>
-  </si>
-  <si>
-    <t>Shabab Al Ordon</t>
-  </si>
-  <si>
-    <t>Shelbourne</t>
-  </si>
-  <si>
-    <t>Slaven Koprivnica</t>
-  </si>
-  <si>
-    <t>Wexford</t>
-  </si>
-  <si>
-    <t>Al Buqa'a</t>
-  </si>
-  <si>
     <t>Al Riyadh</t>
   </si>
   <si>
@@ -817,54 +817,54 @@
     <t>Wolfsberger AC</t>
   </si>
   <si>
+    <t>Rotor Volgograd</t>
+  </si>
+  <si>
+    <t>Lazio</t>
+  </si>
+  <si>
     <t>Rangers</t>
   </si>
   <si>
-    <t>Lazio</t>
-  </si>
-  <si>
-    <t>Rotor Volgograd</t>
-  </si>
-  <si>
     <t>USM Khenchela</t>
   </si>
   <si>
+    <t>Petrojet</t>
+  </si>
+  <si>
+    <t>Kahraba Ismailia</t>
+  </si>
+  <si>
+    <t>Molde</t>
+  </si>
+  <si>
+    <t>Maccabi Bnei Raina</t>
+  </si>
+  <si>
     <t>Hapoel Katamon</t>
   </si>
   <si>
-    <t>Maccabi Bnei Raina</t>
-  </si>
-  <si>
-    <t>Molde</t>
+    <t>Viborg</t>
+  </si>
+  <si>
+    <t>Felgueiras 1932</t>
+  </si>
+  <si>
+    <t>FC Penafiel</t>
+  </si>
+  <si>
+    <t>Brommapojkarna</t>
+  </si>
+  <si>
+    <t>IFK Göteborg</t>
+  </si>
+  <si>
+    <t>Red Star Belgrade</t>
   </si>
   <si>
     <t>Lechia Gdańsk</t>
   </si>
   <si>
-    <t>Petrojet</t>
-  </si>
-  <si>
-    <t>IFK Göteborg</t>
-  </si>
-  <si>
-    <t>FC Penafiel</t>
-  </si>
-  <si>
-    <t>Brommapojkarna</t>
-  </si>
-  <si>
-    <t>Felgueiras 1932</t>
-  </si>
-  <si>
-    <t>Red Star Belgrade</t>
-  </si>
-  <si>
-    <t>Viborg</t>
-  </si>
-  <si>
-    <t>Kahraba Ismailia</t>
-  </si>
-  <si>
     <t>Öster</t>
   </si>
   <si>
@@ -877,6 +877,9 @@
     <t>NSÍ</t>
   </si>
   <si>
+    <t>Al Najma</t>
+  </si>
+  <si>
     <t>Al Kholood</t>
   </si>
   <si>
@@ -886,27 +889,24 @@
     <t>RSB Berkane</t>
   </si>
   <si>
-    <t>Al Najma</t>
+    <t>Rapid Wien</t>
   </si>
   <si>
     <t>Mirandés</t>
   </si>
   <si>
-    <t>Rapid Wien</t>
-  </si>
-  <si>
     <t>Fiorentina</t>
   </si>
   <si>
+    <t>Paradou AC</t>
+  </si>
+  <si>
     <t>Manchester City</t>
   </si>
   <si>
     <t>Real Sociedad</t>
   </si>
   <si>
-    <t>Paradou AC</t>
-  </si>
-  <si>
     <t>Vitória Guimarães</t>
   </si>
   <si>
@@ -919,16 +919,16 @@
     <t>Athletic Club</t>
   </si>
   <si>
+    <t>Ituano</t>
+  </si>
+  <si>
+    <t>Maranhão</t>
+  </si>
+  <si>
     <t>Chacarita Juniors</t>
   </si>
   <si>
     <t>Barra do Garcas</t>
-  </si>
-  <si>
-    <t>Ituano</t>
-  </si>
-  <si>
-    <t>Maranhão</t>
   </si>
   <si>
     <t>Blooming</t>
@@ -1539,133 +1539,133 @@
         <v>308</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="S2">
-        <v>2.7</v>
+        <v>1.72</v>
       </c>
       <c r="T2">
-        <v>2.02</v>
+        <v>2.42</v>
       </c>
       <c r="U2">
-        <v>4.08</v>
+        <v>8.65</v>
       </c>
       <c r="V2">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="W2">
-        <v>2.71</v>
+        <v>3.04</v>
       </c>
       <c r="X2">
-        <v>2.81</v>
+        <v>2.39</v>
       </c>
       <c r="Y2">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="Z2">
-        <v>6.7</v>
+        <v>5.35</v>
       </c>
       <c r="AA2">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AB2">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC2">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AD2">
-        <v>3.34</v>
+        <v>3.96</v>
       </c>
       <c r="AE2">
+        <v>1.63</v>
+      </c>
+      <c r="AF2">
+        <v>2.12</v>
+      </c>
+      <c r="AG2">
+        <v>2.49</v>
+      </c>
+      <c r="AH2">
+        <v>1.42</v>
+      </c>
+      <c r="AI2">
+        <v>4.35</v>
+      </c>
+      <c r="AJ2">
+        <v>1.14</v>
+      </c>
+      <c r="AK2">
+        <v>2.05</v>
+      </c>
+      <c r="AL2">
+        <v>1.7</v>
+      </c>
+      <c r="AM2">
+        <v>1.1</v>
+      </c>
+      <c r="AN2">
+        <v>3.28</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <v>0</v>
+      </c>
+      <c r="AV2">
+        <v>0</v>
+      </c>
+      <c r="AW2">
+        <v>0</v>
+      </c>
+      <c r="AX2">
+        <v>0</v>
+      </c>
+      <c r="AY2">
+        <v>0</v>
+      </c>
+      <c r="AZ2">
+        <v>0</v>
+      </c>
+      <c r="BA2">
+        <v>0</v>
+      </c>
+      <c r="BB2">
+        <v>1.15</v>
+      </c>
+      <c r="BC2">
+        <v>1.83</v>
+      </c>
+      <c r="BD2">
+        <v>4.3</v>
+      </c>
+      <c r="BE2">
         <v>1.85</v>
       </c>
-      <c r="AF2">
-        <v>1.83</v>
-      </c>
-      <c r="AG2">
-        <v>3.05</v>
-      </c>
-      <c r="AH2">
-        <v>1.28</v>
-      </c>
-      <c r="AI2">
-        <v>5.8</v>
-      </c>
-      <c r="AJ2">
-        <v>1.07</v>
-      </c>
-      <c r="AK2">
-        <v>1.68</v>
-      </c>
-      <c r="AL2">
-        <v>2.02</v>
-      </c>
-      <c r="AM2">
-        <v>1.26</v>
-      </c>
-      <c r="AN2">
-        <v>1.61</v>
-      </c>
-      <c r="AO2">
-        <v>0</v>
-      </c>
-      <c r="AP2">
-        <v>0</v>
-      </c>
-      <c r="AQ2">
-        <v>0</v>
-      </c>
-      <c r="AR2">
-        <v>0</v>
-      </c>
-      <c r="AS2">
-        <v>0</v>
-      </c>
-      <c r="AT2">
-        <v>0</v>
-      </c>
-      <c r="AU2">
-        <v>0</v>
-      </c>
-      <c r="AV2">
-        <v>0</v>
-      </c>
-      <c r="AW2">
-        <v>0</v>
-      </c>
-      <c r="AX2">
-        <v>0</v>
-      </c>
-      <c r="AY2">
-        <v>0</v>
-      </c>
-      <c r="AZ2">
-        <v>0</v>
-      </c>
-      <c r="BA2">
-        <v>0</v>
-      </c>
-      <c r="BB2">
-        <v>1.19</v>
-      </c>
-      <c r="BC2">
-        <v>2.03</v>
-      </c>
-      <c r="BD2">
-        <v>3.8</v>
-      </c>
-      <c r="BE2">
-        <v>1.68</v>
-      </c>
       <c r="BF2">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="BG2">
         <v>0</v>
@@ -1724,79 +1724,79 @@
         <v>308</v>
       </c>
       <c r="P3">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Q3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R3">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>1.72</v>
+        <v>2.7</v>
       </c>
       <c r="T3">
-        <v>2.42</v>
+        <v>2.02</v>
       </c>
       <c r="U3">
-        <v>8.65</v>
+        <v>4.08</v>
       </c>
       <c r="V3">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="W3">
-        <v>3.04</v>
+        <v>2.71</v>
       </c>
       <c r="X3">
-        <v>2.39</v>
+        <v>2.81</v>
       </c>
       <c r="Y3">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="Z3">
-        <v>5.35</v>
+        <v>6.7</v>
       </c>
       <c r="AA3">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AB3">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC3">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AD3">
-        <v>3.96</v>
+        <v>3.34</v>
       </c>
       <c r="AE3">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AF3">
-        <v>2.12</v>
+        <v>1.83</v>
       </c>
       <c r="AG3">
-        <v>2.49</v>
+        <v>3.05</v>
       </c>
       <c r="AH3">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AI3">
-        <v>4.35</v>
+        <v>5.8</v>
       </c>
       <c r="AJ3">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AK3">
-        <v>2.05</v>
+        <v>1.68</v>
       </c>
       <c r="AL3">
-        <v>1.7</v>
+        <v>2.02</v>
       </c>
       <c r="AM3">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="AN3">
-        <v>3.28</v>
+        <v>1.61</v>
       </c>
       <c r="AO3">
         <v>0</v>
@@ -1838,19 +1838,19 @@
         <v>0</v>
       </c>
       <c r="BB3">
+        <v>1.19</v>
+      </c>
+      <c r="BC3">
+        <v>2.03</v>
+      </c>
+      <c r="BD3">
+        <v>3.8</v>
+      </c>
+      <c r="BE3">
+        <v>1.68</v>
+      </c>
+      <c r="BF3">
         <v>1.15</v>
-      </c>
-      <c r="BC3">
-        <v>1.83</v>
-      </c>
-      <c r="BD3">
-        <v>4.3</v>
-      </c>
-      <c r="BE3">
-        <v>1.85</v>
-      </c>
-      <c r="BF3">
-        <v>1.22</v>
       </c>
       <c r="BG3">
         <v>0</v>
@@ -3204,133 +3204,133 @@
         <v>308</v>
       </c>
       <c r="P11">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Q11">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="R11">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="S11">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="V11">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="W11">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="X11">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="Y11">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z11">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AA11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC11">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD11">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE11">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AF11">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG11">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AH11">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI11">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AJ11">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK11">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AL11">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AM11">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AN11">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO11">
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AQ11">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR11">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AS11">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AT11">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AU11">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AV11">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AW11">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX11">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AY11">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ11">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="BA11">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BB11">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BC11">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="BD11">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BE11">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BF11">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BG11">
         <v>0</v>
@@ -3389,133 +3389,133 @@
         <v>308</v>
       </c>
       <c r="P12">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="Q12">
-        <v>3.42</v>
+        <v>3.75</v>
       </c>
       <c r="R12">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="S12">
-        <v>2.42</v>
+        <v>2.15</v>
       </c>
       <c r="T12">
-        <v>2.01</v>
+        <v>2.3</v>
       </c>
       <c r="U12">
-        <v>4.85</v>
+        <v>4.2</v>
       </c>
       <c r="V12">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="W12">
+        <v>3.3</v>
+      </c>
+      <c r="X12">
+        <v>2.49</v>
+      </c>
+      <c r="Y12">
+        <v>1.53</v>
+      </c>
+      <c r="Z12">
+        <v>5.8</v>
+      </c>
+      <c r="AA12">
+        <v>1.12</v>
+      </c>
+      <c r="AB12">
+        <v>1.01</v>
+      </c>
+      <c r="AC12">
+        <v>1.18</v>
+      </c>
+      <c r="AD12">
+        <v>4.2</v>
+      </c>
+      <c r="AE12">
+        <v>1.67</v>
+      </c>
+      <c r="AF12">
+        <v>2.27</v>
+      </c>
+      <c r="AG12">
         <v>2.7</v>
       </c>
-      <c r="X12">
-        <v>3.25</v>
-      </c>
-      <c r="Y12">
-        <v>1.32</v>
-      </c>
-      <c r="Z12">
-        <v>7.6</v>
-      </c>
-      <c r="AA12">
-        <v>1.03</v>
-      </c>
-      <c r="AB12">
-        <v>1.03</v>
-      </c>
-      <c r="AC12">
-        <v>1.35</v>
-      </c>
-      <c r="AD12">
-        <v>2.74</v>
-      </c>
-      <c r="AE12">
-        <v>2.17</v>
-      </c>
-      <c r="AF12">
-        <v>1.68</v>
-      </c>
-      <c r="AG12">
-        <v>4.07</v>
-      </c>
       <c r="AH12">
-        <v>1.19</v>
+        <v>1.49</v>
       </c>
       <c r="AI12">
-        <v>7.3</v>
+        <v>4.75</v>
       </c>
       <c r="AJ12">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AK12">
-        <v>1.97</v>
+        <v>1.67</v>
       </c>
       <c r="AL12">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AM12">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AN12">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="AO12">
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AU12">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="AV12">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AW12">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AX12">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AY12">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AZ12">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="BA12">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BB12">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="BC12">
-        <v>2.32</v>
+        <v>1.91</v>
       </c>
       <c r="BD12">
-        <v>3.28</v>
+        <v>4.2</v>
       </c>
       <c r="BE12">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="BF12">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="BG12">
         <v>0</v>
@@ -3720,10 +3720,10 @@
         <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D14" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E14" t="s">
         <v>149</v>
@@ -3759,133 +3759,133 @@
         <v>308</v>
       </c>
       <c r="P14">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q14">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R14">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="S14">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V14">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W14">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X14">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Y14">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z14">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA14">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC14">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD14">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AE14">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF14">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AG14">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH14">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AI14">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AJ14">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK14">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL14">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM14">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN14">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AO14">
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ14">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR14">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AS14">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AT14">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AU14">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="AV14">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="AW14">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AX14">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AY14">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AZ14">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="BA14">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BB14">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC14">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BD14">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE14">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF14">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG14">
         <v>0</v>
@@ -3905,7 +3905,7 @@
         <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D15" t="s">
         <v>134</v>
@@ -3944,133 +3944,133 @@
         <v>308</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI15">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AL15">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AM15">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AN15">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO15">
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AU15">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AV15">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AW15">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX15">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AY15">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ15">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BA15">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BB15">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BC15">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="BD15">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BE15">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BF15">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BG15">
         <v>0</v>
@@ -4090,7 +4090,7 @@
         <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D16" t="s">
         <v>134</v>
@@ -4275,10 +4275,10 @@
         <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D17" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E17" t="s">
         <v>152</v>
@@ -4460,7 +4460,7 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D18" t="s">
         <v>134</v>
@@ -4499,79 +4499,79 @@
         <v>308</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="AH18">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI18">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL18">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM18">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN18">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AO18">
         <v>0</v>
@@ -4613,19 +4613,19 @@
         <v>0</v>
       </c>
       <c r="BB18">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC18">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BD18">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE18">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF18">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG18">
         <v>0</v>
@@ -5054,61 +5054,61 @@
         <v>308</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB21">
         <v>0</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AH21">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI21">
         <v>0</v>
@@ -5117,16 +5117,16 @@
         <v>0</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL21">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AM21">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN21">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO21">
         <v>0</v>
@@ -5171,13 +5171,13 @@
         <v>0</v>
       </c>
       <c r="BC21">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BD21">
         <v>0</v>
       </c>
       <c r="BE21">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BF21">
         <v>0</v>
@@ -5200,10 +5200,10 @@
         <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="D22" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E22" t="s">
         <v>157</v>
@@ -5385,7 +5385,7 @@
         <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D23" t="s">
         <v>134</v>
@@ -5570,10 +5570,10 @@
         <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D24" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E24" t="s">
         <v>159</v>
@@ -5794,61 +5794,61 @@
         <v>308</v>
       </c>
       <c r="P25">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q25">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R25">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S25">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T25">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="U25">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="V25">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W25">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="X25">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Y25">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z25">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AA25">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB25">
         <v>0</v>
       </c>
       <c r="AC25">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD25">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="AE25">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AF25">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG25">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AH25">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AI25">
         <v>0</v>
@@ -5857,16 +5857,16 @@
         <v>0</v>
       </c>
       <c r="AK25">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AL25">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AM25">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN25">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO25">
         <v>0</v>
@@ -5911,13 +5911,13 @@
         <v>0</v>
       </c>
       <c r="BC25">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="BD25">
         <v>0</v>
       </c>
       <c r="BE25">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="BF25">
         <v>0</v>
@@ -5940,7 +5940,7 @@
         <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D26" t="s">
         <v>134</v>
@@ -6534,22 +6534,22 @@
         <v>308</v>
       </c>
       <c r="P29">
-        <v>2.09</v>
+        <v>5.42</v>
       </c>
       <c r="Q29">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="R29">
-        <v>3.24</v>
+        <v>1.56</v>
       </c>
       <c r="S29">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T29">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U29">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="V29">
         <v>0</v>
@@ -6558,10 +6558,10 @@
         <v>0</v>
       </c>
       <c r="X29">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Y29">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -6573,40 +6573,40 @@
         <v>0</v>
       </c>
       <c r="AC29">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD29">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AE29">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF29">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG29">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH29">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI29">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AJ29">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK29">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM29">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN29">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AO29">
         <v>0</v>
@@ -6651,13 +6651,13 @@
         <v>0</v>
       </c>
       <c r="BC29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD29">
         <v>0</v>
       </c>
       <c r="BE29">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BF29">
         <v>0</v>
@@ -6865,10 +6865,10 @@
         <v>72</v>
       </c>
       <c r="C31" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D31" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E31" t="s">
         <v>166</v>
@@ -6904,133 +6904,133 @@
         <v>308</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AH31">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI31">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL31">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AM31">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AN31">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AO31">
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AQ31">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AR31">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AS31">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="AT31">
-        <v>0</v>
+        <v>5.44</v>
       </c>
       <c r="AU31">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AV31">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AW31">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AX31">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AY31">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AZ31">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BA31">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="BB31">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC31">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD31">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE31">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BF31">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG31">
         <v>0</v>
@@ -7050,7 +7050,7 @@
         <v>72</v>
       </c>
       <c r="C32" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D32" t="s">
         <v>136</v>
@@ -7089,13 +7089,13 @@
         <v>308</v>
       </c>
       <c r="P32">
-        <v>5.42</v>
+        <v>0</v>
       </c>
       <c r="Q32">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R32">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -7235,10 +7235,10 @@
         <v>72</v>
       </c>
       <c r="C33" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D33" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E33" t="s">
         <v>168</v>
@@ -7274,79 +7274,79 @@
         <v>308</v>
       </c>
       <c r="P33">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q33">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R33">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S33">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="T33">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="U33">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="V33">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W33">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="X33">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Y33">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z33">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA33">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB33">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC33">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD33">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE33">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF33">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG33">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AH33">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AI33">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AJ33">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK33">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL33">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AM33">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN33">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AO33">
         <v>0</v>
@@ -7388,19 +7388,19 @@
         <v>0</v>
       </c>
       <c r="BB33">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC33">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BD33">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE33">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="BF33">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BG33">
         <v>0</v>
@@ -7420,7 +7420,7 @@
         <v>72</v>
       </c>
       <c r="C34" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D34" t="s">
         <v>136</v>
@@ -7459,22 +7459,22 @@
         <v>308</v>
       </c>
       <c r="P34">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q34">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R34">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S34">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T34">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U34">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="V34">
         <v>0</v>
@@ -7483,10 +7483,10 @@
         <v>0</v>
       </c>
       <c r="X34">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y34">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -7498,40 +7498,40 @@
         <v>0</v>
       </c>
       <c r="AC34">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AD34">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE34">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF34">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG34">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AH34">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI34">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ34">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK34">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL34">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AM34">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN34">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO34">
         <v>0</v>
@@ -7576,13 +7576,13 @@
         <v>0</v>
       </c>
       <c r="BC34">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="BD34">
         <v>0</v>
       </c>
       <c r="BE34">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BF34">
         <v>0</v>
@@ -7605,7 +7605,7 @@
         <v>72</v>
       </c>
       <c r="C35" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D35" t="s">
         <v>136</v>
@@ -7644,22 +7644,22 @@
         <v>308</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V35">
         <v>0</v>
@@ -7668,10 +7668,10 @@
         <v>0</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -7683,40 +7683,40 @@
         <v>0</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH35">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI35">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM35">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN35">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AO35">
         <v>0</v>
@@ -7761,13 +7761,13 @@
         <v>0</v>
       </c>
       <c r="BC35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD35">
         <v>0</v>
       </c>
       <c r="BE35">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BF35">
         <v>0</v>
@@ -7790,7 +7790,7 @@
         <v>72</v>
       </c>
       <c r="C36" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D36" t="s">
         <v>136</v>
@@ -7829,22 +7829,22 @@
         <v>308</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V36">
         <v>0</v>
@@ -7853,10 +7853,10 @@
         <v>0</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -7868,40 +7868,40 @@
         <v>0</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH36">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI36">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL36">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM36">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN36">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AO36">
         <v>0</v>
@@ -7946,13 +7946,13 @@
         <v>0</v>
       </c>
       <c r="BC36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD36">
         <v>0</v>
       </c>
       <c r="BE36">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BF36">
         <v>0</v>
@@ -7975,10 +7975,10 @@
         <v>72</v>
       </c>
       <c r="C37" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D37" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E37" t="s">
         <v>172</v>
@@ -8014,22 +8014,22 @@
         <v>308</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="V37">
         <v>0</v>
@@ -8038,10 +8038,10 @@
         <v>0</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -8053,40 +8053,40 @@
         <v>0</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH37">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI37">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL37">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AM37">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN37">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AO37">
         <v>0</v>
@@ -8131,13 +8131,13 @@
         <v>0</v>
       </c>
       <c r="BC37">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BD37">
         <v>0</v>
       </c>
       <c r="BE37">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF37">
         <v>0</v>
@@ -8160,10 +8160,10 @@
         <v>72</v>
       </c>
       <c r="C38" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D38" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E38" t="s">
         <v>173</v>
@@ -8199,22 +8199,22 @@
         <v>308</v>
       </c>
       <c r="P38">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R38">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S38">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T38">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U38">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="V38">
         <v>0</v>
@@ -8223,10 +8223,10 @@
         <v>0</v>
       </c>
       <c r="X38">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Y38">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -8238,40 +8238,40 @@
         <v>0</v>
       </c>
       <c r="AC38">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD38">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AE38">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AF38">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AG38">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH38">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI38">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ38">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK38">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="AL38">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AM38">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN38">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AO38">
         <v>0</v>
@@ -8316,13 +8316,13 @@
         <v>0</v>
       </c>
       <c r="BC38">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="BD38">
         <v>0</v>
       </c>
       <c r="BE38">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF38">
         <v>0</v>
@@ -8345,7 +8345,7 @@
         <v>72</v>
       </c>
       <c r="C39" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D39" t="s">
         <v>134</v>
@@ -8384,13 +8384,13 @@
         <v>308</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S39">
         <v>0</v>
@@ -8429,10 +8429,10 @@
         <v>0</v>
       </c>
       <c r="AE39">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF39">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG39">
         <v>0</v>
@@ -8447,10 +8447,10 @@
         <v>0</v>
       </c>
       <c r="AK39">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL39">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AM39">
         <v>0</v>
@@ -8530,7 +8530,7 @@
         <v>72</v>
       </c>
       <c r="C40" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D40" t="s">
         <v>136</v>
@@ -8569,22 +8569,22 @@
         <v>308</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V40">
         <v>0</v>
@@ -8593,10 +8593,10 @@
         <v>0</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -8608,40 +8608,40 @@
         <v>0</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AH40">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI40">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL40">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AM40">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN40">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO40">
         <v>0</v>
@@ -8686,13 +8686,13 @@
         <v>0</v>
       </c>
       <c r="BC40">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BD40">
         <v>0</v>
       </c>
       <c r="BE40">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF40">
         <v>0</v>
@@ -8715,10 +8715,10 @@
         <v>72</v>
       </c>
       <c r="C41" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D41" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E41" t="s">
         <v>176</v>
@@ -8754,133 +8754,133 @@
         <v>308</v>
       </c>
       <c r="P41">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q41">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R41">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="S41">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T41">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U41">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="V41">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W41">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="X41">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y41">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z41">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AA41">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB41">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC41">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AD41">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE41">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF41">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG41">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AH41">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI41">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AJ41">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK41">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL41">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AM41">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AN41">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AO41">
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AQ41">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AR41">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AS41">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="AT41">
-        <v>5.44</v>
+        <v>0</v>
       </c>
       <c r="AU41">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AV41">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AW41">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AX41">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AY41">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AZ41">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BA41">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="BB41">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC41">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD41">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE41">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BF41">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG41">
         <v>0</v>
@@ -8900,10 +8900,10 @@
         <v>72</v>
       </c>
       <c r="C42" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D42" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E42" t="s">
         <v>177</v>
@@ -8939,133 +8939,133 @@
         <v>308</v>
       </c>
       <c r="P42">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="Q42">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R42">
+        <v>2.75</v>
+      </c>
+      <c r="S42">
+        <v>2.82</v>
+      </c>
+      <c r="T42">
+        <v>2.19</v>
+      </c>
+      <c r="U42">
+        <v>3.28</v>
+      </c>
+      <c r="V42">
+        <v>1.28</v>
+      </c>
+      <c r="W42">
+        <v>3.15</v>
+      </c>
+      <c r="X42">
+        <v>2.31</v>
+      </c>
+      <c r="Y42">
+        <v>1.51</v>
+      </c>
+      <c r="Z42">
+        <v>5.3</v>
+      </c>
+      <c r="AA42">
+        <v>1.11</v>
+      </c>
+      <c r="AB42">
+        <v>1.02</v>
+      </c>
+      <c r="AC42">
+        <v>1.16</v>
+      </c>
+      <c r="AD42">
+        <v>4</v>
+      </c>
+      <c r="AE42">
+        <v>1.61</v>
+      </c>
+      <c r="AF42">
+        <v>2.08</v>
+      </c>
+      <c r="AG42">
         <v>2.43</v>
       </c>
-      <c r="S42">
-        <v>3.25</v>
-      </c>
-      <c r="T42">
-        <v>2.18</v>
-      </c>
-      <c r="U42">
-        <v>2.9</v>
-      </c>
-      <c r="V42">
-        <v>0</v>
-      </c>
-      <c r="W42">
-        <v>0</v>
-      </c>
-      <c r="X42">
-        <v>2.55</v>
-      </c>
-      <c r="Y42">
-        <v>1.38</v>
-      </c>
-      <c r="Z42">
-        <v>0</v>
-      </c>
-      <c r="AA42">
-        <v>0</v>
-      </c>
-      <c r="AB42">
-        <v>0</v>
-      </c>
-      <c r="AC42">
-        <v>1.25</v>
-      </c>
-      <c r="AD42">
-        <v>3.35</v>
-      </c>
-      <c r="AE42">
-        <v>1.82</v>
-      </c>
-      <c r="AF42">
-        <v>1.82</v>
-      </c>
-      <c r="AG42">
-        <v>3</v>
-      </c>
       <c r="AH42">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AI42">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="AJ42">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AK42">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AL42">
-        <v>2.05</v>
+        <v>2.32</v>
       </c>
       <c r="AM42">
+        <v>1.36</v>
+      </c>
+      <c r="AN42">
+        <v>1.49</v>
+      </c>
+      <c r="AO42">
+        <v>0</v>
+      </c>
+      <c r="AP42">
+        <v>0</v>
+      </c>
+      <c r="AQ42">
+        <v>0</v>
+      </c>
+      <c r="AR42">
+        <v>0</v>
+      </c>
+      <c r="AS42">
+        <v>0</v>
+      </c>
+      <c r="AT42">
+        <v>0</v>
+      </c>
+      <c r="AU42">
+        <v>0</v>
+      </c>
+      <c r="AV42">
+        <v>0</v>
+      </c>
+      <c r="AW42">
+        <v>0</v>
+      </c>
+      <c r="AX42">
+        <v>0</v>
+      </c>
+      <c r="AY42">
+        <v>0</v>
+      </c>
+      <c r="AZ42">
+        <v>0</v>
+      </c>
+      <c r="BA42">
+        <v>0</v>
+      </c>
+      <c r="BB42">
+        <v>1.16</v>
+      </c>
+      <c r="BC42">
+        <v>1.84</v>
+      </c>
+      <c r="BD42">
+        <v>4.6</v>
+      </c>
+      <c r="BE42">
+        <v>1.86</v>
+      </c>
+      <c r="BF42">
         <v>1.24</v>
-      </c>
-      <c r="AN42">
-        <v>1.32</v>
-      </c>
-      <c r="AO42">
-        <v>0</v>
-      </c>
-      <c r="AP42">
-        <v>0</v>
-      </c>
-      <c r="AQ42">
-        <v>0</v>
-      </c>
-      <c r="AR42">
-        <v>0</v>
-      </c>
-      <c r="AS42">
-        <v>0</v>
-      </c>
-      <c r="AT42">
-        <v>0</v>
-      </c>
-      <c r="AU42">
-        <v>0</v>
-      </c>
-      <c r="AV42">
-        <v>0</v>
-      </c>
-      <c r="AW42">
-        <v>0</v>
-      </c>
-      <c r="AX42">
-        <v>0</v>
-      </c>
-      <c r="AY42">
-        <v>0</v>
-      </c>
-      <c r="AZ42">
-        <v>0</v>
-      </c>
-      <c r="BA42">
-        <v>0</v>
-      </c>
-      <c r="BB42">
-        <v>0</v>
-      </c>
-      <c r="BC42">
-        <v>2</v>
-      </c>
-      <c r="BD42">
-        <v>0</v>
-      </c>
-      <c r="BE42">
-        <v>1.64</v>
-      </c>
-      <c r="BF42">
-        <v>0</v>
       </c>
       <c r="BG42">
         <v>0</v>
@@ -9085,7 +9085,7 @@
         <v>72</v>
       </c>
       <c r="C43" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D43" t="s">
         <v>134</v>
@@ -9124,13 +9124,13 @@
         <v>308</v>
       </c>
       <c r="P43">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q43">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R43">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S43">
         <v>0</v>
@@ -9825,7 +9825,7 @@
         <v>75</v>
       </c>
       <c r="C47" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="D47" t="s">
         <v>134</v>
@@ -9864,79 +9864,79 @@
         <v>308</v>
       </c>
       <c r="P47">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="Q47">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="R47">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AE47">
-        <v>1.75</v>
+        <v>2.48</v>
       </c>
       <c r="AF47">
-        <v>1.93</v>
+        <v>1.55</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AH47">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI47">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AL47">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM47">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AN47">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO47">
         <v>0</v>
@@ -9978,19 +9978,19 @@
         <v>0</v>
       </c>
       <c r="BB47">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BC47">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="BD47">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BE47">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF47">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG47">
         <v>0</v>
@@ -10010,7 +10010,7 @@
         <v>75</v>
       </c>
       <c r="C48" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D48" t="s">
         <v>134</v>
@@ -10195,7 +10195,7 @@
         <v>75</v>
       </c>
       <c r="C49" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="D49" t="s">
         <v>134</v>
@@ -10234,79 +10234,79 @@
         <v>308</v>
       </c>
       <c r="P49">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="Q49">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="R49">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S49">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T49">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="U49">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="V49">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="W49">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="X49">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="Y49">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z49">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB49">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC49">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AD49">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AE49">
-        <v>2.48</v>
+        <v>1.75</v>
       </c>
       <c r="AF49">
-        <v>1.55</v>
+        <v>1.93</v>
       </c>
       <c r="AG49">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AH49">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI49">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AJ49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK49">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AL49">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM49">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AN49">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO49">
         <v>0</v>
@@ -10348,19 +10348,19 @@
         <v>0</v>
       </c>
       <c r="BB49">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BC49">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="BD49">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="BE49">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BF49">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="BG49">
         <v>0</v>
@@ -10565,7 +10565,7 @@
         <v>77</v>
       </c>
       <c r="C51" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="D51" t="s">
         <v>134</v>
@@ -10604,133 +10604,133 @@
         <v>308</v>
       </c>
       <c r="P51">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="Q51">
-        <v>3.8</v>
+        <v>2.76</v>
       </c>
       <c r="R51">
-        <v>3.23</v>
+        <v>3.48</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AH51">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI51">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AL51">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AM51">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AN51">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AO51">
         <v>0</v>
       </c>
       <c r="AP51">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AQ51">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AR51">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS51">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AT51">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AU51">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AV51">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AW51">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AX51">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AY51">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ51">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BA51">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BB51">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BC51">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="BD51">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BE51">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BF51">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BG51">
         <v>0</v>
@@ -10750,7 +10750,7 @@
         <v>77</v>
       </c>
       <c r="C52" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="D52" t="s">
         <v>134</v>
@@ -10789,133 +10789,133 @@
         <v>308</v>
       </c>
       <c r="P52">
-        <v>2.04</v>
+        <v>1.73</v>
       </c>
       <c r="Q52">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="R52">
-        <v>3.43</v>
+        <v>4.59</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AH52">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI52">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL52">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM52">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN52">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AO52">
         <v>0</v>
       </c>
       <c r="AP52">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ52">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AR52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS52">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AT52">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AU52">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AV52">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AW52">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AX52">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AY52">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ52">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BA52">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="BB52">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC52">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BD52">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="BE52">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BF52">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG52">
         <v>0</v>
@@ -10935,7 +10935,7 @@
         <v>77</v>
       </c>
       <c r="C53" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D53" t="s">
         <v>136</v>
@@ -11120,7 +11120,7 @@
         <v>77</v>
       </c>
       <c r="C54" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D54" t="s">
         <v>134</v>
@@ -11159,133 +11159,133 @@
         <v>308</v>
       </c>
       <c r="P54">
-        <v>2.17</v>
+        <v>2.04</v>
       </c>
       <c r="Q54">
-        <v>3.54</v>
+        <v>3.42</v>
       </c>
       <c r="R54">
-        <v>3.03</v>
+        <v>3.43</v>
       </c>
       <c r="S54">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T54">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="U54">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="V54">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W54">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="X54">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y54">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z54">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="AA54">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB54">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC54">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD54">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="AE54">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF54">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AG54">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AH54">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AI54">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AJ54">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK54">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL54">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AM54">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN54">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AO54">
         <v>0</v>
       </c>
       <c r="AP54">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ54">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AR54">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AS54">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AT54">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AU54">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AV54">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AW54">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AX54">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AY54">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ54">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="BA54">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="BB54">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC54">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="BD54">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="BE54">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="BF54">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG54">
         <v>0</v>
@@ -11305,7 +11305,7 @@
         <v>77</v>
       </c>
       <c r="C55" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="D55" t="s">
         <v>134</v>
@@ -11344,133 +11344,133 @@
         <v>308</v>
       </c>
       <c r="P55">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="Q55">
-        <v>2.76</v>
+        <v>3.8</v>
       </c>
       <c r="R55">
-        <v>3.48</v>
+        <v>3.23</v>
       </c>
       <c r="S55">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T55">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="U55">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="V55">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="W55">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="X55">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Y55">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z55">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA55">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB55">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC55">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD55">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE55">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AF55">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AG55">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AH55">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI55">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="AJ55">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK55">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AL55">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AM55">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AN55">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AO55">
         <v>0</v>
       </c>
       <c r="AP55">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AQ55">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AR55">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AS55">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AT55">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AU55">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AV55">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AW55">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AX55">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AY55">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ55">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BA55">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BB55">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BC55">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="BD55">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="BE55">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="BF55">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BG55">
         <v>0</v>
@@ -11490,10 +11490,10 @@
         <v>77</v>
       </c>
       <c r="C56" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D56" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E56" t="s">
         <v>191</v>
@@ -11529,133 +11529,133 @@
         <v>308</v>
       </c>
       <c r="P56">
-        <v>1.79</v>
+        <v>1.58</v>
       </c>
       <c r="Q56">
+        <v>4.33</v>
+      </c>
+      <c r="R56">
+        <v>4.92</v>
+      </c>
+      <c r="S56">
+        <v>1.91</v>
+      </c>
+      <c r="T56">
+        <v>2.4</v>
+      </c>
+      <c r="U56">
+        <v>5</v>
+      </c>
+      <c r="V56">
+        <v>1.24</v>
+      </c>
+      <c r="W56">
         <v>3.7</v>
       </c>
-      <c r="R56">
-        <v>4.22</v>
-      </c>
-      <c r="S56">
-        <v>0</v>
-      </c>
-      <c r="T56">
-        <v>0</v>
-      </c>
-      <c r="U56">
-        <v>0</v>
-      </c>
-      <c r="V56">
-        <v>0</v>
-      </c>
-      <c r="W56">
-        <v>0</v>
-      </c>
       <c r="X56">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y56">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z56">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AE56">
+        <v>1.48</v>
+      </c>
+      <c r="AF56">
+        <v>2.4</v>
+      </c>
+      <c r="AG56">
+        <v>2.35</v>
+      </c>
+      <c r="AH56">
+        <v>1.59</v>
+      </c>
+      <c r="AI56">
+        <v>3.88</v>
+      </c>
+      <c r="AJ56">
+        <v>1.18</v>
+      </c>
+      <c r="AK56">
+        <v>1.5</v>
+      </c>
+      <c r="AL56">
+        <v>2.2</v>
+      </c>
+      <c r="AM56">
+        <v>1.17</v>
+      </c>
+      <c r="AN56">
+        <v>2.25</v>
+      </c>
+      <c r="AO56">
+        <v>0</v>
+      </c>
+      <c r="AP56">
+        <v>1.17</v>
+      </c>
+      <c r="AQ56">
+        <v>1.34</v>
+      </c>
+      <c r="AR56">
         <v>1.85</v>
       </c>
-      <c r="AF56">
-        <v>1.92</v>
-      </c>
-      <c r="AG56">
-        <v>0</v>
-      </c>
-      <c r="AH56">
-        <v>0</v>
-      </c>
-      <c r="AI56">
-        <v>0</v>
-      </c>
-      <c r="AJ56">
-        <v>0</v>
-      </c>
-      <c r="AK56">
-        <v>0</v>
-      </c>
-      <c r="AL56">
-        <v>0</v>
-      </c>
-      <c r="AM56">
-        <v>0</v>
-      </c>
-      <c r="AN56">
-        <v>0</v>
-      </c>
-      <c r="AO56">
-        <v>0</v>
-      </c>
-      <c r="AP56">
-        <v>0</v>
-      </c>
-      <c r="AQ56">
-        <v>0</v>
-      </c>
-      <c r="AR56">
-        <v>0</v>
-      </c>
       <c r="AS56">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AT56">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AU56">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV56">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AW56">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AX56">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AY56">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ56">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BA56">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BB56">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC56">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BD56">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BE56">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BF56">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG56">
         <v>0</v>
@@ -11675,7 +11675,7 @@
         <v>77</v>
       </c>
       <c r="C57" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D57" t="s">
         <v>134</v>
@@ -11714,133 +11714,133 @@
         <v>308</v>
       </c>
       <c r="P57">
-        <v>1.8</v>
+        <v>2.61</v>
       </c>
       <c r="Q57">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="R57">
-        <v>4.24</v>
+        <v>2.52</v>
       </c>
       <c r="S57">
-        <v>2.38</v>
+        <v>3.7</v>
       </c>
       <c r="T57">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="U57">
-        <v>5.08</v>
+        <v>3.01</v>
       </c>
       <c r="V57">
+        <v>1.44</v>
+      </c>
+      <c r="W57">
+        <v>2.62</v>
+      </c>
+      <c r="X57">
+        <v>3.16</v>
+      </c>
+      <c r="Y57">
+        <v>1.3</v>
+      </c>
+      <c r="Z57">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AA57">
+        <v>1.01</v>
+      </c>
+      <c r="AB57">
+        <v>1.01</v>
+      </c>
+      <c r="AC57">
         <v>1.39</v>
       </c>
-      <c r="W57">
-        <v>2.69</v>
-      </c>
-      <c r="X57">
-        <v>2.9</v>
-      </c>
-      <c r="Y57">
-        <v>1.35</v>
-      </c>
-      <c r="Z57">
-        <v>7.5</v>
-      </c>
-      <c r="AA57">
-        <v>1.03</v>
-      </c>
-      <c r="AB57">
-        <v>1.06</v>
-      </c>
-      <c r="AC57">
-        <v>1.28</v>
-      </c>
       <c r="AD57">
-        <v>3.08</v>
+        <v>2.81</v>
       </c>
       <c r="AE57">
-        <v>1.88</v>
+        <v>2.19</v>
       </c>
       <c r="AF57">
-        <v>1.88</v>
+        <v>1.64</v>
       </c>
       <c r="AG57">
-        <v>3.51</v>
+        <v>4.02</v>
       </c>
       <c r="AH57">
+        <v>1.17</v>
+      </c>
+      <c r="AI57">
+        <v>8.5</v>
+      </c>
+      <c r="AJ57">
+        <v>1.04</v>
+      </c>
+      <c r="AK57">
+        <v>1.87</v>
+      </c>
+      <c r="AL57">
+        <v>1.83</v>
+      </c>
+      <c r="AM57">
+        <v>1.3</v>
+      </c>
+      <c r="AN57">
+        <v>1.37</v>
+      </c>
+      <c r="AO57">
+        <v>0</v>
+      </c>
+      <c r="AP57">
+        <v>1.27</v>
+      </c>
+      <c r="AQ57">
+        <v>1.54</v>
+      </c>
+      <c r="AR57">
+        <v>1.92</v>
+      </c>
+      <c r="AS57">
+        <v>2.46</v>
+      </c>
+      <c r="AT57">
+        <v>3.35</v>
+      </c>
+      <c r="AU57">
+        <v>3.14</v>
+      </c>
+      <c r="AV57">
+        <v>2.27</v>
+      </c>
+      <c r="AW57">
+        <v>1.79</v>
+      </c>
+      <c r="AX57">
+        <v>1.46</v>
+      </c>
+      <c r="AY57">
         <v>1.24</v>
       </c>
-      <c r="AI57">
-        <v>6.65</v>
-      </c>
-      <c r="AJ57">
-        <v>1.11</v>
-      </c>
-      <c r="AK57">
-        <v>1.86</v>
-      </c>
-      <c r="AL57">
-        <v>1.84</v>
-      </c>
-      <c r="AM57">
+      <c r="AZ57">
+        <v>2.92</v>
+      </c>
+      <c r="BA57">
+        <v>1.67</v>
+      </c>
+      <c r="BB57">
         <v>1.27</v>
       </c>
-      <c r="AN57">
-        <v>1.94</v>
-      </c>
-      <c r="AO57">
-        <v>0</v>
-      </c>
-      <c r="AP57">
-        <v>1.13</v>
-      </c>
-      <c r="AQ57">
-        <v>1.31</v>
-      </c>
-      <c r="AR57">
-        <v>1.59</v>
-      </c>
-      <c r="AS57">
-        <v>1.95</v>
-      </c>
-      <c r="AT57">
-        <v>2.48</v>
-      </c>
-      <c r="AU57">
-        <v>4.5</v>
-      </c>
-      <c r="AV57">
-        <v>2.95</v>
-      </c>
-      <c r="AW57">
-        <v>2.2</v>
-      </c>
-      <c r="AX57">
-        <v>1.76</v>
-      </c>
-      <c r="AY57">
-        <v>1.45</v>
-      </c>
-      <c r="AZ57">
-        <v>1.49</v>
-      </c>
-      <c r="BA57">
-        <v>3.04</v>
-      </c>
-      <c r="BB57">
-        <v>1.22</v>
-      </c>
       <c r="BC57">
-        <v>1.98</v>
+        <v>2.36</v>
       </c>
       <c r="BD57">
-        <v>3.58</v>
+        <v>3.35</v>
       </c>
       <c r="BE57">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="BF57">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="BG57">
         <v>0</v>
@@ -11863,7 +11863,7 @@
         <v>120</v>
       </c>
       <c r="D58" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E58" t="s">
         <v>193</v>
@@ -11899,133 +11899,133 @@
         <v>308</v>
       </c>
       <c r="P58">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="Q58">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="R58">
-        <v>2.54</v>
+        <v>4.24</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T58">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U58">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="V58">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W58">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="X58">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y58">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z58">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA58">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB58">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC58">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE58">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AF58">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AG58">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="AH58">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI58">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="AJ58">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK58">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL58">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AM58">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN58">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AO58">
         <v>0</v>
       </c>
       <c r="AP58">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AQ58">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AR58">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AS58">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AT58">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AU58">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AV58">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW58">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AX58">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AY58">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ58">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BA58">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="BB58">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC58">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD58">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE58">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF58">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG58">
         <v>0</v>
@@ -12048,7 +12048,7 @@
         <v>121</v>
       </c>
       <c r="D59" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E59" t="s">
         <v>194</v>
@@ -12084,133 +12084,133 @@
         <v>308</v>
       </c>
       <c r="P59">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="Q59">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="R59">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="S59">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="T59">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="U59">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="V59">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W59">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="X59">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Y59">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z59">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA59">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB59">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC59">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AD59">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AE59">
-        <v>2.19</v>
+        <v>1.9</v>
       </c>
       <c r="AF59">
-        <v>1.64</v>
+        <v>1.9</v>
       </c>
       <c r="AG59">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="AH59">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AI59">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AJ59">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK59">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AL59">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM59">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN59">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AO59">
         <v>0</v>
       </c>
       <c r="AP59">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ59">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AR59">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AS59">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AT59">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AU59">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AV59">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AW59">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AX59">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AY59">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AZ59">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="BA59">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BB59">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BC59">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="BD59">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BE59">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="BF59">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG59">
         <v>0</v>
@@ -12230,10 +12230,10 @@
         <v>77</v>
       </c>
       <c r="C60" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="D60" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E60" t="s">
         <v>195</v>
@@ -12269,22 +12269,22 @@
         <v>308</v>
       </c>
       <c r="P60">
-        <v>7.95</v>
+        <v>1.79</v>
       </c>
       <c r="Q60">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="R60">
-        <v>1.33</v>
+        <v>4.22</v>
       </c>
       <c r="S60">
-        <v>7.13</v>
+        <v>0</v>
       </c>
       <c r="T60">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U60">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="V60">
         <v>0</v>
@@ -12293,55 +12293,55 @@
         <v>0</v>
       </c>
       <c r="X60">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y60">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z60">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AA60">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AB60">
         <v>0</v>
       </c>
       <c r="AC60">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD60">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AE60">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="AF60">
-        <v>2.18</v>
+        <v>1.92</v>
       </c>
       <c r="AG60">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH60">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI60">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AJ60">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK60">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL60">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AM60">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AN60">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AO60">
         <v>0</v>
@@ -12386,13 +12386,13 @@
         <v>0</v>
       </c>
       <c r="BC60">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BD60">
         <v>0</v>
       </c>
       <c r="BE60">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF60">
         <v>0</v>
@@ -12415,7 +12415,7 @@
         <v>77</v>
       </c>
       <c r="C61" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="D61" t="s">
         <v>134</v>
@@ -12454,133 +12454,133 @@
         <v>308</v>
       </c>
       <c r="P61">
-        <v>1.58</v>
+        <v>7.95</v>
       </c>
       <c r="Q61">
-        <v>4.33</v>
+        <v>4.7</v>
       </c>
       <c r="R61">
-        <v>4.92</v>
+        <v>1.33</v>
       </c>
       <c r="S61">
-        <v>1.91</v>
+        <v>7.13</v>
       </c>
       <c r="T61">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="U61">
-        <v>5</v>
+        <v>1.74</v>
       </c>
       <c r="V61">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W61">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="X61">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Y61">
         <v>1.6</v>
       </c>
       <c r="Z61">
-        <v>5</v>
+        <v>4.55</v>
       </c>
       <c r="AA61">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AB61">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC61">
+        <v>1.16</v>
+      </c>
+      <c r="AD61">
+        <v>4.2</v>
+      </c>
+      <c r="AE61">
+        <v>1.52</v>
+      </c>
+      <c r="AF61">
+        <v>2.18</v>
+      </c>
+      <c r="AG61">
+        <v>2.38</v>
+      </c>
+      <c r="AH61">
+        <v>1.47</v>
+      </c>
+      <c r="AI61">
+        <v>3.8</v>
+      </c>
+      <c r="AJ61">
+        <v>1.21</v>
+      </c>
+      <c r="AK61">
+        <v>1.9</v>
+      </c>
+      <c r="AL61">
+        <v>1.9</v>
+      </c>
+      <c r="AM61">
         <v>1.13</v>
       </c>
-      <c r="AD61">
-        <v>4.95</v>
-      </c>
-      <c r="AE61">
-        <v>1.48</v>
-      </c>
-      <c r="AF61">
-        <v>2.4</v>
-      </c>
-      <c r="AG61">
-        <v>2.35</v>
-      </c>
-      <c r="AH61">
-        <v>1.59</v>
-      </c>
-      <c r="AI61">
-        <v>3.88</v>
-      </c>
-      <c r="AJ61">
-        <v>1.18</v>
-      </c>
-      <c r="AK61">
-        <v>1.5</v>
-      </c>
-      <c r="AL61">
-        <v>2.2</v>
-      </c>
-      <c r="AM61">
-        <v>1.17</v>
-      </c>
       <c r="AN61">
-        <v>2.25</v>
+        <v>1.05</v>
       </c>
       <c r="AO61">
         <v>0</v>
       </c>
       <c r="AP61">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ61">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AR61">
+        <v>0</v>
+      </c>
+      <c r="AS61">
+        <v>0</v>
+      </c>
+      <c r="AT61">
+        <v>0</v>
+      </c>
+      <c r="AU61">
+        <v>0</v>
+      </c>
+      <c r="AV61">
+        <v>0</v>
+      </c>
+      <c r="AW61">
+        <v>0</v>
+      </c>
+      <c r="AX61">
+        <v>0</v>
+      </c>
+      <c r="AY61">
+        <v>0</v>
+      </c>
+      <c r="AZ61">
+        <v>0</v>
+      </c>
+      <c r="BA61">
+        <v>0</v>
+      </c>
+      <c r="BB61">
+        <v>0</v>
+      </c>
+      <c r="BC61">
+        <v>1.75</v>
+      </c>
+      <c r="BD61">
+        <v>0</v>
+      </c>
+      <c r="BE61">
         <v>1.85</v>
       </c>
-      <c r="AS61">
-        <v>1.8</v>
-      </c>
-      <c r="AT61">
-        <v>2.67</v>
-      </c>
-      <c r="AU61">
-        <v>4</v>
-      </c>
-      <c r="AV61">
-        <v>2.78</v>
-      </c>
-      <c r="AW61">
-        <v>2.08</v>
-      </c>
-      <c r="AX61">
-        <v>1.67</v>
-      </c>
-      <c r="AY61">
-        <v>1.38</v>
-      </c>
-      <c r="AZ61">
-        <v>1.36</v>
-      </c>
-      <c r="BA61">
-        <v>3.8</v>
-      </c>
-      <c r="BB61">
-        <v>1.11</v>
-      </c>
-      <c r="BC61">
-        <v>1.74</v>
-      </c>
-      <c r="BD61">
-        <v>5.2</v>
-      </c>
-      <c r="BE61">
-        <v>2.02</v>
-      </c>
       <c r="BF61">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG61">
         <v>0</v>
@@ -12600,7 +12600,7 @@
         <v>77</v>
       </c>
       <c r="C62" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="D62" t="s">
         <v>134</v>
@@ -12639,133 +12639,133 @@
         <v>308</v>
       </c>
       <c r="P62">
-        <v>1.73</v>
+        <v>2.17</v>
       </c>
       <c r="Q62">
-        <v>3.3</v>
+        <v>3.54</v>
       </c>
       <c r="R62">
-        <v>4.59</v>
+        <v>3.03</v>
       </c>
       <c r="S62">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="T62">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="U62">
-        <v>5.6</v>
+        <v>3.58</v>
       </c>
       <c r="V62">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="W62">
-        <v>2.5</v>
+        <v>3.16</v>
       </c>
       <c r="X62">
-        <v>3.08</v>
+        <v>2.3</v>
       </c>
       <c r="Y62">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="Z62">
-        <v>7.9</v>
+        <v>5.55</v>
       </c>
       <c r="AA62">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AB62">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC62">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AD62">
-        <v>2.83</v>
+        <v>4.41</v>
       </c>
       <c r="AE62">
-        <v>2.15</v>
+        <v>1.68</v>
       </c>
       <c r="AF62">
-        <v>1.65</v>
+        <v>2.16</v>
       </c>
       <c r="AG62">
-        <v>3.85</v>
+        <v>2.63</v>
       </c>
       <c r="AH62">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="AI62">
-        <v>7</v>
+        <v>4.55</v>
       </c>
       <c r="AJ62">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AK62">
-        <v>1.97</v>
+        <v>1.55</v>
       </c>
       <c r="AL62">
-        <v>1.73</v>
+        <v>2.35</v>
       </c>
       <c r="AM62">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AN62">
-        <v>1.94</v>
+        <v>1.61</v>
       </c>
       <c r="AO62">
         <v>0</v>
       </c>
       <c r="AP62">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AQ62">
-        <v>1.62</v>
+        <v>1.34</v>
       </c>
       <c r="AR62">
-        <v>2</v>
+        <v>1.58</v>
       </c>
       <c r="AS62">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="AT62">
-        <v>3.3</v>
+        <v>2.45</v>
       </c>
       <c r="AU62">
+        <v>3.95</v>
+      </c>
+      <c r="AV62">
         <v>2.85</v>
       </c>
-      <c r="AV62">
+      <c r="AW62">
         <v>2.14</v>
       </c>
-      <c r="AW62">
-        <v>1.71</v>
-      </c>
       <c r="AX62">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AY62">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="AZ62">
-        <v>1.48</v>
+        <v>1.76</v>
       </c>
       <c r="BA62">
-        <v>2.85</v>
+        <v>2.33</v>
       </c>
       <c r="BB62">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="BC62">
-        <v>2.28</v>
+        <v>1.87</v>
       </c>
       <c r="BD62">
-        <v>3.34</v>
+        <v>4.45</v>
       </c>
       <c r="BE62">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="BF62">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="BG62">
         <v>0</v>
@@ -13531,7 +13531,7 @@
         <v>134</v>
       </c>
       <c r="E67" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="F67" t="s">
         <v>287</v>
@@ -13564,133 +13564,133 @@
         <v>308</v>
       </c>
       <c r="P67">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Q67">
-        <v>5.09</v>
+        <v>0</v>
       </c>
       <c r="R67">
-        <v>6.37</v>
+        <v>0</v>
       </c>
       <c r="S67">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="T67">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U67">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V67">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W67">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="X67">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Y67">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z67">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC67">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD67">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="AE67">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF67">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AG67">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH67">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI67">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AJ67">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK67">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL67">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AM67">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN67">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AO67">
         <v>0</v>
       </c>
       <c r="AP67">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AQ67">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR67">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS67">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AT67">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AU67">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AV67">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AW67">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AX67">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY67">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AZ67">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BA67">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BB67">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC67">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BD67">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE67">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF67">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BG67">
         <v>0</v>
@@ -13710,13 +13710,13 @@
         <v>80</v>
       </c>
       <c r="C68" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="D68" t="s">
         <v>134</v>
       </c>
       <c r="E68" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="F68" t="s">
         <v>288</v>
@@ -13749,13 +13749,13 @@
         <v>308</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>5.09</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>6.37</v>
       </c>
       <c r="S68">
         <v>0</v>
@@ -13895,7 +13895,7 @@
         <v>80</v>
       </c>
       <c r="C69" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="D69" t="s">
         <v>134</v>
@@ -14080,7 +14080,7 @@
         <v>80</v>
       </c>
       <c r="C70" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D70" t="s">
         <v>134</v>
@@ -14128,124 +14128,124 @@
         <v>0</v>
       </c>
       <c r="S70">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="T70">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="U70">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="V70">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="W70">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="X70">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Y70">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z70">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AA70">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB70">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC70">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD70">
-        <v>4.66</v>
+        <v>0</v>
       </c>
       <c r="AE70">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF70">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AG70">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AH70">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI70">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AJ70">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK70">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL70">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AM70">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN70">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AO70">
         <v>0</v>
       </c>
       <c r="AP70">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AQ70">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR70">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AS70">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AT70">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AU70">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AV70">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AW70">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AX70">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AY70">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AZ70">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BA70">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BB70">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC70">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BD70">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BE70">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BF70">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BG70">
         <v>0</v>
@@ -14265,7 +14265,7 @@
         <v>81</v>
       </c>
       <c r="C71" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="D71" t="s">
         <v>134</v>
@@ -14304,79 +14304,79 @@
         <v>308</v>
       </c>
       <c r="P71">
-        <v>1.35</v>
+        <v>1.99</v>
       </c>
       <c r="Q71">
-        <v>5.41</v>
+        <v>3.6</v>
       </c>
       <c r="R71">
-        <v>8.5</v>
+        <v>3.58</v>
       </c>
       <c r="S71">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="T71">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="U71">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="V71">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="W71">
-        <v>3.66</v>
+        <v>3.04</v>
       </c>
       <c r="X71">
-        <v>2.11</v>
+        <v>2.53</v>
       </c>
       <c r="Y71">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="Z71">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AA71">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="AB71">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AC71">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AD71">
-        <v>5.25</v>
+        <v>3.8</v>
       </c>
       <c r="AE71">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AF71">
-        <v>2.58</v>
+        <v>2</v>
       </c>
       <c r="AG71">
-        <v>2.21</v>
+        <v>2.95</v>
       </c>
       <c r="AH71">
-        <v>1.66</v>
+        <v>1.36</v>
       </c>
       <c r="AI71">
-        <v>3.7</v>
+        <v>5.05</v>
       </c>
       <c r="AJ71">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AK71">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL71">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AM71">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AN71">
-        <v>2.72</v>
+        <v>1.77</v>
       </c>
       <c r="AO71">
         <v>0</v>
@@ -14385,52 +14385,52 @@
         <v>1.2</v>
       </c>
       <c r="AQ71">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AR71">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AS71">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="AT71">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="AU71">
-        <v>3.85</v>
+        <v>3.72</v>
       </c>
       <c r="AV71">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="AW71">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AX71">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AY71">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="AZ71">
-        <v>1.28</v>
+        <v>2.03</v>
       </c>
       <c r="BA71">
-        <v>4.1</v>
+        <v>2.19</v>
       </c>
       <c r="BB71">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="BC71">
-        <v>1.66</v>
+        <v>1.97</v>
       </c>
       <c r="BD71">
-        <v>5.3</v>
+        <v>4.15</v>
       </c>
       <c r="BE71">
-        <v>2.14</v>
+        <v>1.78</v>
       </c>
       <c r="BF71">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="BG71">
         <v>0</v>
@@ -14450,7 +14450,7 @@
         <v>81</v>
       </c>
       <c r="C72" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="D72" t="s">
         <v>134</v>
@@ -14489,79 +14489,79 @@
         <v>308</v>
       </c>
       <c r="P72">
-        <v>1.99</v>
+        <v>1.35</v>
       </c>
       <c r="Q72">
-        <v>3.6</v>
+        <v>5.41</v>
       </c>
       <c r="R72">
-        <v>3.58</v>
+        <v>8.5</v>
       </c>
       <c r="S72">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="T72">
+        <v>2.5</v>
+      </c>
+      <c r="U72">
+        <v>5.5</v>
+      </c>
+      <c r="V72">
+        <v>1.22</v>
+      </c>
+      <c r="W72">
+        <v>3.66</v>
+      </c>
+      <c r="X72">
+        <v>2.11</v>
+      </c>
+      <c r="Y72">
+        <v>1.68</v>
+      </c>
+      <c r="Z72">
+        <v>4.4</v>
+      </c>
+      <c r="AA72">
+        <v>1.16</v>
+      </c>
+      <c r="AB72">
+        <v>1.02</v>
+      </c>
+      <c r="AC72">
+        <v>1.15</v>
+      </c>
+      <c r="AD72">
+        <v>5.25</v>
+      </c>
+      <c r="AE72">
+        <v>1.5</v>
+      </c>
+      <c r="AF72">
+        <v>2.58</v>
+      </c>
+      <c r="AG72">
+        <v>2.21</v>
+      </c>
+      <c r="AH72">
+        <v>1.66</v>
+      </c>
+      <c r="AI72">
+        <v>3.7</v>
+      </c>
+      <c r="AJ72">
+        <v>1.18</v>
+      </c>
+      <c r="AK72">
+        <v>1.6</v>
+      </c>
+      <c r="AL72">
         <v>2.15</v>
       </c>
-      <c r="U72">
-        <v>3.6</v>
-      </c>
-      <c r="V72">
-        <v>1.33</v>
-      </c>
-      <c r="W72">
-        <v>3.04</v>
-      </c>
-      <c r="X72">
-        <v>2.53</v>
-      </c>
-      <c r="Y72">
-        <v>1.46</v>
-      </c>
-      <c r="Z72">
-        <v>6</v>
-      </c>
-      <c r="AA72">
-        <v>1.07</v>
-      </c>
-      <c r="AB72">
-        <v>1</v>
-      </c>
-      <c r="AC72">
-        <v>1.24</v>
-      </c>
-      <c r="AD72">
-        <v>3.8</v>
-      </c>
-      <c r="AE72">
-        <v>1.8</v>
-      </c>
-      <c r="AF72">
-        <v>2</v>
-      </c>
-      <c r="AG72">
-        <v>2.95</v>
-      </c>
-      <c r="AH72">
-        <v>1.36</v>
-      </c>
-      <c r="AI72">
-        <v>5.05</v>
-      </c>
-      <c r="AJ72">
-        <v>1.1</v>
-      </c>
-      <c r="AK72">
-        <v>1.62</v>
-      </c>
-      <c r="AL72">
-        <v>2.1</v>
-      </c>
       <c r="AM72">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AN72">
-        <v>1.77</v>
+        <v>2.72</v>
       </c>
       <c r="AO72">
         <v>0</v>
@@ -14570,52 +14570,52 @@
         <v>1.2</v>
       </c>
       <c r="AQ72">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AR72">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AS72">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="AT72">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="AU72">
-        <v>3.72</v>
+        <v>3.85</v>
       </c>
       <c r="AV72">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="AW72">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AX72">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AY72">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="AZ72">
-        <v>2.03</v>
+        <v>1.28</v>
       </c>
       <c r="BA72">
-        <v>2.19</v>
+        <v>4.1</v>
       </c>
       <c r="BB72">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="BC72">
-        <v>1.97</v>
+        <v>1.66</v>
       </c>
       <c r="BD72">
-        <v>4.15</v>
+        <v>5.3</v>
       </c>
       <c r="BE72">
-        <v>1.78</v>
+        <v>2.14</v>
       </c>
       <c r="BF72">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="BG72">
         <v>0</v>
@@ -14635,7 +14635,7 @@
         <v>82</v>
       </c>
       <c r="C73" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D73" t="s">
         <v>134</v>
@@ -14820,7 +14820,7 @@
         <v>83</v>
       </c>
       <c r="C74" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="D74" t="s">
         <v>134</v>
@@ -14859,13 +14859,13 @@
         <v>308</v>
       </c>
       <c r="P74">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="Q74">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="R74">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -14904,10 +14904,10 @@
         <v>0</v>
       </c>
       <c r="AE74">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF74">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG74">
         <v>0</v>
@@ -15005,7 +15005,7 @@
         <v>83</v>
       </c>
       <c r="C75" t="s">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="D75" t="s">
         <v>134</v>
@@ -15044,133 +15044,133 @@
         <v>308</v>
       </c>
       <c r="P75">
-        <v>2.39</v>
+        <v>5.63</v>
       </c>
       <c r="Q75">
-        <v>3.25</v>
+        <v>4.21</v>
       </c>
       <c r="R75">
-        <v>2.87</v>
+        <v>1.67</v>
       </c>
       <c r="S75">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T75">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U75">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V75">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W75">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="X75">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y75">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z75">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA75">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB75">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC75">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AD75">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE75">
-        <v>1.99</v>
+        <v>1.63</v>
       </c>
       <c r="AF75">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AG75">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AH75">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI75">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AJ75">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK75">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL75">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM75">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AN75">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AO75">
         <v>0</v>
       </c>
       <c r="AP75">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ75">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AR75">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AS75">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AT75">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AU75">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AV75">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AW75">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AX75">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AY75">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AZ75">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BA75">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="BB75">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC75">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BD75">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE75">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BF75">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG75">
         <v>0</v>
@@ -15190,7 +15190,7 @@
         <v>83</v>
       </c>
       <c r="C76" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="D76" t="s">
         <v>134</v>
@@ -15229,133 +15229,133 @@
         <v>308</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q76">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R76">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S76">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T76">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U76">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V76">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W76">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="X76">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y76">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z76">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA76">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB76">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC76">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD76">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE76">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF76">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG76">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AH76">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI76">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AJ76">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK76">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL76">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM76">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AN76">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AO76">
         <v>0</v>
       </c>
       <c r="AP76">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ76">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR76">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AS76">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AT76">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AU76">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AV76">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AW76">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AX76">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY76">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AZ76">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BA76">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BB76">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC76">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BD76">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE76">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BF76">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG76">
         <v>0</v>
@@ -15560,7 +15560,7 @@
         <v>85</v>
       </c>
       <c r="C78" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D78" t="s">
         <v>134</v>
@@ -16154,13 +16154,13 @@
         <v>308</v>
       </c>
       <c r="P81">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q81">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R81">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S81">
         <v>0</v>
@@ -16300,7 +16300,7 @@
         <v>87</v>
       </c>
       <c r="C82" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D82" t="s">
         <v>136</v>
@@ -16524,13 +16524,13 @@
         <v>308</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S83">
         <v>0</v>
@@ -16670,7 +16670,7 @@
         <v>87</v>
       </c>
       <c r="C84" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D84" t="s">
         <v>136</v>
@@ -17225,7 +17225,7 @@
         <v>89</v>
       </c>
       <c r="C87" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D87" t="s">
         <v>136</v>

--- a/jogos_2026-05-04.xlsx
+++ b/jogos_2026-05-04.xlsx
@@ -301,43 +301,49 @@
     <t>Croatia Druga HNL</t>
   </si>
   <si>
+    <t>Serbia Prva Liga</t>
+  </si>
+  <si>
+    <t>Russia FNL</t>
+  </si>
+  <si>
+    <t>Oman Professional League</t>
+  </si>
+  <si>
+    <t>Uzbekistan Uzbekistan Super League</t>
+  </si>
+  <si>
+    <t>England Premier League</t>
+  </si>
+  <si>
     <t>India Indian Super League</t>
   </si>
   <si>
-    <t>England Premier League</t>
-  </si>
-  <si>
-    <t>Uzbekistan Uzbekistan Super League</t>
-  </si>
-  <si>
     <t>Egypt Egyptian Premier League</t>
   </si>
   <si>
-    <t>Serbia Prva Liga</t>
-  </si>
-  <si>
-    <t>Russia FNL</t>
-  </si>
-  <si>
-    <t>Oman Professional League</t>
-  </si>
-  <si>
     <t>Romania Liga I</t>
   </si>
   <si>
+    <t>Tunisia Ligue 1</t>
+  </si>
+  <si>
     <t>Serbia SuperLiga</t>
   </si>
   <si>
-    <t>Tunisia Ligue 1</t>
-  </si>
-  <si>
     <t>Azerbaijan Premyer Liqası</t>
   </si>
   <si>
+    <t>Republic of Ireland Premier Division</t>
+  </si>
+  <si>
+    <t>Morocco Botola Pro</t>
+  </si>
+  <si>
     <t>Republic of Ireland First Division</t>
   </si>
   <si>
-    <t>Republic of Ireland Premier Division</t>
+    <t>Poland 1. Liga</t>
   </si>
   <si>
     <t>Croatia Prva HNL</t>
@@ -346,45 +352,39 @@
     <t>Jordan Jordanian Pro League</t>
   </si>
   <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
-    <t>Morocco Botola Pro</t>
-  </si>
-  <si>
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
+    <t>Italy Serie A</t>
+  </si>
+  <si>
     <t>Austria Bundesliga</t>
   </si>
   <si>
-    <t>Italy Serie A</t>
-  </si>
-  <si>
     <t>Scotland Premiership</t>
   </si>
   <si>
     <t>Algeria Ligue 1</t>
   </si>
   <si>
+    <t>Israel Israeli Premier League</t>
+  </si>
+  <si>
+    <t>Portugal LigaPro</t>
+  </si>
+  <si>
+    <t>Denmark Superliga</t>
+  </si>
+  <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
+    <t>Poland Ekstraklasa</t>
+  </si>
+  <si>
     <t>Norway Eliteserien</t>
   </si>
   <si>
-    <t>Israel Israeli Premier League</t>
-  </si>
-  <si>
-    <t>Denmark Superliga</t>
-  </si>
-  <si>
-    <t>Portugal LigaPro</t>
-  </si>
-  <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
-    <t>Poland Ekstraklasa</t>
-  </si>
-  <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
@@ -445,171 +445,171 @@
     <t>Aston Villa Ladies</t>
   </si>
   <si>
+    <t>Awassa Kenema</t>
+  </si>
+  <si>
     <t>Mekelakeya</t>
   </si>
   <si>
-    <t>Awassa Kenema</t>
-  </si>
-  <si>
     <t>Dugopolje</t>
   </si>
   <si>
+    <t>Stepojevac Vaga</t>
+  </si>
+  <si>
+    <t>Ural</t>
+  </si>
+  <si>
+    <t>Al Khabourah</t>
+  </si>
+  <si>
+    <t>Xorazm</t>
+  </si>
+  <si>
+    <t>Chelsea</t>
+  </si>
+  <si>
     <t>Odisha FC</t>
   </si>
   <si>
-    <t>Chelsea</t>
-  </si>
-  <si>
-    <t>Xorazm</t>
+    <t>Pharco</t>
   </si>
   <si>
     <t>Lokomotiv</t>
   </si>
   <si>
-    <t>Pharco</t>
-  </si>
-  <si>
-    <t>Stepojevac Vaga</t>
-  </si>
-  <si>
     <t>OFK Vršac</t>
   </si>
   <si>
-    <t>Ural</t>
-  </si>
-  <si>
-    <t>Al Khabourah</t>
-  </si>
-  <si>
     <t>Unirea Slobozia</t>
   </si>
   <si>
+    <t>Jeunesse Sportive Omrane</t>
+  </si>
+  <si>
+    <t>CA Bizertin</t>
+  </si>
+  <si>
+    <t>Zarzis</t>
+  </si>
+  <si>
+    <t>Monastir</t>
+  </si>
+  <si>
     <t>Radnik Surdulica</t>
   </si>
   <si>
-    <t>Zarzis</t>
-  </si>
-  <si>
-    <t>Monastir</t>
-  </si>
-  <si>
     <t>Nasaf</t>
   </si>
   <si>
-    <t>Jeunesse Sportive Omrane</t>
-  </si>
-  <si>
-    <t>CA Bizertin</t>
-  </si>
-  <si>
     <t>Al Nasr</t>
   </si>
   <si>
     <t>Qarabağ</t>
   </si>
   <si>
+    <t>Shamrock Rovers</t>
+  </si>
+  <si>
+    <t>Hassania Agadir</t>
+  </si>
+  <si>
+    <t>Bohemians</t>
+  </si>
+  <si>
+    <t>Finn Harps</t>
+  </si>
+  <si>
+    <t>Longford Town</t>
+  </si>
+  <si>
+    <t>Derry City</t>
+  </si>
+  <si>
+    <t>Polonia Bytom</t>
+  </si>
+  <si>
+    <t>Istra 1961</t>
+  </si>
+  <si>
+    <t>Al Jazeera</t>
+  </si>
+  <si>
     <t>Kerry</t>
   </si>
   <si>
+    <t>Cobh Ramblers</t>
+  </si>
+  <si>
+    <t>Al Ahli</t>
+  </si>
+  <si>
+    <t>Treaty United</t>
+  </si>
+  <si>
     <t>Sligo Rovers</t>
   </si>
   <si>
-    <t>Istra 1961</t>
-  </si>
-  <si>
     <t>Waterford</t>
   </si>
   <si>
-    <t>Derry City</t>
-  </si>
-  <si>
-    <t>Bohemians</t>
-  </si>
-  <si>
-    <t>Longford Town</t>
-  </si>
-  <si>
-    <t>Treaty United</t>
-  </si>
-  <si>
-    <t>Cobh Ramblers</t>
-  </si>
-  <si>
-    <t>Al Jazeera</t>
-  </si>
-  <si>
-    <t>Al Ahli</t>
-  </si>
-  <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
-    <t>Shamrock Rovers</t>
-  </si>
-  <si>
-    <t>Polonia Bytom</t>
-  </si>
-  <si>
-    <t>Hassania Agadir</t>
-  </si>
-  <si>
     <t>Al Feiha</t>
   </si>
   <si>
     <t>Al Shabab</t>
   </si>
   <si>
+    <t>Cremonese</t>
+  </si>
+  <si>
+    <t>Arsenal Tula</t>
+  </si>
+  <si>
     <t>Rheindorf Altach</t>
   </si>
   <si>
-    <t>Arsenal Tula</t>
-  </si>
-  <si>
-    <t>Cremonese</t>
-  </si>
-  <si>
     <t>Hearts</t>
   </si>
   <si>
     <t>CR Belouizdad</t>
   </si>
   <si>
+    <t>Čukarički</t>
+  </si>
+  <si>
+    <t>Maccabi Netanya</t>
+  </si>
+  <si>
     <t>Al Ittihad</t>
   </si>
   <si>
+    <t>Torreense</t>
+  </si>
+  <si>
+    <t>Midtjylland</t>
+  </si>
+  <si>
+    <t>Porto II</t>
+  </si>
+  <si>
+    <t>Bnei Sakhnin</t>
+  </si>
+  <si>
+    <t>Djurgården</t>
+  </si>
+  <si>
+    <t>Radomiak Radom</t>
+  </si>
+  <si>
     <t>Wadi Degla</t>
   </si>
   <si>
     <t>FK Bodo - Glimt</t>
   </si>
   <si>
-    <t>Bnei Sakhnin</t>
-  </si>
-  <si>
-    <t>Maccabi Netanya</t>
-  </si>
-  <si>
-    <t>Midtjylland</t>
-  </si>
-  <si>
-    <t>Porto II</t>
-  </si>
-  <si>
-    <t>Torreense</t>
-  </si>
-  <si>
     <t>Halmstad</t>
   </si>
   <si>
-    <t>Djurgården</t>
-  </si>
-  <si>
-    <t>Čukarički</t>
-  </si>
-  <si>
-    <t>Radomiak Radom</t>
-  </si>
-  <si>
     <t>Landskrona</t>
   </si>
   <si>
@@ -661,27 +661,27 @@
     <t>Vila Nova</t>
   </si>
   <si>
+    <t>Figueirense</t>
+  </si>
+  <si>
+    <t>Quilmes</t>
+  </si>
+  <si>
     <t>Ypiranga Erechim</t>
   </si>
   <si>
     <t>Floresta</t>
   </si>
   <si>
-    <t>Quilmes</t>
-  </si>
-  <si>
-    <t>Figueirense</t>
-  </si>
-  <si>
     <t>Universitario de Vinto</t>
   </si>
   <si>
+    <t>Gimnasia y Tiro</t>
+  </si>
+  <si>
     <t>San Marcos</t>
   </si>
   <si>
-    <t>Gimnasia y Tiro</t>
-  </si>
-  <si>
     <t>PSIM Yogyakarta</t>
   </si>
   <si>
@@ -700,171 +700,171 @@
     <t>West Ham United Women</t>
   </si>
   <si>
+    <t>Sheger Ketema</t>
+  </si>
+  <si>
     <t>Adama Kenema</t>
   </si>
   <si>
-    <t>Sheger Ketema</t>
-  </si>
-  <si>
     <t>Cibalia</t>
   </si>
   <si>
+    <t>Kabel Novi Sad</t>
+  </si>
+  <si>
+    <t>Shinnik</t>
+  </si>
+  <si>
+    <t>Saham</t>
+  </si>
+  <si>
+    <t>Andijan</t>
+  </si>
+  <si>
+    <t>Nottingham Forest</t>
+  </si>
+  <si>
     <t>Bengaluru</t>
   </si>
   <si>
-    <t>Nottingham Forest</t>
-  </si>
-  <si>
-    <t>Andijan</t>
+    <t>Al Mokawloon</t>
   </si>
   <si>
     <t>Qizilqum</t>
   </si>
   <si>
-    <t>Al Mokawloon</t>
-  </si>
-  <si>
-    <t>Kabel Novi Sad</t>
-  </si>
-  <si>
     <t>Jedinstvo Ub</t>
   </si>
   <si>
-    <t>Shinnik</t>
-  </si>
-  <si>
-    <t>Saham</t>
-  </si>
-  <si>
     <t>Hermannstadt</t>
   </si>
   <si>
+    <t>ES Tunis</t>
+  </si>
+  <si>
+    <t>Marsa</t>
+  </si>
+  <si>
+    <t>Etoile du Sahel</t>
+  </si>
+  <si>
+    <t>Métlaoui</t>
+  </si>
+  <si>
     <t>Vojvodina</t>
   </si>
   <si>
-    <t>Etoile du Sahel</t>
-  </si>
-  <si>
-    <t>Métlaoui</t>
-  </si>
-  <si>
     <t>Navbahor</t>
   </si>
   <si>
-    <t>ES Tunis</t>
-  </si>
-  <si>
-    <t>Marsa</t>
-  </si>
-  <si>
     <t>Al-Nahda</t>
   </si>
   <si>
     <t>Turan</t>
   </si>
   <si>
+    <t>Drogheda United</t>
+  </si>
+  <si>
+    <t>Olympic Safi</t>
+  </si>
+  <si>
+    <t>Shelbourne</t>
+  </si>
+  <si>
+    <t>Bray Wanderers</t>
+  </si>
+  <si>
+    <t>Athlone Town</t>
+  </si>
+  <si>
+    <t>Galway United</t>
+  </si>
+  <si>
+    <t>Polonia Warszawa</t>
+  </si>
+  <si>
+    <t>Slaven Koprivnica</t>
+  </si>
+  <si>
+    <t>Shabab Al Ordon</t>
+  </si>
+  <si>
     <t>Cork City</t>
   </si>
   <si>
+    <t>UCD</t>
+  </si>
+  <si>
+    <t>Al Buqa'a</t>
+  </si>
+  <si>
+    <t>Wexford</t>
+  </si>
+  <si>
     <t>St Patrick's Athl.</t>
   </si>
   <si>
-    <t>Slaven Koprivnica</t>
-  </si>
-  <si>
     <t>Dundalk</t>
   </si>
   <si>
-    <t>Galway United</t>
-  </si>
-  <si>
-    <t>Shelbourne</t>
-  </si>
-  <si>
-    <t>Athlone Town</t>
-  </si>
-  <si>
-    <t>Wexford</t>
-  </si>
-  <si>
-    <t>UCD</t>
-  </si>
-  <si>
-    <t>Shabab Al Ordon</t>
-  </si>
-  <si>
-    <t>Al Buqa'a</t>
-  </si>
-  <si>
-    <t>Bray Wanderers</t>
-  </si>
-  <si>
-    <t>Drogheda United</t>
-  </si>
-  <si>
-    <t>Polonia Warszawa</t>
-  </si>
-  <si>
-    <t>Olympic Safi</t>
-  </si>
-  <si>
     <t>Al Riyadh</t>
   </si>
   <si>
     <t>Al-Rustaq</t>
   </si>
   <si>
+    <t>Lazio</t>
+  </si>
+  <si>
+    <t>Rotor Volgograd</t>
+  </si>
+  <si>
     <t>Wolfsberger AC</t>
   </si>
   <si>
-    <t>Rotor Volgograd</t>
-  </si>
-  <si>
-    <t>Lazio</t>
-  </si>
-  <si>
     <t>Rangers</t>
   </si>
   <si>
     <t>USM Khenchela</t>
   </si>
   <si>
+    <t>Red Star Belgrade</t>
+  </si>
+  <si>
+    <t>Hapoel Katamon</t>
+  </si>
+  <si>
     <t>Petrojet</t>
   </si>
   <si>
+    <t>FC Penafiel</t>
+  </si>
+  <si>
+    <t>Viborg</t>
+  </si>
+  <si>
+    <t>Felgueiras 1932</t>
+  </si>
+  <si>
+    <t>Maccabi Bnei Raina</t>
+  </si>
+  <si>
+    <t>IFK Göteborg</t>
+  </si>
+  <si>
+    <t>Lechia Gdańsk</t>
+  </si>
+  <si>
     <t>Kahraba Ismailia</t>
   </si>
   <si>
     <t>Molde</t>
   </si>
   <si>
-    <t>Maccabi Bnei Raina</t>
-  </si>
-  <si>
-    <t>Hapoel Katamon</t>
-  </si>
-  <si>
-    <t>Viborg</t>
-  </si>
-  <si>
-    <t>Felgueiras 1932</t>
-  </si>
-  <si>
-    <t>FC Penafiel</t>
-  </si>
-  <si>
     <t>Brommapojkarna</t>
   </si>
   <si>
-    <t>IFK Göteborg</t>
-  </si>
-  <si>
-    <t>Red Star Belgrade</t>
-  </si>
-  <si>
-    <t>Lechia Gdańsk</t>
-  </si>
-  <si>
     <t>Öster</t>
   </si>
   <si>
@@ -880,15 +880,15 @@
     <t>Al Najma</t>
   </si>
   <si>
+    <t>Budafoki MTE</t>
+  </si>
+  <si>
+    <t>RSB Berkane</t>
+  </si>
+  <si>
     <t>Al Kholood</t>
   </si>
   <si>
-    <t>Budafoki MTE</t>
-  </si>
-  <si>
-    <t>RSB Berkane</t>
-  </si>
-  <si>
     <t>Rapid Wien</t>
   </si>
   <si>
@@ -919,25 +919,25 @@
     <t>Athletic Club</t>
   </si>
   <si>
+    <t>Barra do Garcas</t>
+  </si>
+  <si>
+    <t>Chacarita Juniors</t>
+  </si>
+  <si>
     <t>Ituano</t>
   </si>
   <si>
     <t>Maranhão</t>
   </si>
   <si>
-    <t>Chacarita Juniors</t>
-  </si>
-  <si>
-    <t>Barra do Garcas</t>
-  </si>
-  <si>
     <t>Blooming</t>
   </si>
   <si>
+    <t>Agropecuario</t>
+  </si>
+  <si>
     <t>Recoleta</t>
-  </si>
-  <si>
-    <t>Agropecuario</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -3389,133 +3389,133 @@
         <v>308</v>
       </c>
       <c r="P12">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="Q12">
-        <v>3.75</v>
+        <v>3.42</v>
       </c>
       <c r="R12">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="S12">
-        <v>2.15</v>
+        <v>2.42</v>
       </c>
       <c r="T12">
-        <v>2.3</v>
+        <v>2.01</v>
       </c>
       <c r="U12">
-        <v>4.2</v>
+        <v>4.85</v>
       </c>
       <c r="V12">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="W12">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="X12">
-        <v>2.49</v>
+        <v>3.25</v>
       </c>
       <c r="Y12">
+        <v>1.32</v>
+      </c>
+      <c r="Z12">
+        <v>7.6</v>
+      </c>
+      <c r="AA12">
+        <v>1.03</v>
+      </c>
+      <c r="AB12">
+        <v>1.03</v>
+      </c>
+      <c r="AC12">
+        <v>1.35</v>
+      </c>
+      <c r="AD12">
+        <v>2.74</v>
+      </c>
+      <c r="AE12">
+        <v>2.17</v>
+      </c>
+      <c r="AF12">
+        <v>1.68</v>
+      </c>
+      <c r="AG12">
+        <v>4.07</v>
+      </c>
+      <c r="AH12">
+        <v>1.19</v>
+      </c>
+      <c r="AI12">
+        <v>7.3</v>
+      </c>
+      <c r="AJ12">
+        <v>1.03</v>
+      </c>
+      <c r="AK12">
+        <v>1.97</v>
+      </c>
+      <c r="AL12">
+        <v>1.75</v>
+      </c>
+      <c r="AM12">
+        <v>1.31</v>
+      </c>
+      <c r="AN12">
+        <v>1.88</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>0</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12">
+        <v>0</v>
+      </c>
+      <c r="AV12">
+        <v>0</v>
+      </c>
+      <c r="AW12">
+        <v>0</v>
+      </c>
+      <c r="AX12">
+        <v>0</v>
+      </c>
+      <c r="AY12">
+        <v>0</v>
+      </c>
+      <c r="AZ12">
+        <v>0</v>
+      </c>
+      <c r="BA12">
+        <v>0</v>
+      </c>
+      <c r="BB12">
+        <v>1.28</v>
+      </c>
+      <c r="BC12">
+        <v>2.32</v>
+      </c>
+      <c r="BD12">
+        <v>3.28</v>
+      </c>
+      <c r="BE12">
         <v>1.53</v>
       </c>
-      <c r="Z12">
-        <v>5.8</v>
-      </c>
-      <c r="AA12">
-        <v>1.12</v>
-      </c>
-      <c r="AB12">
-        <v>1.01</v>
-      </c>
-      <c r="AC12">
-        <v>1.18</v>
-      </c>
-      <c r="AD12">
-        <v>4.2</v>
-      </c>
-      <c r="AE12">
-        <v>1.67</v>
-      </c>
-      <c r="AF12">
-        <v>2.27</v>
-      </c>
-      <c r="AG12">
-        <v>2.7</v>
-      </c>
-      <c r="AH12">
-        <v>1.49</v>
-      </c>
-      <c r="AI12">
-        <v>4.75</v>
-      </c>
-      <c r="AJ12">
-        <v>1.13</v>
-      </c>
-      <c r="AK12">
-        <v>1.67</v>
-      </c>
-      <c r="AL12">
-        <v>2.15</v>
-      </c>
-      <c r="AM12">
-        <v>1.27</v>
-      </c>
-      <c r="AN12">
-        <v>2.05</v>
-      </c>
-      <c r="AO12">
-        <v>0</v>
-      </c>
-      <c r="AP12">
-        <v>1.16</v>
-      </c>
-      <c r="AQ12">
-        <v>1.3</v>
-      </c>
-      <c r="AR12">
-        <v>1.54</v>
-      </c>
-      <c r="AS12">
-        <v>1.89</v>
-      </c>
-      <c r="AT12">
-        <v>2.37</v>
-      </c>
-      <c r="AU12">
-        <v>4.32</v>
-      </c>
-      <c r="AV12">
-        <v>3.07</v>
-      </c>
-      <c r="AW12">
-        <v>2.37</v>
-      </c>
-      <c r="AX12">
-        <v>1.85</v>
-      </c>
-      <c r="AY12">
-        <v>1.52</v>
-      </c>
-      <c r="AZ12">
-        <v>1.39</v>
-      </c>
-      <c r="BA12">
-        <v>3.7</v>
-      </c>
-      <c r="BB12">
-        <v>1.2</v>
-      </c>
-      <c r="BC12">
-        <v>1.91</v>
-      </c>
-      <c r="BD12">
-        <v>4.2</v>
-      </c>
-      <c r="BE12">
-        <v>1.85</v>
-      </c>
       <c r="BF12">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="BG12">
         <v>0</v>
@@ -3538,7 +3538,7 @@
         <v>97</v>
       </c>
       <c r="D13" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E13" t="s">
         <v>148</v>
@@ -3720,7 +3720,7 @@
         <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D14" t="s">
         <v>136</v>
@@ -3905,7 +3905,7 @@
         <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D15" t="s">
         <v>134</v>
@@ -3944,133 +3944,133 @@
         <v>308</v>
       </c>
       <c r="P15">
-        <v>2.95</v>
+        <v>1.69</v>
       </c>
       <c r="Q15">
-        <v>2.62</v>
+        <v>3.75</v>
       </c>
       <c r="R15">
-        <v>2.46</v>
+        <v>4.7</v>
       </c>
       <c r="S15">
-        <v>4.3</v>
+        <v>2.15</v>
       </c>
       <c r="T15">
-        <v>1.72</v>
+        <v>2.3</v>
       </c>
       <c r="U15">
-        <v>3.28</v>
+        <v>4.2</v>
       </c>
       <c r="V15">
+        <v>1.33</v>
+      </c>
+      <c r="W15">
+        <v>3.3</v>
+      </c>
+      <c r="X15">
+        <v>2.49</v>
+      </c>
+      <c r="Y15">
+        <v>1.53</v>
+      </c>
+      <c r="Z15">
+        <v>5.8</v>
+      </c>
+      <c r="AA15">
+        <v>1.12</v>
+      </c>
+      <c r="AB15">
+        <v>1.01</v>
+      </c>
+      <c r="AC15">
+        <v>1.18</v>
+      </c>
+      <c r="AD15">
+        <v>4.2</v>
+      </c>
+      <c r="AE15">
         <v>1.67</v>
       </c>
-      <c r="W15">
-        <v>2.07</v>
-      </c>
-      <c r="X15">
-        <v>3.84</v>
-      </c>
-      <c r="Y15">
-        <v>1.18</v>
-      </c>
-      <c r="Z15">
-        <v>12</v>
-      </c>
-      <c r="AA15">
-        <v>1.01</v>
-      </c>
-      <c r="AB15">
+      <c r="AF15">
+        <v>2.27</v>
+      </c>
+      <c r="AG15">
+        <v>2.7</v>
+      </c>
+      <c r="AH15">
+        <v>1.49</v>
+      </c>
+      <c r="AI15">
+        <v>4.75</v>
+      </c>
+      <c r="AJ15">
         <v>1.13</v>
       </c>
-      <c r="AC15">
-        <v>1.57</v>
-      </c>
-      <c r="AD15">
-        <v>2.25</v>
-      </c>
-      <c r="AE15">
-        <v>2.7</v>
-      </c>
-      <c r="AF15">
-        <v>1.36</v>
-      </c>
-      <c r="AG15">
-        <v>5.75</v>
-      </c>
-      <c r="AH15">
-        <v>1.11</v>
-      </c>
-      <c r="AI15">
-        <v>12.5</v>
-      </c>
-      <c r="AJ15">
-        <v>1.03</v>
-      </c>
       <c r="AK15">
-        <v>2.19</v>
+        <v>1.67</v>
       </c>
       <c r="AL15">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="AM15">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AN15">
-        <v>1.25</v>
+        <v>2.05</v>
       </c>
       <c r="AO15">
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="AQ15">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AR15">
-        <v>1.97</v>
+        <v>1.54</v>
       </c>
       <c r="AS15">
-        <v>2.55</v>
+        <v>1.89</v>
       </c>
       <c r="AT15">
-        <v>3.3</v>
+        <v>2.37</v>
       </c>
       <c r="AU15">
-        <v>2.88</v>
+        <v>4.32</v>
       </c>
       <c r="AV15">
-        <v>2.16</v>
+        <v>3.07</v>
       </c>
       <c r="AW15">
-        <v>1.72</v>
+        <v>2.37</v>
       </c>
       <c r="AX15">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AY15">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="AZ15">
-        <v>2.48</v>
+        <v>1.39</v>
       </c>
       <c r="BA15">
-        <v>1.62</v>
+        <v>3.7</v>
       </c>
       <c r="BB15">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="BC15">
-        <v>2.78</v>
+        <v>1.91</v>
       </c>
       <c r="BD15">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="BE15">
-        <v>1.36</v>
+        <v>1.85</v>
       </c>
       <c r="BF15">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="BG15">
         <v>0</v>
@@ -4090,7 +4090,7 @@
         <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D16" t="s">
         <v>134</v>
@@ -4275,7 +4275,7 @@
         <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D17" t="s">
         <v>134</v>
@@ -4314,133 +4314,133 @@
         <v>308</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AH17">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI17">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AL17">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AM17">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AN17">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO17">
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AU17">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AV17">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AW17">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX17">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AY17">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ17">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BA17">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BB17">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BC17">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="BD17">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BE17">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BF17">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BG17">
         <v>0</v>
@@ -4460,10 +4460,10 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D18" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E18" t="s">
         <v>153</v>
@@ -4499,79 +4499,79 @@
         <v>308</v>
       </c>
       <c r="P18">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q18">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R18">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S18">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="T18">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="U18">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="V18">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W18">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X18">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y18">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z18">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AA18">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB18">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC18">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD18">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AE18">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AF18">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG18">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="AH18">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI18">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AJ18">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK18">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL18">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AM18">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AN18">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AO18">
         <v>0</v>
@@ -4613,19 +4613,19 @@
         <v>0</v>
       </c>
       <c r="BB18">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BC18">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="BD18">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE18">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF18">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG18">
         <v>0</v>
@@ -4645,7 +4645,7 @@
         <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D19" t="s">
         <v>134</v>
@@ -5054,61 +5054,61 @@
         <v>308</v>
       </c>
       <c r="P21">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q21">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R21">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S21">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T21">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="U21">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="V21">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W21">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="X21">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Y21">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z21">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AA21">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB21">
         <v>0</v>
       </c>
       <c r="AC21">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD21">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="AE21">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AF21">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG21">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AH21">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AI21">
         <v>0</v>
@@ -5117,16 +5117,16 @@
         <v>0</v>
       </c>
       <c r="AK21">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AL21">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AM21">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN21">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO21">
         <v>0</v>
@@ -5171,13 +5171,13 @@
         <v>0</v>
       </c>
       <c r="BC21">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="BD21">
         <v>0</v>
       </c>
       <c r="BE21">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="BF21">
         <v>0</v>
@@ -5200,7 +5200,7 @@
         <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D22" t="s">
         <v>134</v>
@@ -5385,7 +5385,7 @@
         <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D23" t="s">
         <v>134</v>
@@ -5570,10 +5570,10 @@
         <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="D24" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E24" t="s">
         <v>159</v>
@@ -5794,61 +5794,61 @@
         <v>308</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB25">
         <v>0</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AH25">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI25">
         <v>0</v>
@@ -5857,16 +5857,16 @@
         <v>0</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL25">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AM25">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN25">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO25">
         <v>0</v>
@@ -5911,13 +5911,13 @@
         <v>0</v>
       </c>
       <c r="BC25">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BD25">
         <v>0</v>
       </c>
       <c r="BE25">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BF25">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D26" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E26" t="s">
         <v>161</v>
@@ -6125,7 +6125,7 @@
         <v>70</v>
       </c>
       <c r="C27" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D27" t="s">
         <v>134</v>
@@ -6534,13 +6534,13 @@
         <v>308</v>
       </c>
       <c r="P29">
-        <v>5.42</v>
+        <v>0</v>
       </c>
       <c r="Q29">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R29">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S29">
         <v>0</v>
@@ -6683,7 +6683,7 @@
         <v>107</v>
       </c>
       <c r="D30" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E30" t="s">
         <v>165</v>
@@ -6865,10 +6865,10 @@
         <v>72</v>
       </c>
       <c r="C31" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D31" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E31" t="s">
         <v>166</v>
@@ -6904,133 +6904,133 @@
         <v>308</v>
       </c>
       <c r="P31">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q31">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R31">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="S31">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T31">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U31">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="V31">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W31">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="X31">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y31">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z31">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AA31">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB31">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC31">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AD31">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE31">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF31">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG31">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AH31">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI31">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AJ31">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK31">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL31">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AM31">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AN31">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AO31">
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AQ31">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AR31">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AS31">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="AT31">
-        <v>5.44</v>
+        <v>0</v>
       </c>
       <c r="AU31">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AV31">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AW31">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AX31">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AY31">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AZ31">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BA31">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="BB31">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC31">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD31">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE31">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BF31">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG31">
         <v>0</v>
@@ -7050,7 +7050,7 @@
         <v>72</v>
       </c>
       <c r="C32" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D32" t="s">
         <v>136</v>
@@ -7089,22 +7089,22 @@
         <v>308</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V32">
         <v>0</v>
@@ -7113,10 +7113,10 @@
         <v>0</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -7128,40 +7128,40 @@
         <v>0</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AH32">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI32">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL32">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AM32">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN32">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO32">
         <v>0</v>
@@ -7206,13 +7206,13 @@
         <v>0</v>
       </c>
       <c r="BC32">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BD32">
         <v>0</v>
       </c>
       <c r="BE32">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF32">
         <v>0</v>
@@ -7235,7 +7235,7 @@
         <v>72</v>
       </c>
       <c r="C33" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D33" t="s">
         <v>136</v>
@@ -7274,22 +7274,22 @@
         <v>308</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V33">
         <v>0</v>
@@ -7298,10 +7298,10 @@
         <v>0</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -7313,40 +7313,40 @@
         <v>0</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH33">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI33">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM33">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN33">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AO33">
         <v>0</v>
@@ -7391,13 +7391,13 @@
         <v>0</v>
       </c>
       <c r="BC33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD33">
         <v>0</v>
       </c>
       <c r="BE33">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BF33">
         <v>0</v>
@@ -7420,7 +7420,7 @@
         <v>72</v>
       </c>
       <c r="C34" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D34" t="s">
         <v>136</v>
@@ -7605,10 +7605,10 @@
         <v>72</v>
       </c>
       <c r="C35" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D35" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E35" t="s">
         <v>170</v>
@@ -7644,79 +7644,79 @@
         <v>308</v>
       </c>
       <c r="P35">
-        <v>2.09</v>
+        <v>2.36</v>
       </c>
       <c r="Q35">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R35">
-        <v>3.24</v>
+        <v>2.75</v>
       </c>
       <c r="S35">
-        <v>2.55</v>
+        <v>2.82</v>
       </c>
       <c r="T35">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="U35">
-        <v>3.75</v>
+        <v>3.28</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="X35">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="Y35">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC35">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AD35">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="AE35">
-        <v>1.82</v>
+        <v>1.61</v>
       </c>
       <c r="AF35">
-        <v>1.82</v>
+        <v>2.08</v>
       </c>
       <c r="AG35">
-        <v>3</v>
+        <v>2.43</v>
       </c>
       <c r="AH35">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AI35">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="AJ35">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AK35">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AL35">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="AM35">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AN35">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AO35">
         <v>0</v>
@@ -7758,19 +7758,19 @@
         <v>0</v>
       </c>
       <c r="BB35">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC35">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="BD35">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE35">
-        <v>1.64</v>
+        <v>1.86</v>
       </c>
       <c r="BF35">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG35">
         <v>0</v>
@@ -7790,10 +7790,10 @@
         <v>72</v>
       </c>
       <c r="C36" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D36" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E36" t="s">
         <v>171</v>
@@ -7829,133 +7829,133 @@
         <v>308</v>
       </c>
       <c r="P36">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="Q36">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R36">
-        <v>2.43</v>
+        <v>2.72</v>
       </c>
       <c r="S36">
+        <v>3.1</v>
+      </c>
+      <c r="T36">
+        <v>2.08</v>
+      </c>
+      <c r="U36">
         <v>3.25</v>
       </c>
-      <c r="T36">
-        <v>2.18</v>
-      </c>
-      <c r="U36">
-        <v>2.9</v>
-      </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="X36">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="Y36">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC36">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AD36">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="AE36">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="AF36">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG36">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="AH36">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AI36">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AJ36">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AK36">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AL36">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AM36">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="AN36">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="AO36">
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AQ36">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AR36">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AS36">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="AT36">
-        <v>0</v>
+        <v>5.44</v>
       </c>
       <c r="AU36">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AV36">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AW36">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AX36">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AY36">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AZ36">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BA36">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="BB36">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC36">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="BD36">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE36">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="BF36">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG36">
         <v>0</v>
@@ -7975,10 +7975,10 @@
         <v>72</v>
       </c>
       <c r="C37" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D37" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E37" t="s">
         <v>172</v>
@@ -8014,22 +8014,22 @@
         <v>308</v>
       </c>
       <c r="P37">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q37">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R37">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S37">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T37">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U37">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="V37">
         <v>0</v>
@@ -8038,10 +8038,10 @@
         <v>0</v>
       </c>
       <c r="X37">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Y37">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -8053,40 +8053,40 @@
         <v>0</v>
       </c>
       <c r="AC37">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD37">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AE37">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AF37">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AG37">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH37">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI37">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ37">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK37">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="AL37">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AM37">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN37">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AO37">
         <v>0</v>
@@ -8131,13 +8131,13 @@
         <v>0</v>
       </c>
       <c r="BC37">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="BD37">
         <v>0</v>
       </c>
       <c r="BE37">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF37">
         <v>0</v>
@@ -8160,10 +8160,10 @@
         <v>72</v>
       </c>
       <c r="C38" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D38" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E38" t="s">
         <v>173</v>
@@ -8199,13 +8199,13 @@
         <v>308</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>5.42</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -8244,10 +8244,10 @@
         <v>0</v>
       </c>
       <c r="AE38">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF38">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG38">
         <v>0</v>
@@ -8262,10 +8262,10 @@
         <v>0</v>
       </c>
       <c r="AK38">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL38">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AM38">
         <v>0</v>
@@ -8345,10 +8345,10 @@
         <v>72</v>
       </c>
       <c r="C39" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D39" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E39" t="s">
         <v>174</v>
@@ -8384,22 +8384,22 @@
         <v>308</v>
       </c>
       <c r="P39">
-        <v>2.35</v>
+        <v>2.14</v>
       </c>
       <c r="Q39">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R39">
-        <v>2.62</v>
+        <v>3.14</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="V39">
         <v>0</v>
@@ -8408,10 +8408,10 @@
         <v>0</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -8423,40 +8423,40 @@
         <v>0</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH39">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI39">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL39">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AM39">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN39">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AO39">
         <v>0</v>
@@ -8501,13 +8501,13 @@
         <v>0</v>
       </c>
       <c r="BC39">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BD39">
         <v>0</v>
       </c>
       <c r="BE39">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF39">
         <v>0</v>
@@ -8530,10 +8530,10 @@
         <v>72</v>
       </c>
       <c r="C40" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D40" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E40" t="s">
         <v>175</v>
@@ -8569,22 +8569,22 @@
         <v>308</v>
       </c>
       <c r="P40">
-        <v>2.65</v>
+        <v>2.35</v>
       </c>
       <c r="Q40">
         <v>3.2</v>
       </c>
       <c r="R40">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="S40">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T40">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U40">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="V40">
         <v>0</v>
@@ -8593,10 +8593,10 @@
         <v>0</v>
       </c>
       <c r="X40">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y40">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -8608,40 +8608,40 @@
         <v>0</v>
       </c>
       <c r="AC40">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AD40">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE40">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF40">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG40">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AH40">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI40">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ40">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK40">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL40">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AM40">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN40">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO40">
         <v>0</v>
@@ -8686,13 +8686,13 @@
         <v>0</v>
       </c>
       <c r="BC40">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="BD40">
         <v>0</v>
       </c>
       <c r="BE40">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BF40">
         <v>0</v>
@@ -8715,7 +8715,7 @@
         <v>72</v>
       </c>
       <c r="C41" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D41" t="s">
         <v>136</v>
@@ -8754,22 +8754,22 @@
         <v>308</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V41">
         <v>0</v>
@@ -8778,10 +8778,10 @@
         <v>0</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -8793,40 +8793,40 @@
         <v>0</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH41">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI41">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL41">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM41">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN41">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AO41">
         <v>0</v>
@@ -8871,13 +8871,13 @@
         <v>0</v>
       </c>
       <c r="BC41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD41">
         <v>0</v>
       </c>
       <c r="BE41">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BF41">
         <v>0</v>
@@ -8900,10 +8900,10 @@
         <v>72</v>
       </c>
       <c r="C42" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D42" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E42" t="s">
         <v>177</v>
@@ -8939,79 +8939,79 @@
         <v>308</v>
       </c>
       <c r="P42">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q42">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R42">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S42">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="T42">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="U42">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="V42">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W42">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="X42">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Y42">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z42">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA42">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB42">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC42">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD42">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE42">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF42">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG42">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AH42">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AI42">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AJ42">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK42">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL42">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AM42">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN42">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AO42">
         <v>0</v>
@@ -9053,19 +9053,19 @@
         <v>0</v>
       </c>
       <c r="BB42">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC42">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BD42">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE42">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="BF42">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BG42">
         <v>0</v>
@@ -9085,10 +9085,10 @@
         <v>72</v>
       </c>
       <c r="C43" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D43" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E43" t="s">
         <v>178</v>
@@ -9455,7 +9455,7 @@
         <v>74</v>
       </c>
       <c r="C45" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D45" t="s">
         <v>134</v>
@@ -9679,133 +9679,133 @@
         <v>308</v>
       </c>
       <c r="P46">
-        <v>2.55</v>
+        <v>3.89</v>
       </c>
       <c r="Q46">
-        <v>3.28</v>
+        <v>3.67</v>
       </c>
       <c r="R46">
-        <v>2.67</v>
+        <v>2.06</v>
       </c>
       <c r="S46">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="T46">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="U46">
-        <v>3.55</v>
+        <v>3.18</v>
       </c>
       <c r="V46">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W46">
+        <v>2.65</v>
+      </c>
+      <c r="X46">
         <v>2.9</v>
       </c>
-      <c r="X46">
-        <v>2.85</v>
-      </c>
       <c r="Y46">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="Z46">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA46">
         <v>1.04</v>
       </c>
       <c r="AB46">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AC46">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AD46">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="AE46">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AF46">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="AG46">
+        <v>4</v>
+      </c>
+      <c r="AH46">
+        <v>1.23</v>
+      </c>
+      <c r="AI46">
+        <v>8.1</v>
+      </c>
+      <c r="AJ46">
+        <v>1.02</v>
+      </c>
+      <c r="AK46">
+        <v>1.85</v>
+      </c>
+      <c r="AL46">
+        <v>1.85</v>
+      </c>
+      <c r="AM46">
+        <v>1.33</v>
+      </c>
+      <c r="AN46">
+        <v>1.36</v>
+      </c>
+      <c r="AO46">
+        <v>0</v>
+      </c>
+      <c r="AP46">
+        <v>1.38</v>
+      </c>
+      <c r="AQ46">
+        <v>1.66</v>
+      </c>
+      <c r="AR46">
+        <v>2.5</v>
+      </c>
+      <c r="AS46">
+        <v>2.77</v>
+      </c>
+      <c r="AT46">
+        <v>3.15</v>
+      </c>
+      <c r="AU46">
+        <v>2.8</v>
+      </c>
+      <c r="AV46">
+        <v>2.08</v>
+      </c>
+      <c r="AW46">
+        <v>1.7</v>
+      </c>
+      <c r="AX46">
+        <v>1.39</v>
+      </c>
+      <c r="AY46">
+        <v>1.22</v>
+      </c>
+      <c r="AZ46">
+        <v>2.5</v>
+      </c>
+      <c r="BA46">
+        <v>1.72</v>
+      </c>
+      <c r="BB46">
+        <v>1.3</v>
+      </c>
+      <c r="BC46">
+        <v>2.4</v>
+      </c>
+      <c r="BD46">
         <v>3.3</v>
       </c>
-      <c r="AH46">
-        <v>1.28</v>
-      </c>
-      <c r="AI46">
-        <v>6.5</v>
-      </c>
-      <c r="AJ46">
-        <v>1.09</v>
-      </c>
-      <c r="AK46">
-        <v>1.74</v>
-      </c>
-      <c r="AL46">
-        <v>2</v>
-      </c>
-      <c r="AM46">
-        <v>1.28</v>
-      </c>
-      <c r="AN46">
-        <v>1.54</v>
-      </c>
-      <c r="AO46">
-        <v>0</v>
-      </c>
-      <c r="AP46">
-        <v>1.33</v>
-      </c>
-      <c r="AQ46">
-        <v>1.61</v>
-      </c>
-      <c r="AR46">
-        <v>1.83</v>
-      </c>
-      <c r="AS46">
-        <v>2.75</v>
-      </c>
-      <c r="AT46">
-        <v>3.8</v>
-      </c>
-      <c r="AU46">
-        <v>2.83</v>
-      </c>
-      <c r="AV46">
-        <v>2.09</v>
-      </c>
-      <c r="AW46">
-        <v>1.66</v>
-      </c>
-      <c r="AX46">
-        <v>1.36</v>
-      </c>
-      <c r="AY46">
-        <v>1.19</v>
-      </c>
-      <c r="AZ46">
-        <v>1.67</v>
-      </c>
-      <c r="BA46">
-        <v>2.85</v>
-      </c>
-      <c r="BB46">
-        <v>1.25</v>
-      </c>
-      <c r="BC46">
-        <v>2.2</v>
-      </c>
-      <c r="BD46">
-        <v>3.58</v>
-      </c>
       <c r="BE46">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="BF46">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="BG46">
         <v>0</v>
@@ -9825,7 +9825,7 @@
         <v>75</v>
       </c>
       <c r="C47" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D47" t="s">
         <v>134</v>
@@ -10049,133 +10049,133 @@
         <v>308</v>
       </c>
       <c r="P48">
-        <v>3.89</v>
+        <v>2.55</v>
       </c>
       <c r="Q48">
-        <v>3.67</v>
+        <v>3.28</v>
       </c>
       <c r="R48">
-        <v>2.06</v>
+        <v>2.67</v>
       </c>
       <c r="S48">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="T48">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="U48">
-        <v>3.18</v>
+        <v>3.55</v>
       </c>
       <c r="V48">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W48">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="X48">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="Y48">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="Z48">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA48">
         <v>1.04</v>
       </c>
       <c r="AB48">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AC48">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AD48">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="AE48">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AF48">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="AG48">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="AH48">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AI48">
-        <v>8.1</v>
+        <v>6.5</v>
       </c>
       <c r="AJ48">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="AK48">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AL48">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AM48">
+        <v>1.28</v>
+      </c>
+      <c r="AN48">
+        <v>1.54</v>
+      </c>
+      <c r="AO48">
+        <v>0</v>
+      </c>
+      <c r="AP48">
         <v>1.33</v>
       </c>
-      <c r="AN48">
+      <c r="AQ48">
+        <v>1.61</v>
+      </c>
+      <c r="AR48">
+        <v>1.83</v>
+      </c>
+      <c r="AS48">
+        <v>2.75</v>
+      </c>
+      <c r="AT48">
+        <v>3.8</v>
+      </c>
+      <c r="AU48">
+        <v>2.83</v>
+      </c>
+      <c r="AV48">
+        <v>2.09</v>
+      </c>
+      <c r="AW48">
+        <v>1.66</v>
+      </c>
+      <c r="AX48">
         <v>1.36</v>
       </c>
-      <c r="AO48">
-        <v>0</v>
-      </c>
-      <c r="AP48">
-        <v>1.38</v>
-      </c>
-      <c r="AQ48">
-        <v>1.66</v>
-      </c>
-      <c r="AR48">
-        <v>2.5</v>
-      </c>
-      <c r="AS48">
-        <v>2.77</v>
-      </c>
-      <c r="AT48">
-        <v>3.15</v>
-      </c>
-      <c r="AU48">
-        <v>2.8</v>
-      </c>
-      <c r="AV48">
-        <v>2.08</v>
-      </c>
-      <c r="AW48">
-        <v>1.7</v>
-      </c>
-      <c r="AX48">
-        <v>1.39</v>
-      </c>
       <c r="AY48">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AZ48">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="BA48">
-        <v>1.72</v>
+        <v>2.85</v>
       </c>
       <c r="BB48">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BC48">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="BD48">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="BE48">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="BF48">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BG48">
         <v>0</v>
@@ -10565,7 +10565,7 @@
         <v>77</v>
       </c>
       <c r="C51" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D51" t="s">
         <v>134</v>
@@ -10604,133 +10604,133 @@
         <v>308</v>
       </c>
       <c r="P51">
-        <v>2.22</v>
+        <v>7.95</v>
       </c>
       <c r="Q51">
-        <v>2.76</v>
+        <v>4.7</v>
       </c>
       <c r="R51">
-        <v>3.48</v>
+        <v>1.33</v>
       </c>
       <c r="S51">
-        <v>3.04</v>
+        <v>7.13</v>
       </c>
       <c r="T51">
-        <v>1.8</v>
+        <v>2.65</v>
       </c>
       <c r="U51">
-        <v>4.53</v>
+        <v>1.74</v>
       </c>
       <c r="V51">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="W51">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="X51">
-        <v>3.48</v>
+        <v>2.15</v>
       </c>
       <c r="Y51">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="Z51">
-        <v>10</v>
+        <v>4.55</v>
       </c>
       <c r="AA51">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="AB51">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC51">
-        <v>1.53</v>
+        <v>1.16</v>
       </c>
       <c r="AD51">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="AE51">
-        <v>2.41</v>
+        <v>1.52</v>
       </c>
       <c r="AF51">
-        <v>1.45</v>
+        <v>2.18</v>
       </c>
       <c r="AG51">
-        <v>5.25</v>
+        <v>2.38</v>
       </c>
       <c r="AH51">
+        <v>1.47</v>
+      </c>
+      <c r="AI51">
+        <v>3.8</v>
+      </c>
+      <c r="AJ51">
+        <v>1.21</v>
+      </c>
+      <c r="AK51">
+        <v>1.9</v>
+      </c>
+      <c r="AL51">
+        <v>1.9</v>
+      </c>
+      <c r="AM51">
         <v>1.13</v>
       </c>
-      <c r="AI51">
-        <v>9.5</v>
-      </c>
-      <c r="AJ51">
-        <v>1.01</v>
-      </c>
-      <c r="AK51">
-        <v>2.04</v>
-      </c>
-      <c r="AL51">
-        <v>1.68</v>
-      </c>
-      <c r="AM51">
-        <v>1.34</v>
-      </c>
       <c r="AN51">
-        <v>1.52</v>
+        <v>1.05</v>
       </c>
       <c r="AO51">
         <v>0</v>
       </c>
       <c r="AP51">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AQ51">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AR51">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AS51">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AT51">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AU51">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AV51">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AW51">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AX51">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AY51">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ51">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BA51">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BB51">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BC51">
-        <v>2.53</v>
+        <v>1.75</v>
       </c>
       <c r="BD51">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="BE51">
-        <v>1.43</v>
+        <v>1.85</v>
       </c>
       <c r="BF51">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BG51">
         <v>0</v>
@@ -10750,7 +10750,7 @@
         <v>77</v>
       </c>
       <c r="C52" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="D52" t="s">
         <v>134</v>
@@ -10789,133 +10789,133 @@
         <v>308</v>
       </c>
       <c r="P52">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="Q52">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="R52">
-        <v>4.59</v>
+        <v>3.23</v>
       </c>
       <c r="S52">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="T52">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U52">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="V52">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W52">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X52">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Y52">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z52">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="AA52">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB52">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC52">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD52">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AE52">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF52">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG52">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AH52">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI52">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AJ52">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK52">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL52">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AM52">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN52">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AO52">
         <v>0</v>
       </c>
       <c r="AP52">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AQ52">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AR52">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AS52">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AT52">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AU52">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AV52">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AW52">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AX52">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AY52">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ52">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="BA52">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="BB52">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC52">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="BD52">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="BE52">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BF52">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG52">
         <v>0</v>
@@ -10935,10 +10935,10 @@
         <v>77</v>
       </c>
       <c r="C53" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="D53" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E53" t="s">
         <v>188</v>
@@ -10974,133 +10974,133 @@
         <v>308</v>
       </c>
       <c r="P53">
+        <v>2.22</v>
+      </c>
+      <c r="Q53">
+        <v>2.76</v>
+      </c>
+      <c r="R53">
+        <v>3.48</v>
+      </c>
+      <c r="S53">
+        <v>3.04</v>
+      </c>
+      <c r="T53">
+        <v>1.8</v>
+      </c>
+      <c r="U53">
+        <v>4.53</v>
+      </c>
+      <c r="V53">
+        <v>1.58</v>
+      </c>
+      <c r="W53">
+        <v>2.22</v>
+      </c>
+      <c r="X53">
+        <v>3.48</v>
+      </c>
+      <c r="Y53">
+        <v>1.22</v>
+      </c>
+      <c r="Z53">
+        <v>10</v>
+      </c>
+      <c r="AA53">
+        <v>1.02</v>
+      </c>
+      <c r="AB53">
+        <v>1.11</v>
+      </c>
+      <c r="AC53">
+        <v>1.53</v>
+      </c>
+      <c r="AD53">
+        <v>2.4</v>
+      </c>
+      <c r="AE53">
+        <v>2.41</v>
+      </c>
+      <c r="AF53">
+        <v>1.45</v>
+      </c>
+      <c r="AG53">
+        <v>5.25</v>
+      </c>
+      <c r="AH53">
+        <v>1.13</v>
+      </c>
+      <c r="AI53">
+        <v>9.5</v>
+      </c>
+      <c r="AJ53">
+        <v>1.01</v>
+      </c>
+      <c r="AK53">
+        <v>2.04</v>
+      </c>
+      <c r="AL53">
+        <v>1.68</v>
+      </c>
+      <c r="AM53">
+        <v>1.34</v>
+      </c>
+      <c r="AN53">
+        <v>1.52</v>
+      </c>
+      <c r="AO53">
+        <v>0</v>
+      </c>
+      <c r="AP53">
+        <v>1.4</v>
+      </c>
+      <c r="AQ53">
+        <v>1.68</v>
+      </c>
+      <c r="AR53">
+        <v>2.1</v>
+      </c>
+      <c r="AS53">
+        <v>2.75</v>
+      </c>
+      <c r="AT53">
+        <v>3.65</v>
+      </c>
+      <c r="AU53">
+        <v>2.65</v>
+      </c>
+      <c r="AV53">
+        <v>2.04</v>
+      </c>
+      <c r="AW53">
+        <v>1.64</v>
+      </c>
+      <c r="AX53">
         <v>1.38</v>
       </c>
-      <c r="Q53">
-        <v>5.48</v>
-      </c>
-      <c r="R53">
-        <v>7.06</v>
-      </c>
-      <c r="S53">
-        <v>0</v>
-      </c>
-      <c r="T53">
-        <v>0</v>
-      </c>
-      <c r="U53">
-        <v>0</v>
-      </c>
-      <c r="V53">
-        <v>0</v>
-      </c>
-      <c r="W53">
-        <v>0</v>
-      </c>
-      <c r="X53">
-        <v>0</v>
-      </c>
-      <c r="Y53">
-        <v>0</v>
-      </c>
-      <c r="Z53">
-        <v>0</v>
-      </c>
-      <c r="AA53">
-        <v>0</v>
-      </c>
-      <c r="AB53">
-        <v>0</v>
-      </c>
-      <c r="AC53">
-        <v>0</v>
-      </c>
-      <c r="AD53">
-        <v>0</v>
-      </c>
-      <c r="AE53">
-        <v>0</v>
-      </c>
-      <c r="AF53">
-        <v>0</v>
-      </c>
-      <c r="AG53">
-        <v>0</v>
-      </c>
-      <c r="AH53">
-        <v>0</v>
-      </c>
-      <c r="AI53">
-        <v>0</v>
-      </c>
-      <c r="AJ53">
-        <v>0</v>
-      </c>
-      <c r="AK53">
-        <v>0</v>
-      </c>
-      <c r="AL53">
-        <v>0</v>
-      </c>
-      <c r="AM53">
-        <v>0</v>
-      </c>
-      <c r="AN53">
-        <v>0</v>
-      </c>
-      <c r="AO53">
-        <v>0</v>
-      </c>
-      <c r="AP53">
-        <v>0</v>
-      </c>
-      <c r="AQ53">
-        <v>0</v>
-      </c>
-      <c r="AR53">
-        <v>0</v>
-      </c>
-      <c r="AS53">
-        <v>0</v>
-      </c>
-      <c r="AT53">
-        <v>0</v>
-      </c>
-      <c r="AU53">
-        <v>0</v>
-      </c>
-      <c r="AV53">
-        <v>0</v>
-      </c>
-      <c r="AW53">
-        <v>0</v>
-      </c>
-      <c r="AX53">
-        <v>0</v>
-      </c>
       <c r="AY53">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ53">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BA53">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BB53">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BC53">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="BD53">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BE53">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BF53">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BG53">
         <v>0</v>
@@ -11159,133 +11159,133 @@
         <v>308</v>
       </c>
       <c r="P54">
-        <v>2.04</v>
+        <v>1.8</v>
       </c>
       <c r="Q54">
-        <v>3.42</v>
+        <v>3.54</v>
       </c>
       <c r="R54">
-        <v>3.43</v>
+        <v>4.24</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T54">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U54">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="V54">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA54">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG54">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="AH54">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI54">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="AJ54">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK54">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL54">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AM54">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN54">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AO54">
         <v>0</v>
       </c>
       <c r="AP54">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AQ54">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AR54">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AS54">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AT54">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AU54">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AV54">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW54">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AX54">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AY54">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ54">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BA54">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="BB54">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC54">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD54">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE54">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF54">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG54">
         <v>0</v>
@@ -11305,7 +11305,7 @@
         <v>77</v>
       </c>
       <c r="C55" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D55" t="s">
         <v>134</v>
@@ -11344,133 +11344,133 @@
         <v>308</v>
       </c>
       <c r="P55">
-        <v>2</v>
+        <v>1.58</v>
       </c>
       <c r="Q55">
+        <v>4.33</v>
+      </c>
+      <c r="R55">
+        <v>4.92</v>
+      </c>
+      <c r="S55">
+        <v>1.91</v>
+      </c>
+      <c r="T55">
+        <v>2.4</v>
+      </c>
+      <c r="U55">
+        <v>5</v>
+      </c>
+      <c r="V55">
+        <v>1.24</v>
+      </c>
+      <c r="W55">
+        <v>3.7</v>
+      </c>
+      <c r="X55">
+        <v>2.25</v>
+      </c>
+      <c r="Y55">
+        <v>1.6</v>
+      </c>
+      <c r="Z55">
+        <v>5</v>
+      </c>
+      <c r="AA55">
+        <v>1.14</v>
+      </c>
+      <c r="AB55">
+        <v>1.02</v>
+      </c>
+      <c r="AC55">
+        <v>1.13</v>
+      </c>
+      <c r="AD55">
+        <v>4.95</v>
+      </c>
+      <c r="AE55">
+        <v>1.48</v>
+      </c>
+      <c r="AF55">
+        <v>2.4</v>
+      </c>
+      <c r="AG55">
+        <v>2.35</v>
+      </c>
+      <c r="AH55">
+        <v>1.59</v>
+      </c>
+      <c r="AI55">
+        <v>3.88</v>
+      </c>
+      <c r="AJ55">
+        <v>1.18</v>
+      </c>
+      <c r="AK55">
+        <v>1.5</v>
+      </c>
+      <c r="AL55">
+        <v>2.2</v>
+      </c>
+      <c r="AM55">
+        <v>1.17</v>
+      </c>
+      <c r="AN55">
+        <v>2.25</v>
+      </c>
+      <c r="AO55">
+        <v>0</v>
+      </c>
+      <c r="AP55">
+        <v>1.17</v>
+      </c>
+      <c r="AQ55">
+        <v>1.34</v>
+      </c>
+      <c r="AR55">
+        <v>1.85</v>
+      </c>
+      <c r="AS55">
+        <v>1.8</v>
+      </c>
+      <c r="AT55">
+        <v>2.67</v>
+      </c>
+      <c r="AU55">
+        <v>4</v>
+      </c>
+      <c r="AV55">
+        <v>2.78</v>
+      </c>
+      <c r="AW55">
+        <v>2.08</v>
+      </c>
+      <c r="AX55">
+        <v>1.67</v>
+      </c>
+      <c r="AY55">
+        <v>1.38</v>
+      </c>
+      <c r="AZ55">
+        <v>1.36</v>
+      </c>
+      <c r="BA55">
         <v>3.8</v>
       </c>
-      <c r="R55">
-        <v>3.23</v>
-      </c>
-      <c r="S55">
-        <v>0</v>
-      </c>
-      <c r="T55">
-        <v>0</v>
-      </c>
-      <c r="U55">
-        <v>0</v>
-      </c>
-      <c r="V55">
-        <v>0</v>
-      </c>
-      <c r="W55">
-        <v>0</v>
-      </c>
-      <c r="X55">
-        <v>0</v>
-      </c>
-      <c r="Y55">
-        <v>0</v>
-      </c>
-      <c r="Z55">
-        <v>0</v>
-      </c>
-      <c r="AA55">
-        <v>0</v>
-      </c>
-      <c r="AB55">
-        <v>0</v>
-      </c>
-      <c r="AC55">
-        <v>0</v>
-      </c>
-      <c r="AD55">
-        <v>0</v>
-      </c>
-      <c r="AE55">
-        <v>0</v>
-      </c>
-      <c r="AF55">
-        <v>0</v>
-      </c>
-      <c r="AG55">
-        <v>0</v>
-      </c>
-      <c r="AH55">
-        <v>0</v>
-      </c>
-      <c r="AI55">
-        <v>0</v>
-      </c>
-      <c r="AJ55">
-        <v>0</v>
-      </c>
-      <c r="AK55">
-        <v>0</v>
-      </c>
-      <c r="AL55">
-        <v>0</v>
-      </c>
-      <c r="AM55">
-        <v>0</v>
-      </c>
-      <c r="AN55">
-        <v>0</v>
-      </c>
-      <c r="AO55">
-        <v>0</v>
-      </c>
-      <c r="AP55">
-        <v>0</v>
-      </c>
-      <c r="AQ55">
-        <v>0</v>
-      </c>
-      <c r="AR55">
-        <v>0</v>
-      </c>
-      <c r="AS55">
-        <v>0</v>
-      </c>
-      <c r="AT55">
-        <v>0</v>
-      </c>
-      <c r="AU55">
-        <v>0</v>
-      </c>
-      <c r="AV55">
-        <v>0</v>
-      </c>
-      <c r="AW55">
-        <v>0</v>
-      </c>
-      <c r="AX55">
-        <v>0</v>
-      </c>
-      <c r="AY55">
-        <v>0</v>
-      </c>
-      <c r="AZ55">
-        <v>0</v>
-      </c>
-      <c r="BA55">
-        <v>0</v>
-      </c>
       <c r="BB55">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC55">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BD55">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BE55">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BF55">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG55">
         <v>0</v>
@@ -11490,7 +11490,7 @@
         <v>77</v>
       </c>
       <c r="C56" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D56" t="s">
         <v>134</v>
@@ -11529,133 +11529,133 @@
         <v>308</v>
       </c>
       <c r="P56">
-        <v>1.58</v>
+        <v>2.61</v>
       </c>
       <c r="Q56">
-        <v>4.33</v>
+        <v>3.34</v>
       </c>
       <c r="R56">
-        <v>4.92</v>
+        <v>2.52</v>
       </c>
       <c r="S56">
-        <v>1.91</v>
+        <v>3.7</v>
       </c>
       <c r="T56">
-        <v>2.4</v>
+        <v>2.01</v>
       </c>
       <c r="U56">
-        <v>5</v>
+        <v>3.01</v>
       </c>
       <c r="V56">
+        <v>1.44</v>
+      </c>
+      <c r="W56">
+        <v>2.62</v>
+      </c>
+      <c r="X56">
+        <v>3.16</v>
+      </c>
+      <c r="Y56">
+        <v>1.3</v>
+      </c>
+      <c r="Z56">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AA56">
+        <v>1.01</v>
+      </c>
+      <c r="AB56">
+        <v>1.01</v>
+      </c>
+      <c r="AC56">
+        <v>1.39</v>
+      </c>
+      <c r="AD56">
+        <v>2.81</v>
+      </c>
+      <c r="AE56">
+        <v>2.19</v>
+      </c>
+      <c r="AF56">
+        <v>1.64</v>
+      </c>
+      <c r="AG56">
+        <v>4.02</v>
+      </c>
+      <c r="AH56">
+        <v>1.17</v>
+      </c>
+      <c r="AI56">
+        <v>8.5</v>
+      </c>
+      <c r="AJ56">
+        <v>1.04</v>
+      </c>
+      <c r="AK56">
+        <v>1.87</v>
+      </c>
+      <c r="AL56">
+        <v>1.83</v>
+      </c>
+      <c r="AM56">
+        <v>1.3</v>
+      </c>
+      <c r="AN56">
+        <v>1.37</v>
+      </c>
+      <c r="AO56">
+        <v>0</v>
+      </c>
+      <c r="AP56">
+        <v>1.27</v>
+      </c>
+      <c r="AQ56">
+        <v>1.54</v>
+      </c>
+      <c r="AR56">
+        <v>1.92</v>
+      </c>
+      <c r="AS56">
+        <v>2.46</v>
+      </c>
+      <c r="AT56">
+        <v>3.35</v>
+      </c>
+      <c r="AU56">
+        <v>3.14</v>
+      </c>
+      <c r="AV56">
+        <v>2.27</v>
+      </c>
+      <c r="AW56">
+        <v>1.79</v>
+      </c>
+      <c r="AX56">
+        <v>1.46</v>
+      </c>
+      <c r="AY56">
         <v>1.24</v>
       </c>
-      <c r="W56">
-        <v>3.7</v>
-      </c>
-      <c r="X56">
-        <v>2.25</v>
-      </c>
-      <c r="Y56">
-        <v>1.6</v>
-      </c>
-      <c r="Z56">
-        <v>5</v>
-      </c>
-      <c r="AA56">
-        <v>1.14</v>
-      </c>
-      <c r="AB56">
-        <v>1.02</v>
-      </c>
-      <c r="AC56">
-        <v>1.13</v>
-      </c>
-      <c r="AD56">
-        <v>4.95</v>
-      </c>
-      <c r="AE56">
-        <v>1.48</v>
-      </c>
-      <c r="AF56">
-        <v>2.4</v>
-      </c>
-      <c r="AG56">
-        <v>2.35</v>
-      </c>
-      <c r="AH56">
-        <v>1.59</v>
-      </c>
-      <c r="AI56">
-        <v>3.88</v>
-      </c>
-      <c r="AJ56">
-        <v>1.18</v>
-      </c>
-      <c r="AK56">
-        <v>1.5</v>
-      </c>
-      <c r="AL56">
-        <v>2.2</v>
-      </c>
-      <c r="AM56">
-        <v>1.17</v>
-      </c>
-      <c r="AN56">
-        <v>2.25</v>
-      </c>
-      <c r="AO56">
-        <v>0</v>
-      </c>
-      <c r="AP56">
-        <v>1.17</v>
-      </c>
-      <c r="AQ56">
-        <v>1.34</v>
-      </c>
-      <c r="AR56">
-        <v>1.85</v>
-      </c>
-      <c r="AS56">
-        <v>1.8</v>
-      </c>
-      <c r="AT56">
-        <v>2.67</v>
-      </c>
-      <c r="AU56">
-        <v>4</v>
-      </c>
-      <c r="AV56">
-        <v>2.78</v>
-      </c>
-      <c r="AW56">
-        <v>2.08</v>
-      </c>
-      <c r="AX56">
+      <c r="AZ56">
+        <v>2.92</v>
+      </c>
+      <c r="BA56">
         <v>1.67</v>
       </c>
-      <c r="AY56">
-        <v>1.38</v>
-      </c>
-      <c r="AZ56">
-        <v>1.36</v>
-      </c>
-      <c r="BA56">
-        <v>3.8</v>
-      </c>
       <c r="BB56">
-        <v>1.11</v>
+        <v>1.27</v>
       </c>
       <c r="BC56">
-        <v>1.74</v>
+        <v>2.36</v>
       </c>
       <c r="BD56">
-        <v>5.2</v>
+        <v>3.35</v>
       </c>
       <c r="BE56">
-        <v>2.02</v>
+        <v>1.51</v>
       </c>
       <c r="BF56">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="BG56">
         <v>0</v>
@@ -11675,7 +11675,7 @@
         <v>77</v>
       </c>
       <c r="C57" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D57" t="s">
         <v>134</v>
@@ -11714,133 +11714,133 @@
         <v>308</v>
       </c>
       <c r="P57">
-        <v>2.61</v>
+        <v>2.04</v>
       </c>
       <c r="Q57">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="R57">
-        <v>2.52</v>
+        <v>3.43</v>
       </c>
       <c r="S57">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="T57">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="U57">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="V57">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W57">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="X57">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Y57">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z57">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA57">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB57">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC57">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AD57">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AE57">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AF57">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG57">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="AH57">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AI57">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AJ57">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK57">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AL57">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM57">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN57">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AO57">
         <v>0</v>
       </c>
       <c r="AP57">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ57">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AR57">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AS57">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AT57">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AU57">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AV57">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AW57">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AX57">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AY57">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AZ57">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="BA57">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BB57">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BC57">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="BD57">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BE57">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="BF57">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG57">
         <v>0</v>
@@ -11863,7 +11863,7 @@
         <v>120</v>
       </c>
       <c r="D58" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E58" t="s">
         <v>193</v>
@@ -11899,133 +11899,133 @@
         <v>308</v>
       </c>
       <c r="P58">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="Q58">
-        <v>3.54</v>
+        <v>3.67</v>
       </c>
       <c r="R58">
-        <v>4.24</v>
+        <v>4.35</v>
       </c>
       <c r="S58">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="T58">
-        <v>2.07</v>
+        <v>2.17</v>
       </c>
       <c r="U58">
-        <v>5.08</v>
+        <v>5.23</v>
       </c>
       <c r="V58">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W58">
+        <v>2.89</v>
+      </c>
+      <c r="X58">
         <v>2.69</v>
       </c>
-      <c r="X58">
-        <v>2.9</v>
-      </c>
       <c r="Y58">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="Z58">
-        <v>7.5</v>
+        <v>6.45</v>
       </c>
       <c r="AA58">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AB58">
         <v>1.06</v>
       </c>
       <c r="AC58">
+        <v>1.21</v>
+      </c>
+      <c r="AD58">
+        <v>3.44</v>
+      </c>
+      <c r="AE58">
+        <v>1.84</v>
+      </c>
+      <c r="AF58">
+        <v>1.94</v>
+      </c>
+      <c r="AG58">
+        <v>3.07</v>
+      </c>
+      <c r="AH58">
+        <v>1.36</v>
+      </c>
+      <c r="AI58">
+        <v>5.84</v>
+      </c>
+      <c r="AJ58">
+        <v>1.13</v>
+      </c>
+      <c r="AK58">
+        <v>1.75</v>
+      </c>
+      <c r="AL58">
+        <v>1.95</v>
+      </c>
+      <c r="AM58">
+        <v>1.25</v>
+      </c>
+      <c r="AN58">
+        <v>2.09</v>
+      </c>
+      <c r="AO58">
+        <v>0</v>
+      </c>
+      <c r="AP58">
+        <v>0</v>
+      </c>
+      <c r="AQ58">
         <v>1.28</v>
       </c>
-      <c r="AD58">
-        <v>3.08</v>
-      </c>
-      <c r="AE58">
-        <v>1.88</v>
-      </c>
-      <c r="AF58">
-        <v>1.88</v>
-      </c>
-      <c r="AG58">
-        <v>3.51</v>
-      </c>
-      <c r="AH58">
-        <v>1.24</v>
-      </c>
-      <c r="AI58">
-        <v>6.65</v>
-      </c>
-      <c r="AJ58">
-        <v>1.11</v>
-      </c>
-      <c r="AK58">
-        <v>1.86</v>
-      </c>
-      <c r="AL58">
-        <v>1.84</v>
-      </c>
-      <c r="AM58">
-        <v>1.27</v>
-      </c>
-      <c r="AN58">
+      <c r="AR58">
+        <v>1.48</v>
+      </c>
+      <c r="AS58">
+        <v>1.75</v>
+      </c>
+      <c r="AT58">
+        <v>2.12</v>
+      </c>
+      <c r="AU58">
+        <v>0</v>
+      </c>
+      <c r="AV58">
+        <v>3.25</v>
+      </c>
+      <c r="AW58">
+        <v>2.43</v>
+      </c>
+      <c r="AX58">
         <v>1.94</v>
       </c>
-      <c r="AO58">
-        <v>0</v>
-      </c>
-      <c r="AP58">
-        <v>1.13</v>
-      </c>
-      <c r="AQ58">
-        <v>1.31</v>
-      </c>
-      <c r="AR58">
-        <v>1.59</v>
-      </c>
-      <c r="AS58">
-        <v>1.95</v>
-      </c>
-      <c r="AT58">
-        <v>2.48</v>
-      </c>
-      <c r="AU58">
-        <v>4.5</v>
-      </c>
-      <c r="AV58">
-        <v>2.95</v>
-      </c>
-      <c r="AW58">
-        <v>2.2</v>
-      </c>
-      <c r="AX58">
-        <v>1.76</v>
-      </c>
       <c r="AY58">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="AZ58">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="BA58">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="BB58">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="BC58">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="BD58">
-        <v>3.58</v>
+        <v>3.98</v>
       </c>
       <c r="BE58">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="BF58">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="BG58">
         <v>0</v>
@@ -12048,7 +12048,7 @@
         <v>121</v>
       </c>
       <c r="D59" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E59" t="s">
         <v>194</v>
@@ -12084,133 +12084,133 @@
         <v>308</v>
       </c>
       <c r="P59">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="Q59">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="R59">
-        <v>2.54</v>
+        <v>3.03</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="AE59">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AF59">
-        <v>1.9</v>
+        <v>2.16</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH59">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI59">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL59">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AM59">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN59">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AO59">
         <v>0</v>
       </c>
       <c r="AP59">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ59">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR59">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AS59">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AT59">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AU59">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AV59">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AW59">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AX59">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AY59">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ59">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BA59">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="BB59">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC59">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BD59">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="BE59">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BF59">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG59">
         <v>0</v>
@@ -12230,10 +12230,10 @@
         <v>77</v>
       </c>
       <c r="C60" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="D60" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E60" t="s">
         <v>195</v>
@@ -12269,133 +12269,133 @@
         <v>308</v>
       </c>
       <c r="P60">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="Q60">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="R60">
-        <v>4.22</v>
+        <v>4.59</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X60">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AE60">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AF60">
-        <v>1.92</v>
+        <v>1.65</v>
       </c>
       <c r="AG60">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AH60">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI60">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ60">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK60">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL60">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM60">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN60">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AO60">
         <v>0</v>
       </c>
       <c r="AP60">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ60">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AR60">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS60">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AT60">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AU60">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AV60">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AW60">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AX60">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AY60">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ60">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BA60">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="BB60">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC60">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BD60">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="BE60">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BF60">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG60">
         <v>0</v>
@@ -12415,10 +12415,10 @@
         <v>77</v>
       </c>
       <c r="C61" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="D61" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E61" t="s">
         <v>196</v>
@@ -12454,22 +12454,22 @@
         <v>308</v>
       </c>
       <c r="P61">
-        <v>7.95</v>
+        <v>1.38</v>
       </c>
       <c r="Q61">
-        <v>4.7</v>
+        <v>5.48</v>
       </c>
       <c r="R61">
-        <v>1.33</v>
+        <v>7.06</v>
       </c>
       <c r="S61">
-        <v>7.13</v>
+        <v>0</v>
       </c>
       <c r="T61">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U61">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="V61">
         <v>0</v>
@@ -12478,55 +12478,55 @@
         <v>0</v>
       </c>
       <c r="X61">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y61">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z61">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AA61">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AB61">
         <v>0</v>
       </c>
       <c r="AC61">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD61">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AE61">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AF61">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AG61">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH61">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI61">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AJ61">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK61">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL61">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AM61">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AN61">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AO61">
         <v>0</v>
@@ -12571,13 +12571,13 @@
         <v>0</v>
       </c>
       <c r="BC61">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BD61">
         <v>0</v>
       </c>
       <c r="BE61">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF61">
         <v>0</v>
@@ -12600,10 +12600,10 @@
         <v>77</v>
       </c>
       <c r="C62" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D62" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E62" t="s">
         <v>197</v>
@@ -12639,133 +12639,133 @@
         <v>308</v>
       </c>
       <c r="P62">
-        <v>2.17</v>
+        <v>2.81</v>
       </c>
       <c r="Q62">
-        <v>3.54</v>
+        <v>3.3</v>
       </c>
       <c r="R62">
-        <v>3.03</v>
+        <v>2.41</v>
       </c>
       <c r="S62">
-        <v>2.5</v>
+        <v>3.23</v>
       </c>
       <c r="T62">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="U62">
-        <v>3.58</v>
+        <v>2.83</v>
       </c>
       <c r="V62">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="W62">
-        <v>3.16</v>
+        <v>2.95</v>
       </c>
       <c r="X62">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="Y62">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="Z62">
-        <v>5.55</v>
+        <v>7.1</v>
       </c>
       <c r="AA62">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AB62">
         <v>1.01</v>
       </c>
       <c r="AC62">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AD62">
-        <v>4.41</v>
+        <v>3.18</v>
       </c>
       <c r="AE62">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AF62">
-        <v>2.16</v>
+        <v>1.84</v>
       </c>
       <c r="AG62">
-        <v>2.63</v>
+        <v>3.41</v>
       </c>
       <c r="AH62">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AI62">
-        <v>4.55</v>
+        <v>5.75</v>
       </c>
       <c r="AJ62">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AK62">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AL62">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="AM62">
+        <v>1.28</v>
+      </c>
+      <c r="AN62">
+        <v>1.37</v>
+      </c>
+      <c r="AO62">
+        <v>0</v>
+      </c>
+      <c r="AP62">
+        <v>1.26</v>
+      </c>
+      <c r="AQ62">
+        <v>1.46</v>
+      </c>
+      <c r="AR62">
+        <v>1.75</v>
+      </c>
+      <c r="AS62">
+        <v>2.18</v>
+      </c>
+      <c r="AT62">
+        <v>2.8</v>
+      </c>
+      <c r="AU62">
+        <v>3.4</v>
+      </c>
+      <c r="AV62">
+        <v>2.5</v>
+      </c>
+      <c r="AW62">
+        <v>1.93</v>
+      </c>
+      <c r="AX62">
+        <v>1.58</v>
+      </c>
+      <c r="AY62">
+        <v>1.37</v>
+      </c>
+      <c r="AZ62">
+        <v>2.12</v>
+      </c>
+      <c r="BA62">
+        <v>1.91</v>
+      </c>
+      <c r="BB62">
         <v>1.25</v>
       </c>
-      <c r="AN62">
-        <v>1.61</v>
-      </c>
-      <c r="AO62">
-        <v>0</v>
-      </c>
-      <c r="AP62">
-        <v>1.18</v>
-      </c>
-      <c r="AQ62">
-        <v>1.34</v>
-      </c>
-      <c r="AR62">
-        <v>1.58</v>
-      </c>
-      <c r="AS62">
-        <v>2.05</v>
-      </c>
-      <c r="AT62">
-        <v>2.45</v>
-      </c>
-      <c r="AU62">
-        <v>3.95</v>
-      </c>
-      <c r="AV62">
-        <v>2.85</v>
-      </c>
-      <c r="AW62">
+      <c r="BC62">
         <v>2.14</v>
       </c>
-      <c r="AX62">
-        <v>1.7</v>
-      </c>
-      <c r="AY62">
-        <v>1.45</v>
-      </c>
-      <c r="AZ62">
-        <v>1.76</v>
-      </c>
-      <c r="BA62">
-        <v>2.33</v>
-      </c>
-      <c r="BB62">
+      <c r="BD62">
+        <v>3.66</v>
+      </c>
+      <c r="BE62">
+        <v>1.66</v>
+      </c>
+      <c r="BF62">
         <v>1.14</v>
-      </c>
-      <c r="BC62">
-        <v>1.87</v>
-      </c>
-      <c r="BD62">
-        <v>4.45</v>
-      </c>
-      <c r="BE62">
-        <v>1.87</v>
-      </c>
-      <c r="BF62">
-        <v>1.22</v>
       </c>
       <c r="BG62">
         <v>0</v>
@@ -12824,79 +12824,79 @@
         <v>308</v>
       </c>
       <c r="P63">
-        <v>2.93</v>
+        <v>2.42</v>
       </c>
       <c r="Q63">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="R63">
-        <v>2.29</v>
+        <v>2.65</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AE63">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AF63">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AH63">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI63">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AJ63">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK63">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL63">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AM63">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN63">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO63">
         <v>0</v>
@@ -12905,52 +12905,52 @@
         <v>0</v>
       </c>
       <c r="AQ63">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AR63">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AS63">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AT63">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AU63">
         <v>0</v>
       </c>
       <c r="AV63">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AW63">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AX63">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AY63">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AZ63">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BA63">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BB63">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC63">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="BD63">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="BE63">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BF63">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG63">
         <v>0</v>
@@ -13018,13 +13018,13 @@
         <v>7.55</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="T64">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U64">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="V64">
         <v>0</v>
@@ -13033,10 +13033,10 @@
         <v>0</v>
       </c>
       <c r="X64">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -13048,40 +13048,40 @@
         <v>0</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD64">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AE64">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AF64">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG64">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH64">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI64">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AJ64">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK64">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL64">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AM64">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN64">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AO64">
         <v>0</v>
@@ -13126,13 +13126,13 @@
         <v>0</v>
       </c>
       <c r="BC64">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BD64">
         <v>0</v>
       </c>
       <c r="BE64">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BF64">
         <v>0</v>
@@ -13388,13 +13388,13 @@
         <v>2.21</v>
       </c>
       <c r="S66">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T66">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U66">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V66">
         <v>0</v>
@@ -13403,10 +13403,10 @@
         <v>0</v>
       </c>
       <c r="X66">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y66">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -13418,40 +13418,40 @@
         <v>0</v>
       </c>
       <c r="AC66">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD66">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE66">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF66">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG66">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH66">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI66">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AJ66">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK66">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL66">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM66">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN66">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AO66">
         <v>0</v>
@@ -13496,13 +13496,13 @@
         <v>0</v>
       </c>
       <c r="BC66">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BD66">
         <v>0</v>
       </c>
       <c r="BE66">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF66">
         <v>0</v>
@@ -13710,13 +13710,13 @@
         <v>80</v>
       </c>
       <c r="C68" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="D68" t="s">
         <v>134</v>
       </c>
       <c r="E68" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="F68" t="s">
         <v>288</v>
@@ -13749,13 +13749,13 @@
         <v>308</v>
       </c>
       <c r="P68">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Q68">
-        <v>5.09</v>
+        <v>0</v>
       </c>
       <c r="R68">
-        <v>6.37</v>
+        <v>0</v>
       </c>
       <c r="S68">
         <v>0</v>
@@ -13895,13 +13895,13 @@
         <v>80</v>
       </c>
       <c r="C69" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="D69" t="s">
         <v>134</v>
       </c>
       <c r="E69" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F69" t="s">
         <v>289</v>
@@ -14080,13 +14080,13 @@
         <v>80</v>
       </c>
       <c r="C70" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D70" t="s">
         <v>134</v>
       </c>
       <c r="E70" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="F70" t="s">
         <v>290</v>
@@ -14119,13 +14119,13 @@
         <v>308</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>5.09</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>6.37</v>
       </c>
       <c r="S70">
         <v>0</v>
@@ -14265,7 +14265,7 @@
         <v>81</v>
       </c>
       <c r="C71" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D71" t="s">
         <v>134</v>
@@ -14635,7 +14635,7 @@
         <v>82</v>
       </c>
       <c r="C73" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D73" t="s">
         <v>134</v>
@@ -15005,7 +15005,7 @@
         <v>83</v>
       </c>
       <c r="C75" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D75" t="s">
         <v>134</v>
@@ -15560,7 +15560,7 @@
         <v>85</v>
       </c>
       <c r="C78" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D78" t="s">
         <v>134</v>
@@ -15784,13 +15784,13 @@
         <v>308</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q79">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R79">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="S79">
         <v>0</v>
@@ -15969,133 +15969,133 @@
         <v>308</v>
       </c>
       <c r="P80">
+        <v>1.8</v>
+      </c>
+      <c r="Q80">
+        <v>3.35</v>
+      </c>
+      <c r="R80">
+        <v>4.5</v>
+      </c>
+      <c r="S80">
+        <v>2.38</v>
+      </c>
+      <c r="T80">
+        <v>2</v>
+      </c>
+      <c r="U80">
+        <v>5.57</v>
+      </c>
+      <c r="V80">
+        <v>1.44</v>
+      </c>
+      <c r="W80">
+        <v>2.61</v>
+      </c>
+      <c r="X80">
+        <v>3.16</v>
+      </c>
+      <c r="Y80">
+        <v>1.3</v>
+      </c>
+      <c r="Z80">
+        <v>8.1</v>
+      </c>
+      <c r="AA80">
+        <v>1.02</v>
+      </c>
+      <c r="AB80">
+        <v>1.08</v>
+      </c>
+      <c r="AC80">
+        <v>1.36</v>
+      </c>
+      <c r="AD80">
+        <v>2.7</v>
+      </c>
+      <c r="AE80">
+        <v>2.23</v>
+      </c>
+      <c r="AF80">
+        <v>1.65</v>
+      </c>
+      <c r="AG80">
+        <v>4.2</v>
+      </c>
+      <c r="AH80">
+        <v>1.21</v>
+      </c>
+      <c r="AI80">
+        <v>7.9</v>
+      </c>
+      <c r="AJ80">
+        <v>1.04</v>
+      </c>
+      <c r="AK80">
         <v>2.03</v>
       </c>
-      <c r="Q80">
-        <v>3.24</v>
-      </c>
-      <c r="R80">
-        <v>3.67</v>
-      </c>
-      <c r="S80">
-        <v>0</v>
-      </c>
-      <c r="T80">
-        <v>0</v>
-      </c>
-      <c r="U80">
-        <v>0</v>
-      </c>
-      <c r="V80">
-        <v>0</v>
-      </c>
-      <c r="W80">
-        <v>0</v>
-      </c>
-      <c r="X80">
-        <v>0</v>
-      </c>
-      <c r="Y80">
-        <v>0</v>
-      </c>
-      <c r="Z80">
-        <v>0</v>
-      </c>
-      <c r="AA80">
-        <v>0</v>
-      </c>
-      <c r="AB80">
-        <v>0</v>
-      </c>
-      <c r="AC80">
-        <v>0</v>
-      </c>
-      <c r="AD80">
-        <v>0</v>
-      </c>
-      <c r="AE80">
-        <v>0</v>
-      </c>
-      <c r="AF80">
-        <v>0</v>
-      </c>
-      <c r="AG80">
-        <v>0</v>
-      </c>
-      <c r="AH80">
-        <v>0</v>
-      </c>
-      <c r="AI80">
-        <v>0</v>
-      </c>
-      <c r="AJ80">
-        <v>0</v>
-      </c>
-      <c r="AK80">
-        <v>0</v>
-      </c>
       <c r="AL80">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AM80">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN80">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AO80">
         <v>0</v>
       </c>
       <c r="AP80">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AQ80">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR80">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AS80">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AT80">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AU80">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AV80">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW80">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AX80">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY80">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ80">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="BA80">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="BB80">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC80">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="BD80">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE80">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF80">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG80">
         <v>0</v>
@@ -16154,13 +16154,13 @@
         <v>308</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="S81">
         <v>0</v>
@@ -16300,7 +16300,7 @@
         <v>87</v>
       </c>
       <c r="C82" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D82" t="s">
         <v>136</v>
@@ -16339,13 +16339,13 @@
         <v>308</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="S82">
         <v>0</v>
@@ -16384,10 +16384,10 @@
         <v>0</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG82">
         <v>0</v>
@@ -16485,7 +16485,7 @@
         <v>87</v>
       </c>
       <c r="C83" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D83" t="s">
         <v>136</v>
@@ -16524,79 +16524,79 @@
         <v>308</v>
       </c>
       <c r="P83">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q83">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R83">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S83">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T83">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="U83">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="V83">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W83">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="X83">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Y83">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z83">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB83">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC83">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD83">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG83">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AH83">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI83">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AJ83">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK83">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AL83">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AM83">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN83">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AO83">
         <v>0</v>
@@ -16638,19 +16638,19 @@
         <v>0</v>
       </c>
       <c r="BB83">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC83">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="BD83">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="BE83">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF83">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG83">
         <v>0</v>
@@ -16709,79 +16709,79 @@
         <v>308</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S84">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="T84">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U84">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="V84">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W84">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="X84">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y84">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z84">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AA84">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC84">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD84">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AE84">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AF84">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG84">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AH84">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI84">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AJ84">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK84">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AL84">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AM84">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN84">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AO84">
         <v>0</v>
@@ -16823,19 +16823,19 @@
         <v>0</v>
       </c>
       <c r="BB84">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BC84">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BD84">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="BE84">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BF84">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BG84">
         <v>0</v>
@@ -16903,103 +16903,103 @@
         <v>3.86</v>
       </c>
       <c r="S85">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="T85">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U85">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V85">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W85">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="X85">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Y85">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z85">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA85">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB85">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC85">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AD85">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AE85">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AF85">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AG85">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AH85">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI85">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AJ85">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK85">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL85">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AM85">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN85">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AO85">
         <v>0</v>
       </c>
       <c r="AP85">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ85">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR85">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AS85">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AT85">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AU85">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AV85">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW85">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX85">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AY85">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AZ85">
         <v>0</v>
@@ -17008,19 +17008,19 @@
         <v>0</v>
       </c>
       <c r="BB85">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BC85">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BD85">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BE85">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="BF85">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BG85">
         <v>0</v>
@@ -17040,7 +17040,7 @@
         <v>89</v>
       </c>
       <c r="C86" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D86" t="s">
         <v>136</v>
@@ -17079,133 +17079,133 @@
         <v>308</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S86">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T86">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="U86">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="V86">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W86">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="X86">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Y86">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z86">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA86">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD86">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG86">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="AH86">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI86">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AJ86">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK86">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL86">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AM86">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN86">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AO86">
         <v>0</v>
       </c>
       <c r="AP86">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AQ86">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AR86">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AS86">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AT86">
         <v>0</v>
       </c>
       <c r="AU86">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AV86">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AW86">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AX86">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AY86">
         <v>0</v>
       </c>
       <c r="AZ86">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BA86">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="BB86">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BC86">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="BD86">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BE86">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BF86">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG86">
         <v>0</v>
@@ -17225,7 +17225,7 @@
         <v>89</v>
       </c>
       <c r="C87" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D87" t="s">
         <v>136</v>
@@ -17264,13 +17264,13 @@
         <v>308</v>
       </c>
       <c r="P87">
-        <v>2.15</v>
+        <v>1.82</v>
       </c>
       <c r="Q87">
-        <v>2.8</v>
+        <v>3.38</v>
       </c>
       <c r="R87">
-        <v>3.8</v>
+        <v>4.01</v>
       </c>
       <c r="S87">
         <v>0</v>

--- a/jogos_2026-05-04.xlsx
+++ b/jogos_2026-05-04.xlsx
@@ -301,78 +301,78 @@
     <t>Croatia Druga HNL</t>
   </si>
   <si>
+    <t>Russia FNL</t>
+  </si>
+  <si>
+    <t>Uzbekistan Uzbekistan Super League</t>
+  </si>
+  <si>
     <t>Serbia Prva Liga</t>
   </si>
   <si>
-    <t>Russia FNL</t>
+    <t>India Indian Super League</t>
+  </si>
+  <si>
+    <t>Egypt Egyptian Premier League</t>
+  </si>
+  <si>
+    <t>England Premier League</t>
   </si>
   <si>
     <t>Oman Professional League</t>
   </si>
   <si>
-    <t>Uzbekistan Uzbekistan Super League</t>
-  </si>
-  <si>
-    <t>England Premier League</t>
-  </si>
-  <si>
-    <t>India Indian Super League</t>
-  </si>
-  <si>
-    <t>Egypt Egyptian Premier League</t>
-  </si>
-  <si>
     <t>Romania Liga I</t>
   </si>
   <si>
+    <t>Serbia SuperLiga</t>
+  </si>
+  <si>
     <t>Tunisia Ligue 1</t>
   </si>
   <si>
-    <t>Serbia SuperLiga</t>
-  </si>
-  <si>
     <t>Azerbaijan Premyer Liqası</t>
   </si>
   <si>
+    <t>Jordan Jordanian Pro League</t>
+  </si>
+  <si>
     <t>Republic of Ireland Premier Division</t>
   </si>
   <si>
+    <t>Poland 1. Liga</t>
+  </si>
+  <si>
+    <t>Republic of Ireland First Division</t>
+  </si>
+  <si>
+    <t>Croatia Prva HNL</t>
+  </si>
+  <si>
     <t>Morocco Botola Pro</t>
   </si>
   <si>
-    <t>Republic of Ireland First Division</t>
-  </si>
-  <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
-    <t>Croatia Prva HNL</t>
-  </si>
-  <si>
-    <t>Jordan Jordanian Pro League</t>
-  </si>
-  <si>
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
+    <t>Austria Bundesliga</t>
+  </si>
+  <si>
     <t>Italy Serie A</t>
   </si>
   <si>
-    <t>Austria Bundesliga</t>
-  </si>
-  <si>
     <t>Scotland Premiership</t>
   </si>
   <si>
     <t>Algeria Ligue 1</t>
   </si>
   <si>
+    <t>Portugal LigaPro</t>
+  </si>
+  <si>
     <t>Israel Israeli Premier League</t>
   </si>
   <si>
-    <t>Portugal LigaPro</t>
-  </si>
-  <si>
     <t>Denmark Superliga</t>
   </si>
   <si>
@@ -403,12 +403,12 @@
     <t>Portugal Liga NOS</t>
   </si>
   <si>
+    <t>Brazil Serie B</t>
+  </si>
+  <si>
     <t>Chile Primera B</t>
   </si>
   <si>
-    <t>Brazil Serie B</t>
-  </si>
-  <si>
     <t>Brazil Serie C</t>
   </si>
   <si>
@@ -427,199 +427,202 @@
     <t>2026</t>
   </si>
   <si>
+    <t>PSM</t>
+  </si>
+  <si>
     <t>Persib</t>
   </si>
   <si>
-    <t>PSM</t>
-  </si>
-  <si>
     <t>Welayta Dicha</t>
   </si>
   <si>
     <t>Albirex Niigata S</t>
   </si>
   <si>
+    <t>Aston Villa Ladies</t>
+  </si>
+  <si>
     <t>Persijap</t>
   </si>
   <si>
-    <t>Aston Villa Ladies</t>
+    <t>Mekelakeya</t>
   </si>
   <si>
     <t>Awassa Kenema</t>
   </si>
   <si>
-    <t>Mekelakeya</t>
-  </si>
-  <si>
     <t>Dugopolje</t>
   </si>
   <si>
+    <t>Ural</t>
+  </si>
+  <si>
+    <t>Xorazm</t>
+  </si>
+  <si>
+    <t>Lokomotiv</t>
+  </si>
+  <si>
     <t>Stepojevac Vaga</t>
   </si>
   <si>
-    <t>Ural</t>
+    <t>Odisha FC</t>
+  </si>
+  <si>
+    <t>OFK Vršac</t>
+  </si>
+  <si>
+    <t>Pharco</t>
+  </si>
+  <si>
+    <t>Chelsea</t>
   </si>
   <si>
     <t>Al Khabourah</t>
   </si>
   <si>
-    <t>Xorazm</t>
-  </si>
-  <si>
-    <t>Chelsea</t>
-  </si>
-  <si>
-    <t>Odisha FC</t>
-  </si>
-  <si>
-    <t>Pharco</t>
-  </si>
-  <si>
-    <t>Lokomotiv</t>
-  </si>
-  <si>
-    <t>OFK Vršac</t>
-  </si>
-  <si>
     <t>Unirea Slobozia</t>
   </si>
   <si>
+    <t>Radnik Surdulica</t>
+  </si>
+  <si>
     <t>Jeunesse Sportive Omrane</t>
   </si>
   <si>
     <t>CA Bizertin</t>
   </si>
   <si>
+    <t>Nasaf</t>
+  </si>
+  <si>
     <t>Zarzis</t>
   </si>
   <si>
     <t>Monastir</t>
   </si>
   <si>
-    <t>Radnik Surdulica</t>
-  </si>
-  <si>
-    <t>Nasaf</t>
-  </si>
-  <si>
     <t>Al Nasr</t>
   </si>
   <si>
     <t>Qarabağ</t>
   </si>
   <si>
+    <t>Al Jazeera</t>
+  </si>
+  <si>
+    <t>Sligo Rovers</t>
+  </si>
+  <si>
+    <t>Derry City</t>
+  </si>
+  <si>
     <t>Shamrock Rovers</t>
   </si>
   <si>
+    <t>Polonia Bytom</t>
+  </si>
+  <si>
+    <t>Finn Harps</t>
+  </si>
+  <si>
+    <t>Cobh Ramblers</t>
+  </si>
+  <si>
+    <t>Bohemians</t>
+  </si>
+  <si>
+    <t>Waterford</t>
+  </si>
+  <si>
+    <t>Istra 1961</t>
+  </si>
+  <si>
+    <t>Longford Town</t>
+  </si>
+  <si>
+    <t>Treaty United</t>
+  </si>
+  <si>
+    <t>Al Ahli</t>
+  </si>
+  <si>
     <t>Hassania Agadir</t>
   </si>
   <si>
-    <t>Bohemians</t>
-  </si>
-  <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
-    <t>Longford Town</t>
-  </si>
-  <si>
-    <t>Derry City</t>
-  </si>
-  <si>
-    <t>Polonia Bytom</t>
-  </si>
-  <si>
-    <t>Istra 1961</t>
-  </si>
-  <si>
-    <t>Al Jazeera</t>
-  </si>
-  <si>
     <t>Kerry</t>
   </si>
   <si>
-    <t>Cobh Ramblers</t>
-  </si>
-  <si>
-    <t>Al Ahli</t>
-  </si>
-  <si>
-    <t>Treaty United</t>
-  </si>
-  <si>
-    <t>Sligo Rovers</t>
-  </si>
-  <si>
-    <t>Waterford</t>
-  </si>
-  <si>
     <t>Al Feiha</t>
   </si>
   <si>
     <t>Al Shabab</t>
   </si>
   <si>
+    <t>Rheindorf Altach</t>
+  </si>
+  <si>
+    <t>Arsenal Tula</t>
+  </si>
+  <si>
     <t>Cremonese</t>
   </si>
   <si>
-    <t>Arsenal Tula</t>
-  </si>
-  <si>
-    <t>Rheindorf Altach</t>
-  </si>
-  <si>
     <t>Hearts</t>
   </si>
   <si>
     <t>CR Belouizdad</t>
   </si>
   <si>
+    <t>Torreense</t>
+  </si>
+  <si>
+    <t>Bnei Sakhnin</t>
+  </si>
+  <si>
+    <t>Wadi Degla</t>
+  </si>
+  <si>
     <t>Čukarički</t>
   </si>
   <si>
+    <t>Al Ittihad</t>
+  </si>
+  <si>
+    <t>Midtjylland</t>
+  </si>
+  <si>
     <t>Maccabi Netanya</t>
   </si>
   <si>
-    <t>Al Ittihad</t>
-  </si>
-  <si>
-    <t>Torreense</t>
-  </si>
-  <si>
-    <t>Midtjylland</t>
+    <t>Djurgården</t>
+  </si>
+  <si>
+    <t>Halmstad</t>
   </si>
   <si>
     <t>Porto II</t>
   </si>
   <si>
-    <t>Bnei Sakhnin</t>
-  </si>
-  <si>
-    <t>Djurgården</t>
-  </si>
-  <si>
     <t>Radomiak Radom</t>
   </si>
   <si>
-    <t>Wadi Degla</t>
-  </si>
-  <si>
     <t>FK Bodo - Glimt</t>
   </si>
   <si>
-    <t>Halmstad</t>
-  </si>
-  <si>
     <t>Landskrona</t>
   </si>
   <si>
     <t>Víkingur</t>
   </si>
   <si>
+    <t>B36</t>
+  </si>
+  <si>
     <t>Rapid Bucureşti</t>
   </si>
   <si>
-    <t>B36</t>
+    <t>Yacoub El Mansour</t>
   </si>
   <si>
     <t>Al Ittifaq</t>
@@ -628,9 +631,6 @@
     <t>Vasas</t>
   </si>
   <si>
-    <t>Yacoub El Mansour</t>
-  </si>
-  <si>
     <t>LASK Linz</t>
   </si>
   <si>
@@ -640,39 +640,39 @@
     <t>Roma</t>
   </si>
   <si>
+    <t>Sevilla FC</t>
+  </si>
+  <si>
+    <t>Everton</t>
+  </si>
+  <si>
     <t>USM Alger</t>
   </si>
   <si>
-    <t>Everton</t>
-  </si>
-  <si>
-    <t>Sevilla FC</t>
-  </si>
-  <si>
     <t>Sporting CP</t>
   </si>
   <si>
     <t>Kawkab Marrakech</t>
   </si>
   <si>
+    <t>Vila Nova</t>
+  </si>
+  <si>
     <t>San Luis</t>
   </si>
   <si>
-    <t>Vila Nova</t>
-  </si>
-  <si>
     <t>Figueirense</t>
   </si>
   <si>
+    <t>Ypiranga Erechim</t>
+  </si>
+  <si>
+    <t>Floresta</t>
+  </si>
+  <si>
     <t>Quilmes</t>
   </si>
   <si>
-    <t>Ypiranga Erechim</t>
-  </si>
-  <si>
-    <t>Floresta</t>
-  </si>
-  <si>
     <t>Universitario de Vinto</t>
   </si>
   <si>
@@ -682,199 +682,205 @@
     <t>San Marcos</t>
   </si>
   <si>
+    <t>Bhayangkara</t>
+  </si>
+  <si>
     <t>PSIM Yogyakarta</t>
   </si>
   <si>
-    <t>Bhayangkara</t>
-  </si>
-  <si>
     <t>Hadiya Hosaena</t>
   </si>
   <si>
     <t>Young Lions</t>
   </si>
   <si>
+    <t>West Ham United Women</t>
+  </si>
+  <si>
     <t>Persija</t>
   </si>
   <si>
-    <t>West Ham United Women</t>
+    <t>Adama Kenema</t>
   </si>
   <si>
     <t>Sheger Ketema</t>
   </si>
   <si>
-    <t>Adama Kenema</t>
-  </si>
-  <si>
     <t>Cibalia</t>
   </si>
   <si>
+    <t>Shinnik</t>
+  </si>
+  <si>
+    <t>Andijan</t>
+  </si>
+  <si>
+    <t>Qizilqum</t>
+  </si>
+  <si>
     <t>Kabel Novi Sad</t>
   </si>
   <si>
-    <t>Shinnik</t>
+    <t>Bengaluru</t>
+  </si>
+  <si>
+    <t>Jedinstvo Ub</t>
+  </si>
+  <si>
+    <t>Al Mokawloon</t>
+  </si>
+  <si>
+    <t>Nottingham Forest</t>
   </si>
   <si>
     <t>Saham</t>
   </si>
   <si>
-    <t>Andijan</t>
-  </si>
-  <si>
-    <t>Nottingham Forest</t>
-  </si>
-  <si>
-    <t>Bengaluru</t>
-  </si>
-  <si>
-    <t>Al Mokawloon</t>
-  </si>
-  <si>
-    <t>Qizilqum</t>
-  </si>
-  <si>
-    <t>Jedinstvo Ub</t>
-  </si>
-  <si>
     <t>Hermannstadt</t>
   </si>
   <si>
+    <t>Vojvodina</t>
+  </si>
+  <si>
     <t>ES Tunis</t>
   </si>
   <si>
     <t>Marsa</t>
   </si>
   <si>
+    <t>Navbahor</t>
+  </si>
+  <si>
     <t>Etoile du Sahel</t>
   </si>
   <si>
     <t>Métlaoui</t>
   </si>
   <si>
-    <t>Vojvodina</t>
-  </si>
-  <si>
-    <t>Navbahor</t>
-  </si>
-  <si>
     <t>Al-Nahda</t>
   </si>
   <si>
     <t>Turan</t>
   </si>
   <si>
+    <t>Shabab Al Ordon</t>
+  </si>
+  <si>
+    <t>St Patrick's Athl.</t>
+  </si>
+  <si>
+    <t>Galway United</t>
+  </si>
+  <si>
     <t>Drogheda United</t>
   </si>
   <si>
+    <t>Polonia Warszawa</t>
+  </si>
+  <si>
+    <t>Bray Wanderers</t>
+  </si>
+  <si>
+    <t>UCD</t>
+  </si>
+  <si>
+    <t>Shelbourne</t>
+  </si>
+  <si>
+    <t>Dundalk</t>
+  </si>
+  <si>
+    <t>Slaven Koprivnica</t>
+  </si>
+  <si>
+    <t>Athlone Town</t>
+  </si>
+  <si>
+    <t>Wexford</t>
+  </si>
+  <si>
+    <t>Al Buqa'a</t>
+  </si>
+  <si>
     <t>Olympic Safi</t>
   </si>
   <si>
-    <t>Shelbourne</t>
-  </si>
-  <si>
-    <t>Bray Wanderers</t>
-  </si>
-  <si>
-    <t>Athlone Town</t>
-  </si>
-  <si>
-    <t>Galway United</t>
-  </si>
-  <si>
-    <t>Polonia Warszawa</t>
-  </si>
-  <si>
-    <t>Slaven Koprivnica</t>
-  </si>
-  <si>
-    <t>Shabab Al Ordon</t>
-  </si>
-  <si>
     <t>Cork City</t>
   </si>
   <si>
-    <t>UCD</t>
-  </si>
-  <si>
-    <t>Al Buqa'a</t>
-  </si>
-  <si>
-    <t>Wexford</t>
-  </si>
-  <si>
-    <t>St Patrick's Athl.</t>
-  </si>
-  <si>
-    <t>Dundalk</t>
-  </si>
-  <si>
     <t>Al Riyadh</t>
   </si>
   <si>
     <t>Al-Rustaq</t>
   </si>
   <si>
+    <t>Wolfsberger AC</t>
+  </si>
+  <si>
+    <t>Rotor Volgograd</t>
+  </si>
+  <si>
     <t>Lazio</t>
   </si>
   <si>
-    <t>Rotor Volgograd</t>
-  </si>
-  <si>
-    <t>Wolfsberger AC</t>
-  </si>
-  <si>
     <t>Rangers</t>
   </si>
   <si>
     <t>USM Khenchela</t>
   </si>
   <si>
+    <t>FC Penafiel</t>
+  </si>
+  <si>
+    <t>Maccabi Bnei Raina</t>
+  </si>
+  <si>
+    <t>Kahraba Ismailia</t>
+  </si>
+  <si>
     <t>Red Star Belgrade</t>
   </si>
   <si>
+    <t>Petrojet</t>
+  </si>
+  <si>
+    <t>Viborg</t>
+  </si>
+  <si>
     <t>Hapoel Katamon</t>
   </si>
   <si>
-    <t>Petrojet</t>
-  </si>
-  <si>
-    <t>FC Penafiel</t>
-  </si>
-  <si>
-    <t>Viborg</t>
+    <t>IFK Göteborg</t>
+  </si>
+  <si>
+    <t>Brommapojkarna</t>
   </si>
   <si>
     <t>Felgueiras 1932</t>
   </si>
   <si>
-    <t>Maccabi Bnei Raina</t>
-  </si>
-  <si>
-    <t>IFK Göteborg</t>
-  </si>
-  <si>
     <t>Lechia Gdańsk</t>
   </si>
   <si>
-    <t>Kahraba Ismailia</t>
-  </si>
-  <si>
     <t>Molde</t>
   </si>
   <si>
-    <t>Brommapojkarna</t>
-  </si>
-  <si>
     <t>Öster</t>
   </si>
   <si>
     <t>07 Vestur</t>
   </si>
   <si>
+    <t>NSÍ</t>
+  </si>
+  <si>
     <t>CFR Cluj</t>
   </si>
   <si>
-    <t>NSÍ</t>
+    <t>Al Kholood</t>
+  </si>
+  <si>
+    <t>RSB Berkane</t>
   </si>
   <si>
     <t>Al Najma</t>
@@ -883,12 +889,6 @@
     <t>Budafoki MTE</t>
   </si>
   <si>
-    <t>RSB Berkane</t>
-  </si>
-  <si>
-    <t>Al Kholood</t>
-  </si>
-  <si>
     <t>Rapid Wien</t>
   </si>
   <si>
@@ -898,37 +898,37 @@
     <t>Fiorentina</t>
   </si>
   <si>
+    <t>Real Sociedad</t>
+  </si>
+  <si>
+    <t>Manchester City</t>
+  </si>
+  <si>
     <t>Paradou AC</t>
   </si>
   <si>
-    <t>Manchester City</t>
-  </si>
-  <si>
-    <t>Real Sociedad</t>
-  </si>
-  <si>
     <t>Vitória Guimarães</t>
   </si>
   <si>
     <t>Olympique Dcheïra</t>
   </si>
   <si>
+    <t>Athletic Club</t>
+  </si>
+  <si>
     <t>Unión San Felipe</t>
   </si>
   <si>
-    <t>Athletic Club</t>
-  </si>
-  <si>
     <t>Barra do Garcas</t>
   </si>
   <si>
+    <t>Ituano</t>
+  </si>
+  <si>
+    <t>Maranhão</t>
+  </si>
+  <si>
     <t>Chacarita Juniors</t>
-  </si>
-  <si>
-    <t>Ituano</t>
-  </si>
-  <si>
-    <t>Maranhão</t>
   </si>
   <si>
     <t>Blooming</t>
@@ -1539,133 +1539,133 @@
         <v>308</v>
       </c>
       <c r="P2">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="S2">
-        <v>1.72</v>
+        <v>2.63</v>
       </c>
       <c r="T2">
-        <v>2.42</v>
+        <v>2.03</v>
       </c>
       <c r="U2">
-        <v>8.65</v>
+        <v>4.23</v>
       </c>
       <c r="V2">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="W2">
+        <v>2.71</v>
+      </c>
+      <c r="X2">
+        <v>2.71</v>
+      </c>
+      <c r="Y2">
+        <v>1.37</v>
+      </c>
+      <c r="Z2">
+        <v>6.7</v>
+      </c>
+      <c r="AA2">
+        <v>1.05</v>
+      </c>
+      <c r="AB2">
+        <v>1.01</v>
+      </c>
+      <c r="AC2">
+        <v>1.24</v>
+      </c>
+      <c r="AD2">
+        <v>3.34</v>
+      </c>
+      <c r="AE2">
+        <v>1.85</v>
+      </c>
+      <c r="AF2">
+        <v>1.84</v>
+      </c>
+      <c r="AG2">
         <v>3.04</v>
       </c>
-      <c r="X2">
-        <v>2.39</v>
-      </c>
-      <c r="Y2">
-        <v>1.47</v>
-      </c>
-      <c r="Z2">
-        <v>5.35</v>
-      </c>
-      <c r="AA2">
-        <v>1.09</v>
-      </c>
-      <c r="AB2">
-        <v>1</v>
-      </c>
-      <c r="AC2">
-        <v>1.17</v>
-      </c>
-      <c r="AD2">
-        <v>3.96</v>
-      </c>
-      <c r="AE2">
-        <v>1.63</v>
-      </c>
-      <c r="AF2">
-        <v>2.12</v>
-      </c>
-      <c r="AG2">
-        <v>2.49</v>
-      </c>
       <c r="AH2">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AI2">
-        <v>4.35</v>
+        <v>5.88</v>
       </c>
       <c r="AJ2">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AK2">
-        <v>2.05</v>
+        <v>1.68</v>
       </c>
       <c r="AL2">
-        <v>1.7</v>
+        <v>2.02</v>
       </c>
       <c r="AM2">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AN2">
-        <v>3.28</v>
+        <v>1.65</v>
       </c>
       <c r="AO2">
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AU2">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="AV2">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW2">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX2">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AY2">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AZ2">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BA2">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="BB2">
+        <v>1.19</v>
+      </c>
+      <c r="BC2">
+        <v>2.03</v>
+      </c>
+      <c r="BD2">
+        <v>3.8</v>
+      </c>
+      <c r="BE2">
+        <v>1.68</v>
+      </c>
+      <c r="BF2">
         <v>1.15</v>
-      </c>
-      <c r="BC2">
-        <v>1.83</v>
-      </c>
-      <c r="BD2">
-        <v>4.3</v>
-      </c>
-      <c r="BE2">
-        <v>1.85</v>
-      </c>
-      <c r="BF2">
-        <v>1.22</v>
       </c>
       <c r="BG2">
         <v>0</v>
@@ -1724,133 +1724,133 @@
         <v>308</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>5.09</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S3">
-        <v>2.7</v>
+        <v>1.72</v>
       </c>
       <c r="T3">
-        <v>2.02</v>
+        <v>2.42</v>
       </c>
       <c r="U3">
-        <v>4.08</v>
+        <v>8.65</v>
       </c>
       <c r="V3">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="W3">
-        <v>2.71</v>
+        <v>3.04</v>
       </c>
       <c r="X3">
-        <v>2.81</v>
+        <v>2.39</v>
       </c>
       <c r="Y3">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="Z3">
-        <v>6.7</v>
+        <v>5.8</v>
       </c>
       <c r="AA3">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AB3">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC3">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AD3">
-        <v>3.34</v>
+        <v>3.94</v>
       </c>
       <c r="AE3">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AF3">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AG3">
-        <v>3.05</v>
+        <v>2.49</v>
       </c>
       <c r="AH3">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AI3">
-        <v>5.8</v>
+        <v>4.51</v>
       </c>
       <c r="AJ3">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AK3">
-        <v>1.68</v>
+        <v>2.09</v>
       </c>
       <c r="AL3">
-        <v>2.02</v>
+        <v>1.63</v>
       </c>
       <c r="AM3">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="AN3">
-        <v>1.61</v>
+        <v>3.28</v>
       </c>
       <c r="AO3">
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="AU3">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AV3">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AW3">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AX3">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AY3">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AZ3">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BA3">
-        <v>0</v>
+        <v>6.22</v>
       </c>
       <c r="BB3">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="BC3">
-        <v>2.03</v>
+        <v>1.84</v>
       </c>
       <c r="BD3">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="BE3">
-        <v>1.68</v>
+        <v>1.84</v>
       </c>
       <c r="BF3">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="BG3">
         <v>0</v>
@@ -2240,7 +2240,7 @@
         <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D6" t="s">
         <v>134</v>
@@ -2279,13 +2279,13 @@
         <v>308</v>
       </c>
       <c r="P6">
-        <v>4.83</v>
+        <v>2.17</v>
       </c>
       <c r="Q6">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="R6">
-        <v>1.57</v>
+        <v>2.83</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D7" t="s">
         <v>134</v>
@@ -2464,13 +2464,13 @@
         <v>308</v>
       </c>
       <c r="P7">
-        <v>2.17</v>
+        <v>5.2</v>
       </c>
       <c r="Q7">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="R7">
-        <v>2.83</v>
+        <v>1.57</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -3204,79 +3204,79 @@
         <v>308</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN11">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AO11">
         <v>0</v>
@@ -3318,19 +3318,19 @@
         <v>0</v>
       </c>
       <c r="BB11">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC11">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BD11">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE11">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF11">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG11">
         <v>0</v>
@@ -3353,7 +3353,7 @@
         <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E12" t="s">
         <v>147</v>
@@ -3389,79 +3389,79 @@
         <v>308</v>
       </c>
       <c r="P12">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R12">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="T12">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="V12">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W12">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X12">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y12">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z12">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AA12">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC12">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD12">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AE12">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AF12">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG12">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="AH12">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI12">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AJ12">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK12">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL12">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AM12">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AN12">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AO12">
         <v>0</v>
@@ -3503,19 +3503,19 @@
         <v>0</v>
       </c>
       <c r="BB12">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BC12">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="BD12">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE12">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF12">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG12">
         <v>0</v>
@@ -3535,10 +3535,10 @@
         <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D13" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E13" t="s">
         <v>148</v>
@@ -3720,10 +3720,10 @@
         <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D14" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E14" t="s">
         <v>149</v>
@@ -3905,7 +3905,7 @@
         <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D15" t="s">
         <v>134</v>
@@ -3944,133 +3944,133 @@
         <v>308</v>
       </c>
       <c r="P15">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q15">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R15">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="S15">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T15">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U15">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V15">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W15">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X15">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Y15">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z15">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA15">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC15">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD15">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AE15">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF15">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AG15">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH15">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AI15">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AJ15">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK15">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL15">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM15">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN15">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AO15">
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ15">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR15">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AS15">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AT15">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AU15">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="AV15">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="AW15">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AX15">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AY15">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AZ15">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="BA15">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BB15">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC15">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BD15">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE15">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF15">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG15">
         <v>0</v>
@@ -4090,7 +4090,7 @@
         <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D16" t="s">
         <v>134</v>
@@ -4275,7 +4275,7 @@
         <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D17" t="s">
         <v>134</v>
@@ -4314,22 +4314,22 @@
         <v>308</v>
       </c>
       <c r="P17">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="Q17">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="R17">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="S17">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="T17">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="U17">
-        <v>3.28</v>
+        <v>3.41</v>
       </c>
       <c r="V17">
         <v>1.67</v>
@@ -4338,7 +4338,7 @@
         <v>2.07</v>
       </c>
       <c r="X17">
-        <v>3.84</v>
+        <v>3.85</v>
       </c>
       <c r="Y17">
         <v>1.18</v>
@@ -4350,13 +4350,13 @@
         <v>1.01</v>
       </c>
       <c r="AB17">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AC17">
         <v>1.57</v>
       </c>
       <c r="AD17">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AE17">
         <v>2.7</v>
@@ -4365,10 +4365,10 @@
         <v>1.36</v>
       </c>
       <c r="AG17">
-        <v>5.75</v>
+        <v>5.35</v>
       </c>
       <c r="AH17">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AI17">
         <v>12.5</v>
@@ -4377,7 +4377,7 @@
         <v>1.03</v>
       </c>
       <c r="AK17">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AL17">
         <v>1.57</v>
@@ -4386,7 +4386,7 @@
         <v>1.38</v>
       </c>
       <c r="AN17">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AO17">
         <v>0</v>
@@ -4428,7 +4428,7 @@
         <v>1.62</v>
       </c>
       <c r="BB17">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="BC17">
         <v>2.78</v>
@@ -4460,10 +4460,10 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D18" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E18" t="s">
         <v>153</v>
@@ -4499,133 +4499,133 @@
         <v>308</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>5.18</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH18">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AI18">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL18">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM18">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN18">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AO18">
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AU18">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="AV18">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AW18">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AX18">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AY18">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AZ18">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BA18">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BB18">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC18">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BD18">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE18">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF18">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG18">
         <v>0</v>
@@ -4645,7 +4645,7 @@
         <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="D19" t="s">
         <v>134</v>
@@ -4869,28 +4869,28 @@
         <v>308</v>
       </c>
       <c r="P20">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="Q20">
         <v>3.2</v>
       </c>
       <c r="R20">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="S20">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="T20">
         <v>1.99</v>
       </c>
       <c r="U20">
-        <v>2.77</v>
+        <v>2.68</v>
       </c>
       <c r="V20">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W20">
-        <v>2.56</v>
+        <v>2.69</v>
       </c>
       <c r="X20">
         <v>3.1</v>
@@ -4911,10 +4911,10 @@
         <v>1.37</v>
       </c>
       <c r="AD20">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="AE20">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AF20">
         <v>1.66</v>
@@ -4932,61 +4932,61 @@
         <v>1.03</v>
       </c>
       <c r="AK20">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AL20">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AM20">
         <v>1.3</v>
       </c>
       <c r="AN20">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AO20">
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AQ20">
+        <v>1.63</v>
+      </c>
+      <c r="AR20">
+        <v>2.38</v>
+      </c>
+      <c r="AS20">
+        <v>2.66</v>
+      </c>
+      <c r="AT20">
+        <v>3.71</v>
+      </c>
+      <c r="AU20">
+        <v>2.88</v>
+      </c>
+      <c r="AV20">
+        <v>2.13</v>
+      </c>
+      <c r="AW20">
+        <v>1.69</v>
+      </c>
+      <c r="AX20">
+        <v>1.39</v>
+      </c>
+      <c r="AY20">
+        <v>1.19</v>
+      </c>
+      <c r="AZ20">
+        <v>3.12</v>
+      </c>
+      <c r="BA20">
         <v>1.62</v>
-      </c>
-      <c r="AR20">
-        <v>2.35</v>
-      </c>
-      <c r="AS20">
-        <v>2.62</v>
-      </c>
-      <c r="AT20">
-        <v>3.65</v>
-      </c>
-      <c r="AU20">
-        <v>2.92</v>
-      </c>
-      <c r="AV20">
-        <v>2.15</v>
-      </c>
-      <c r="AW20">
-        <v>1.71</v>
-      </c>
-      <c r="AX20">
-        <v>1.4</v>
-      </c>
-      <c r="AY20">
-        <v>1.2</v>
-      </c>
-      <c r="AZ20">
-        <v>2.48</v>
-      </c>
-      <c r="BA20">
-        <v>1.7</v>
       </c>
       <c r="BB20">
         <v>1.27</v>
       </c>
       <c r="BC20">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="BD20">
         <v>3.35</v>
@@ -5054,61 +5054,61 @@
         <v>308</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB21">
         <v>0</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH21">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI21">
         <v>0</v>
@@ -5117,16 +5117,16 @@
         <v>0</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL21">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM21">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN21">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO21">
         <v>0</v>
@@ -5171,13 +5171,13 @@
         <v>0</v>
       </c>
       <c r="BC21">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BD21">
         <v>0</v>
       </c>
       <c r="BE21">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BF21">
         <v>0</v>
@@ -5200,7 +5200,7 @@
         <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D22" t="s">
         <v>134</v>
@@ -5385,7 +5385,7 @@
         <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D23" t="s">
         <v>134</v>
@@ -5570,10 +5570,10 @@
         <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D24" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E24" t="s">
         <v>159</v>
@@ -5794,61 +5794,61 @@
         <v>308</v>
       </c>
       <c r="P25">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q25">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R25">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S25">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T25">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="U25">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="V25">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W25">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="X25">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Y25">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z25">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AA25">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB25">
         <v>0</v>
       </c>
       <c r="AC25">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD25">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="AE25">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AF25">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG25">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AH25">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AI25">
         <v>0</v>
@@ -5857,16 +5857,16 @@
         <v>0</v>
       </c>
       <c r="AK25">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AL25">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AM25">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN25">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO25">
         <v>0</v>
@@ -5911,13 +5911,13 @@
         <v>0</v>
       </c>
       <c r="BC25">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="BD25">
         <v>0</v>
       </c>
       <c r="BE25">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="BF25">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D26" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E26" t="s">
         <v>161</v>
@@ -6125,7 +6125,7 @@
         <v>70</v>
       </c>
       <c r="C27" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D27" t="s">
         <v>134</v>
@@ -6498,7 +6498,7 @@
         <v>106</v>
       </c>
       <c r="D29" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E29" t="s">
         <v>164</v>
@@ -6579,10 +6579,10 @@
         <v>0</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG29">
         <v>0</v>
@@ -6597,10 +6597,10 @@
         <v>0</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL29">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AM29">
         <v>0</v>
@@ -6683,7 +6683,7 @@
         <v>107</v>
       </c>
       <c r="D30" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E30" t="s">
         <v>165</v>
@@ -6865,7 +6865,7 @@
         <v>72</v>
       </c>
       <c r="C31" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D31" t="s">
         <v>136</v>
@@ -7050,7 +7050,7 @@
         <v>72</v>
       </c>
       <c r="C32" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D32" t="s">
         <v>136</v>
@@ -7089,22 +7089,22 @@
         <v>308</v>
       </c>
       <c r="P32">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q32">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R32">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S32">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T32">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U32">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="V32">
         <v>0</v>
@@ -7113,10 +7113,10 @@
         <v>0</v>
       </c>
       <c r="X32">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y32">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -7128,40 +7128,40 @@
         <v>0</v>
       </c>
       <c r="AC32">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AD32">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE32">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF32">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG32">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AH32">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI32">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ32">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK32">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL32">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AM32">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN32">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO32">
         <v>0</v>
@@ -7206,13 +7206,13 @@
         <v>0</v>
       </c>
       <c r="BC32">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="BD32">
         <v>0</v>
       </c>
       <c r="BE32">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BF32">
         <v>0</v>
@@ -7238,7 +7238,7 @@
         <v>108</v>
       </c>
       <c r="D33" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E33" t="s">
         <v>168</v>
@@ -7274,79 +7274,79 @@
         <v>308</v>
       </c>
       <c r="P33">
-        <v>2.09</v>
+        <v>2.36</v>
       </c>
       <c r="Q33">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R33">
-        <v>3.24</v>
+        <v>2.75</v>
       </c>
       <c r="S33">
-        <v>2.55</v>
+        <v>2.82</v>
       </c>
       <c r="T33">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="U33">
-        <v>3.75</v>
+        <v>3.28</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="X33">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="Y33">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC33">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AD33">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="AE33">
-        <v>1.82</v>
+        <v>1.61</v>
       </c>
       <c r="AF33">
-        <v>1.82</v>
+        <v>2.08</v>
       </c>
       <c r="AG33">
-        <v>3</v>
+        <v>2.43</v>
       </c>
       <c r="AH33">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AI33">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="AJ33">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AK33">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AL33">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="AM33">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AN33">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AO33">
         <v>0</v>
@@ -7388,19 +7388,19 @@
         <v>0</v>
       </c>
       <c r="BB33">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC33">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="BD33">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE33">
-        <v>1.64</v>
+        <v>1.86</v>
       </c>
       <c r="BF33">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG33">
         <v>0</v>
@@ -7420,7 +7420,7 @@
         <v>72</v>
       </c>
       <c r="C34" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D34" t="s">
         <v>136</v>
@@ -7459,22 +7459,22 @@
         <v>308</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V34">
         <v>0</v>
@@ -7483,10 +7483,10 @@
         <v>0</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -7498,40 +7498,40 @@
         <v>0</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AH34">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI34">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL34">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AM34">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN34">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO34">
         <v>0</v>
@@ -7576,13 +7576,13 @@
         <v>0</v>
       </c>
       <c r="BC34">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BD34">
         <v>0</v>
       </c>
       <c r="BE34">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF34">
         <v>0</v>
@@ -7608,7 +7608,7 @@
         <v>109</v>
       </c>
       <c r="D35" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E35" t="s">
         <v>170</v>
@@ -7644,79 +7644,79 @@
         <v>308</v>
       </c>
       <c r="P35">
-        <v>2.36</v>
+        <v>2.14</v>
       </c>
       <c r="Q35">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R35">
-        <v>2.75</v>
+        <v>3.14</v>
       </c>
       <c r="S35">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
       <c r="T35">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="U35">
-        <v>3.28</v>
+        <v>3.65</v>
       </c>
       <c r="V35">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W35">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="X35">
-        <v>2.31</v>
+        <v>2.55</v>
       </c>
       <c r="Y35">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="Z35">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA35">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB35">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC35">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AD35">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="AE35">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
       <c r="AF35">
-        <v>2.08</v>
+        <v>1.82</v>
       </c>
       <c r="AG35">
-        <v>2.43</v>
+        <v>3</v>
       </c>
       <c r="AH35">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AI35">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="AJ35">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AK35">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AL35">
-        <v>2.32</v>
+        <v>2.02</v>
       </c>
       <c r="AM35">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AN35">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AO35">
         <v>0</v>
@@ -7758,19 +7758,19 @@
         <v>0</v>
       </c>
       <c r="BB35">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC35">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="BD35">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE35">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="BF35">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BG35">
         <v>0</v>
@@ -7790,10 +7790,10 @@
         <v>72</v>
       </c>
       <c r="C36" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D36" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E36" t="s">
         <v>171</v>
@@ -7829,133 +7829,133 @@
         <v>308</v>
       </c>
       <c r="P36">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q36">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R36">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="S36">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T36">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U36">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="V36">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W36">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="X36">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y36">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z36">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AA36">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB36">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC36">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AD36">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE36">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF36">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG36">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AH36">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI36">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AJ36">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK36">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL36">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AM36">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AN36">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AO36">
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AQ36">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AR36">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AS36">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="AT36">
-        <v>5.44</v>
+        <v>0</v>
       </c>
       <c r="AU36">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AV36">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AW36">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AX36">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AY36">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AZ36">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BA36">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="BB36">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC36">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD36">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE36">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BF36">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG36">
         <v>0</v>
@@ -7975,10 +7975,10 @@
         <v>72</v>
       </c>
       <c r="C37" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D37" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E37" t="s">
         <v>172</v>
@@ -8059,10 +8059,10 @@
         <v>0</v>
       </c>
       <c r="AE37">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF37">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG37">
         <v>0</v>
@@ -8077,10 +8077,10 @@
         <v>0</v>
       </c>
       <c r="AK37">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL37">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AM37">
         <v>0</v>
@@ -8160,10 +8160,10 @@
         <v>72</v>
       </c>
       <c r="C38" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D38" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E38" t="s">
         <v>173</v>
@@ -8199,133 +8199,133 @@
         <v>308</v>
       </c>
       <c r="P38">
-        <v>5.42</v>
+        <v>2.45</v>
       </c>
       <c r="Q38">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="R38">
-        <v>1.56</v>
+        <v>2.63</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AH38">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI38">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL38">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM38">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN38">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AO38">
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AQ38">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AR38">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AS38">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AT38">
-        <v>0</v>
+        <v>5.44</v>
       </c>
       <c r="AU38">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AV38">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AW38">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AX38">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AY38">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AZ38">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BA38">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BB38">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC38">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BD38">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE38">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BF38">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG38">
         <v>0</v>
@@ -8345,7 +8345,7 @@
         <v>72</v>
       </c>
       <c r="C39" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D39" t="s">
         <v>136</v>
@@ -8384,22 +8384,22 @@
         <v>308</v>
       </c>
       <c r="P39">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="Q39">
         <v>3.3</v>
       </c>
       <c r="R39">
-        <v>3.14</v>
+        <v>3.24</v>
       </c>
       <c r="S39">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="T39">
         <v>2.2</v>
       </c>
       <c r="U39">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="V39">
         <v>0</v>
@@ -8441,22 +8441,22 @@
         <v>1.3</v>
       </c>
       <c r="AI39">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AJ39">
         <v>1.09</v>
       </c>
       <c r="AK39">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AL39">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AM39">
         <v>1.23</v>
       </c>
       <c r="AN39">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AO39">
         <v>0</v>
@@ -8501,13 +8501,13 @@
         <v>0</v>
       </c>
       <c r="BC39">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="BD39">
         <v>0</v>
       </c>
       <c r="BE39">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="BF39">
         <v>0</v>
@@ -8530,10 +8530,10 @@
         <v>72</v>
       </c>
       <c r="C40" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D40" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E40" t="s">
         <v>175</v>
@@ -8569,22 +8569,22 @@
         <v>308</v>
       </c>
       <c r="P40">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="Q40">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R40">
-        <v>2.62</v>
+        <v>2.43</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V40">
         <v>0</v>
@@ -8593,10 +8593,10 @@
         <v>0</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -8608,40 +8608,40 @@
         <v>0</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH40">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI40">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL40">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM40">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN40">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AO40">
         <v>0</v>
@@ -8686,13 +8686,13 @@
         <v>0</v>
       </c>
       <c r="BC40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD40">
         <v>0</v>
       </c>
       <c r="BE40">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BF40">
         <v>0</v>
@@ -8715,10 +8715,10 @@
         <v>72</v>
       </c>
       <c r="C41" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D41" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E41" t="s">
         <v>176</v>
@@ -8754,22 +8754,22 @@
         <v>308</v>
       </c>
       <c r="P41">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="Q41">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R41">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="S41">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T41">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U41">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V41">
         <v>0</v>
@@ -8778,10 +8778,10 @@
         <v>0</v>
       </c>
       <c r="X41">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Y41">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -8793,40 +8793,40 @@
         <v>0</v>
       </c>
       <c r="AC41">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD41">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AE41">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF41">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG41">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH41">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI41">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AJ41">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK41">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AL41">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM41">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN41">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AO41">
         <v>0</v>
@@ -8871,13 +8871,13 @@
         <v>0</v>
       </c>
       <c r="BC41">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD41">
         <v>0</v>
       </c>
       <c r="BE41">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BF41">
         <v>0</v>
@@ -8900,10 +8900,10 @@
         <v>72</v>
       </c>
       <c r="C42" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D42" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E42" t="s">
         <v>177</v>
@@ -9085,7 +9085,7 @@
         <v>72</v>
       </c>
       <c r="C43" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D43" t="s">
         <v>136</v>
@@ -9124,13 +9124,13 @@
         <v>308</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S43">
         <v>0</v>
@@ -9318,124 +9318,124 @@
         <v>0</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AH44">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI44">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL44">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM44">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN44">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AO44">
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AQ44">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AR44">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AS44">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AT44">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AU44">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AV44">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AW44">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AX44">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY44">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ44">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BA44">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BB44">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC44">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD44">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BE44">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF44">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG44">
         <v>0</v>
@@ -9455,7 +9455,7 @@
         <v>74</v>
       </c>
       <c r="C45" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D45" t="s">
         <v>134</v>
@@ -9679,133 +9679,133 @@
         <v>308</v>
       </c>
       <c r="P46">
-        <v>3.89</v>
+        <v>2.55</v>
       </c>
       <c r="Q46">
-        <v>3.67</v>
+        <v>3.28</v>
       </c>
       <c r="R46">
-        <v>2.06</v>
+        <v>2.67</v>
       </c>
       <c r="S46">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="T46">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="U46">
-        <v>3.18</v>
+        <v>3.55</v>
       </c>
       <c r="V46">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W46">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="X46">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="Y46">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="Z46">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA46">
         <v>1.04</v>
       </c>
       <c r="AB46">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AC46">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AD46">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="AE46">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AF46">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="AG46">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="AH46">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AI46">
-        <v>8.1</v>
+        <v>6.5</v>
       </c>
       <c r="AJ46">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="AK46">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AL46">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AM46">
+        <v>1.28</v>
+      </c>
+      <c r="AN46">
+        <v>1.54</v>
+      </c>
+      <c r="AO46">
+        <v>0</v>
+      </c>
+      <c r="AP46">
         <v>1.33</v>
       </c>
-      <c r="AN46">
+      <c r="AQ46">
+        <v>1.61</v>
+      </c>
+      <c r="AR46">
+        <v>1.83</v>
+      </c>
+      <c r="AS46">
+        <v>2.75</v>
+      </c>
+      <c r="AT46">
+        <v>3.8</v>
+      </c>
+      <c r="AU46">
+        <v>2.83</v>
+      </c>
+      <c r="AV46">
+        <v>2.09</v>
+      </c>
+      <c r="AW46">
+        <v>1.66</v>
+      </c>
+      <c r="AX46">
         <v>1.36</v>
       </c>
-      <c r="AO46">
-        <v>0</v>
-      </c>
-      <c r="AP46">
-        <v>1.38</v>
-      </c>
-      <c r="AQ46">
-        <v>1.66</v>
-      </c>
-      <c r="AR46">
-        <v>2.5</v>
-      </c>
-      <c r="AS46">
-        <v>2.77</v>
-      </c>
-      <c r="AT46">
-        <v>3.15</v>
-      </c>
-      <c r="AU46">
-        <v>2.8</v>
-      </c>
-      <c r="AV46">
-        <v>2.08</v>
-      </c>
-      <c r="AW46">
-        <v>1.7</v>
-      </c>
-      <c r="AX46">
-        <v>1.39</v>
-      </c>
       <c r="AY46">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AZ46">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="BA46">
-        <v>1.72</v>
+        <v>2.85</v>
       </c>
       <c r="BB46">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BC46">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="BD46">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="BE46">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="BF46">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BG46">
         <v>0</v>
@@ -9825,7 +9825,7 @@
         <v>75</v>
       </c>
       <c r="C47" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D47" t="s">
         <v>134</v>
@@ -9864,25 +9864,25 @@
         <v>308</v>
       </c>
       <c r="P47">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="Q47">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="R47">
-        <v>2.5</v>
+        <v>2.84</v>
       </c>
       <c r="S47">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="T47">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="U47">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="V47">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W47">
         <v>2.44</v>
@@ -9903,40 +9903,40 @@
         <v>1.05</v>
       </c>
       <c r="AC47">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AD47">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="AE47">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="AF47">
         <v>1.55</v>
       </c>
       <c r="AG47">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="AH47">
         <v>1.13</v>
       </c>
       <c r="AI47">
-        <v>9.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="AJ47">
         <v>1</v>
       </c>
       <c r="AK47">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AL47">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AM47">
         <v>1.38</v>
       </c>
       <c r="AN47">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AO47">
         <v>0</v>
@@ -9978,19 +9978,19 @@
         <v>0</v>
       </c>
       <c r="BB47">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="BC47">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BD47">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="BE47">
         <v>1.44</v>
       </c>
       <c r="BF47">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="BG47">
         <v>0</v>
@@ -10049,130 +10049,130 @@
         <v>308</v>
       </c>
       <c r="P48">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="Q48">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="R48">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="S48">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="T48">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="U48">
+        <v>2.9</v>
+      </c>
+      <c r="V48">
+        <v>1.44</v>
+      </c>
+      <c r="W48">
+        <v>2.65</v>
+      </c>
+      <c r="X48">
+        <v>2.9</v>
+      </c>
+      <c r="Y48">
+        <v>1.34</v>
+      </c>
+      <c r="Z48">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AA48">
+        <v>1.03</v>
+      </c>
+      <c r="AB48">
+        <v>1.06</v>
+      </c>
+      <c r="AC48">
+        <v>1.34</v>
+      </c>
+      <c r="AD48">
+        <v>3</v>
+      </c>
+      <c r="AE48">
+        <v>2.21</v>
+      </c>
+      <c r="AF48">
+        <v>1.7</v>
+      </c>
+      <c r="AG48">
+        <v>3.58</v>
+      </c>
+      <c r="AH48">
+        <v>1.29</v>
+      </c>
+      <c r="AI48">
+        <v>7.8</v>
+      </c>
+      <c r="AJ48">
+        <v>1.02</v>
+      </c>
+      <c r="AK48">
+        <v>1.83</v>
+      </c>
+      <c r="AL48">
+        <v>1.92</v>
+      </c>
+      <c r="AM48">
+        <v>1.33</v>
+      </c>
+      <c r="AN48">
+        <v>1.36</v>
+      </c>
+      <c r="AO48">
+        <v>0</v>
+      </c>
+      <c r="AP48">
+        <v>1.38</v>
+      </c>
+      <c r="AQ48">
+        <v>1.68</v>
+      </c>
+      <c r="AR48">
+        <v>2.1</v>
+      </c>
+      <c r="AS48">
+        <v>2.38</v>
+      </c>
+      <c r="AT48">
+        <v>3.15</v>
+      </c>
+      <c r="AU48">
+        <v>3.1</v>
+      </c>
+      <c r="AV48">
+        <v>2.06</v>
+      </c>
+      <c r="AW48">
+        <v>1.6</v>
+      </c>
+      <c r="AX48">
+        <v>1.5</v>
+      </c>
+      <c r="AY48">
+        <v>1.3</v>
+      </c>
+      <c r="AZ48">
+        <v>2.5</v>
+      </c>
+      <c r="BA48">
+        <v>1.8</v>
+      </c>
+      <c r="BB48">
+        <v>1.27</v>
+      </c>
+      <c r="BC48">
+        <v>2.38</v>
+      </c>
+      <c r="BD48">
         <v>3.55</v>
       </c>
-      <c r="V48">
-        <v>1.4</v>
-      </c>
-      <c r="W48">
-        <v>2.9</v>
-      </c>
-      <c r="X48">
-        <v>2.85</v>
-      </c>
-      <c r="Y48">
-        <v>1.37</v>
-      </c>
-      <c r="Z48">
-        <v>7</v>
-      </c>
-      <c r="AA48">
-        <v>1.04</v>
-      </c>
-      <c r="AB48">
-        <v>1.01</v>
-      </c>
-      <c r="AC48">
-        <v>1.28</v>
-      </c>
-      <c r="AD48">
-        <v>3.12</v>
-      </c>
-      <c r="AE48">
-        <v>2.02</v>
-      </c>
-      <c r="AF48">
-        <v>1.79</v>
-      </c>
-      <c r="AG48">
-        <v>3.3</v>
-      </c>
-      <c r="AH48">
-        <v>1.28</v>
-      </c>
-      <c r="AI48">
-        <v>6.5</v>
-      </c>
-      <c r="AJ48">
-        <v>1.09</v>
-      </c>
-      <c r="AK48">
-        <v>1.74</v>
-      </c>
-      <c r="AL48">
-        <v>2</v>
-      </c>
-      <c r="AM48">
-        <v>1.28</v>
-      </c>
-      <c r="AN48">
-        <v>1.54</v>
-      </c>
-      <c r="AO48">
-        <v>0</v>
-      </c>
-      <c r="AP48">
-        <v>1.33</v>
-      </c>
-      <c r="AQ48">
-        <v>1.61</v>
-      </c>
-      <c r="AR48">
-        <v>1.83</v>
-      </c>
-      <c r="AS48">
-        <v>2.75</v>
-      </c>
-      <c r="AT48">
-        <v>3.8</v>
-      </c>
-      <c r="AU48">
-        <v>2.83</v>
-      </c>
-      <c r="AV48">
-        <v>2.09</v>
-      </c>
-      <c r="AW48">
-        <v>1.66</v>
-      </c>
-      <c r="AX48">
-        <v>1.36</v>
-      </c>
-      <c r="AY48">
-        <v>1.19</v>
-      </c>
-      <c r="AZ48">
-        <v>1.67</v>
-      </c>
-      <c r="BA48">
-        <v>2.85</v>
-      </c>
-      <c r="BB48">
-        <v>1.25</v>
-      </c>
-      <c r="BC48">
-        <v>2.2</v>
-      </c>
-      <c r="BD48">
-        <v>3.58</v>
-      </c>
       <c r="BE48">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="BF48">
         <v>1.13</v>
@@ -10234,10 +10234,10 @@
         <v>308</v>
       </c>
       <c r="P49">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="Q49">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R49">
         <v>2.4</v>
@@ -10279,10 +10279,10 @@
         <v>0</v>
       </c>
       <c r="AE49">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AF49">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AG49">
         <v>0</v>
@@ -10565,7 +10565,7 @@
         <v>77</v>
       </c>
       <c r="C51" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="D51" t="s">
         <v>134</v>
@@ -10604,133 +10604,133 @@
         <v>308</v>
       </c>
       <c r="P51">
-        <v>7.95</v>
+        <v>1.75</v>
       </c>
       <c r="Q51">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="R51">
-        <v>1.33</v>
+        <v>4</v>
       </c>
       <c r="S51">
-        <v>7.13</v>
+        <v>2.45</v>
       </c>
       <c r="T51">
-        <v>2.65</v>
+        <v>2.05</v>
       </c>
       <c r="U51">
+        <v>4.9</v>
+      </c>
+      <c r="V51">
+        <v>1.4</v>
+      </c>
+      <c r="W51">
+        <v>2.69</v>
+      </c>
+      <c r="X51">
+        <v>2.9</v>
+      </c>
+      <c r="Y51">
+        <v>1.35</v>
+      </c>
+      <c r="Z51">
+        <v>7.3</v>
+      </c>
+      <c r="AA51">
+        <v>1.03</v>
+      </c>
+      <c r="AB51">
+        <v>1.01</v>
+      </c>
+      <c r="AC51">
+        <v>1.32</v>
+      </c>
+      <c r="AD51">
+        <v>3.1</v>
+      </c>
+      <c r="AE51">
+        <v>1.77</v>
+      </c>
+      <c r="AF51">
+        <v>1.75</v>
+      </c>
+      <c r="AG51">
+        <v>3.34</v>
+      </c>
+      <c r="AH51">
+        <v>1.24</v>
+      </c>
+      <c r="AI51">
+        <v>6.65</v>
+      </c>
+      <c r="AJ51">
+        <v>1.05</v>
+      </c>
+      <c r="AK51">
+        <v>1.8</v>
+      </c>
+      <c r="AL51">
+        <v>1.85</v>
+      </c>
+      <c r="AM51">
+        <v>1.26</v>
+      </c>
+      <c r="AN51">
+        <v>1.94</v>
+      </c>
+      <c r="AO51">
+        <v>0</v>
+      </c>
+      <c r="AP51">
+        <v>1.13</v>
+      </c>
+      <c r="AQ51">
+        <v>1.31</v>
+      </c>
+      <c r="AR51">
         <v>1.74</v>
       </c>
-      <c r="V51">
-        <v>0</v>
-      </c>
-      <c r="W51">
-        <v>0</v>
-      </c>
-      <c r="X51">
-        <v>2.15</v>
-      </c>
-      <c r="Y51">
-        <v>1.6</v>
-      </c>
-      <c r="Z51">
-        <v>4.55</v>
-      </c>
-      <c r="AA51">
-        <v>1.15</v>
-      </c>
-      <c r="AB51">
-        <v>0</v>
-      </c>
-      <c r="AC51">
-        <v>1.16</v>
-      </c>
-      <c r="AD51">
-        <v>4.2</v>
-      </c>
-      <c r="AE51">
-        <v>1.52</v>
-      </c>
-      <c r="AF51">
-        <v>2.18</v>
-      </c>
-      <c r="AG51">
-        <v>2.38</v>
-      </c>
-      <c r="AH51">
-        <v>1.47</v>
-      </c>
-      <c r="AI51">
-        <v>3.8</v>
-      </c>
-      <c r="AJ51">
-        <v>1.21</v>
-      </c>
-      <c r="AK51">
-        <v>1.9</v>
-      </c>
-      <c r="AL51">
-        <v>1.9</v>
-      </c>
-      <c r="AM51">
+      <c r="AS51">
+        <v>1.95</v>
+      </c>
+      <c r="AT51">
+        <v>2.48</v>
+      </c>
+      <c r="AU51">
+        <v>4.38</v>
+      </c>
+      <c r="AV51">
+        <v>2.95</v>
+      </c>
+      <c r="AW51">
+        <v>2.2</v>
+      </c>
+      <c r="AX51">
+        <v>1.76</v>
+      </c>
+      <c r="AY51">
+        <v>1.45</v>
+      </c>
+      <c r="AZ51">
+        <v>1.49</v>
+      </c>
+      <c r="BA51">
+        <v>3.04</v>
+      </c>
+      <c r="BB51">
+        <v>1.22</v>
+      </c>
+      <c r="BC51">
+        <v>2.2</v>
+      </c>
+      <c r="BD51">
+        <v>3.58</v>
+      </c>
+      <c r="BE51">
+        <v>1.62</v>
+      </c>
+      <c r="BF51">
         <v>1.13</v>
-      </c>
-      <c r="AN51">
-        <v>1.05</v>
-      </c>
-      <c r="AO51">
-        <v>0</v>
-      </c>
-      <c r="AP51">
-        <v>0</v>
-      </c>
-      <c r="AQ51">
-        <v>0</v>
-      </c>
-      <c r="AR51">
-        <v>0</v>
-      </c>
-      <c r="AS51">
-        <v>0</v>
-      </c>
-      <c r="AT51">
-        <v>0</v>
-      </c>
-      <c r="AU51">
-        <v>0</v>
-      </c>
-      <c r="AV51">
-        <v>0</v>
-      </c>
-      <c r="AW51">
-        <v>0</v>
-      </c>
-      <c r="AX51">
-        <v>0</v>
-      </c>
-      <c r="AY51">
-        <v>0</v>
-      </c>
-      <c r="AZ51">
-        <v>0</v>
-      </c>
-      <c r="BA51">
-        <v>0</v>
-      </c>
-      <c r="BB51">
-        <v>0</v>
-      </c>
-      <c r="BC51">
-        <v>1.75</v>
-      </c>
-      <c r="BD51">
-        <v>0</v>
-      </c>
-      <c r="BE51">
-        <v>1.85</v>
-      </c>
-      <c r="BF51">
-        <v>0</v>
       </c>
       <c r="BG51">
         <v>0</v>
@@ -10750,7 +10750,7 @@
         <v>77</v>
       </c>
       <c r="C52" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D52" t="s">
         <v>134</v>
@@ -10789,79 +10789,79 @@
         <v>308</v>
       </c>
       <c r="P52">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="Q52">
-        <v>3.8</v>
+        <v>3.41</v>
       </c>
       <c r="R52">
-        <v>3.23</v>
+        <v>3.07</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AH52">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI52">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL52">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM52">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN52">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AO52">
         <v>0</v>
@@ -10903,19 +10903,19 @@
         <v>0</v>
       </c>
       <c r="BB52">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC52">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="BD52">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="BE52">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF52">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG52">
         <v>0</v>
@@ -10935,7 +10935,7 @@
         <v>77</v>
       </c>
       <c r="C53" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D53" t="s">
         <v>134</v>
@@ -10974,133 +10974,133 @@
         <v>308</v>
       </c>
       <c r="P53">
-        <v>2.22</v>
+        <v>1.71</v>
       </c>
       <c r="Q53">
-        <v>2.76</v>
+        <v>3.3</v>
       </c>
       <c r="R53">
-        <v>3.48</v>
+        <v>4</v>
       </c>
       <c r="S53">
-        <v>3.04</v>
+        <v>2.45</v>
       </c>
       <c r="T53">
-        <v>1.8</v>
+        <v>2.18</v>
       </c>
       <c r="U53">
-        <v>4.53</v>
+        <v>5</v>
       </c>
       <c r="V53">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="W53">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="X53">
-        <v>3.48</v>
+        <v>2.95</v>
       </c>
       <c r="Y53">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z53">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA53">
         <v>1.02</v>
       </c>
       <c r="AB53">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AC53">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AD53">
-        <v>2.4</v>
+        <v>2.83</v>
       </c>
       <c r="AE53">
-        <v>2.41</v>
+        <v>2.15</v>
       </c>
       <c r="AF53">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="AG53">
-        <v>5.25</v>
+        <v>3.82</v>
       </c>
       <c r="AH53">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AI53">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="AJ53">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AK53">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AL53">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AM53">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="AN53">
-        <v>1.52</v>
+        <v>1.94</v>
       </c>
       <c r="AO53">
         <v>0</v>
       </c>
       <c r="AP53">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ53">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AR53">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AS53">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="AT53">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="AU53">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="AV53">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="AW53">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="AX53">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AY53">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AZ53">
-        <v>1.83</v>
+        <v>1.48</v>
       </c>
       <c r="BA53">
-        <v>2.14</v>
+        <v>2.85</v>
       </c>
       <c r="BB53">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="BC53">
-        <v>2.53</v>
+        <v>2.25</v>
       </c>
       <c r="BD53">
-        <v>2.96</v>
+        <v>3.34</v>
       </c>
       <c r="BE53">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="BF53">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="BG53">
         <v>0</v>
@@ -11120,7 +11120,7 @@
         <v>77</v>
       </c>
       <c r="C54" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D54" t="s">
         <v>134</v>
@@ -11159,133 +11159,133 @@
         <v>308</v>
       </c>
       <c r="P54">
-        <v>1.8</v>
+        <v>7.95</v>
       </c>
       <c r="Q54">
-        <v>3.54</v>
+        <v>4.7</v>
       </c>
       <c r="R54">
-        <v>4.24</v>
+        <v>1.33</v>
       </c>
       <c r="S54">
-        <v>2.38</v>
+        <v>7.13</v>
       </c>
       <c r="T54">
-        <v>2.07</v>
+        <v>2.55</v>
       </c>
       <c r="U54">
-        <v>5.08</v>
+        <v>1.81</v>
       </c>
       <c r="V54">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W54">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="X54">
-        <v>2.9</v>
+        <v>2.18</v>
       </c>
       <c r="Y54">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="Z54">
-        <v>7.5</v>
+        <v>4.55</v>
       </c>
       <c r="AA54">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AB54">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC54">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AD54">
-        <v>3.08</v>
+        <v>4.2</v>
       </c>
       <c r="AE54">
-        <v>1.88</v>
+        <v>1.52</v>
       </c>
       <c r="AF54">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="AG54">
-        <v>3.51</v>
+        <v>2.29</v>
       </c>
       <c r="AH54">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="AI54">
-        <v>6.65</v>
+        <v>4</v>
       </c>
       <c r="AJ54">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AK54">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AL54">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AM54">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="AN54">
-        <v>1.94</v>
+        <v>1.05</v>
       </c>
       <c r="AO54">
         <v>0</v>
       </c>
       <c r="AP54">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AQ54">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AR54">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AS54">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AT54">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AU54">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AV54">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AW54">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AX54">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AY54">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ54">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="BA54">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="BB54">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC54">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="BD54">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BE54">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="BF54">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG54">
         <v>0</v>
@@ -11305,7 +11305,7 @@
         <v>77</v>
       </c>
       <c r="C55" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="D55" t="s">
         <v>134</v>
@@ -11344,133 +11344,133 @@
         <v>308</v>
       </c>
       <c r="P55">
-        <v>1.58</v>
+        <v>2.13</v>
       </c>
       <c r="Q55">
-        <v>4.33</v>
+        <v>2.99</v>
       </c>
       <c r="R55">
-        <v>4.92</v>
+        <v>3.3</v>
       </c>
       <c r="S55">
-        <v>1.91</v>
+        <v>3</v>
       </c>
       <c r="T55">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="U55">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V55">
-        <v>1.24</v>
+        <v>1.6</v>
       </c>
       <c r="W55">
-        <v>3.7</v>
+        <v>2.22</v>
       </c>
       <c r="X55">
-        <v>2.25</v>
+        <v>3.48</v>
       </c>
       <c r="Y55">
-        <v>1.6</v>
+        <v>1.22</v>
       </c>
       <c r="Z55">
-        <v>5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA55">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="AB55">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AC55">
+        <v>1.49</v>
+      </c>
+      <c r="AD55">
+        <v>2.49</v>
+      </c>
+      <c r="AE55">
+        <v>2.6</v>
+      </c>
+      <c r="AF55">
+        <v>1.45</v>
+      </c>
+      <c r="AG55">
+        <v>4.7</v>
+      </c>
+      <c r="AH55">
         <v>1.13</v>
       </c>
-      <c r="AD55">
-        <v>4.95</v>
-      </c>
-      <c r="AE55">
-        <v>1.48</v>
-      </c>
-      <c r="AF55">
-        <v>2.4</v>
-      </c>
-      <c r="AG55">
-        <v>2.35</v>
-      </c>
-      <c r="AH55">
-        <v>1.59</v>
-      </c>
       <c r="AI55">
-        <v>3.88</v>
+        <v>9.5</v>
       </c>
       <c r="AJ55">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="AK55">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="AL55">
-        <v>2.2</v>
+        <v>1.66</v>
       </c>
       <c r="AM55">
-        <v>1.17</v>
+        <v>1.34</v>
       </c>
       <c r="AN55">
-        <v>2.25</v>
+        <v>1.52</v>
       </c>
       <c r="AO55">
         <v>0</v>
       </c>
       <c r="AP55">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="AQ55">
-        <v>1.34</v>
+        <v>1.68</v>
       </c>
       <c r="AR55">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AS55">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="AT55">
-        <v>2.67</v>
+        <v>3.65</v>
       </c>
       <c r="AU55">
-        <v>4</v>
+        <v>2.65</v>
       </c>
       <c r="AV55">
-        <v>2.78</v>
+        <v>2.04</v>
       </c>
       <c r="AW55">
-        <v>2.08</v>
+        <v>1.64</v>
       </c>
       <c r="AX55">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="AY55">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="AZ55">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="BA55">
-        <v>3.8</v>
+        <v>2.14</v>
       </c>
       <c r="BB55">
-        <v>1.11</v>
+        <v>1.32</v>
       </c>
       <c r="BC55">
-        <v>1.74</v>
+        <v>2.63</v>
       </c>
       <c r="BD55">
-        <v>5.2</v>
+        <v>2.96</v>
       </c>
       <c r="BE55">
-        <v>2.02</v>
+        <v>1.43</v>
       </c>
       <c r="BF55">
-        <v>1.28</v>
+        <v>1.06</v>
       </c>
       <c r="BG55">
         <v>0</v>
@@ -11490,7 +11490,7 @@
         <v>77</v>
       </c>
       <c r="C56" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D56" t="s">
         <v>134</v>
@@ -11529,133 +11529,133 @@
         <v>308</v>
       </c>
       <c r="P56">
-        <v>2.61</v>
+        <v>1.57</v>
       </c>
       <c r="Q56">
-        <v>3.34</v>
+        <v>4.2</v>
       </c>
       <c r="R56">
-        <v>2.52</v>
+        <v>4.33</v>
       </c>
       <c r="S56">
-        <v>3.7</v>
+        <v>1.91</v>
       </c>
       <c r="T56">
-        <v>2.01</v>
+        <v>2.4</v>
       </c>
       <c r="U56">
-        <v>3.01</v>
+        <v>5</v>
       </c>
       <c r="V56">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="W56">
-        <v>2.62</v>
+        <v>3.5</v>
       </c>
       <c r="X56">
-        <v>3.16</v>
+        <v>2.25</v>
       </c>
       <c r="Y56">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="Z56">
-        <v>8.699999999999999</v>
+        <v>5</v>
       </c>
       <c r="AA56">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AB56">
         <v>1.01</v>
       </c>
       <c r="AC56">
-        <v>1.39</v>
+        <v>1.13</v>
       </c>
       <c r="AD56">
-        <v>2.81</v>
+        <v>4.95</v>
       </c>
       <c r="AE56">
-        <v>2.19</v>
+        <v>1.48</v>
       </c>
       <c r="AF56">
-        <v>1.64</v>
+        <v>2.4</v>
       </c>
       <c r="AG56">
-        <v>4.02</v>
+        <v>2.35</v>
       </c>
       <c r="AH56">
+        <v>1.59</v>
+      </c>
+      <c r="AI56">
+        <v>3.88</v>
+      </c>
+      <c r="AJ56">
+        <v>1.18</v>
+      </c>
+      <c r="AK56">
+        <v>1.57</v>
+      </c>
+      <c r="AL56">
+        <v>2.2</v>
+      </c>
+      <c r="AM56">
         <v>1.17</v>
       </c>
-      <c r="AI56">
-        <v>8.5</v>
-      </c>
-      <c r="AJ56">
-        <v>1.04</v>
-      </c>
-      <c r="AK56">
-        <v>1.87</v>
-      </c>
-      <c r="AL56">
-        <v>1.83</v>
-      </c>
-      <c r="AM56">
-        <v>1.3</v>
-      </c>
       <c r="AN56">
-        <v>1.37</v>
+        <v>2.25</v>
       </c>
       <c r="AO56">
         <v>0</v>
       </c>
       <c r="AP56">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ56">
-        <v>1.54</v>
+        <v>1.34</v>
       </c>
       <c r="AR56">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AS56">
-        <v>2.46</v>
+        <v>2.05</v>
       </c>
       <c r="AT56">
-        <v>3.35</v>
+        <v>2.67</v>
       </c>
       <c r="AU56">
-        <v>3.14</v>
+        <v>4</v>
       </c>
       <c r="AV56">
-        <v>2.27</v>
+        <v>2.78</v>
       </c>
       <c r="AW56">
-        <v>1.79</v>
+        <v>2.08</v>
       </c>
       <c r="AX56">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="AY56">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="AZ56">
-        <v>2.92</v>
+        <v>1.36</v>
       </c>
       <c r="BA56">
-        <v>1.67</v>
+        <v>3.55</v>
       </c>
       <c r="BB56">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="BC56">
-        <v>2.36</v>
+        <v>1.74</v>
       </c>
       <c r="BD56">
-        <v>3.35</v>
+        <v>5.4</v>
       </c>
       <c r="BE56">
-        <v>1.51</v>
+        <v>2.02</v>
       </c>
       <c r="BF56">
-        <v>1.08</v>
+        <v>1.32</v>
       </c>
       <c r="BG56">
         <v>0</v>
@@ -11675,7 +11675,7 @@
         <v>77</v>
       </c>
       <c r="C57" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D57" t="s">
         <v>134</v>
@@ -11714,13 +11714,13 @@
         <v>308</v>
       </c>
       <c r="P57">
-        <v>2.04</v>
+        <v>1.7</v>
       </c>
       <c r="Q57">
-        <v>3.42</v>
+        <v>4.35</v>
       </c>
       <c r="R57">
-        <v>3.43</v>
+        <v>3.47</v>
       </c>
       <c r="S57">
         <v>0</v>
@@ -12045,10 +12045,10 @@
         <v>77</v>
       </c>
       <c r="C59" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D59" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E59" t="s">
         <v>194</v>
@@ -12084,133 +12084,133 @@
         <v>308</v>
       </c>
       <c r="P59">
-        <v>2.17</v>
+        <v>2.81</v>
       </c>
       <c r="Q59">
-        <v>3.54</v>
+        <v>3.3</v>
       </c>
       <c r="R59">
-        <v>3.03</v>
+        <v>2.41</v>
       </c>
       <c r="S59">
-        <v>2.5</v>
+        <v>3.23</v>
       </c>
       <c r="T59">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="U59">
-        <v>3.58</v>
+        <v>2.83</v>
       </c>
       <c r="V59">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="W59">
-        <v>3.16</v>
+        <v>2.95</v>
       </c>
       <c r="X59">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="Y59">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="Z59">
-        <v>5.55</v>
+        <v>7.1</v>
       </c>
       <c r="AA59">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AB59">
         <v>1.01</v>
       </c>
       <c r="AC59">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AD59">
-        <v>4.41</v>
+        <v>3.18</v>
       </c>
       <c r="AE59">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AF59">
-        <v>2.16</v>
+        <v>1.84</v>
       </c>
       <c r="AG59">
-        <v>2.63</v>
+        <v>3.41</v>
       </c>
       <c r="AH59">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AI59">
-        <v>4.55</v>
+        <v>5.75</v>
       </c>
       <c r="AJ59">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AK59">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AL59">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="AM59">
+        <v>1.28</v>
+      </c>
+      <c r="AN59">
+        <v>1.37</v>
+      </c>
+      <c r="AO59">
+        <v>0</v>
+      </c>
+      <c r="AP59">
+        <v>1.26</v>
+      </c>
+      <c r="AQ59">
+        <v>1.46</v>
+      </c>
+      <c r="AR59">
+        <v>1.75</v>
+      </c>
+      <c r="AS59">
+        <v>2.18</v>
+      </c>
+      <c r="AT59">
+        <v>2.8</v>
+      </c>
+      <c r="AU59">
+        <v>3.4</v>
+      </c>
+      <c r="AV59">
+        <v>2.5</v>
+      </c>
+      <c r="AW59">
+        <v>1.93</v>
+      </c>
+      <c r="AX59">
+        <v>1.58</v>
+      </c>
+      <c r="AY59">
+        <v>1.37</v>
+      </c>
+      <c r="AZ59">
+        <v>2.12</v>
+      </c>
+      <c r="BA59">
+        <v>1.91</v>
+      </c>
+      <c r="BB59">
         <v>1.25</v>
       </c>
-      <c r="AN59">
-        <v>1.61</v>
-      </c>
-      <c r="AO59">
-        <v>0</v>
-      </c>
-      <c r="AP59">
-        <v>1.18</v>
-      </c>
-      <c r="AQ59">
-        <v>1.34</v>
-      </c>
-      <c r="AR59">
-        <v>1.58</v>
-      </c>
-      <c r="AS59">
-        <v>2.05</v>
-      </c>
-      <c r="AT59">
-        <v>2.45</v>
-      </c>
-      <c r="AU59">
-        <v>3.95</v>
-      </c>
-      <c r="AV59">
-        <v>2.85</v>
-      </c>
-      <c r="AW59">
+      <c r="BC59">
         <v>2.14</v>
       </c>
-      <c r="AX59">
-        <v>1.7</v>
-      </c>
-      <c r="AY59">
-        <v>1.45</v>
-      </c>
-      <c r="AZ59">
-        <v>1.76</v>
-      </c>
-      <c r="BA59">
-        <v>2.33</v>
-      </c>
-      <c r="BB59">
+      <c r="BD59">
+        <v>3.66</v>
+      </c>
+      <c r="BE59">
+        <v>1.66</v>
+      </c>
+      <c r="BF59">
         <v>1.14</v>
-      </c>
-      <c r="BC59">
-        <v>1.87</v>
-      </c>
-      <c r="BD59">
-        <v>4.45</v>
-      </c>
-      <c r="BE59">
-        <v>1.87</v>
-      </c>
-      <c r="BF59">
-        <v>1.22</v>
       </c>
       <c r="BG59">
         <v>0</v>
@@ -12230,7 +12230,7 @@
         <v>77</v>
       </c>
       <c r="C60" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="D60" t="s">
         <v>134</v>
@@ -12269,133 +12269,133 @@
         <v>308</v>
       </c>
       <c r="P60">
-        <v>1.73</v>
+        <v>2.61</v>
       </c>
       <c r="Q60">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="R60">
-        <v>4.59</v>
+        <v>2.52</v>
       </c>
       <c r="S60">
-        <v>2.32</v>
+        <v>3.25</v>
       </c>
       <c r="T60">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="U60">
-        <v>5.6</v>
+        <v>3.01</v>
       </c>
       <c r="V60">
         <v>1.44</v>
       </c>
       <c r="W60">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="X60">
-        <v>3.08</v>
+        <v>3.16</v>
       </c>
       <c r="Y60">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z60">
-        <v>7.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA60">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AB60">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC60">
         <v>1.33</v>
       </c>
       <c r="AD60">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="AE60">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AF60">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG60">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AH60">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AI60">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="AJ60">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AK60">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="AL60">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AM60">
+        <v>1.3</v>
+      </c>
+      <c r="AN60">
+        <v>1.37</v>
+      </c>
+      <c r="AO60">
+        <v>0</v>
+      </c>
+      <c r="AP60">
+        <v>1.27</v>
+      </c>
+      <c r="AQ60">
+        <v>1.54</v>
+      </c>
+      <c r="AR60">
+        <v>2.2</v>
+      </c>
+      <c r="AS60">
+        <v>2.46</v>
+      </c>
+      <c r="AT60">
+        <v>3.35</v>
+      </c>
+      <c r="AU60">
+        <v>3.14</v>
+      </c>
+      <c r="AV60">
+        <v>2.27</v>
+      </c>
+      <c r="AW60">
+        <v>1.79</v>
+      </c>
+      <c r="AX60">
+        <v>1.46</v>
+      </c>
+      <c r="AY60">
         <v>1.24</v>
       </c>
-      <c r="AN60">
-        <v>1.94</v>
-      </c>
-      <c r="AO60">
-        <v>0</v>
-      </c>
-      <c r="AP60">
-        <v>1.36</v>
-      </c>
-      <c r="AQ60">
-        <v>1.62</v>
-      </c>
-      <c r="AR60">
-        <v>2</v>
-      </c>
-      <c r="AS60">
-        <v>2.55</v>
-      </c>
-      <c r="AT60">
-        <v>3.3</v>
-      </c>
-      <c r="AU60">
-        <v>2.85</v>
-      </c>
-      <c r="AV60">
-        <v>2.14</v>
-      </c>
-      <c r="AW60">
-        <v>1.71</v>
-      </c>
-      <c r="AX60">
-        <v>1.44</v>
-      </c>
-      <c r="AY60">
+      <c r="AZ60">
+        <v>2.92</v>
+      </c>
+      <c r="BA60">
+        <v>1.66</v>
+      </c>
+      <c r="BB60">
         <v>1.27</v>
       </c>
-      <c r="AZ60">
-        <v>1.48</v>
-      </c>
-      <c r="BA60">
-        <v>2.85</v>
-      </c>
-      <c r="BB60">
-        <v>1.24</v>
-      </c>
       <c r="BC60">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="BD60">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="BE60">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="BF60">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="BG60">
         <v>0</v>
@@ -12415,10 +12415,10 @@
         <v>77</v>
       </c>
       <c r="C61" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D61" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E61" t="s">
         <v>196</v>
@@ -12454,133 +12454,133 @@
         <v>308</v>
       </c>
       <c r="P61">
-        <v>1.38</v>
+        <v>2.21</v>
       </c>
       <c r="Q61">
-        <v>5.48</v>
+        <v>3.52</v>
       </c>
       <c r="R61">
-        <v>7.06</v>
+        <v>2.96</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T61">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="U61">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="V61">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W61">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X61">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y61">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z61">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA61">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD61">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE61">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF61">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG61">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH61">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI61">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AJ61">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK61">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL61">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AM61">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN61">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AO61">
         <v>0</v>
       </c>
       <c r="AP61">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ61">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR61">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AS61">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AT61">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AU61">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AV61">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AW61">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AX61">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AY61">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ61">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BA61">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="BB61">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC61">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BD61">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="BE61">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BF61">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG61">
         <v>0</v>
@@ -12600,7 +12600,7 @@
         <v>77</v>
       </c>
       <c r="C62" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D62" t="s">
         <v>136</v>
@@ -12639,133 +12639,133 @@
         <v>308</v>
       </c>
       <c r="P62">
-        <v>2.81</v>
+        <v>1.35</v>
       </c>
       <c r="Q62">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="R62">
-        <v>2.41</v>
+        <v>7.2</v>
       </c>
       <c r="S62">
-        <v>3.23</v>
+        <v>1.67</v>
       </c>
       <c r="T62">
-        <v>2.06</v>
+        <v>2.8</v>
       </c>
       <c r="U62">
-        <v>2.83</v>
+        <v>5.9</v>
       </c>
       <c r="V62">
-        <v>1.42</v>
+        <v>1.17</v>
       </c>
       <c r="W62">
-        <v>2.95</v>
+        <v>4.25</v>
       </c>
       <c r="X62">
-        <v>2.75</v>
+        <v>1.9</v>
       </c>
       <c r="Y62">
-        <v>1.36</v>
+        <v>1.84</v>
       </c>
       <c r="Z62">
-        <v>7.1</v>
+        <v>3.66</v>
       </c>
       <c r="AA62">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="AB62">
         <v>1.01</v>
       </c>
       <c r="AC62">
-        <v>1.27</v>
+        <v>1.06</v>
       </c>
       <c r="AD62">
-        <v>3.18</v>
+        <v>7</v>
       </c>
       <c r="AE62">
-        <v>2</v>
+        <v>1.28</v>
       </c>
       <c r="AF62">
-        <v>1.84</v>
+        <v>3.5</v>
       </c>
       <c r="AG62">
-        <v>3.41</v>
+        <v>1.85</v>
       </c>
       <c r="AH62">
-        <v>1.3</v>
+        <v>1.98</v>
       </c>
       <c r="AI62">
-        <v>5.75</v>
+        <v>2.64</v>
       </c>
       <c r="AJ62">
-        <v>1.06</v>
+        <v>1.38</v>
       </c>
       <c r="AK62">
-        <v>1.75</v>
+        <v>1.48</v>
       </c>
       <c r="AL62">
-        <v>1.97</v>
+        <v>2.43</v>
       </c>
       <c r="AM62">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AN62">
-        <v>1.37</v>
+        <v>3.08</v>
       </c>
       <c r="AO62">
         <v>0</v>
       </c>
       <c r="AP62">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AQ62">
+        <v>1.29</v>
+      </c>
+      <c r="AR62">
+        <v>1.49</v>
+      </c>
+      <c r="AS62">
+        <v>1.78</v>
+      </c>
+      <c r="AT62">
+        <v>2.2</v>
+      </c>
+      <c r="AU62">
+        <v>0</v>
+      </c>
+      <c r="AV62">
+        <v>3.2</v>
+      </c>
+      <c r="AW62">
+        <v>2.38</v>
+      </c>
+      <c r="AX62">
+        <v>1.9</v>
+      </c>
+      <c r="AY62">
+        <v>1.58</v>
+      </c>
+      <c r="AZ62">
+        <v>1.22</v>
+      </c>
+      <c r="BA62">
+        <v>4.35</v>
+      </c>
+      <c r="BB62">
+        <v>1.07</v>
+      </c>
+      <c r="BC62">
+        <v>1.55</v>
+      </c>
+      <c r="BD62">
+        <v>6</v>
+      </c>
+      <c r="BE62">
+        <v>2.41</v>
+      </c>
+      <c r="BF62">
         <v>1.46</v>
-      </c>
-      <c r="AR62">
-        <v>1.75</v>
-      </c>
-      <c r="AS62">
-        <v>2.18</v>
-      </c>
-      <c r="AT62">
-        <v>2.8</v>
-      </c>
-      <c r="AU62">
-        <v>3.4</v>
-      </c>
-      <c r="AV62">
-        <v>2.5</v>
-      </c>
-      <c r="AW62">
-        <v>1.93</v>
-      </c>
-      <c r="AX62">
-        <v>1.58</v>
-      </c>
-      <c r="AY62">
-        <v>1.37</v>
-      </c>
-      <c r="AZ62">
-        <v>2.12</v>
-      </c>
-      <c r="BA62">
-        <v>1.91</v>
-      </c>
-      <c r="BB62">
-        <v>1.25</v>
-      </c>
-      <c r="BC62">
-        <v>2.14</v>
-      </c>
-      <c r="BD62">
-        <v>3.66</v>
-      </c>
-      <c r="BE62">
-        <v>1.66</v>
-      </c>
-      <c r="BF62">
-        <v>1.14</v>
       </c>
       <c r="BG62">
         <v>0</v>
@@ -13155,10 +13155,10 @@
         <v>79</v>
       </c>
       <c r="C65" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="D65" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E65" t="s">
         <v>200</v>
@@ -13194,133 +13194,133 @@
         <v>308</v>
       </c>
       <c r="P65">
-        <v>2.65</v>
+        <v>2.94</v>
       </c>
       <c r="Q65">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R65">
-        <v>2.65</v>
+        <v>2.21</v>
       </c>
       <c r="S65">
-        <v>2.96</v>
+        <v>3.35</v>
       </c>
       <c r="T65">
-        <v>2.04</v>
+        <v>2.23</v>
       </c>
       <c r="U65">
-        <v>3.69</v>
+        <v>2.75</v>
       </c>
       <c r="V65">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W65">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="X65">
-        <v>2.95</v>
+        <v>2.48</v>
       </c>
       <c r="Y65">
+        <v>1.41</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+      <c r="AA65">
+        <v>0</v>
+      </c>
+      <c r="AB65">
+        <v>0</v>
+      </c>
+      <c r="AC65">
+        <v>1.23</v>
+      </c>
+      <c r="AD65">
+        <v>3.5</v>
+      </c>
+      <c r="AE65">
+        <v>1.77</v>
+      </c>
+      <c r="AF65">
+        <v>1.87</v>
+      </c>
+      <c r="AG65">
+        <v>2.9</v>
+      </c>
+      <c r="AH65">
         <v>1.33</v>
       </c>
-      <c r="Z65">
-        <v>8</v>
-      </c>
-      <c r="AA65">
-        <v>1.02</v>
-      </c>
-      <c r="AB65">
-        <v>1.01</v>
-      </c>
-      <c r="AC65">
-        <v>1.31</v>
-      </c>
-      <c r="AD65">
-        <v>2.92</v>
-      </c>
-      <c r="AE65">
-        <v>2.09</v>
-      </c>
-      <c r="AF65">
-        <v>1.7</v>
-      </c>
-      <c r="AG65">
-        <v>3.58</v>
-      </c>
-      <c r="AH65">
-        <v>1.21</v>
-      </c>
       <c r="AI65">
-        <v>7.3</v>
+        <v>5.2</v>
       </c>
       <c r="AJ65">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AK65">
-        <v>1.82</v>
+        <v>1.64</v>
       </c>
       <c r="AL65">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="AM65">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AN65">
-        <v>1.54</v>
+        <v>1.29</v>
       </c>
       <c r="AO65">
         <v>0</v>
       </c>
       <c r="AP65">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ65">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR65">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AS65">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AT65">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AU65">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AV65">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AW65">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AX65">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AY65">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ65">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BA65">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BB65">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC65">
-        <v>2.29</v>
+        <v>1.97</v>
       </c>
       <c r="BD65">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="BE65">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="BF65">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG65">
         <v>0</v>
@@ -13340,10 +13340,10 @@
         <v>79</v>
       </c>
       <c r="C66" t="s">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="D66" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E66" t="s">
         <v>201</v>
@@ -13379,133 +13379,133 @@
         <v>308</v>
       </c>
       <c r="P66">
-        <v>2.94</v>
+        <v>2.3</v>
       </c>
       <c r="Q66">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R66">
-        <v>2.21</v>
+        <v>3</v>
       </c>
       <c r="S66">
-        <v>3.35</v>
+        <v>2.96</v>
       </c>
       <c r="T66">
-        <v>2.23</v>
+        <v>2.04</v>
       </c>
       <c r="U66">
+        <v>3.69</v>
+      </c>
+      <c r="V66">
+        <v>1.41</v>
+      </c>
+      <c r="W66">
+        <v>2.66</v>
+      </c>
+      <c r="X66">
+        <v>2.99</v>
+      </c>
+      <c r="Y66">
+        <v>1.33</v>
+      </c>
+      <c r="Z66">
+        <v>8</v>
+      </c>
+      <c r="AA66">
+        <v>1.02</v>
+      </c>
+      <c r="AB66">
+        <v>1.01</v>
+      </c>
+      <c r="AC66">
+        <v>1.31</v>
+      </c>
+      <c r="AD66">
+        <v>2.92</v>
+      </c>
+      <c r="AE66">
+        <v>2.09</v>
+      </c>
+      <c r="AF66">
+        <v>1.7</v>
+      </c>
+      <c r="AG66">
+        <v>3.7</v>
+      </c>
+      <c r="AH66">
+        <v>1.24</v>
+      </c>
+      <c r="AI66">
+        <v>7.3</v>
+      </c>
+      <c r="AJ66">
+        <v>1.03</v>
+      </c>
+      <c r="AK66">
+        <v>1.82</v>
+      </c>
+      <c r="AL66">
+        <v>1.86</v>
+      </c>
+      <c r="AM66">
+        <v>1.29</v>
+      </c>
+      <c r="AN66">
+        <v>1.54</v>
+      </c>
+      <c r="AO66">
+        <v>0</v>
+      </c>
+      <c r="AP66">
+        <v>1.31</v>
+      </c>
+      <c r="AQ66">
+        <v>1.47</v>
+      </c>
+      <c r="AR66">
+        <v>2.31</v>
+      </c>
+      <c r="AS66">
+        <v>2.58</v>
+      </c>
+      <c r="AT66">
+        <v>3.57</v>
+      </c>
+      <c r="AU66">
+        <v>2.98</v>
+      </c>
+      <c r="AV66">
+        <v>2.18</v>
+      </c>
+      <c r="AW66">
+        <v>1.73</v>
+      </c>
+      <c r="AX66">
+        <v>1.42</v>
+      </c>
+      <c r="AY66">
+        <v>1.21</v>
+      </c>
+      <c r="AZ66">
+        <v>1.68</v>
+      </c>
+      <c r="BA66">
         <v>2.75</v>
       </c>
-      <c r="V66">
-        <v>0</v>
-      </c>
-      <c r="W66">
-        <v>0</v>
-      </c>
-      <c r="X66">
-        <v>2.48</v>
-      </c>
-      <c r="Y66">
-        <v>1.41</v>
-      </c>
-      <c r="Z66">
-        <v>0</v>
-      </c>
-      <c r="AA66">
-        <v>0</v>
-      </c>
-      <c r="AB66">
-        <v>0</v>
-      </c>
-      <c r="AC66">
-        <v>1.23</v>
-      </c>
-      <c r="AD66">
-        <v>3.5</v>
-      </c>
-      <c r="AE66">
-        <v>1.77</v>
-      </c>
-      <c r="AF66">
-        <v>1.87</v>
-      </c>
-      <c r="AG66">
-        <v>2.9</v>
-      </c>
-      <c r="AH66">
-        <v>1.33</v>
-      </c>
-      <c r="AI66">
-        <v>5.2</v>
-      </c>
-      <c r="AJ66">
-        <v>1.1</v>
-      </c>
-      <c r="AK66">
-        <v>1.64</v>
-      </c>
-      <c r="AL66">
-        <v>2.1</v>
-      </c>
-      <c r="AM66">
-        <v>1.23</v>
-      </c>
-      <c r="AN66">
-        <v>1.29</v>
-      </c>
-      <c r="AO66">
-        <v>0</v>
-      </c>
-      <c r="AP66">
-        <v>0</v>
-      </c>
-      <c r="AQ66">
-        <v>0</v>
-      </c>
-      <c r="AR66">
-        <v>0</v>
-      </c>
-      <c r="AS66">
-        <v>0</v>
-      </c>
-      <c r="AT66">
-        <v>0</v>
-      </c>
-      <c r="AU66">
-        <v>0</v>
-      </c>
-      <c r="AV66">
-        <v>0</v>
-      </c>
-      <c r="AW66">
-        <v>0</v>
-      </c>
-      <c r="AX66">
-        <v>0</v>
-      </c>
-      <c r="AY66">
-        <v>0</v>
-      </c>
-      <c r="AZ66">
-        <v>0</v>
-      </c>
-      <c r="BA66">
-        <v>0</v>
-      </c>
       <c r="BB66">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC66">
-        <v>1.97</v>
+        <v>2.29</v>
       </c>
       <c r="BD66">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="BE66">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="BF66">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG66">
         <v>0</v>
@@ -13531,7 +13531,7 @@
         <v>134</v>
       </c>
       <c r="E67" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="F67" t="s">
         <v>287</v>
@@ -13564,133 +13564,133 @@
         <v>308</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>5.97</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="S67">
-        <v>2.07</v>
+        <v>1.65</v>
       </c>
       <c r="T67">
-        <v>2.42</v>
+        <v>2.8</v>
       </c>
       <c r="U67">
-        <v>4.5</v>
+        <v>6.45</v>
       </c>
       <c r="V67">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="W67">
-        <v>3.42</v>
+        <v>4.15</v>
       </c>
       <c r="X67">
-        <v>2.18</v>
+        <v>1.97</v>
       </c>
       <c r="Y67">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="Z67">
-        <v>4.7</v>
+        <v>3.98</v>
       </c>
       <c r="AA67">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AB67">
         <v>1.01</v>
       </c>
       <c r="AC67">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="AD67">
-        <v>4.66</v>
+        <v>5.95</v>
       </c>
       <c r="AE67">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="AF67">
-        <v>2.33</v>
+        <v>2.81</v>
       </c>
       <c r="AG67">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="AH67">
+        <v>1.78</v>
+      </c>
+      <c r="AI67">
+        <v>3.05</v>
+      </c>
+      <c r="AJ67">
+        <v>1.28</v>
+      </c>
+      <c r="AK67">
+        <v>1.63</v>
+      </c>
+      <c r="AL67">
+        <v>2.12</v>
+      </c>
+      <c r="AM67">
+        <v>1.1</v>
+      </c>
+      <c r="AN67">
+        <v>3.42</v>
+      </c>
+      <c r="AO67">
+        <v>0</v>
+      </c>
+      <c r="AP67">
+        <v>1.19</v>
+      </c>
+      <c r="AQ67">
+        <v>1.35</v>
+      </c>
+      <c r="AR67">
+        <v>1.57</v>
+      </c>
+      <c r="AS67">
+        <v>1.92</v>
+      </c>
+      <c r="AT67">
+        <v>2.43</v>
+      </c>
+      <c r="AU67">
+        <v>3.9</v>
+      </c>
+      <c r="AV67">
+        <v>2.8</v>
+      </c>
+      <c r="AW67">
+        <v>2.15</v>
+      </c>
+      <c r="AX67">
+        <v>1.73</v>
+      </c>
+      <c r="AY67">
+        <v>1.45</v>
+      </c>
+      <c r="AZ67">
+        <v>1.3</v>
+      </c>
+      <c r="BA67">
+        <v>3.95</v>
+      </c>
+      <c r="BB67">
+        <v>1.09</v>
+      </c>
+      <c r="BC67">
         <v>1.58</v>
       </c>
-      <c r="AI67">
-        <v>3.75</v>
-      </c>
-      <c r="AJ67">
-        <v>1.19</v>
-      </c>
-      <c r="AK67">
-        <v>1.55</v>
-      </c>
-      <c r="AL67">
-        <v>2.27</v>
-      </c>
-      <c r="AM67">
-        <v>1.2</v>
-      </c>
-      <c r="AN67">
-        <v>2.17</v>
-      </c>
-      <c r="AO67">
-        <v>0</v>
-      </c>
-      <c r="AP67">
-        <v>1.2</v>
-      </c>
-      <c r="AQ67">
+      <c r="BD67">
+        <v>6.1</v>
+      </c>
+      <c r="BE67">
+        <v>2.16</v>
+      </c>
+      <c r="BF67">
         <v>1.36</v>
-      </c>
-      <c r="AR67">
-        <v>1.61</v>
-      </c>
-      <c r="AS67">
-        <v>1.97</v>
-      </c>
-      <c r="AT67">
-        <v>2.5</v>
-      </c>
-      <c r="AU67">
-        <v>3.8</v>
-      </c>
-      <c r="AV67">
-        <v>2.75</v>
-      </c>
-      <c r="AW67">
-        <v>2.1</v>
-      </c>
-      <c r="AX67">
-        <v>1.68</v>
-      </c>
-      <c r="AY67">
-        <v>1.43</v>
-      </c>
-      <c r="AZ67">
-        <v>1.55</v>
-      </c>
-      <c r="BA67">
-        <v>2.8</v>
-      </c>
-      <c r="BB67">
-        <v>1.12</v>
-      </c>
-      <c r="BC67">
-        <v>1.75</v>
-      </c>
-      <c r="BD67">
-        <v>4.7</v>
-      </c>
-      <c r="BE67">
-        <v>1.95</v>
-      </c>
-      <c r="BF67">
-        <v>1.26</v>
       </c>
       <c r="BG67">
         <v>0</v>
@@ -13710,13 +13710,13 @@
         <v>80</v>
       </c>
       <c r="C68" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="D68" t="s">
         <v>134</v>
       </c>
       <c r="E68" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F68" t="s">
         <v>288</v>
@@ -13895,13 +13895,13 @@
         <v>80</v>
       </c>
       <c r="C69" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D69" t="s">
         <v>134</v>
       </c>
       <c r="E69" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F69" t="s">
         <v>289</v>
@@ -13943,124 +13943,124 @@
         <v>0</v>
       </c>
       <c r="S69">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T69">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U69">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V69">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W69">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="X69">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Y69">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z69">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA69">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC69">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD69">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AE69">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF69">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AG69">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH69">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI69">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AJ69">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK69">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL69">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AM69">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN69">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AO69">
         <v>0</v>
       </c>
       <c r="AP69">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AQ69">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR69">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS69">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AT69">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AU69">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AV69">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AW69">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AX69">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY69">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AZ69">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BA69">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BB69">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC69">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BD69">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE69">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF69">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BG69">
         <v>0</v>
@@ -14080,13 +14080,13 @@
         <v>80</v>
       </c>
       <c r="C70" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="D70" t="s">
         <v>134</v>
       </c>
       <c r="E70" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="F70" t="s">
         <v>290</v>
@@ -14119,13 +14119,13 @@
         <v>308</v>
       </c>
       <c r="P70">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Q70">
-        <v>5.09</v>
+        <v>0</v>
       </c>
       <c r="R70">
-        <v>6.37</v>
+        <v>0</v>
       </c>
       <c r="S70">
         <v>0</v>
@@ -14265,7 +14265,7 @@
         <v>81</v>
       </c>
       <c r="C71" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D71" t="s">
         <v>134</v>
@@ -14489,22 +14489,22 @@
         <v>308</v>
       </c>
       <c r="P72">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="Q72">
-        <v>5.41</v>
+        <v>4.2</v>
       </c>
       <c r="R72">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="S72">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="T72">
         <v>2.5</v>
       </c>
       <c r="U72">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="V72">
         <v>1.22</v>
@@ -14531,22 +14531,22 @@
         <v>1.15</v>
       </c>
       <c r="AD72">
-        <v>5.25</v>
+        <v>5.35</v>
       </c>
       <c r="AE72">
         <v>1.5</v>
       </c>
       <c r="AF72">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="AG72">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="AH72">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AI72">
-        <v>3.7</v>
+        <v>3.78</v>
       </c>
       <c r="AJ72">
         <v>1.18</v>
@@ -14561,7 +14561,7 @@
         <v>1.19</v>
       </c>
       <c r="AN72">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="AO72">
         <v>0</v>
@@ -14570,40 +14570,40 @@
         <v>1.2</v>
       </c>
       <c r="AQ72">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AR72">
-        <v>1.6</v>
+        <v>1.94</v>
       </c>
       <c r="AS72">
         <v>1.96</v>
       </c>
       <c r="AT72">
-        <v>2.45</v>
+        <v>3.42</v>
       </c>
       <c r="AU72">
         <v>3.85</v>
       </c>
       <c r="AV72">
-        <v>2.8</v>
+        <v>2.24</v>
       </c>
       <c r="AW72">
-        <v>2.14</v>
+        <v>1.75</v>
       </c>
       <c r="AX72">
-        <v>1.71</v>
+        <v>1.43</v>
       </c>
       <c r="AY72">
-        <v>1.46</v>
+        <v>1.23</v>
       </c>
       <c r="AZ72">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="BA72">
-        <v>4.1</v>
+        <v>5.25</v>
       </c>
       <c r="BB72">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="BC72">
         <v>1.66</v>
@@ -14635,7 +14635,7 @@
         <v>82</v>
       </c>
       <c r="C73" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D73" t="s">
         <v>134</v>
@@ -14674,133 +14674,133 @@
         <v>308</v>
       </c>
       <c r="P73">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="Q73">
-        <v>3.93</v>
+        <v>4.08</v>
       </c>
       <c r="R73">
-        <v>4.66</v>
+        <v>5.1</v>
       </c>
       <c r="S73">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T73">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U73">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="V73">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W73">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X73">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y73">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z73">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA73">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB73">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC73">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD73">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE73">
+        <v>1.9</v>
+      </c>
+      <c r="AF73">
+        <v>1.91</v>
+      </c>
+      <c r="AG73">
+        <v>3.1</v>
+      </c>
+      <c r="AH73">
+        <v>1.32</v>
+      </c>
+      <c r="AI73">
+        <v>5.7</v>
+      </c>
+      <c r="AJ73">
+        <v>1.08</v>
+      </c>
+      <c r="AK73">
         <v>1.85</v>
       </c>
-      <c r="AF73">
-        <v>1.85</v>
-      </c>
-      <c r="AG73">
-        <v>0</v>
-      </c>
-      <c r="AH73">
-        <v>0</v>
-      </c>
-      <c r="AI73">
-        <v>0</v>
-      </c>
-      <c r="AJ73">
-        <v>0</v>
-      </c>
-      <c r="AK73">
-        <v>0</v>
-      </c>
       <c r="AL73">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM73">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN73">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AO73">
         <v>0</v>
       </c>
       <c r="AP73">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ73">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AR73">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AS73">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AT73">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="AU73">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AV73">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AW73">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AX73">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY73">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AZ73">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BA73">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BB73">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC73">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD73">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE73">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF73">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG73">
         <v>0</v>
@@ -14820,7 +14820,7 @@
         <v>83</v>
       </c>
       <c r="C74" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="D74" t="s">
         <v>134</v>
@@ -14859,133 +14859,133 @@
         <v>308</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q74">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S74">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T74">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U74">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V74">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W74">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="X74">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y74">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z74">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA74">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC74">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD74">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AE74">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF74">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG74">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AH74">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI74">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AJ74">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK74">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL74">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM74">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AN74">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AO74">
         <v>0</v>
       </c>
       <c r="AP74">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ74">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR74">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AS74">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AT74">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AU74">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AV74">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AW74">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AX74">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY74">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ74">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BA74">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BB74">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC74">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BD74">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="BE74">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BF74">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG74">
         <v>0</v>
@@ -15005,7 +15005,7 @@
         <v>83</v>
       </c>
       <c r="C75" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D75" t="s">
         <v>134</v>
@@ -15044,133 +15044,133 @@
         <v>308</v>
       </c>
       <c r="P75">
-        <v>5.63</v>
+        <v>6.3</v>
       </c>
       <c r="Q75">
-        <v>4.21</v>
+        <v>4.6</v>
       </c>
       <c r="R75">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="S75">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="T75">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U75">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V75">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W75">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="X75">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Y75">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z75">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA75">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB75">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC75">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD75">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AE75">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AF75">
+        <v>2.3</v>
+      </c>
+      <c r="AG75">
+        <v>2.43</v>
+      </c>
+      <c r="AH75">
+        <v>1.5</v>
+      </c>
+      <c r="AI75">
+        <v>4.15</v>
+      </c>
+      <c r="AJ75">
+        <v>1.19</v>
+      </c>
+      <c r="AK75">
+        <v>1.75</v>
+      </c>
+      <c r="AL75">
+        <v>2.04</v>
+      </c>
+      <c r="AM75">
+        <v>1.2</v>
+      </c>
+      <c r="AN75">
+        <v>1.13</v>
+      </c>
+      <c r="AO75">
+        <v>0</v>
+      </c>
+      <c r="AP75">
+        <v>1.23</v>
+      </c>
+      <c r="AQ75">
+        <v>1.42</v>
+      </c>
+      <c r="AR75">
+        <v>1.71</v>
+      </c>
+      <c r="AS75">
         <v>2.15</v>
       </c>
-      <c r="AG75">
-        <v>0</v>
-      </c>
-      <c r="AH75">
-        <v>0</v>
-      </c>
-      <c r="AI75">
-        <v>0</v>
-      </c>
-      <c r="AJ75">
-        <v>0</v>
-      </c>
-      <c r="AK75">
-        <v>0</v>
-      </c>
-      <c r="AL75">
-        <v>0</v>
-      </c>
-      <c r="AM75">
-        <v>0</v>
-      </c>
-      <c r="AN75">
-        <v>0</v>
-      </c>
-      <c r="AO75">
-        <v>0</v>
-      </c>
-      <c r="AP75">
-        <v>0</v>
-      </c>
-      <c r="AQ75">
-        <v>0</v>
-      </c>
-      <c r="AR75">
-        <v>0</v>
-      </c>
-      <c r="AS75">
-        <v>0</v>
-      </c>
       <c r="AT75">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU75">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV75">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AW75">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AX75">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY75">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ75">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BA75">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BB75">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC75">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD75">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE75">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF75">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG75">
         <v>0</v>
@@ -15190,7 +15190,7 @@
         <v>83</v>
       </c>
       <c r="C76" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="D76" t="s">
         <v>134</v>
@@ -15229,133 +15229,133 @@
         <v>308</v>
       </c>
       <c r="P76">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q76">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R76">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="S76">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T76">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U76">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V76">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W76">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="X76">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y76">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z76">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA76">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB76">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC76">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AD76">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE76">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF76">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG76">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AH76">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI76">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AJ76">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK76">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL76">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM76">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AN76">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AO76">
         <v>0</v>
       </c>
       <c r="AP76">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ76">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AR76">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AS76">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AT76">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AU76">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AV76">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AW76">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AX76">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AY76">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AZ76">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BA76">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="BB76">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC76">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BD76">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE76">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BF76">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG76">
         <v>0</v>
@@ -15414,13 +15414,13 @@
         <v>308</v>
       </c>
       <c r="P77">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Q77">
-        <v>6.46</v>
+        <v>6.2</v>
       </c>
       <c r="R77">
-        <v>12.8</v>
+        <v>10.6</v>
       </c>
       <c r="S77">
         <v>0</v>
@@ -15459,10 +15459,10 @@
         <v>0</v>
       </c>
       <c r="AE77">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AF77">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AG77">
         <v>0</v>
@@ -15560,7 +15560,7 @@
         <v>85</v>
       </c>
       <c r="C78" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D78" t="s">
         <v>134</v>
@@ -15784,133 +15784,133 @@
         <v>308</v>
       </c>
       <c r="P79">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="Q79">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="R79">
-        <v>3.41</v>
+        <v>4.5</v>
       </c>
       <c r="S79">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T79">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U79">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="V79">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W79">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Y79">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z79">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA79">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC79">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD79">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE79">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AF79">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG79">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH79">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI79">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="AJ79">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK79">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AL79">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AM79">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN79">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AO79">
         <v>0</v>
       </c>
       <c r="AP79">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AQ79">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR79">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AS79">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AT79">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AU79">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AV79">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW79">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AX79">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY79">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ79">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="BA79">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="BB79">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC79">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="BD79">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE79">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF79">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG79">
         <v>0</v>
@@ -15969,133 +15969,133 @@
         <v>308</v>
       </c>
       <c r="P80">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="Q80">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="R80">
-        <v>4.5</v>
+        <v>3.41</v>
       </c>
       <c r="S80">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T80">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U80">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="V80">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W80">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="X80">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Y80">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z80">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AA80">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB80">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC80">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD80">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AE80">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AF80">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG80">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AH80">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI80">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="AJ80">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK80">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AL80">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AM80">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN80">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AO80">
         <v>0</v>
       </c>
       <c r="AP80">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AQ80">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AR80">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AS80">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AT80">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AU80">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AV80">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AW80">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AX80">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AY80">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ80">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="BA80">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="BB80">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BC80">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="BD80">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BE80">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF80">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG80">
         <v>0</v>
@@ -16300,7 +16300,7 @@
         <v>87</v>
       </c>
       <c r="C82" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D82" t="s">
         <v>136</v>
@@ -16339,79 +16339,79 @@
         <v>308</v>
       </c>
       <c r="P82">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q82">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="R82">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="S82">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T82">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="U82">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="V82">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W82">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="X82">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Y82">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z82">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA82">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB82">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC82">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD82">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AE82">
-        <v>2.87</v>
+        <v>2.31</v>
       </c>
       <c r="AF82">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AG82">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AH82">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI82">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AJ82">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK82">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AL82">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AM82">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN82">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AO82">
         <v>0</v>
@@ -16453,19 +16453,19 @@
         <v>0</v>
       </c>
       <c r="BB82">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC82">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="BD82">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="BE82">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF82">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG82">
         <v>0</v>
@@ -16524,79 +16524,79 @@
         <v>308</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S83">
-        <v>2.53</v>
+        <v>2.37</v>
       </c>
       <c r="T83">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="U83">
-        <v>5.16</v>
+        <v>6.5</v>
       </c>
       <c r="V83">
+        <v>1.55</v>
+      </c>
+      <c r="W83">
+        <v>2.26</v>
+      </c>
+      <c r="X83">
+        <v>3.5</v>
+      </c>
+      <c r="Y83">
+        <v>1.22</v>
+      </c>
+      <c r="Z83">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AA83">
+        <v>1.02</v>
+      </c>
+      <c r="AB83">
+        <v>1.06</v>
+      </c>
+      <c r="AC83">
         <v>1.48</v>
       </c>
-      <c r="W83">
-        <v>2.36</v>
-      </c>
-      <c r="X83">
-        <v>3.34</v>
-      </c>
-      <c r="Y83">
-        <v>1.25</v>
-      </c>
-      <c r="Z83">
-        <v>9</v>
-      </c>
-      <c r="AA83">
-        <v>1.01</v>
-      </c>
-      <c r="AB83">
-        <v>1.04</v>
-      </c>
-      <c r="AC83">
-        <v>1.4</v>
-      </c>
       <c r="AD83">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="AE83">
-        <v>2.31</v>
+        <v>2.43</v>
       </c>
       <c r="AF83">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AG83">
-        <v>4.35</v>
+        <v>4.7</v>
       </c>
       <c r="AH83">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AI83">
-        <v>8.9</v>
+        <v>10.5</v>
       </c>
       <c r="AJ83">
         <v>1.01</v>
       </c>
       <c r="AK83">
-        <v>2.06</v>
+        <v>2.29</v>
       </c>
       <c r="AL83">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AM83">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AN83">
-        <v>1.77</v>
+        <v>1.97</v>
       </c>
       <c r="AO83">
         <v>0</v>
@@ -16638,19 +16638,19 @@
         <v>0</v>
       </c>
       <c r="BB83">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="BC83">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="BD83">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="BE83">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="BF83">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="BG83">
         <v>0</v>
@@ -16670,7 +16670,7 @@
         <v>87</v>
       </c>
       <c r="C84" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D84" t="s">
         <v>136</v>
@@ -16709,79 +16709,79 @@
         <v>308</v>
       </c>
       <c r="P84">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="Q84">
-        <v>3.25</v>
+        <v>2.78</v>
       </c>
       <c r="R84">
-        <v>5</v>
+        <v>3.72</v>
       </c>
       <c r="S84">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="T84">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U84">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="V84">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W84">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="X84">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y84">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z84">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA84">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB84">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC84">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AD84">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AE84">
-        <v>2.43</v>
+        <v>2.87</v>
       </c>
       <c r="AF84">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG84">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AH84">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AI84">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AJ84">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK84">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AL84">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AM84">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN84">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AO84">
         <v>0</v>
@@ -16823,19 +16823,19 @@
         <v>0</v>
       </c>
       <c r="BB84">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BC84">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="BD84">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="BE84">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BF84">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BG84">
         <v>0</v>
@@ -16894,13 +16894,13 @@
         <v>308</v>
       </c>
       <c r="P85">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="Q85">
-        <v>3.82</v>
+        <v>3.9</v>
       </c>
       <c r="R85">
-        <v>3.86</v>
+        <v>3.4</v>
       </c>
       <c r="S85">
         <v>2.32</v>
@@ -16930,7 +16930,7 @@
         <v>1.13</v>
       </c>
       <c r="AB85">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC85">
         <v>1.09</v>
@@ -17225,7 +17225,7 @@
         <v>89</v>
       </c>
       <c r="C87" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D87" t="s">
         <v>136</v>

--- a/jogos_2026-05-04.xlsx
+++ b/jogos_2026-05-04.xlsx
@@ -301,57 +301,57 @@
     <t>Croatia Druga HNL</t>
   </si>
   <si>
+    <t>Serbia Prva Liga</t>
+  </si>
+  <si>
+    <t>England Premier League</t>
+  </si>
+  <si>
+    <t>India Indian Super League</t>
+  </si>
+  <si>
+    <t>Oman Professional League</t>
+  </si>
+  <si>
     <t>Russia FNL</t>
   </si>
   <si>
     <t>Uzbekistan Uzbekistan Super League</t>
   </si>
   <si>
-    <t>Serbia Prva Liga</t>
-  </si>
-  <si>
-    <t>India Indian Super League</t>
-  </si>
-  <si>
     <t>Egypt Egyptian Premier League</t>
   </si>
   <si>
-    <t>England Premier League</t>
-  </si>
-  <si>
-    <t>Oman Professional League</t>
-  </si>
-  <si>
     <t>Romania Liga I</t>
   </si>
   <si>
+    <t>Tunisia Ligue 1</t>
+  </si>
+  <si>
     <t>Serbia SuperLiga</t>
   </si>
   <si>
-    <t>Tunisia Ligue 1</t>
-  </si>
-  <si>
     <t>Azerbaijan Premyer Liqası</t>
   </si>
   <si>
+    <t>Republic of Ireland Premier Division</t>
+  </si>
+  <si>
+    <t>Republic of Ireland First Division</t>
+  </si>
+  <si>
+    <t>Croatia Prva HNL</t>
+  </si>
+  <si>
+    <t>Poland 1. Liga</t>
+  </si>
+  <si>
+    <t>Morocco Botola Pro</t>
+  </si>
+  <si>
     <t>Jordan Jordanian Pro League</t>
   </si>
   <si>
-    <t>Republic of Ireland Premier Division</t>
-  </si>
-  <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
-    <t>Republic of Ireland First Division</t>
-  </si>
-  <si>
-    <t>Croatia Prva HNL</t>
-  </si>
-  <si>
-    <t>Morocco Botola Pro</t>
-  </si>
-  <si>
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
@@ -367,24 +367,24 @@
     <t>Algeria Ligue 1</t>
   </si>
   <si>
+    <t>Israel Israeli Premier League</t>
+  </si>
+  <si>
     <t>Portugal LigaPro</t>
   </si>
   <si>
-    <t>Israel Israeli Premier League</t>
+    <t>Poland Ekstraklasa</t>
+  </si>
+  <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
+    <t>Norway Eliteserien</t>
   </si>
   <si>
     <t>Denmark Superliga</t>
   </si>
   <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
-    <t>Poland Ekstraklasa</t>
-  </si>
-  <si>
-    <t>Norway Eliteserien</t>
-  </si>
-  <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
@@ -403,18 +403,18 @@
     <t>Portugal Liga NOS</t>
   </si>
   <si>
+    <t>Chile Primera B</t>
+  </si>
+  <si>
     <t>Brazil Serie B</t>
   </si>
   <si>
-    <t>Chile Primera B</t>
+    <t>Argentina Prim B Nacional</t>
   </si>
   <si>
     <t>Brazil Serie C</t>
   </si>
   <si>
-    <t>Argentina Prim B Nacional</t>
-  </si>
-  <si>
     <t>Bolivia LFPB</t>
   </si>
   <si>
@@ -454,105 +454,105 @@
     <t>Dugopolje</t>
   </si>
   <si>
+    <t>OFK Vršac</t>
+  </si>
+  <si>
+    <t>Chelsea</t>
+  </si>
+  <si>
+    <t>Odisha FC</t>
+  </si>
+  <si>
+    <t>Al Khabourah</t>
+  </si>
+  <si>
     <t>Ural</t>
   </si>
   <si>
+    <t>Lokomotiv</t>
+  </si>
+  <si>
+    <t>Pharco</t>
+  </si>
+  <si>
+    <t>Stepojevac Vaga</t>
+  </si>
+  <si>
     <t>Xorazm</t>
   </si>
   <si>
-    <t>Lokomotiv</t>
-  </si>
-  <si>
-    <t>Stepojevac Vaga</t>
-  </si>
-  <si>
-    <t>Odisha FC</t>
-  </si>
-  <si>
-    <t>OFK Vršac</t>
-  </si>
-  <si>
-    <t>Pharco</t>
-  </si>
-  <si>
-    <t>Chelsea</t>
-  </si>
-  <si>
-    <t>Al Khabourah</t>
-  </si>
-  <si>
     <t>Unirea Slobozia</t>
   </si>
   <si>
+    <t>Monastir</t>
+  </si>
+  <si>
+    <t>CA Bizertin</t>
+  </si>
+  <si>
+    <t>Zarzis</t>
+  </si>
+  <si>
+    <t>Jeunesse Sportive Omrane</t>
+  </si>
+  <si>
     <t>Radnik Surdulica</t>
   </si>
   <si>
-    <t>Jeunesse Sportive Omrane</t>
-  </si>
-  <si>
-    <t>CA Bizertin</t>
-  </si>
-  <si>
     <t>Nasaf</t>
   </si>
   <si>
-    <t>Zarzis</t>
-  </si>
-  <si>
-    <t>Monastir</t>
-  </si>
-  <si>
     <t>Al Nasr</t>
   </si>
   <si>
     <t>Qarabağ</t>
   </si>
   <si>
+    <t>Derry City</t>
+  </si>
+  <si>
+    <t>Waterford</t>
+  </si>
+  <si>
+    <t>Sligo Rovers</t>
+  </si>
+  <si>
+    <t>Shamrock Rovers</t>
+  </si>
+  <si>
+    <t>Longford Town</t>
+  </si>
+  <si>
+    <t>Istra 1961</t>
+  </si>
+  <si>
+    <t>Polonia Bytom</t>
+  </si>
+  <si>
+    <t>Kerry</t>
+  </si>
+  <si>
+    <t>Hassania Agadir</t>
+  </si>
+  <si>
+    <t>Al Ahli</t>
+  </si>
+  <si>
+    <t>Treaty United</t>
+  </si>
+  <si>
+    <t>Finn Harps</t>
+  </si>
+  <si>
     <t>Al Jazeera</t>
   </si>
   <si>
-    <t>Sligo Rovers</t>
-  </si>
-  <si>
-    <t>Derry City</t>
-  </si>
-  <si>
-    <t>Shamrock Rovers</t>
-  </si>
-  <si>
-    <t>Polonia Bytom</t>
-  </si>
-  <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
     <t>Cobh Ramblers</t>
   </si>
   <si>
     <t>Bohemians</t>
   </si>
   <si>
-    <t>Waterford</t>
-  </si>
-  <si>
-    <t>Istra 1961</t>
-  </si>
-  <si>
-    <t>Longford Town</t>
-  </si>
-  <si>
-    <t>Treaty United</t>
-  </si>
-  <si>
-    <t>Al Ahli</t>
-  </si>
-  <si>
-    <t>Hassania Agadir</t>
-  </si>
-  <si>
-    <t>Kerry</t>
-  </si>
-  <si>
     <t>Al Feiha</t>
   </si>
   <si>
@@ -562,72 +562,72 @@
     <t>Rheindorf Altach</t>
   </si>
   <si>
+    <t>Cremonese</t>
+  </si>
+  <si>
     <t>Arsenal Tula</t>
   </si>
   <si>
-    <t>Cremonese</t>
-  </si>
-  <si>
     <t>Hearts</t>
   </si>
   <si>
     <t>CR Belouizdad</t>
   </si>
   <si>
+    <t>Maccabi Netanya</t>
+  </si>
+  <si>
+    <t>Wadi Degla</t>
+  </si>
+  <si>
+    <t>Bnei Sakhnin</t>
+  </si>
+  <si>
     <t>Torreense</t>
   </si>
   <si>
-    <t>Bnei Sakhnin</t>
-  </si>
-  <si>
-    <t>Wadi Degla</t>
+    <t>Radomiak Radom</t>
+  </si>
+  <si>
+    <t>Djurgården</t>
+  </si>
+  <si>
+    <t>Al Ittihad</t>
+  </si>
+  <si>
+    <t>Halmstad</t>
+  </si>
+  <si>
+    <t>FK Bodo - Glimt</t>
+  </si>
+  <si>
+    <t>Midtjylland</t>
   </si>
   <si>
     <t>Čukarički</t>
   </si>
   <si>
-    <t>Al Ittihad</t>
-  </si>
-  <si>
-    <t>Midtjylland</t>
-  </si>
-  <si>
-    <t>Maccabi Netanya</t>
-  </si>
-  <si>
-    <t>Djurgården</t>
-  </si>
-  <si>
-    <t>Halmstad</t>
-  </si>
-  <si>
     <t>Porto II</t>
   </si>
   <si>
-    <t>Radomiak Radom</t>
-  </si>
-  <si>
-    <t>FK Bodo - Glimt</t>
-  </si>
-  <si>
     <t>Landskrona</t>
   </si>
   <si>
+    <t>Rapid Bucureşti</t>
+  </si>
+  <si>
     <t>Víkingur</t>
   </si>
   <si>
     <t>B36</t>
   </si>
   <si>
-    <t>Rapid Bucureşti</t>
+    <t>Al Ittifaq</t>
   </si>
   <si>
     <t>Yacoub El Mansour</t>
   </si>
   <si>
-    <t>Al Ittifaq</t>
-  </si>
-  <si>
     <t>Vasas</t>
   </si>
   <si>
@@ -640,48 +640,48 @@
     <t>Roma</t>
   </si>
   <si>
+    <t>USM Alger</t>
+  </si>
+  <si>
     <t>Sevilla FC</t>
   </si>
   <si>
     <t>Everton</t>
   </si>
   <si>
-    <t>USM Alger</t>
-  </si>
-  <si>
     <t>Sporting CP</t>
   </si>
   <si>
     <t>Kawkab Marrakech</t>
   </si>
   <si>
+    <t>San Luis</t>
+  </si>
+  <si>
     <t>Vila Nova</t>
   </si>
   <si>
-    <t>San Luis</t>
+    <t>Quilmes</t>
+  </si>
+  <si>
+    <t>Ypiranga Erechim</t>
   </si>
   <si>
     <t>Figueirense</t>
   </si>
   <si>
-    <t>Ypiranga Erechim</t>
-  </si>
-  <si>
     <t>Floresta</t>
   </si>
   <si>
-    <t>Quilmes</t>
-  </si>
-  <si>
     <t>Universitario de Vinto</t>
   </si>
   <si>
+    <t>San Marcos</t>
+  </si>
+  <si>
     <t>Gimnasia y Tiro</t>
   </si>
   <si>
-    <t>San Marcos</t>
-  </si>
-  <si>
     <t>Bhayangkara</t>
   </si>
   <si>
@@ -709,105 +709,105 @@
     <t>Cibalia</t>
   </si>
   <si>
+    <t>Jedinstvo Ub</t>
+  </si>
+  <si>
+    <t>Nottingham Forest</t>
+  </si>
+  <si>
+    <t>Bengaluru</t>
+  </si>
+  <si>
+    <t>Saham</t>
+  </si>
+  <si>
     <t>Shinnik</t>
   </si>
   <si>
+    <t>Qizilqum</t>
+  </si>
+  <si>
+    <t>Al Mokawloon</t>
+  </si>
+  <si>
+    <t>Kabel Novi Sad</t>
+  </si>
+  <si>
     <t>Andijan</t>
   </si>
   <si>
-    <t>Qizilqum</t>
-  </si>
-  <si>
-    <t>Kabel Novi Sad</t>
-  </si>
-  <si>
-    <t>Bengaluru</t>
-  </si>
-  <si>
-    <t>Jedinstvo Ub</t>
-  </si>
-  <si>
-    <t>Al Mokawloon</t>
-  </si>
-  <si>
-    <t>Nottingham Forest</t>
-  </si>
-  <si>
-    <t>Saham</t>
-  </si>
-  <si>
     <t>Hermannstadt</t>
   </si>
   <si>
+    <t>Métlaoui</t>
+  </si>
+  <si>
+    <t>Marsa</t>
+  </si>
+  <si>
+    <t>Etoile du Sahel</t>
+  </si>
+  <si>
+    <t>ES Tunis</t>
+  </si>
+  <si>
     <t>Vojvodina</t>
   </si>
   <si>
-    <t>ES Tunis</t>
-  </si>
-  <si>
-    <t>Marsa</t>
-  </si>
-  <si>
     <t>Navbahor</t>
   </si>
   <si>
-    <t>Etoile du Sahel</t>
-  </si>
-  <si>
-    <t>Métlaoui</t>
-  </si>
-  <si>
     <t>Al-Nahda</t>
   </si>
   <si>
     <t>Turan</t>
   </si>
   <si>
+    <t>Galway United</t>
+  </si>
+  <si>
+    <t>Dundalk</t>
+  </si>
+  <si>
+    <t>St Patrick's Athl.</t>
+  </si>
+  <si>
+    <t>Drogheda United</t>
+  </si>
+  <si>
+    <t>Athlone Town</t>
+  </si>
+  <si>
+    <t>Slaven Koprivnica</t>
+  </si>
+  <si>
+    <t>Polonia Warszawa</t>
+  </si>
+  <si>
+    <t>Cork City</t>
+  </si>
+  <si>
+    <t>Olympic Safi</t>
+  </si>
+  <si>
+    <t>Al Buqa'a</t>
+  </si>
+  <si>
+    <t>Wexford</t>
+  </si>
+  <si>
+    <t>Bray Wanderers</t>
+  </si>
+  <si>
     <t>Shabab Al Ordon</t>
   </si>
   <si>
-    <t>St Patrick's Athl.</t>
-  </si>
-  <si>
-    <t>Galway United</t>
-  </si>
-  <si>
-    <t>Drogheda United</t>
-  </si>
-  <si>
-    <t>Polonia Warszawa</t>
-  </si>
-  <si>
-    <t>Bray Wanderers</t>
-  </si>
-  <si>
     <t>UCD</t>
   </si>
   <si>
     <t>Shelbourne</t>
   </si>
   <si>
-    <t>Dundalk</t>
-  </si>
-  <si>
-    <t>Slaven Koprivnica</t>
-  </si>
-  <si>
-    <t>Athlone Town</t>
-  </si>
-  <si>
-    <t>Wexford</t>
-  </si>
-  <si>
-    <t>Al Buqa'a</t>
-  </si>
-  <si>
-    <t>Olympic Safi</t>
-  </si>
-  <si>
-    <t>Cork City</t>
-  </si>
-  <si>
     <t>Al Riyadh</t>
   </si>
   <si>
@@ -817,75 +817,75 @@
     <t>Wolfsberger AC</t>
   </si>
   <si>
+    <t>Lazio</t>
+  </si>
+  <si>
     <t>Rotor Volgograd</t>
   </si>
   <si>
-    <t>Lazio</t>
-  </si>
-  <si>
     <t>Rangers</t>
   </si>
   <si>
     <t>USM Khenchela</t>
   </si>
   <si>
+    <t>Hapoel Katamon</t>
+  </si>
+  <si>
+    <t>Kahraba Ismailia</t>
+  </si>
+  <si>
+    <t>Maccabi Bnei Raina</t>
+  </si>
+  <si>
     <t>FC Penafiel</t>
   </si>
   <si>
-    <t>Maccabi Bnei Raina</t>
-  </si>
-  <si>
-    <t>Kahraba Ismailia</t>
+    <t>Lechia Gdańsk</t>
+  </si>
+  <si>
+    <t>IFK Göteborg</t>
+  </si>
+  <si>
+    <t>Petrojet</t>
+  </si>
+  <si>
+    <t>Brommapojkarna</t>
+  </si>
+  <si>
+    <t>Molde</t>
+  </si>
+  <si>
+    <t>Viborg</t>
   </si>
   <si>
     <t>Red Star Belgrade</t>
   </si>
   <si>
-    <t>Petrojet</t>
-  </si>
-  <si>
-    <t>Viborg</t>
-  </si>
-  <si>
-    <t>Hapoel Katamon</t>
-  </si>
-  <si>
-    <t>IFK Göteborg</t>
-  </si>
-  <si>
-    <t>Brommapojkarna</t>
-  </si>
-  <si>
     <t>Felgueiras 1932</t>
   </si>
   <si>
-    <t>Lechia Gdańsk</t>
-  </si>
-  <si>
-    <t>Molde</t>
-  </si>
-  <si>
     <t>Öster</t>
   </si>
   <si>
+    <t>CFR Cluj</t>
+  </si>
+  <si>
     <t>07 Vestur</t>
   </si>
   <si>
     <t>NSÍ</t>
   </si>
   <si>
-    <t>CFR Cluj</t>
-  </si>
-  <si>
     <t>Al Kholood</t>
   </si>
   <si>
+    <t>Al Najma</t>
+  </si>
+  <si>
     <t>RSB Berkane</t>
   </si>
   <si>
-    <t>Al Najma</t>
-  </si>
-  <si>
     <t>Budafoki MTE</t>
   </si>
   <si>
@@ -898,46 +898,46 @@
     <t>Fiorentina</t>
   </si>
   <si>
+    <t>Paradou AC</t>
+  </si>
+  <si>
     <t>Real Sociedad</t>
   </si>
   <si>
     <t>Manchester City</t>
   </si>
   <si>
-    <t>Paradou AC</t>
-  </si>
-  <si>
     <t>Vitória Guimarães</t>
   </si>
   <si>
     <t>Olympique Dcheïra</t>
   </si>
   <si>
+    <t>Unión San Felipe</t>
+  </si>
+  <si>
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>Unión San Felipe</t>
+    <t>Chacarita Juniors</t>
+  </si>
+  <si>
+    <t>Ituano</t>
   </si>
   <si>
     <t>Barra do Garcas</t>
   </si>
   <si>
-    <t>Ituano</t>
-  </si>
-  <si>
     <t>Maranhão</t>
   </si>
   <si>
-    <t>Chacarita Juniors</t>
-  </si>
-  <si>
     <t>Blooming</t>
   </si>
   <si>
+    <t>Recoleta</t>
+  </si>
+  <si>
     <t>Agropecuario</t>
-  </si>
-  <si>
-    <t>Recoleta</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -3204,79 +3204,79 @@
         <v>308</v>
       </c>
       <c r="P11">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q11">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R11">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="S11">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="V11">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W11">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="X11">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y11">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z11">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AA11">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC11">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD11">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AE11">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AF11">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG11">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AH11">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI11">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AJ11">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK11">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL11">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AM11">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN11">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AO11">
         <v>0</v>
@@ -3318,19 +3318,19 @@
         <v>0</v>
       </c>
       <c r="BB11">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BC11">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="BD11">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE11">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF11">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG11">
         <v>0</v>
@@ -3353,7 +3353,7 @@
         <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E12" t="s">
         <v>147</v>
@@ -3389,133 +3389,133 @@
         <v>308</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>5.18</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL12">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM12">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AO12">
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AU12">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="AV12">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AW12">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AX12">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AY12">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AZ12">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BA12">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BB12">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC12">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BD12">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE12">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF12">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG12">
         <v>0</v>
@@ -3535,10 +3535,10 @@
         <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D13" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E13" t="s">
         <v>148</v>
@@ -3720,7 +3720,7 @@
         <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D14" t="s">
         <v>134</v>
@@ -3905,7 +3905,7 @@
         <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D15" t="s">
         <v>134</v>
@@ -3944,79 +3944,79 @@
         <v>308</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI15">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL15">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM15">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN15">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AO15">
         <v>0</v>
@@ -4058,19 +4058,19 @@
         <v>0</v>
       </c>
       <c r="BB15">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC15">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BD15">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE15">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF15">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG15">
         <v>0</v>
@@ -4090,10 +4090,10 @@
         <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D16" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E16" t="s">
         <v>151</v>
@@ -4275,7 +4275,7 @@
         <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D17" t="s">
         <v>134</v>
@@ -4460,7 +4460,7 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D18" t="s">
         <v>134</v>
@@ -4499,133 +4499,133 @@
         <v>308</v>
       </c>
       <c r="P18">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q18">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R18">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="S18">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="T18">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U18">
-        <v>5.18</v>
+        <v>0</v>
       </c>
       <c r="V18">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W18">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X18">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Y18">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z18">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="AA18">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB18">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC18">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD18">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AE18">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF18">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AG18">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH18">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AI18">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AJ18">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK18">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL18">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM18">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN18">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AO18">
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ18">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR18">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AS18">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AT18">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AU18">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="AV18">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="AW18">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AX18">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AY18">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AZ18">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BA18">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BB18">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC18">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BD18">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE18">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF18">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG18">
         <v>0</v>
@@ -4645,10 +4645,10 @@
         <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D19" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E19" t="s">
         <v>154</v>
@@ -5054,61 +5054,61 @@
         <v>308</v>
       </c>
       <c r="P21">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q21">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R21">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S21">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="T21">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="U21">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="V21">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W21">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="X21">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Y21">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z21">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AA21">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB21">
         <v>0</v>
       </c>
       <c r="AC21">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD21">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="AE21">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AF21">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG21">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH21">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AI21">
         <v>0</v>
@@ -5117,16 +5117,16 @@
         <v>0</v>
       </c>
       <c r="AK21">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AL21">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AM21">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN21">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO21">
         <v>0</v>
@@ -5171,13 +5171,13 @@
         <v>0</v>
       </c>
       <c r="BC21">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="BD21">
         <v>0</v>
       </c>
       <c r="BE21">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="BF21">
         <v>0</v>
@@ -5200,7 +5200,7 @@
         <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D22" t="s">
         <v>134</v>
@@ -5385,7 +5385,7 @@
         <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D23" t="s">
         <v>134</v>
@@ -5570,10 +5570,10 @@
         <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="D24" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E24" t="s">
         <v>159</v>
@@ -5794,61 +5794,61 @@
         <v>308</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB25">
         <v>0</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH25">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI25">
         <v>0</v>
@@ -5857,16 +5857,16 @@
         <v>0</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL25">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM25">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN25">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO25">
         <v>0</v>
@@ -5911,13 +5911,13 @@
         <v>0</v>
       </c>
       <c r="BC25">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BD25">
         <v>0</v>
       </c>
       <c r="BE25">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BF25">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D26" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E26" t="s">
         <v>161</v>
@@ -6125,7 +6125,7 @@
         <v>70</v>
       </c>
       <c r="C27" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D27" t="s">
         <v>134</v>
@@ -6498,7 +6498,7 @@
         <v>106</v>
       </c>
       <c r="D29" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E29" t="s">
         <v>164</v>
@@ -6579,10 +6579,10 @@
         <v>0</v>
       </c>
       <c r="AE29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF29">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG29">
         <v>0</v>
@@ -6597,10 +6597,10 @@
         <v>0</v>
       </c>
       <c r="AK29">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL29">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AM29">
         <v>0</v>
@@ -6680,7 +6680,7 @@
         <v>72</v>
       </c>
       <c r="C30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D30" t="s">
         <v>136</v>
@@ -6865,7 +6865,7 @@
         <v>72</v>
       </c>
       <c r="C31" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D31" t="s">
         <v>136</v>
@@ -7050,7 +7050,7 @@
         <v>72</v>
       </c>
       <c r="C32" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D32" t="s">
         <v>136</v>
@@ -7235,10 +7235,10 @@
         <v>72</v>
       </c>
       <c r="C33" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D33" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E33" t="s">
         <v>168</v>
@@ -7274,79 +7274,79 @@
         <v>308</v>
       </c>
       <c r="P33">
-        <v>2.36</v>
+        <v>2.09</v>
       </c>
       <c r="Q33">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R33">
-        <v>2.75</v>
+        <v>3.24</v>
       </c>
       <c r="S33">
-        <v>2.82</v>
+        <v>2.55</v>
       </c>
       <c r="T33">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="U33">
-        <v>3.28</v>
+        <v>3.75</v>
       </c>
       <c r="V33">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W33">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="X33">
-        <v>2.31</v>
+        <v>2.55</v>
       </c>
       <c r="Y33">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="Z33">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA33">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB33">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC33">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AD33">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="AE33">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
       <c r="AF33">
-        <v>2.08</v>
+        <v>1.82</v>
       </c>
       <c r="AG33">
-        <v>2.43</v>
+        <v>3</v>
       </c>
       <c r="AH33">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AI33">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="AJ33">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AK33">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AL33">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="AM33">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AN33">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="AO33">
         <v>0</v>
@@ -7388,19 +7388,19 @@
         <v>0</v>
       </c>
       <c r="BB33">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC33">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="BD33">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE33">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="BF33">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BG33">
         <v>0</v>
@@ -7420,10 +7420,10 @@
         <v>72</v>
       </c>
       <c r="C34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D34" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E34" t="s">
         <v>169</v>
@@ -7459,133 +7459,133 @@
         <v>308</v>
       </c>
       <c r="P34">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="Q34">
+        <v>3.1</v>
+      </c>
+      <c r="R34">
+        <v>2.63</v>
+      </c>
+      <c r="S34">
+        <v>3.1</v>
+      </c>
+      <c r="T34">
+        <v>2.08</v>
+      </c>
+      <c r="U34">
+        <v>3.25</v>
+      </c>
+      <c r="V34">
+        <v>1.39</v>
+      </c>
+      <c r="W34">
+        <v>2.73</v>
+      </c>
+      <c r="X34">
+        <v>2.73</v>
+      </c>
+      <c r="Y34">
+        <v>1.33</v>
+      </c>
+      <c r="Z34">
+        <v>6.4</v>
+      </c>
+      <c r="AA34">
+        <v>1.05</v>
+      </c>
+      <c r="AB34">
+        <v>1.06</v>
+      </c>
+      <c r="AC34">
+        <v>1.3</v>
+      </c>
+      <c r="AD34">
         <v>3.2</v>
       </c>
-      <c r="R34">
-        <v>2.44</v>
-      </c>
-      <c r="S34">
-        <v>3.15</v>
-      </c>
-      <c r="T34">
-        <v>2.18</v>
-      </c>
-      <c r="U34">
-        <v>2.95</v>
-      </c>
-      <c r="V34">
-        <v>0</v>
-      </c>
-      <c r="W34">
-        <v>0</v>
-      </c>
-      <c r="X34">
-        <v>2.6</v>
-      </c>
-      <c r="Y34">
-        <v>1.38</v>
-      </c>
-      <c r="Z34">
-        <v>0</v>
-      </c>
-      <c r="AA34">
-        <v>0</v>
-      </c>
-      <c r="AB34">
-        <v>0</v>
-      </c>
-      <c r="AC34">
-        <v>1.26</v>
-      </c>
-      <c r="AD34">
-        <v>3.3</v>
-      </c>
       <c r="AE34">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AF34">
         <v>1.8</v>
       </c>
       <c r="AG34">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="AH34">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AI34">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AJ34">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AK34">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AL34">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AM34">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AN34">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="AO34">
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AQ34">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AR34">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AS34">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AT34">
-        <v>0</v>
+        <v>5.44</v>
       </c>
       <c r="AU34">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AV34">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AW34">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AX34">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AY34">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AZ34">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BA34">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BB34">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC34">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="BD34">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE34">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="BF34">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG34">
         <v>0</v>
@@ -7608,7 +7608,7 @@
         <v>109</v>
       </c>
       <c r="D35" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E35" t="s">
         <v>170</v>
@@ -7644,79 +7644,79 @@
         <v>308</v>
       </c>
       <c r="P35">
-        <v>2.14</v>
+        <v>2.27</v>
       </c>
       <c r="Q35">
-        <v>3.3</v>
+        <v>3.43</v>
       </c>
       <c r="R35">
-        <v>3.14</v>
+        <v>2.73</v>
       </c>
       <c r="S35">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="T35">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="U35">
-        <v>3.65</v>
+        <v>3.28</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="X35">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="Y35">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC35">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AD35">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="AE35">
-        <v>1.82</v>
+        <v>1.63</v>
       </c>
       <c r="AF35">
-        <v>1.82</v>
+        <v>2.19</v>
       </c>
       <c r="AG35">
-        <v>3</v>
+        <v>2.53</v>
       </c>
       <c r="AH35">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AI35">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="AJ35">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AK35">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AL35">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="AM35">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AN35">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AO35">
         <v>0</v>
@@ -7758,19 +7758,19 @@
         <v>0</v>
       </c>
       <c r="BB35">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC35">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="BD35">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE35">
-        <v>1.62</v>
+        <v>1.86</v>
       </c>
       <c r="BF35">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG35">
         <v>0</v>
@@ -7829,13 +7829,13 @@
         <v>308</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -7975,10 +7975,10 @@
         <v>72</v>
       </c>
       <c r="C37" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D37" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E37" t="s">
         <v>172</v>
@@ -8160,7 +8160,7 @@
         <v>72</v>
       </c>
       <c r="C38" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D38" t="s">
         <v>134</v>
@@ -8199,133 +8199,133 @@
         <v>308</v>
       </c>
       <c r="P38">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="Q38">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R38">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="S38">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T38">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U38">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="V38">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W38">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="X38">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Y38">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z38">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AA38">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB38">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC38">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD38">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE38">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF38">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG38">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AH38">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI38">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AJ38">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK38">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AL38">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM38">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN38">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AO38">
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AQ38">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AR38">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AS38">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AT38">
-        <v>5.44</v>
+        <v>0</v>
       </c>
       <c r="AU38">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AV38">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AW38">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AX38">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AY38">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AZ38">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BA38">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BB38">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC38">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="BD38">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE38">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BF38">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG38">
         <v>0</v>
@@ -8345,7 +8345,7 @@
         <v>72</v>
       </c>
       <c r="C39" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D39" t="s">
         <v>136</v>
@@ -8384,22 +8384,22 @@
         <v>308</v>
       </c>
       <c r="P39">
-        <v>2.09</v>
+        <v>2.6</v>
       </c>
       <c r="Q39">
         <v>3.3</v>
       </c>
       <c r="R39">
-        <v>3.24</v>
+        <v>2.43</v>
       </c>
       <c r="S39">
-        <v>2.55</v>
+        <v>3.25</v>
       </c>
       <c r="T39">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U39">
-        <v>3.75</v>
+        <v>2.9</v>
       </c>
       <c r="V39">
         <v>0</v>
@@ -8444,19 +8444,19 @@
         <v>5.4</v>
       </c>
       <c r="AJ39">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AK39">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AL39">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AM39">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AN39">
-        <v>1.62</v>
+        <v>1.32</v>
       </c>
       <c r="AO39">
         <v>0</v>
@@ -8530,7 +8530,7 @@
         <v>72</v>
       </c>
       <c r="C40" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D40" t="s">
         <v>136</v>
@@ -8569,22 +8569,22 @@
         <v>308</v>
       </c>
       <c r="P40">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="Q40">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R40">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="S40">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="T40">
         <v>2.18</v>
       </c>
       <c r="U40">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="V40">
         <v>0</v>
@@ -8593,7 +8593,7 @@
         <v>0</v>
       </c>
       <c r="X40">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Y40">
         <v>1.38</v>
@@ -8608,40 +8608,40 @@
         <v>0</v>
       </c>
       <c r="AC40">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AD40">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AE40">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AF40">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AG40">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AH40">
         <v>1.3</v>
       </c>
       <c r="AI40">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AJ40">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AK40">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AL40">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AM40">
         <v>1.24</v>
       </c>
       <c r="AN40">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AO40">
         <v>0</v>
@@ -8686,13 +8686,13 @@
         <v>0</v>
       </c>
       <c r="BC40">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="BD40">
         <v>0</v>
       </c>
       <c r="BE40">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="BF40">
         <v>0</v>
@@ -8715,7 +8715,7 @@
         <v>72</v>
       </c>
       <c r="C41" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D41" t="s">
         <v>134</v>
@@ -8754,13 +8754,13 @@
         <v>308</v>
       </c>
       <c r="P41">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q41">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R41">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -8799,10 +8799,10 @@
         <v>0</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG41">
         <v>0</v>
@@ -8817,10 +8817,10 @@
         <v>0</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL41">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AM41">
         <v>0</v>
@@ -8900,10 +8900,10 @@
         <v>72</v>
       </c>
       <c r="C42" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D42" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E42" t="s">
         <v>177</v>
@@ -8939,22 +8939,22 @@
         <v>308</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="V42">
         <v>0</v>
@@ -8963,10 +8963,10 @@
         <v>0</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -8978,40 +8978,40 @@
         <v>0</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH42">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI42">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL42">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AM42">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN42">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AO42">
         <v>0</v>
@@ -9056,13 +9056,13 @@
         <v>0</v>
       </c>
       <c r="BC42">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BD42">
         <v>0</v>
       </c>
       <c r="BE42">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF42">
         <v>0</v>
@@ -9085,7 +9085,7 @@
         <v>72</v>
       </c>
       <c r="C43" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D43" t="s">
         <v>136</v>
@@ -9124,13 +9124,13 @@
         <v>308</v>
       </c>
       <c r="P43">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="Q43">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R43">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S43">
         <v>0</v>
@@ -9455,7 +9455,7 @@
         <v>74</v>
       </c>
       <c r="C45" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D45" t="s">
         <v>134</v>
@@ -9679,13 +9679,13 @@
         <v>308</v>
       </c>
       <c r="P46">
-        <v>2.55</v>
+        <v>2.32</v>
       </c>
       <c r="Q46">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="R46">
-        <v>2.67</v>
+        <v>2.92</v>
       </c>
       <c r="S46">
         <v>2.8</v>
@@ -9700,7 +9700,7 @@
         <v>1.4</v>
       </c>
       <c r="W46">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="X46">
         <v>2.85</v>
@@ -9724,31 +9724,31 @@
         <v>3.12</v>
       </c>
       <c r="AE46">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AF46">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG46">
         <v>3.3</v>
       </c>
       <c r="AH46">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AI46">
         <v>6.5</v>
       </c>
       <c r="AJ46">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AK46">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AL46">
         <v>2</v>
       </c>
       <c r="AM46">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AN46">
         <v>1.54</v>
@@ -9763,7 +9763,7 @@
         <v>1.61</v>
       </c>
       <c r="AR46">
-        <v>1.83</v>
+        <v>2.06</v>
       </c>
       <c r="AS46">
         <v>2.75</v>
@@ -9787,7 +9787,7 @@
         <v>1.19</v>
       </c>
       <c r="AZ46">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="BA46">
         <v>2.85</v>
@@ -9825,7 +9825,7 @@
         <v>75</v>
       </c>
       <c r="C47" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="D47" t="s">
         <v>134</v>
@@ -9864,133 +9864,133 @@
         <v>308</v>
       </c>
       <c r="P47">
+        <v>2.95</v>
+      </c>
+      <c r="Q47">
         <v>3.22</v>
       </c>
-      <c r="Q47">
-        <v>2.93</v>
-      </c>
       <c r="R47">
-        <v>2.84</v>
+        <v>2.4</v>
       </c>
       <c r="S47">
-        <v>3.24</v>
+        <v>3.5</v>
       </c>
       <c r="T47">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="U47">
-        <v>3.82</v>
+        <v>2.9</v>
       </c>
       <c r="V47">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="W47">
-        <v>2.44</v>
+        <v>2.65</v>
       </c>
       <c r="X47">
-        <v>3.44</v>
+        <v>2.9</v>
       </c>
       <c r="Y47">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="Z47">
-        <v>9.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA47">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AB47">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AC47">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="AD47">
-        <v>2.56</v>
+        <v>3</v>
       </c>
       <c r="AE47">
-        <v>2.52</v>
+        <v>2.21</v>
       </c>
       <c r="AF47">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AG47">
-        <v>4.55</v>
+        <v>3.58</v>
       </c>
       <c r="AH47">
+        <v>1.29</v>
+      </c>
+      <c r="AI47">
+        <v>7.8</v>
+      </c>
+      <c r="AJ47">
+        <v>1.02</v>
+      </c>
+      <c r="AK47">
+        <v>1.83</v>
+      </c>
+      <c r="AL47">
+        <v>1.92</v>
+      </c>
+      <c r="AM47">
+        <v>1.33</v>
+      </c>
+      <c r="AN47">
+        <v>1.36</v>
+      </c>
+      <c r="AO47">
+        <v>0</v>
+      </c>
+      <c r="AP47">
+        <v>1.38</v>
+      </c>
+      <c r="AQ47">
+        <v>1.68</v>
+      </c>
+      <c r="AR47">
+        <v>2.1</v>
+      </c>
+      <c r="AS47">
+        <v>2.38</v>
+      </c>
+      <c r="AT47">
+        <v>3.15</v>
+      </c>
+      <c r="AU47">
+        <v>3.1</v>
+      </c>
+      <c r="AV47">
+        <v>2.06</v>
+      </c>
+      <c r="AW47">
+        <v>1.6</v>
+      </c>
+      <c r="AX47">
+        <v>1.5</v>
+      </c>
+      <c r="AY47">
+        <v>1.3</v>
+      </c>
+      <c r="AZ47">
+        <v>2.5</v>
+      </c>
+      <c r="BA47">
+        <v>1.8</v>
+      </c>
+      <c r="BB47">
+        <v>1.27</v>
+      </c>
+      <c r="BC47">
+        <v>2.38</v>
+      </c>
+      <c r="BD47">
+        <v>3.55</v>
+      </c>
+      <c r="BE47">
+        <v>1.6</v>
+      </c>
+      <c r="BF47">
         <v>1.13</v>
-      </c>
-      <c r="AI47">
-        <v>9.5</v>
-      </c>
-      <c r="AJ47">
-        <v>1</v>
-      </c>
-      <c r="AK47">
-        <v>2.02</v>
-      </c>
-      <c r="AL47">
-        <v>1.69</v>
-      </c>
-      <c r="AM47">
-        <v>1.38</v>
-      </c>
-      <c r="AN47">
-        <v>1.52</v>
-      </c>
-      <c r="AO47">
-        <v>0</v>
-      </c>
-      <c r="AP47">
-        <v>0</v>
-      </c>
-      <c r="AQ47">
-        <v>0</v>
-      </c>
-      <c r="AR47">
-        <v>0</v>
-      </c>
-      <c r="AS47">
-        <v>0</v>
-      </c>
-      <c r="AT47">
-        <v>0</v>
-      </c>
-      <c r="AU47">
-        <v>0</v>
-      </c>
-      <c r="AV47">
-        <v>0</v>
-      </c>
-      <c r="AW47">
-        <v>0</v>
-      </c>
-      <c r="AX47">
-        <v>0</v>
-      </c>
-      <c r="AY47">
-        <v>0</v>
-      </c>
-      <c r="AZ47">
-        <v>0</v>
-      </c>
-      <c r="BA47">
-        <v>0</v>
-      </c>
-      <c r="BB47">
-        <v>1.33</v>
-      </c>
-      <c r="BC47">
-        <v>2.56</v>
-      </c>
-      <c r="BD47">
-        <v>2.99</v>
-      </c>
-      <c r="BE47">
-        <v>1.44</v>
-      </c>
-      <c r="BF47">
-        <v>1.06</v>
       </c>
       <c r="BG47">
         <v>0</v>
@@ -10010,7 +10010,7 @@
         <v>75</v>
       </c>
       <c r="C48" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="D48" t="s">
         <v>134</v>
@@ -10049,133 +10049,133 @@
         <v>308</v>
       </c>
       <c r="P48">
-        <v>2.95</v>
+        <v>3.22</v>
       </c>
       <c r="Q48">
-        <v>3.22</v>
+        <v>2.93</v>
       </c>
       <c r="R48">
-        <v>2.4</v>
+        <v>2.84</v>
       </c>
       <c r="S48">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="T48">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="U48">
-        <v>2.9</v>
+        <v>3.82</v>
       </c>
       <c r="V48">
+        <v>1.53</v>
+      </c>
+      <c r="W48">
+        <v>2.44</v>
+      </c>
+      <c r="X48">
+        <v>3.44</v>
+      </c>
+      <c r="Y48">
+        <v>1.24</v>
+      </c>
+      <c r="Z48">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AA48">
+        <v>1</v>
+      </c>
+      <c r="AB48">
+        <v>1.05</v>
+      </c>
+      <c r="AC48">
+        <v>1.48</v>
+      </c>
+      <c r="AD48">
+        <v>2.56</v>
+      </c>
+      <c r="AE48">
+        <v>2.52</v>
+      </c>
+      <c r="AF48">
+        <v>1.55</v>
+      </c>
+      <c r="AG48">
+        <v>4.55</v>
+      </c>
+      <c r="AH48">
+        <v>1.13</v>
+      </c>
+      <c r="AI48">
+        <v>9.5</v>
+      </c>
+      <c r="AJ48">
+        <v>1</v>
+      </c>
+      <c r="AK48">
+        <v>2.02</v>
+      </c>
+      <c r="AL48">
+        <v>1.69</v>
+      </c>
+      <c r="AM48">
+        <v>1.38</v>
+      </c>
+      <c r="AN48">
+        <v>1.52</v>
+      </c>
+      <c r="AO48">
+        <v>0</v>
+      </c>
+      <c r="AP48">
+        <v>0</v>
+      </c>
+      <c r="AQ48">
+        <v>0</v>
+      </c>
+      <c r="AR48">
+        <v>0</v>
+      </c>
+      <c r="AS48">
+        <v>0</v>
+      </c>
+      <c r="AT48">
+        <v>0</v>
+      </c>
+      <c r="AU48">
+        <v>0</v>
+      </c>
+      <c r="AV48">
+        <v>0</v>
+      </c>
+      <c r="AW48">
+        <v>0</v>
+      </c>
+      <c r="AX48">
+        <v>0</v>
+      </c>
+      <c r="AY48">
+        <v>0</v>
+      </c>
+      <c r="AZ48">
+        <v>0</v>
+      </c>
+      <c r="BA48">
+        <v>0</v>
+      </c>
+      <c r="BB48">
+        <v>1.33</v>
+      </c>
+      <c r="BC48">
+        <v>2.56</v>
+      </c>
+      <c r="BD48">
+        <v>2.99</v>
+      </c>
+      <c r="BE48">
         <v>1.44</v>
       </c>
-      <c r="W48">
-        <v>2.65</v>
-      </c>
-      <c r="X48">
-        <v>2.9</v>
-      </c>
-      <c r="Y48">
-        <v>1.34</v>
-      </c>
-      <c r="Z48">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AA48">
-        <v>1.03</v>
-      </c>
-      <c r="AB48">
+      <c r="BF48">
         <v>1.06</v>
-      </c>
-      <c r="AC48">
-        <v>1.34</v>
-      </c>
-      <c r="AD48">
-        <v>3</v>
-      </c>
-      <c r="AE48">
-        <v>2.21</v>
-      </c>
-      <c r="AF48">
-        <v>1.7</v>
-      </c>
-      <c r="AG48">
-        <v>3.58</v>
-      </c>
-      <c r="AH48">
-        <v>1.29</v>
-      </c>
-      <c r="AI48">
-        <v>7.8</v>
-      </c>
-      <c r="AJ48">
-        <v>1.02</v>
-      </c>
-      <c r="AK48">
-        <v>1.83</v>
-      </c>
-      <c r="AL48">
-        <v>1.92</v>
-      </c>
-      <c r="AM48">
-        <v>1.33</v>
-      </c>
-      <c r="AN48">
-        <v>1.36</v>
-      </c>
-      <c r="AO48">
-        <v>0</v>
-      </c>
-      <c r="AP48">
-        <v>1.38</v>
-      </c>
-      <c r="AQ48">
-        <v>1.68</v>
-      </c>
-      <c r="AR48">
-        <v>2.1</v>
-      </c>
-      <c r="AS48">
-        <v>2.38</v>
-      </c>
-      <c r="AT48">
-        <v>3.15</v>
-      </c>
-      <c r="AU48">
-        <v>3.1</v>
-      </c>
-      <c r="AV48">
-        <v>2.06</v>
-      </c>
-      <c r="AW48">
-        <v>1.6</v>
-      </c>
-      <c r="AX48">
-        <v>1.5</v>
-      </c>
-      <c r="AY48">
-        <v>1.3</v>
-      </c>
-      <c r="AZ48">
-        <v>2.5</v>
-      </c>
-      <c r="BA48">
-        <v>1.8</v>
-      </c>
-      <c r="BB48">
-        <v>1.27</v>
-      </c>
-      <c r="BC48">
-        <v>2.38</v>
-      </c>
-      <c r="BD48">
-        <v>3.55</v>
-      </c>
-      <c r="BE48">
-        <v>1.6</v>
-      </c>
-      <c r="BF48">
-        <v>1.13</v>
       </c>
       <c r="BG48">
         <v>0</v>
@@ -10604,133 +10604,133 @@
         <v>308</v>
       </c>
       <c r="P51">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="Q51">
-        <v>3.4</v>
+        <v>4.35</v>
       </c>
       <c r="R51">
-        <v>4</v>
+        <v>3.47</v>
       </c>
       <c r="S51">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T51">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U51">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="V51">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W51">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="X51">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y51">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z51">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA51">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB51">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC51">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD51">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AE51">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF51">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG51">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AH51">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI51">
-        <v>6.65</v>
+        <v>0</v>
       </c>
       <c r="AJ51">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK51">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL51">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM51">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN51">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AO51">
         <v>0</v>
       </c>
       <c r="AP51">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AQ51">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AR51">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AS51">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AT51">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AU51">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="AV51">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AW51">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AX51">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AY51">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ51">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="BA51">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="BB51">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC51">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD51">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BE51">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF51">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG51">
         <v>0</v>
@@ -10750,7 +10750,7 @@
         <v>77</v>
       </c>
       <c r="C52" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="D52" t="s">
         <v>134</v>
@@ -10789,130 +10789,130 @@
         <v>308</v>
       </c>
       <c r="P52">
-        <v>2.13</v>
+        <v>1.71</v>
       </c>
       <c r="Q52">
-        <v>3.41</v>
+        <v>3.3</v>
       </c>
       <c r="R52">
-        <v>3.07</v>
+        <v>4</v>
       </c>
       <c r="S52">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="T52">
-        <v>2.07</v>
+        <v>2.18</v>
       </c>
       <c r="U52">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="V52">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="W52">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="X52">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="Y52">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z52">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA52">
         <v>1.02</v>
       </c>
       <c r="AB52">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC52">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AD52">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AE52">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AF52">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AG52">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="AH52">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AI52">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="AJ52">
         <v>1.03</v>
       </c>
       <c r="AK52">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AL52">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AM52">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AN52">
-        <v>1.66</v>
+        <v>1.94</v>
       </c>
       <c r="AO52">
         <v>0</v>
       </c>
       <c r="AP52">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ52">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AR52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS52">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AT52">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AU52">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AV52">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AW52">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AX52">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AY52">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ52">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BA52">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="BB52">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BC52">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="BD52">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="BE52">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="BF52">
         <v>1.1</v>
@@ -10935,7 +10935,7 @@
         <v>77</v>
       </c>
       <c r="C53" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="D53" t="s">
         <v>134</v>
@@ -10974,130 +10974,130 @@
         <v>308</v>
       </c>
       <c r="P53">
-        <v>1.71</v>
+        <v>2.13</v>
       </c>
       <c r="Q53">
-        <v>3.3</v>
+        <v>3.41</v>
       </c>
       <c r="R53">
-        <v>4</v>
+        <v>3.07</v>
       </c>
       <c r="S53">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="T53">
-        <v>2.18</v>
+        <v>2.07</v>
       </c>
       <c r="U53">
-        <v>5</v>
+        <v>3.85</v>
       </c>
       <c r="V53">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="W53">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="X53">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="Y53">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z53">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA53">
         <v>1.02</v>
       </c>
       <c r="AB53">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC53">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AD53">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AE53">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AF53">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AG53">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
       <c r="AH53">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AI53">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AJ53">
         <v>1.03</v>
       </c>
       <c r="AK53">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AL53">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AM53">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AN53">
-        <v>1.94</v>
+        <v>1.66</v>
       </c>
       <c r="AO53">
         <v>0</v>
       </c>
       <c r="AP53">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AQ53">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AR53">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AS53">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AT53">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AU53">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AV53">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AW53">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AX53">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AY53">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ53">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="BA53">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="BB53">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="BC53">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="BD53">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="BE53">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="BF53">
         <v>1.1</v>
@@ -11120,7 +11120,7 @@
         <v>77</v>
       </c>
       <c r="C54" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="D54" t="s">
         <v>134</v>
@@ -11159,133 +11159,133 @@
         <v>308</v>
       </c>
       <c r="P54">
-        <v>7.95</v>
+        <v>1.75</v>
       </c>
       <c r="Q54">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="R54">
-        <v>1.33</v>
+        <v>4</v>
       </c>
       <c r="S54">
-        <v>7.13</v>
+        <v>2.45</v>
       </c>
       <c r="T54">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="U54">
-        <v>1.81</v>
+        <v>4.9</v>
       </c>
       <c r="V54">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="X54">
-        <v>2.18</v>
+        <v>2.9</v>
       </c>
       <c r="Y54">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="Z54">
-        <v>4.55</v>
+        <v>7.3</v>
       </c>
       <c r="AA54">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC54">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="AD54">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="AE54">
-        <v>1.52</v>
+        <v>1.77</v>
       </c>
       <c r="AF54">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="AG54">
-        <v>2.29</v>
+        <v>3.34</v>
       </c>
       <c r="AH54">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="AI54">
-        <v>4</v>
+        <v>6.65</v>
       </c>
       <c r="AJ54">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="AK54">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AL54">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AM54">
+        <v>1.26</v>
+      </c>
+      <c r="AN54">
+        <v>1.94</v>
+      </c>
+      <c r="AO54">
+        <v>0</v>
+      </c>
+      <c r="AP54">
         <v>1.13</v>
       </c>
-      <c r="AN54">
-        <v>1.05</v>
-      </c>
-      <c r="AO54">
-        <v>0</v>
-      </c>
-      <c r="AP54">
-        <v>0</v>
-      </c>
       <c r="AQ54">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AR54">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS54">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AT54">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AU54">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="AV54">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW54">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AX54">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AY54">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ54">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BA54">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="BB54">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC54">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="BD54">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE54">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="BF54">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG54">
         <v>0</v>
@@ -11305,7 +11305,7 @@
         <v>77</v>
       </c>
       <c r="C55" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="D55" t="s">
         <v>134</v>
@@ -11344,133 +11344,133 @@
         <v>308</v>
       </c>
       <c r="P55">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="Q55">
-        <v>2.99</v>
+        <v>3.52</v>
       </c>
       <c r="R55">
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
       <c r="S55">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="T55">
-        <v>1.85</v>
+        <v>2.19</v>
       </c>
       <c r="U55">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="V55">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="W55">
-        <v>2.22</v>
+        <v>3.16</v>
       </c>
       <c r="X55">
-        <v>3.48</v>
+        <v>2.3</v>
       </c>
       <c r="Y55">
+        <v>1.5</v>
+      </c>
+      <c r="Z55">
+        <v>5.55</v>
+      </c>
+      <c r="AA55">
+        <v>1.08</v>
+      </c>
+      <c r="AB55">
+        <v>1.04</v>
+      </c>
+      <c r="AC55">
+        <v>1.2</v>
+      </c>
+      <c r="AD55">
+        <v>4.1</v>
+      </c>
+      <c r="AE55">
+        <v>1.66</v>
+      </c>
+      <c r="AF55">
+        <v>2.16</v>
+      </c>
+      <c r="AG55">
+        <v>2.63</v>
+      </c>
+      <c r="AH55">
+        <v>1.41</v>
+      </c>
+      <c r="AI55">
+        <v>4.55</v>
+      </c>
+      <c r="AJ55">
+        <v>1.13</v>
+      </c>
+      <c r="AK55">
+        <v>1.55</v>
+      </c>
+      <c r="AL55">
+        <v>2.35</v>
+      </c>
+      <c r="AM55">
+        <v>1.26</v>
+      </c>
+      <c r="AN55">
+        <v>1.61</v>
+      </c>
+      <c r="AO55">
+        <v>0</v>
+      </c>
+      <c r="AP55">
+        <v>1.18</v>
+      </c>
+      <c r="AQ55">
+        <v>1.34</v>
+      </c>
+      <c r="AR55">
+        <v>1.58</v>
+      </c>
+      <c r="AS55">
+        <v>2.05</v>
+      </c>
+      <c r="AT55">
+        <v>2.45</v>
+      </c>
+      <c r="AU55">
+        <v>3.95</v>
+      </c>
+      <c r="AV55">
+        <v>2.85</v>
+      </c>
+      <c r="AW55">
+        <v>2.14</v>
+      </c>
+      <c r="AX55">
+        <v>1.7</v>
+      </c>
+      <c r="AY55">
+        <v>1.45</v>
+      </c>
+      <c r="AZ55">
+        <v>1.76</v>
+      </c>
+      <c r="BA55">
+        <v>2.33</v>
+      </c>
+      <c r="BB55">
+        <v>1.14</v>
+      </c>
+      <c r="BC55">
+        <v>1.87</v>
+      </c>
+      <c r="BD55">
+        <v>4.45</v>
+      </c>
+      <c r="BE55">
+        <v>1.87</v>
+      </c>
+      <c r="BF55">
         <v>1.22</v>
-      </c>
-      <c r="Z55">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AA55">
-        <v>1.02</v>
-      </c>
-      <c r="AB55">
-        <v>1.06</v>
-      </c>
-      <c r="AC55">
-        <v>1.49</v>
-      </c>
-      <c r="AD55">
-        <v>2.49</v>
-      </c>
-      <c r="AE55">
-        <v>2.6</v>
-      </c>
-      <c r="AF55">
-        <v>1.45</v>
-      </c>
-      <c r="AG55">
-        <v>4.7</v>
-      </c>
-      <c r="AH55">
-        <v>1.13</v>
-      </c>
-      <c r="AI55">
-        <v>9.5</v>
-      </c>
-      <c r="AJ55">
-        <v>1.01</v>
-      </c>
-      <c r="AK55">
-        <v>2.1</v>
-      </c>
-      <c r="AL55">
-        <v>1.66</v>
-      </c>
-      <c r="AM55">
-        <v>1.34</v>
-      </c>
-      <c r="AN55">
-        <v>1.52</v>
-      </c>
-      <c r="AO55">
-        <v>0</v>
-      </c>
-      <c r="AP55">
-        <v>1.4</v>
-      </c>
-      <c r="AQ55">
-        <v>1.68</v>
-      </c>
-      <c r="AR55">
-        <v>2.1</v>
-      </c>
-      <c r="AS55">
-        <v>2.75</v>
-      </c>
-      <c r="AT55">
-        <v>3.65</v>
-      </c>
-      <c r="AU55">
-        <v>2.65</v>
-      </c>
-      <c r="AV55">
-        <v>2.04</v>
-      </c>
-      <c r="AW55">
-        <v>1.64</v>
-      </c>
-      <c r="AX55">
-        <v>1.38</v>
-      </c>
-      <c r="AY55">
-        <v>1.23</v>
-      </c>
-      <c r="AZ55">
-        <v>1.83</v>
-      </c>
-      <c r="BA55">
-        <v>2.14</v>
-      </c>
-      <c r="BB55">
-        <v>1.32</v>
-      </c>
-      <c r="BC55">
-        <v>2.63</v>
-      </c>
-      <c r="BD55">
-        <v>2.96</v>
-      </c>
-      <c r="BE55">
-        <v>1.43</v>
-      </c>
-      <c r="BF55">
-        <v>1.06</v>
       </c>
       <c r="BG55">
         <v>0</v>
@@ -11490,10 +11490,10 @@
         <v>77</v>
       </c>
       <c r="C56" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D56" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E56" t="s">
         <v>191</v>
@@ -11529,133 +11529,133 @@
         <v>308</v>
       </c>
       <c r="P56">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="Q56">
-        <v>4.2</v>
+        <v>3.67</v>
       </c>
       <c r="R56">
-        <v>4.33</v>
+        <v>4.35</v>
       </c>
       <c r="S56">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="T56">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="U56">
-        <v>5</v>
+        <v>5.23</v>
       </c>
       <c r="V56">
+        <v>1.36</v>
+      </c>
+      <c r="W56">
+        <v>2.89</v>
+      </c>
+      <c r="X56">
+        <v>2.69</v>
+      </c>
+      <c r="Y56">
+        <v>1.41</v>
+      </c>
+      <c r="Z56">
+        <v>6.45</v>
+      </c>
+      <c r="AA56">
+        <v>1.09</v>
+      </c>
+      <c r="AB56">
+        <v>1.06</v>
+      </c>
+      <c r="AC56">
+        <v>1.21</v>
+      </c>
+      <c r="AD56">
+        <v>3.44</v>
+      </c>
+      <c r="AE56">
+        <v>1.84</v>
+      </c>
+      <c r="AF56">
+        <v>1.94</v>
+      </c>
+      <c r="AG56">
+        <v>3.07</v>
+      </c>
+      <c r="AH56">
+        <v>1.36</v>
+      </c>
+      <c r="AI56">
+        <v>5.84</v>
+      </c>
+      <c r="AJ56">
+        <v>1.13</v>
+      </c>
+      <c r="AK56">
+        <v>1.75</v>
+      </c>
+      <c r="AL56">
+        <v>1.95</v>
+      </c>
+      <c r="AM56">
         <v>1.25</v>
       </c>
-      <c r="W56">
-        <v>3.5</v>
-      </c>
-      <c r="X56">
-        <v>2.25</v>
-      </c>
-      <c r="Y56">
-        <v>1.6</v>
-      </c>
-      <c r="Z56">
-        <v>5</v>
-      </c>
-      <c r="AA56">
-        <v>1.12</v>
-      </c>
-      <c r="AB56">
-        <v>1.01</v>
-      </c>
-      <c r="AC56">
-        <v>1.13</v>
-      </c>
-      <c r="AD56">
-        <v>4.95</v>
-      </c>
-      <c r="AE56">
+      <c r="AN56">
+        <v>2.09</v>
+      </c>
+      <c r="AO56">
+        <v>0</v>
+      </c>
+      <c r="AP56">
+        <v>0</v>
+      </c>
+      <c r="AQ56">
+        <v>1.28</v>
+      </c>
+      <c r="AR56">
         <v>1.48</v>
       </c>
-      <c r="AF56">
-        <v>2.4</v>
-      </c>
-      <c r="AG56">
-        <v>2.35</v>
-      </c>
-      <c r="AH56">
-        <v>1.59</v>
-      </c>
-      <c r="AI56">
-        <v>3.88</v>
-      </c>
-      <c r="AJ56">
-        <v>1.18</v>
-      </c>
-      <c r="AK56">
-        <v>1.57</v>
-      </c>
-      <c r="AL56">
-        <v>2.2</v>
-      </c>
-      <c r="AM56">
+      <c r="AS56">
+        <v>1.75</v>
+      </c>
+      <c r="AT56">
+        <v>2.12</v>
+      </c>
+      <c r="AU56">
+        <v>0</v>
+      </c>
+      <c r="AV56">
+        <v>3.25</v>
+      </c>
+      <c r="AW56">
+        <v>2.43</v>
+      </c>
+      <c r="AX56">
+        <v>1.94</v>
+      </c>
+      <c r="AY56">
+        <v>1.62</v>
+      </c>
+      <c r="AZ56">
+        <v>1.4</v>
+      </c>
+      <c r="BA56">
+        <v>3.3</v>
+      </c>
+      <c r="BB56">
+        <v>1.19</v>
+      </c>
+      <c r="BC56">
+        <v>2.04</v>
+      </c>
+      <c r="BD56">
+        <v>3.98</v>
+      </c>
+      <c r="BE56">
+        <v>1.73</v>
+      </c>
+      <c r="BF56">
         <v>1.17</v>
-      </c>
-      <c r="AN56">
-        <v>2.25</v>
-      </c>
-      <c r="AO56">
-        <v>0</v>
-      </c>
-      <c r="AP56">
-        <v>1.17</v>
-      </c>
-      <c r="AQ56">
-        <v>1.34</v>
-      </c>
-      <c r="AR56">
-        <v>1.85</v>
-      </c>
-      <c r="AS56">
-        <v>2.05</v>
-      </c>
-      <c r="AT56">
-        <v>2.67</v>
-      </c>
-      <c r="AU56">
-        <v>4</v>
-      </c>
-      <c r="AV56">
-        <v>2.78</v>
-      </c>
-      <c r="AW56">
-        <v>2.08</v>
-      </c>
-      <c r="AX56">
-        <v>1.67</v>
-      </c>
-      <c r="AY56">
-        <v>1.38</v>
-      </c>
-      <c r="AZ56">
-        <v>1.36</v>
-      </c>
-      <c r="BA56">
-        <v>3.55</v>
-      </c>
-      <c r="BB56">
-        <v>1.11</v>
-      </c>
-      <c r="BC56">
-        <v>1.74</v>
-      </c>
-      <c r="BD56">
-        <v>5.4</v>
-      </c>
-      <c r="BE56">
-        <v>2.02</v>
-      </c>
-      <c r="BF56">
-        <v>1.32</v>
       </c>
       <c r="BG56">
         <v>0</v>
@@ -11675,7 +11675,7 @@
         <v>77</v>
       </c>
       <c r="C57" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="D57" t="s">
         <v>134</v>
@@ -11714,133 +11714,133 @@
         <v>308</v>
       </c>
       <c r="P57">
-        <v>1.7</v>
+        <v>2.13</v>
       </c>
       <c r="Q57">
-        <v>4.35</v>
+        <v>2.99</v>
       </c>
       <c r="R57">
-        <v>3.47</v>
+        <v>3.3</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T57">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U57">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V57">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W57">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="X57">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Y57">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z57">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC57">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AE57">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AF57">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG57">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AH57">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI57">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AJ57">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK57">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL57">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AM57">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AN57">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AO57">
         <v>0</v>
       </c>
       <c r="AP57">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AQ57">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AR57">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS57">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AT57">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AU57">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AV57">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AW57">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AX57">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AY57">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ57">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BA57">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BB57">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BC57">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="BD57">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BE57">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BF57">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BG57">
         <v>0</v>
@@ -11899,133 +11899,133 @@
         <v>308</v>
       </c>
       <c r="P58">
-        <v>1.71</v>
+        <v>2.81</v>
       </c>
       <c r="Q58">
-        <v>3.67</v>
+        <v>3.3</v>
       </c>
       <c r="R58">
-        <v>4.35</v>
+        <v>2.41</v>
       </c>
       <c r="S58">
-        <v>2.25</v>
+        <v>3.23</v>
       </c>
       <c r="T58">
-        <v>2.17</v>
+        <v>2.06</v>
       </c>
       <c r="U58">
-        <v>5.23</v>
+        <v>2.83</v>
       </c>
       <c r="V58">
+        <v>1.42</v>
+      </c>
+      <c r="W58">
+        <v>2.95</v>
+      </c>
+      <c r="X58">
+        <v>2.75</v>
+      </c>
+      <c r="Y58">
         <v>1.36</v>
       </c>
-      <c r="W58">
-        <v>2.89</v>
-      </c>
-      <c r="X58">
-        <v>2.69</v>
-      </c>
-      <c r="Y58">
-        <v>1.41</v>
-      </c>
       <c r="Z58">
-        <v>6.45</v>
+        <v>7.1</v>
       </c>
       <c r="AA58">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AB58">
+        <v>1.01</v>
+      </c>
+      <c r="AC58">
+        <v>1.27</v>
+      </c>
+      <c r="AD58">
+        <v>3.18</v>
+      </c>
+      <c r="AE58">
+        <v>2</v>
+      </c>
+      <c r="AF58">
+        <v>1.84</v>
+      </c>
+      <c r="AG58">
+        <v>3.41</v>
+      </c>
+      <c r="AH58">
+        <v>1.3</v>
+      </c>
+      <c r="AI58">
+        <v>5.75</v>
+      </c>
+      <c r="AJ58">
         <v>1.06</v>
-      </c>
-      <c r="AC58">
-        <v>1.21</v>
-      </c>
-      <c r="AD58">
-        <v>3.44</v>
-      </c>
-      <c r="AE58">
-        <v>1.84</v>
-      </c>
-      <c r="AF58">
-        <v>1.94</v>
-      </c>
-      <c r="AG58">
-        <v>3.07</v>
-      </c>
-      <c r="AH58">
-        <v>1.36</v>
-      </c>
-      <c r="AI58">
-        <v>5.84</v>
-      </c>
-      <c r="AJ58">
-        <v>1.13</v>
       </c>
       <c r="AK58">
         <v>1.75</v>
       </c>
       <c r="AL58">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AM58">
+        <v>1.28</v>
+      </c>
+      <c r="AN58">
+        <v>1.37</v>
+      </c>
+      <c r="AO58">
+        <v>0</v>
+      </c>
+      <c r="AP58">
+        <v>1.26</v>
+      </c>
+      <c r="AQ58">
+        <v>1.46</v>
+      </c>
+      <c r="AR58">
+        <v>1.75</v>
+      </c>
+      <c r="AS58">
+        <v>2.18</v>
+      </c>
+      <c r="AT58">
+        <v>2.8</v>
+      </c>
+      <c r="AU58">
+        <v>3.4</v>
+      </c>
+      <c r="AV58">
+        <v>2.5</v>
+      </c>
+      <c r="AW58">
+        <v>1.93</v>
+      </c>
+      <c r="AX58">
+        <v>1.58</v>
+      </c>
+      <c r="AY58">
+        <v>1.37</v>
+      </c>
+      <c r="AZ58">
+        <v>2.12</v>
+      </c>
+      <c r="BA58">
+        <v>1.91</v>
+      </c>
+      <c r="BB58">
         <v>1.25</v>
       </c>
-      <c r="AN58">
-        <v>2.09</v>
-      </c>
-      <c r="AO58">
-        <v>0</v>
-      </c>
-      <c r="AP58">
-        <v>0</v>
-      </c>
-      <c r="AQ58">
-        <v>1.28</v>
-      </c>
-      <c r="AR58">
-        <v>1.48</v>
-      </c>
-      <c r="AS58">
-        <v>1.75</v>
-      </c>
-      <c r="AT58">
-        <v>2.12</v>
-      </c>
-      <c r="AU58">
-        <v>0</v>
-      </c>
-      <c r="AV58">
-        <v>3.25</v>
-      </c>
-      <c r="AW58">
-        <v>2.43</v>
-      </c>
-      <c r="AX58">
-        <v>1.94</v>
-      </c>
-      <c r="AY58">
-        <v>1.62</v>
-      </c>
-      <c r="AZ58">
-        <v>1.4</v>
-      </c>
-      <c r="BA58">
-        <v>3.3</v>
-      </c>
-      <c r="BB58">
-        <v>1.19</v>
-      </c>
       <c r="BC58">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="BD58">
-        <v>3.98</v>
+        <v>3.66</v>
       </c>
       <c r="BE58">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="BF58">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="BG58">
         <v>0</v>
@@ -12045,7 +12045,7 @@
         <v>77</v>
       </c>
       <c r="C59" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D59" t="s">
         <v>136</v>
@@ -12084,133 +12084,133 @@
         <v>308</v>
       </c>
       <c r="P59">
-        <v>2.81</v>
+        <v>1.35</v>
       </c>
       <c r="Q59">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="R59">
-        <v>2.41</v>
+        <v>7.2</v>
       </c>
       <c r="S59">
-        <v>3.23</v>
+        <v>1.67</v>
       </c>
       <c r="T59">
-        <v>2.06</v>
+        <v>2.8</v>
       </c>
       <c r="U59">
-        <v>2.83</v>
+        <v>5.9</v>
       </c>
       <c r="V59">
-        <v>1.42</v>
+        <v>1.17</v>
       </c>
       <c r="W59">
-        <v>2.95</v>
+        <v>4.25</v>
       </c>
       <c r="X59">
-        <v>2.75</v>
+        <v>1.9</v>
       </c>
       <c r="Y59">
-        <v>1.36</v>
+        <v>1.84</v>
       </c>
       <c r="Z59">
-        <v>7.1</v>
+        <v>3.66</v>
       </c>
       <c r="AA59">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="AB59">
         <v>1.01</v>
       </c>
       <c r="AC59">
-        <v>1.27</v>
+        <v>1.06</v>
       </c>
       <c r="AD59">
-        <v>3.18</v>
+        <v>7</v>
       </c>
       <c r="AE59">
-        <v>2</v>
+        <v>1.28</v>
       </c>
       <c r="AF59">
-        <v>1.84</v>
+        <v>3.5</v>
       </c>
       <c r="AG59">
-        <v>3.41</v>
+        <v>1.85</v>
       </c>
       <c r="AH59">
-        <v>1.3</v>
+        <v>1.98</v>
       </c>
       <c r="AI59">
-        <v>5.75</v>
+        <v>2.64</v>
       </c>
       <c r="AJ59">
-        <v>1.06</v>
+        <v>1.38</v>
       </c>
       <c r="AK59">
-        <v>1.75</v>
+        <v>1.48</v>
       </c>
       <c r="AL59">
-        <v>1.97</v>
+        <v>2.43</v>
       </c>
       <c r="AM59">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AN59">
-        <v>1.37</v>
+        <v>3.08</v>
       </c>
       <c r="AO59">
         <v>0</v>
       </c>
       <c r="AP59">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AQ59">
+        <v>1.29</v>
+      </c>
+      <c r="AR59">
+        <v>1.49</v>
+      </c>
+      <c r="AS59">
+        <v>1.78</v>
+      </c>
+      <c r="AT59">
+        <v>2.2</v>
+      </c>
+      <c r="AU59">
+        <v>0</v>
+      </c>
+      <c r="AV59">
+        <v>3.2</v>
+      </c>
+      <c r="AW59">
+        <v>2.38</v>
+      </c>
+      <c r="AX59">
+        <v>1.9</v>
+      </c>
+      <c r="AY59">
+        <v>1.58</v>
+      </c>
+      <c r="AZ59">
+        <v>1.22</v>
+      </c>
+      <c r="BA59">
+        <v>4.35</v>
+      </c>
+      <c r="BB59">
+        <v>1.07</v>
+      </c>
+      <c r="BC59">
+        <v>1.55</v>
+      </c>
+      <c r="BD59">
+        <v>6</v>
+      </c>
+      <c r="BE59">
+        <v>2.41</v>
+      </c>
+      <c r="BF59">
         <v>1.46</v>
-      </c>
-      <c r="AR59">
-        <v>1.75</v>
-      </c>
-      <c r="AS59">
-        <v>2.18</v>
-      </c>
-      <c r="AT59">
-        <v>2.8</v>
-      </c>
-      <c r="AU59">
-        <v>3.4</v>
-      </c>
-      <c r="AV59">
-        <v>2.5</v>
-      </c>
-      <c r="AW59">
-        <v>1.93</v>
-      </c>
-      <c r="AX59">
-        <v>1.58</v>
-      </c>
-      <c r="AY59">
-        <v>1.37</v>
-      </c>
-      <c r="AZ59">
-        <v>2.12</v>
-      </c>
-      <c r="BA59">
-        <v>1.91</v>
-      </c>
-      <c r="BB59">
-        <v>1.25</v>
-      </c>
-      <c r="BC59">
-        <v>2.14</v>
-      </c>
-      <c r="BD59">
-        <v>3.66</v>
-      </c>
-      <c r="BE59">
-        <v>1.66</v>
-      </c>
-      <c r="BF59">
-        <v>1.14</v>
       </c>
       <c r="BG59">
         <v>0</v>
@@ -12230,7 +12230,7 @@
         <v>77</v>
       </c>
       <c r="C60" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D60" t="s">
         <v>134</v>
@@ -12269,133 +12269,133 @@
         <v>308</v>
       </c>
       <c r="P60">
-        <v>2.61</v>
+        <v>1.57</v>
       </c>
       <c r="Q60">
-        <v>3.34</v>
+        <v>4.2</v>
       </c>
       <c r="R60">
-        <v>2.52</v>
+        <v>4.33</v>
       </c>
       <c r="S60">
-        <v>3.25</v>
+        <v>1.91</v>
       </c>
       <c r="T60">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="U60">
-        <v>3.01</v>
+        <v>5</v>
       </c>
       <c r="V60">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="W60">
-        <v>2.66</v>
+        <v>3.5</v>
       </c>
       <c r="X60">
-        <v>3.16</v>
+        <v>2.25</v>
       </c>
       <c r="Y60">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="Z60">
-        <v>8.699999999999999</v>
+        <v>5</v>
       </c>
       <c r="AA60">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AB60">
         <v>1.01</v>
       </c>
       <c r="AC60">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AD60">
-        <v>2.81</v>
+        <v>4.95</v>
       </c>
       <c r="AE60">
-        <v>2.19</v>
+        <v>1.48</v>
       </c>
       <c r="AF60">
-        <v>1.64</v>
+        <v>2.4</v>
       </c>
       <c r="AG60">
+        <v>2.35</v>
+      </c>
+      <c r="AH60">
+        <v>1.59</v>
+      </c>
+      <c r="AI60">
+        <v>3.88</v>
+      </c>
+      <c r="AJ60">
+        <v>1.18</v>
+      </c>
+      <c r="AK60">
+        <v>1.57</v>
+      </c>
+      <c r="AL60">
+        <v>2.2</v>
+      </c>
+      <c r="AM60">
+        <v>1.17</v>
+      </c>
+      <c r="AN60">
+        <v>2.25</v>
+      </c>
+      <c r="AO60">
+        <v>0</v>
+      </c>
+      <c r="AP60">
+        <v>1.17</v>
+      </c>
+      <c r="AQ60">
+        <v>1.34</v>
+      </c>
+      <c r="AR60">
+        <v>1.85</v>
+      </c>
+      <c r="AS60">
+        <v>2.05</v>
+      </c>
+      <c r="AT60">
+        <v>2.67</v>
+      </c>
+      <c r="AU60">
         <v>4</v>
       </c>
-      <c r="AH60">
-        <v>1.17</v>
-      </c>
-      <c r="AI60">
-        <v>8.5</v>
-      </c>
-      <c r="AJ60">
-        <v>1.01</v>
-      </c>
-      <c r="AK60">
-        <v>1.8</v>
-      </c>
-      <c r="AL60">
-        <v>1.83</v>
-      </c>
-      <c r="AM60">
-        <v>1.3</v>
-      </c>
-      <c r="AN60">
-        <v>1.37</v>
-      </c>
-      <c r="AO60">
-        <v>0</v>
-      </c>
-      <c r="AP60">
-        <v>1.27</v>
-      </c>
-      <c r="AQ60">
-        <v>1.54</v>
-      </c>
-      <c r="AR60">
-        <v>2.2</v>
-      </c>
-      <c r="AS60">
-        <v>2.46</v>
-      </c>
-      <c r="AT60">
-        <v>3.35</v>
-      </c>
-      <c r="AU60">
-        <v>3.14</v>
-      </c>
       <c r="AV60">
-        <v>2.27</v>
+        <v>2.78</v>
       </c>
       <c r="AW60">
-        <v>1.79</v>
+        <v>2.08</v>
       </c>
       <c r="AX60">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="AY60">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="AZ60">
-        <v>2.92</v>
+        <v>1.36</v>
       </c>
       <c r="BA60">
-        <v>1.66</v>
+        <v>3.55</v>
       </c>
       <c r="BB60">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="BC60">
-        <v>2.2</v>
+        <v>1.74</v>
       </c>
       <c r="BD60">
-        <v>3.35</v>
+        <v>5.4</v>
       </c>
       <c r="BE60">
-        <v>1.51</v>
+        <v>2.02</v>
       </c>
       <c r="BF60">
-        <v>1.08</v>
+        <v>1.32</v>
       </c>
       <c r="BG60">
         <v>0</v>
@@ -12415,7 +12415,7 @@
         <v>77</v>
       </c>
       <c r="C61" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="D61" t="s">
         <v>134</v>
@@ -12454,133 +12454,133 @@
         <v>308</v>
       </c>
       <c r="P61">
-        <v>2.21</v>
+        <v>7.95</v>
       </c>
       <c r="Q61">
-        <v>3.52</v>
+        <v>4.7</v>
       </c>
       <c r="R61">
-        <v>2.96</v>
+        <v>1.33</v>
       </c>
       <c r="S61">
-        <v>2.5</v>
+        <v>7.13</v>
       </c>
       <c r="T61">
-        <v>2.19</v>
+        <v>2.55</v>
       </c>
       <c r="U61">
-        <v>3.58</v>
+        <v>1.81</v>
       </c>
       <c r="V61">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W61">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="X61">
+        <v>2.18</v>
+      </c>
+      <c r="Y61">
+        <v>1.6</v>
+      </c>
+      <c r="Z61">
+        <v>4.55</v>
+      </c>
+      <c r="AA61">
+        <v>1.15</v>
+      </c>
+      <c r="AB61">
+        <v>0</v>
+      </c>
+      <c r="AC61">
+        <v>1.16</v>
+      </c>
+      <c r="AD61">
+        <v>4.2</v>
+      </c>
+      <c r="AE61">
+        <v>1.52</v>
+      </c>
+      <c r="AF61">
         <v>2.3</v>
       </c>
-      <c r="Y61">
-        <v>1.5</v>
-      </c>
-      <c r="Z61">
-        <v>5.55</v>
-      </c>
-      <c r="AA61">
-        <v>1.08</v>
-      </c>
-      <c r="AB61">
-        <v>1.04</v>
-      </c>
-      <c r="AC61">
-        <v>1.2</v>
-      </c>
-      <c r="AD61">
-        <v>4.1</v>
-      </c>
-      <c r="AE61">
-        <v>1.66</v>
-      </c>
-      <c r="AF61">
-        <v>2.16</v>
-      </c>
       <c r="AG61">
-        <v>2.63</v>
+        <v>2.29</v>
       </c>
       <c r="AH61">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AI61">
-        <v>4.55</v>
+        <v>4</v>
       </c>
       <c r="AJ61">
+        <v>1.21</v>
+      </c>
+      <c r="AK61">
+        <v>1.9</v>
+      </c>
+      <c r="AL61">
+        <v>1.9</v>
+      </c>
+      <c r="AM61">
         <v>1.13</v>
       </c>
-      <c r="AK61">
-        <v>1.55</v>
-      </c>
-      <c r="AL61">
-        <v>2.35</v>
-      </c>
-      <c r="AM61">
-        <v>1.26</v>
-      </c>
       <c r="AN61">
-        <v>1.61</v>
+        <v>1.05</v>
       </c>
       <c r="AO61">
         <v>0</v>
       </c>
       <c r="AP61">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ61">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AR61">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AS61">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AT61">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AU61">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AV61">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AW61">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AX61">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AY61">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ61">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="BA61">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="BB61">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC61">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="BD61">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="BE61">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="BF61">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG61">
         <v>0</v>
@@ -12600,10 +12600,10 @@
         <v>77</v>
       </c>
       <c r="C62" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D62" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E62" t="s">
         <v>197</v>
@@ -12639,133 +12639,133 @@
         <v>308</v>
       </c>
       <c r="P62">
-        <v>1.35</v>
+        <v>2.61</v>
       </c>
       <c r="Q62">
-        <v>5</v>
+        <v>3.34</v>
       </c>
       <c r="R62">
-        <v>7.2</v>
+        <v>2.52</v>
       </c>
       <c r="S62">
-        <v>1.67</v>
+        <v>3.25</v>
       </c>
       <c r="T62">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="U62">
-        <v>5.9</v>
+        <v>3.01</v>
       </c>
       <c r="V62">
-        <v>1.17</v>
+        <v>1.44</v>
       </c>
       <c r="W62">
-        <v>4.25</v>
+        <v>2.66</v>
       </c>
       <c r="X62">
-        <v>1.9</v>
+        <v>3.16</v>
       </c>
       <c r="Y62">
-        <v>1.84</v>
+        <v>1.3</v>
       </c>
       <c r="Z62">
-        <v>3.66</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA62">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="AB62">
         <v>1.01</v>
       </c>
       <c r="AC62">
-        <v>1.06</v>
+        <v>1.33</v>
       </c>
       <c r="AD62">
-        <v>7</v>
+        <v>2.81</v>
       </c>
       <c r="AE62">
-        <v>1.28</v>
+        <v>2.19</v>
       </c>
       <c r="AF62">
-        <v>3.5</v>
+        <v>1.64</v>
       </c>
       <c r="AG62">
-        <v>1.85</v>
+        <v>4</v>
       </c>
       <c r="AH62">
-        <v>1.98</v>
+        <v>1.17</v>
       </c>
       <c r="AI62">
-        <v>2.64</v>
+        <v>8.5</v>
       </c>
       <c r="AJ62">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="AK62">
-        <v>1.48</v>
+        <v>1.8</v>
       </c>
       <c r="AL62">
-        <v>2.43</v>
+        <v>1.83</v>
       </c>
       <c r="AM62">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AN62">
-        <v>3.08</v>
+        <v>1.37</v>
       </c>
       <c r="AO62">
         <v>0</v>
       </c>
       <c r="AP62">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ62">
-        <v>1.29</v>
+        <v>1.54</v>
       </c>
       <c r="AR62">
-        <v>1.49</v>
+        <v>2.2</v>
       </c>
       <c r="AS62">
-        <v>1.78</v>
+        <v>2.46</v>
       </c>
       <c r="AT62">
+        <v>3.35</v>
+      </c>
+      <c r="AU62">
+        <v>3.14</v>
+      </c>
+      <c r="AV62">
+        <v>2.27</v>
+      </c>
+      <c r="AW62">
+        <v>1.79</v>
+      </c>
+      <c r="AX62">
+        <v>1.46</v>
+      </c>
+      <c r="AY62">
+        <v>1.24</v>
+      </c>
+      <c r="AZ62">
+        <v>2.92</v>
+      </c>
+      <c r="BA62">
+        <v>1.66</v>
+      </c>
+      <c r="BB62">
+        <v>1.27</v>
+      </c>
+      <c r="BC62">
         <v>2.2</v>
       </c>
-      <c r="AU62">
-        <v>0</v>
-      </c>
-      <c r="AV62">
-        <v>3.2</v>
-      </c>
-      <c r="AW62">
-        <v>2.38</v>
-      </c>
-      <c r="AX62">
-        <v>1.9</v>
-      </c>
-      <c r="AY62">
-        <v>1.58</v>
-      </c>
-      <c r="AZ62">
-        <v>1.22</v>
-      </c>
-      <c r="BA62">
-        <v>4.35</v>
-      </c>
-      <c r="BB62">
-        <v>1.07</v>
-      </c>
-      <c r="BC62">
-        <v>1.55</v>
-      </c>
       <c r="BD62">
-        <v>6</v>
+        <v>3.35</v>
       </c>
       <c r="BE62">
-        <v>2.41</v>
+        <v>1.51</v>
       </c>
       <c r="BF62">
-        <v>1.46</v>
+        <v>1.08</v>
       </c>
       <c r="BG62">
         <v>0</v>
@@ -12970,10 +12970,10 @@
         <v>79</v>
       </c>
       <c r="C64" t="s">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="D64" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E64" t="s">
         <v>199</v>
@@ -13009,133 +13009,133 @@
         <v>308</v>
       </c>
       <c r="P64">
-        <v>1.34</v>
+        <v>2.3</v>
       </c>
       <c r="Q64">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="R64">
-        <v>7.55</v>
+        <v>3</v>
       </c>
       <c r="S64">
-        <v>1.81</v>
+        <v>2.96</v>
       </c>
       <c r="T64">
-        <v>2.65</v>
+        <v>2.04</v>
       </c>
       <c r="U64">
-        <v>5.6</v>
+        <v>3.69</v>
       </c>
       <c r="V64">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W64">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="X64">
-        <v>2.07</v>
+        <v>2.99</v>
       </c>
       <c r="Y64">
-        <v>1.58</v>
+        <v>1.33</v>
       </c>
       <c r="Z64">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC64">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="AD64">
-        <v>4.7</v>
+        <v>2.92</v>
       </c>
       <c r="AE64">
-        <v>1.46</v>
+        <v>2.09</v>
       </c>
       <c r="AF64">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="AG64">
-        <v>2.17</v>
+        <v>3.7</v>
       </c>
       <c r="AH64">
+        <v>1.24</v>
+      </c>
+      <c r="AI64">
+        <v>7.3</v>
+      </c>
+      <c r="AJ64">
+        <v>1.03</v>
+      </c>
+      <c r="AK64">
+        <v>1.82</v>
+      </c>
+      <c r="AL64">
+        <v>1.86</v>
+      </c>
+      <c r="AM64">
+        <v>1.29</v>
+      </c>
+      <c r="AN64">
+        <v>1.54</v>
+      </c>
+      <c r="AO64">
+        <v>0</v>
+      </c>
+      <c r="AP64">
+        <v>1.31</v>
+      </c>
+      <c r="AQ64">
+        <v>1.47</v>
+      </c>
+      <c r="AR64">
+        <v>2.31</v>
+      </c>
+      <c r="AS64">
+        <v>2.58</v>
+      </c>
+      <c r="AT64">
+        <v>3.57</v>
+      </c>
+      <c r="AU64">
+        <v>2.98</v>
+      </c>
+      <c r="AV64">
+        <v>2.18</v>
+      </c>
+      <c r="AW64">
+        <v>1.73</v>
+      </c>
+      <c r="AX64">
+        <v>1.42</v>
+      </c>
+      <c r="AY64">
+        <v>1.21</v>
+      </c>
+      <c r="AZ64">
+        <v>1.68</v>
+      </c>
+      <c r="BA64">
+        <v>2.75</v>
+      </c>
+      <c r="BB64">
+        <v>1.25</v>
+      </c>
+      <c r="BC64">
+        <v>2.29</v>
+      </c>
+      <c r="BD64">
+        <v>3.36</v>
+      </c>
+      <c r="BE64">
         <v>1.57</v>
       </c>
-      <c r="AI64">
-        <v>3.6</v>
-      </c>
-      <c r="AJ64">
-        <v>1.22</v>
-      </c>
-      <c r="AK64">
-        <v>1.66</v>
-      </c>
-      <c r="AL64">
-        <v>2.07</v>
-      </c>
-      <c r="AM64">
-        <v>1.13</v>
-      </c>
-      <c r="AN64">
-        <v>2.5</v>
-      </c>
-      <c r="AO64">
-        <v>0</v>
-      </c>
-      <c r="AP64">
-        <v>0</v>
-      </c>
-      <c r="AQ64">
-        <v>0</v>
-      </c>
-      <c r="AR64">
-        <v>0</v>
-      </c>
-      <c r="AS64">
-        <v>0</v>
-      </c>
-      <c r="AT64">
-        <v>0</v>
-      </c>
-      <c r="AU64">
-        <v>0</v>
-      </c>
-      <c r="AV64">
-        <v>0</v>
-      </c>
-      <c r="AW64">
-        <v>0</v>
-      </c>
-      <c r="AX64">
-        <v>0</v>
-      </c>
-      <c r="AY64">
-        <v>0</v>
-      </c>
-      <c r="AZ64">
-        <v>0</v>
-      </c>
-      <c r="BA64">
-        <v>0</v>
-      </c>
-      <c r="BB64">
-        <v>0</v>
-      </c>
-      <c r="BC64">
-        <v>1.66</v>
-      </c>
-      <c r="BD64">
-        <v>0</v>
-      </c>
-      <c r="BE64">
-        <v>1.96</v>
-      </c>
       <c r="BF64">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG64">
         <v>0</v>
@@ -13194,22 +13194,22 @@
         <v>308</v>
       </c>
       <c r="P65">
-        <v>2.94</v>
+        <v>1.34</v>
       </c>
       <c r="Q65">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="R65">
-        <v>2.21</v>
+        <v>7.55</v>
       </c>
       <c r="S65">
-        <v>3.35</v>
+        <v>1.81</v>
       </c>
       <c r="T65">
-        <v>2.23</v>
+        <v>2.65</v>
       </c>
       <c r="U65">
-        <v>2.75</v>
+        <v>5.6</v>
       </c>
       <c r="V65">
         <v>0</v>
@@ -13218,10 +13218,10 @@
         <v>0</v>
       </c>
       <c r="X65">
-        <v>2.48</v>
+        <v>2.07</v>
       </c>
       <c r="Y65">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -13233,40 +13233,40 @@
         <v>0</v>
       </c>
       <c r="AC65">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AD65">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="AE65">
-        <v>1.77</v>
+        <v>1.46</v>
       </c>
       <c r="AF65">
-        <v>1.87</v>
+        <v>2.4</v>
       </c>
       <c r="AG65">
-        <v>2.9</v>
+        <v>2.17</v>
       </c>
       <c r="AH65">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AI65">
-        <v>5.2</v>
+        <v>3.6</v>
       </c>
       <c r="AJ65">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AK65">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AL65">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AM65">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AN65">
-        <v>1.29</v>
+        <v>2.5</v>
       </c>
       <c r="AO65">
         <v>0</v>
@@ -13311,13 +13311,13 @@
         <v>0</v>
       </c>
       <c r="BC65">
-        <v>1.97</v>
+        <v>1.66</v>
       </c>
       <c r="BD65">
         <v>0</v>
       </c>
       <c r="BE65">
-        <v>1.65</v>
+        <v>1.96</v>
       </c>
       <c r="BF65">
         <v>0</v>
@@ -13340,10 +13340,10 @@
         <v>79</v>
       </c>
       <c r="C66" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="D66" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E66" t="s">
         <v>201</v>
@@ -13379,133 +13379,133 @@
         <v>308</v>
       </c>
       <c r="P66">
-        <v>2.3</v>
+        <v>2.94</v>
       </c>
       <c r="Q66">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R66">
-        <v>3</v>
+        <v>2.21</v>
       </c>
       <c r="S66">
-        <v>2.96</v>
+        <v>3.35</v>
       </c>
       <c r="T66">
-        <v>2.04</v>
+        <v>2.23</v>
       </c>
       <c r="U66">
-        <v>3.69</v>
+        <v>2.75</v>
       </c>
       <c r="V66">
+        <v>0</v>
+      </c>
+      <c r="W66">
+        <v>0</v>
+      </c>
+      <c r="X66">
+        <v>2.48</v>
+      </c>
+      <c r="Y66">
         <v>1.41</v>
       </c>
-      <c r="W66">
-        <v>2.66</v>
-      </c>
-      <c r="X66">
-        <v>2.99</v>
-      </c>
-      <c r="Y66">
+      <c r="Z66">
+        <v>0</v>
+      </c>
+      <c r="AA66">
+        <v>0</v>
+      </c>
+      <c r="AB66">
+        <v>0</v>
+      </c>
+      <c r="AC66">
+        <v>1.23</v>
+      </c>
+      <c r="AD66">
+        <v>3.5</v>
+      </c>
+      <c r="AE66">
+        <v>1.77</v>
+      </c>
+      <c r="AF66">
+        <v>1.87</v>
+      </c>
+      <c r="AG66">
+        <v>2.9</v>
+      </c>
+      <c r="AH66">
         <v>1.33</v>
       </c>
-      <c r="Z66">
-        <v>8</v>
-      </c>
-      <c r="AA66">
-        <v>1.02</v>
-      </c>
-      <c r="AB66">
-        <v>1.01</v>
-      </c>
-      <c r="AC66">
-        <v>1.31</v>
-      </c>
-      <c r="AD66">
-        <v>2.92</v>
-      </c>
-      <c r="AE66">
-        <v>2.09</v>
-      </c>
-      <c r="AF66">
-        <v>1.7</v>
-      </c>
-      <c r="AG66">
-        <v>3.7</v>
-      </c>
-      <c r="AH66">
-        <v>1.24</v>
-      </c>
       <c r="AI66">
-        <v>7.3</v>
+        <v>5.2</v>
       </c>
       <c r="AJ66">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AK66">
-        <v>1.82</v>
+        <v>1.64</v>
       </c>
       <c r="AL66">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="AM66">
+        <v>1.23</v>
+      </c>
+      <c r="AN66">
         <v>1.29</v>
       </c>
-      <c r="AN66">
-        <v>1.54</v>
-      </c>
       <c r="AO66">
         <v>0</v>
       </c>
       <c r="AP66">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AQ66">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AR66">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AS66">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="AT66">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="AU66">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AV66">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW66">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AX66">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY66">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AZ66">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BA66">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BB66">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC66">
-        <v>2.29</v>
+        <v>1.97</v>
       </c>
       <c r="BD66">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="BE66">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="BF66">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG66">
         <v>0</v>
@@ -13531,7 +13531,7 @@
         <v>134</v>
       </c>
       <c r="E67" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F67" t="s">
         <v>287</v>
@@ -13710,7 +13710,7 @@
         <v>80</v>
       </c>
       <c r="C68" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D68" t="s">
         <v>134</v>
@@ -13758,124 +13758,124 @@
         <v>0</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T68">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W68">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="X68">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z68">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH68">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI68">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AJ68">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK68">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL68">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AM68">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN68">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AO68">
         <v>0</v>
       </c>
       <c r="AP68">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AQ68">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR68">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS68">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AT68">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AU68">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AV68">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AW68">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AX68">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY68">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AZ68">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BA68">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BB68">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC68">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BD68">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE68">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF68">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BG68">
         <v>0</v>
@@ -13895,7 +13895,7 @@
         <v>80</v>
       </c>
       <c r="C69" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D69" t="s">
         <v>134</v>
@@ -13943,124 +13943,124 @@
         <v>0</v>
       </c>
       <c r="S69">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="T69">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="U69">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="V69">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="W69">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="X69">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Y69">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z69">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AA69">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB69">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC69">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AD69">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AE69">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF69">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AG69">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AH69">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI69">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AJ69">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK69">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL69">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AM69">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN69">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AO69">
         <v>0</v>
       </c>
       <c r="AP69">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AQ69">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR69">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AS69">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AT69">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AU69">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AV69">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AW69">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AX69">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AY69">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AZ69">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BA69">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BB69">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC69">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BD69">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BE69">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BF69">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BG69">
         <v>0</v>
@@ -14304,19 +14304,19 @@
         <v>308</v>
       </c>
       <c r="P71">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="Q71">
         <v>3.6</v>
       </c>
       <c r="R71">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="S71">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="T71">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="U71">
         <v>3.6</v>
@@ -14328,13 +14328,13 @@
         <v>3.04</v>
       </c>
       <c r="X71">
-        <v>2.53</v>
+        <v>2.32</v>
       </c>
       <c r="Y71">
         <v>1.46</v>
       </c>
       <c r="Z71">
-        <v>6</v>
+        <v>5.85</v>
       </c>
       <c r="AA71">
         <v>1.07</v>
@@ -14346,10 +14346,10 @@
         <v>1.24</v>
       </c>
       <c r="AD71">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AE71">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AF71">
         <v>2</v>
@@ -14388,10 +14388,10 @@
         <v>1.4</v>
       </c>
       <c r="AR71">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="AS71">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="AT71">
         <v>2.88</v>
@@ -14403,10 +14403,10 @@
         <v>2.6</v>
       </c>
       <c r="AW71">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AX71">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AY71">
         <v>1.32</v>
@@ -14427,7 +14427,7 @@
         <v>4.15</v>
       </c>
       <c r="BE71">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="BF71">
         <v>1.19</v>
@@ -14820,7 +14820,7 @@
         <v>83</v>
       </c>
       <c r="C74" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="D74" t="s">
         <v>134</v>
@@ -14859,133 +14859,133 @@
         <v>308</v>
       </c>
       <c r="P74">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q74">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R74">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S74">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T74">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U74">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V74">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W74">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="X74">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y74">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z74">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA74">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB74">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC74">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AD74">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AE74">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF74">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG74">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AH74">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI74">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AJ74">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK74">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL74">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM74">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AN74">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AO74">
         <v>0</v>
       </c>
       <c r="AP74">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AQ74">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AR74">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AS74">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AT74">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AU74">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AV74">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AW74">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AX74">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AY74">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ74">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BA74">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BB74">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC74">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="BD74">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="BE74">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BF74">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG74">
         <v>0</v>
@@ -15005,7 +15005,7 @@
         <v>83</v>
       </c>
       <c r="C75" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="D75" t="s">
         <v>134</v>
@@ -15044,133 +15044,133 @@
         <v>308</v>
       </c>
       <c r="P75">
-        <v>6.3</v>
+        <v>2.45</v>
       </c>
       <c r="Q75">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="R75">
-        <v>1.45</v>
+        <v>2.88</v>
       </c>
       <c r="S75">
-        <v>5.75</v>
+        <v>3</v>
       </c>
       <c r="T75">
-        <v>2.45</v>
+        <v>2.14</v>
       </c>
       <c r="U75">
-        <v>1.99</v>
+        <v>3.3</v>
       </c>
       <c r="V75">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="W75">
-        <v>3.45</v>
+        <v>2.85</v>
       </c>
       <c r="X75">
-        <v>2.33</v>
+        <v>2.8</v>
       </c>
       <c r="Y75">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="Z75">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="AA75">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AB75">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC75">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AD75">
-        <v>4.45</v>
+        <v>3.34</v>
       </c>
       <c r="AE75">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AF75">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AG75">
-        <v>2.43</v>
+        <v>3.55</v>
       </c>
       <c r="AH75">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="AI75">
-        <v>4.15</v>
+        <v>6.1</v>
       </c>
       <c r="AJ75">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AK75">
         <v>1.75</v>
       </c>
       <c r="AL75">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AM75">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AN75">
-        <v>1.13</v>
+        <v>1.62</v>
       </c>
       <c r="AO75">
         <v>0</v>
       </c>
       <c r="AP75">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ75">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AR75">
+        <v>1.78</v>
+      </c>
+      <c r="AS75">
+        <v>2.19</v>
+      </c>
+      <c r="AT75">
+        <v>2.88</v>
+      </c>
+      <c r="AU75">
+        <v>3.58</v>
+      </c>
+      <c r="AV75">
+        <v>2.57</v>
+      </c>
+      <c r="AW75">
+        <v>1.96</v>
+      </c>
+      <c r="AX75">
+        <v>1.57</v>
+      </c>
+      <c r="AY75">
+        <v>1.32</v>
+      </c>
+      <c r="AZ75">
+        <v>1.65</v>
+      </c>
+      <c r="BA75">
+        <v>2.15</v>
+      </c>
+      <c r="BB75">
+        <v>1.24</v>
+      </c>
+      <c r="BC75">
+        <v>2.08</v>
+      </c>
+      <c r="BD75">
+        <v>3.84</v>
+      </c>
+      <c r="BE75">
         <v>1.71</v>
       </c>
-      <c r="AS75">
-        <v>2.15</v>
-      </c>
-      <c r="AT75">
-        <v>2.8</v>
-      </c>
-      <c r="AU75">
-        <v>3.6</v>
-      </c>
-      <c r="AV75">
-        <v>2.65</v>
-      </c>
-      <c r="AW75">
-        <v>2.01</v>
-      </c>
-      <c r="AX75">
-        <v>1.62</v>
-      </c>
-      <c r="AY75">
-        <v>1.38</v>
-      </c>
-      <c r="AZ75">
-        <v>3.7</v>
-      </c>
-      <c r="BA75">
-        <v>1.31</v>
-      </c>
-      <c r="BB75">
-        <v>1.2</v>
-      </c>
-      <c r="BC75">
-        <v>1.91</v>
-      </c>
-      <c r="BD75">
-        <v>4.8</v>
-      </c>
-      <c r="BE75">
-        <v>1.85</v>
-      </c>
       <c r="BF75">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="BG75">
         <v>0</v>
@@ -15190,7 +15190,7 @@
         <v>83</v>
       </c>
       <c r="C76" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="D76" t="s">
         <v>134</v>
@@ -15229,133 +15229,133 @@
         <v>308</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="Q76">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R76">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S76">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="T76">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U76">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V76">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W76">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="X76">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Y76">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z76">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA76">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB76">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC76">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD76">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AE76">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF76">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG76">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AH76">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI76">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AJ76">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK76">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL76">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AM76">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN76">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AO76">
         <v>0</v>
       </c>
       <c r="AP76">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AQ76">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR76">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AS76">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AT76">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU76">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV76">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AW76">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AX76">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY76">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ76">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BA76">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BB76">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC76">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD76">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE76">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF76">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG76">
         <v>0</v>
@@ -15560,7 +15560,7 @@
         <v>85</v>
       </c>
       <c r="C78" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D78" t="s">
         <v>134</v>
@@ -15784,133 +15784,133 @@
         <v>308</v>
       </c>
       <c r="P79">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="Q79">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="R79">
-        <v>4.5</v>
+        <v>3.41</v>
       </c>
       <c r="S79">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T79">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U79">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="V79">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W79">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="X79">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Y79">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z79">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AA79">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB79">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC79">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD79">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AE79">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AF79">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG79">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AH79">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI79">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="AJ79">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK79">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AL79">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AM79">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN79">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AO79">
         <v>0</v>
       </c>
       <c r="AP79">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AQ79">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AR79">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AS79">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AT79">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AU79">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AV79">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AW79">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AX79">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AY79">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ79">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="BA79">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="BB79">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BC79">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="BD79">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BE79">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF79">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG79">
         <v>0</v>
@@ -15969,133 +15969,133 @@
         <v>308</v>
       </c>
       <c r="P80">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="Q80">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="R80">
-        <v>3.41</v>
+        <v>4.5</v>
       </c>
       <c r="S80">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T80">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U80">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="V80">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W80">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="X80">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Y80">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z80">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA80">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB80">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC80">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD80">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE80">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AF80">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG80">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH80">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI80">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="AJ80">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK80">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AL80">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AM80">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN80">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AO80">
         <v>0</v>
       </c>
       <c r="AP80">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AQ80">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR80">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AS80">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AT80">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AU80">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AV80">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW80">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AX80">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY80">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ80">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="BA80">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="BB80">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC80">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="BD80">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE80">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF80">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG80">
         <v>0</v>
@@ -16154,55 +16154,55 @@
         <v>308</v>
       </c>
       <c r="P81">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="Q81">
+        <v>2.78</v>
+      </c>
+      <c r="R81">
+        <v>3.72</v>
+      </c>
+      <c r="S81">
+        <v>0</v>
+      </c>
+      <c r="T81">
+        <v>0</v>
+      </c>
+      <c r="U81">
+        <v>0</v>
+      </c>
+      <c r="V81">
+        <v>0</v>
+      </c>
+      <c r="W81">
+        <v>0</v>
+      </c>
+      <c r="X81">
+        <v>0</v>
+      </c>
+      <c r="Y81">
+        <v>0</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+      <c r="AA81">
+        <v>0</v>
+      </c>
+      <c r="AB81">
+        <v>0</v>
+      </c>
+      <c r="AC81">
+        <v>0</v>
+      </c>
+      <c r="AD81">
+        <v>0</v>
+      </c>
+      <c r="AE81">
         <v>2.87</v>
       </c>
-      <c r="R81">
-        <v>3.54</v>
-      </c>
-      <c r="S81">
-        <v>0</v>
-      </c>
-      <c r="T81">
-        <v>0</v>
-      </c>
-      <c r="U81">
-        <v>0</v>
-      </c>
-      <c r="V81">
-        <v>0</v>
-      </c>
-      <c r="W81">
-        <v>0</v>
-      </c>
-      <c r="X81">
-        <v>0</v>
-      </c>
-      <c r="Y81">
-        <v>0</v>
-      </c>
-      <c r="Z81">
-        <v>0</v>
-      </c>
-      <c r="AA81">
-        <v>0</v>
-      </c>
-      <c r="AB81">
-        <v>0</v>
-      </c>
-      <c r="AC81">
-        <v>0</v>
-      </c>
-      <c r="AD81">
-        <v>0</v>
-      </c>
-      <c r="AE81">
-        <v>0</v>
-      </c>
       <c r="AF81">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG81">
         <v>0</v>
@@ -16300,7 +16300,7 @@
         <v>87</v>
       </c>
       <c r="C82" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D82" t="s">
         <v>136</v>
@@ -16485,7 +16485,7 @@
         <v>87</v>
       </c>
       <c r="C83" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D83" t="s">
         <v>136</v>
@@ -16524,79 +16524,79 @@
         <v>308</v>
       </c>
       <c r="P83">
-        <v>1.65</v>
+        <v>2.12</v>
       </c>
       <c r="Q83">
-        <v>3.25</v>
+        <v>2.87</v>
       </c>
       <c r="R83">
-        <v>5</v>
+        <v>3.54</v>
       </c>
       <c r="S83">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="T83">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U83">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="V83">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W83">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="X83">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y83">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z83">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA83">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB83">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC83">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AD83">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AE83">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AF83">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG83">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AH83">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AI83">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AJ83">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK83">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AL83">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AM83">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN83">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AO83">
         <v>0</v>
@@ -16638,19 +16638,19 @@
         <v>0</v>
       </c>
       <c r="BB83">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BC83">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="BD83">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="BE83">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BF83">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BG83">
         <v>0</v>
@@ -16709,79 +16709,79 @@
         <v>308</v>
       </c>
       <c r="P84">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="Q84">
-        <v>2.78</v>
+        <v>3.25</v>
       </c>
       <c r="R84">
-        <v>3.72</v>
+        <v>5</v>
       </c>
       <c r="S84">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="T84">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U84">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="V84">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W84">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="X84">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y84">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z84">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AA84">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC84">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD84">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AE84">
-        <v>2.87</v>
+        <v>2.43</v>
       </c>
       <c r="AF84">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG84">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AH84">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI84">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AJ84">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK84">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AL84">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AM84">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN84">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AO84">
         <v>0</v>
@@ -16823,19 +16823,19 @@
         <v>0</v>
       </c>
       <c r="BB84">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BC84">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BD84">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="BE84">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BF84">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BG84">
         <v>0</v>
@@ -17040,7 +17040,7 @@
         <v>89</v>
       </c>
       <c r="C86" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D86" t="s">
         <v>136</v>
@@ -17079,133 +17079,133 @@
         <v>308</v>
       </c>
       <c r="P86">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="Q86">
-        <v>3</v>
+        <v>3.38</v>
       </c>
       <c r="R86">
-        <v>3.8</v>
+        <v>4.01</v>
       </c>
       <c r="S86">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T86">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="U86">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="V86">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="W86">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="X86">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Y86">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z86">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA86">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB86">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC86">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD86">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AE86">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AF86">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AG86">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="AH86">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AI86">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AJ86">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK86">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AL86">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AM86">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN86">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AO86">
         <v>0</v>
       </c>
       <c r="AP86">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AQ86">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AR86">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AS86">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AT86">
         <v>0</v>
       </c>
       <c r="AU86">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AV86">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AW86">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AX86">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AY86">
         <v>0</v>
       </c>
       <c r="AZ86">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="BA86">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="BB86">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BC86">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="BD86">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BE86">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BF86">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BG86">
         <v>0</v>
@@ -17225,7 +17225,7 @@
         <v>89</v>
       </c>
       <c r="C87" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D87" t="s">
         <v>136</v>
@@ -17264,133 +17264,133 @@
         <v>308</v>
       </c>
       <c r="P87">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="Q87">
-        <v>3.38</v>
+        <v>3</v>
       </c>
       <c r="R87">
-        <v>4.01</v>
+        <v>3.8</v>
       </c>
       <c r="S87">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T87">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="U87">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="V87">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W87">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="X87">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Y87">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z87">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA87">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB87">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC87">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD87">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AE87">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AF87">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG87">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="AH87">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI87">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AJ87">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK87">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL87">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AM87">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN87">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AO87">
         <v>0</v>
       </c>
       <c r="AP87">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AQ87">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AR87">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AS87">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AT87">
         <v>0</v>
       </c>
       <c r="AU87">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AV87">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AW87">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AX87">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AY87">
         <v>0</v>
       </c>
       <c r="AZ87">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BA87">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="BB87">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BC87">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="BD87">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BE87">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BF87">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG87">
         <v>0</v>

--- a/jogos_2026-05-04.xlsx
+++ b/jogos_2026-05-04.xlsx
@@ -301,24 +301,24 @@
     <t>Croatia Druga HNL</t>
   </si>
   <si>
+    <t>Uzbekistan Uzbekistan Super League</t>
+  </si>
+  <si>
+    <t>Oman Professional League</t>
+  </si>
+  <si>
+    <t>Russia FNL</t>
+  </si>
+  <si>
+    <t>India Indian Super League</t>
+  </si>
+  <si>
     <t>Serbia Prva Liga</t>
   </si>
   <si>
     <t>England Premier League</t>
   </si>
   <si>
-    <t>India Indian Super League</t>
-  </si>
-  <si>
-    <t>Oman Professional League</t>
-  </si>
-  <si>
-    <t>Russia FNL</t>
-  </si>
-  <si>
-    <t>Uzbekistan Uzbekistan Super League</t>
-  </si>
-  <si>
     <t>Egypt Egyptian Premier League</t>
   </si>
   <si>
@@ -334,10 +334,16 @@
     <t>Azerbaijan Premyer Liqası</t>
   </si>
   <si>
+    <t>Republic of Ireland First Division</t>
+  </si>
+  <si>
     <t>Republic of Ireland Premier Division</t>
   </si>
   <si>
-    <t>Republic of Ireland First Division</t>
+    <t>Morocco Botola Pro</t>
+  </si>
+  <si>
+    <t>Jordan Jordanian Pro League</t>
   </si>
   <si>
     <t>Croatia Prva HNL</t>
@@ -346,27 +352,27 @@
     <t>Poland 1. Liga</t>
   </si>
   <si>
-    <t>Morocco Botola Pro</t>
-  </si>
-  <si>
-    <t>Jordan Jordanian Pro League</t>
-  </si>
-  <si>
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
+    <t>Italy Serie A</t>
+  </si>
+  <si>
     <t>Austria Bundesliga</t>
   </si>
   <si>
-    <t>Italy Serie A</t>
-  </si>
-  <si>
     <t>Scotland Premiership</t>
   </si>
   <si>
     <t>Algeria Ligue 1</t>
   </si>
   <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
+    <t>Denmark Superliga</t>
+  </si>
+  <si>
     <t>Israel Israeli Premier League</t>
   </si>
   <si>
@@ -376,15 +382,9 @@
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
     <t>Norway Eliteserien</t>
   </si>
   <si>
-    <t>Denmark Superliga</t>
-  </si>
-  <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
@@ -409,12 +409,12 @@
     <t>Brazil Serie B</t>
   </si>
   <si>
+    <t>Brazil Serie C</t>
+  </si>
+  <si>
     <t>Argentina Prim B Nacional</t>
   </si>
   <si>
-    <t>Brazil Serie C</t>
-  </si>
-  <si>
     <t>Bolivia LFPB</t>
   </si>
   <si>
@@ -427,24 +427,24 @@
     <t>2026</t>
   </si>
   <si>
+    <t>Persib</t>
+  </si>
+  <si>
     <t>PSM</t>
   </si>
   <si>
-    <t>Persib</t>
-  </si>
-  <si>
     <t>Welayta Dicha</t>
   </si>
   <si>
     <t>Albirex Niigata S</t>
   </si>
   <si>
+    <t>Persijap</t>
+  </si>
+  <si>
     <t>Aston Villa Ladies</t>
   </si>
   <si>
-    <t>Persijap</t>
-  </si>
-  <si>
     <t>Mekelakeya</t>
   </si>
   <si>
@@ -454,183 +454,183 @@
     <t>Dugopolje</t>
   </si>
   <si>
+    <t>Lokomotiv</t>
+  </si>
+  <si>
+    <t>Al Khabourah</t>
+  </si>
+  <si>
+    <t>Ural</t>
+  </si>
+  <si>
+    <t>Xorazm</t>
+  </si>
+  <si>
+    <t>Odisha FC</t>
+  </si>
+  <si>
+    <t>Stepojevac Vaga</t>
+  </si>
+  <si>
     <t>OFK Vršac</t>
   </si>
   <si>
     <t>Chelsea</t>
   </si>
   <si>
-    <t>Odisha FC</t>
-  </si>
-  <si>
-    <t>Al Khabourah</t>
-  </si>
-  <si>
-    <t>Ural</t>
-  </si>
-  <si>
-    <t>Lokomotiv</t>
-  </si>
-  <si>
     <t>Pharco</t>
   </si>
   <si>
-    <t>Stepojevac Vaga</t>
-  </si>
-  <si>
-    <t>Xorazm</t>
-  </si>
-  <si>
     <t>Unirea Slobozia</t>
   </si>
   <si>
+    <t>Zarzis</t>
+  </si>
+  <si>
     <t>Monastir</t>
   </si>
   <si>
+    <t>Nasaf</t>
+  </si>
+  <si>
+    <t>Radnik Surdulica</t>
+  </si>
+  <si>
+    <t>Jeunesse Sportive Omrane</t>
+  </si>
+  <si>
     <t>CA Bizertin</t>
   </si>
   <si>
-    <t>Zarzis</t>
-  </si>
-  <si>
-    <t>Jeunesse Sportive Omrane</t>
-  </si>
-  <si>
-    <t>Radnik Surdulica</t>
-  </si>
-  <si>
-    <t>Nasaf</t>
-  </si>
-  <si>
     <t>Al Nasr</t>
   </si>
   <si>
     <t>Qarabağ</t>
   </si>
   <si>
+    <t>Kerry</t>
+  </si>
+  <si>
+    <t>Treaty United</t>
+  </si>
+  <si>
+    <t>Waterford</t>
+  </si>
+  <si>
+    <t>Hassania Agadir</t>
+  </si>
+  <si>
+    <t>Cobh Ramblers</t>
+  </si>
+  <si>
+    <t>Sligo Rovers</t>
+  </si>
+  <si>
+    <t>Longford Town</t>
+  </si>
+  <si>
+    <t>Al Ahli</t>
+  </si>
+  <si>
+    <t>Finn Harps</t>
+  </si>
+  <si>
+    <t>Al Jazeera</t>
+  </si>
+  <si>
+    <t>Bohemians</t>
+  </si>
+  <si>
+    <t>Shamrock Rovers</t>
+  </si>
+  <si>
+    <t>Istra 1961</t>
+  </si>
+  <si>
+    <t>Polonia Bytom</t>
+  </si>
+  <si>
     <t>Derry City</t>
   </si>
   <si>
-    <t>Waterford</t>
-  </si>
-  <si>
-    <t>Sligo Rovers</t>
-  </si>
-  <si>
-    <t>Shamrock Rovers</t>
-  </si>
-  <si>
-    <t>Longford Town</t>
-  </si>
-  <si>
-    <t>Istra 1961</t>
-  </si>
-  <si>
-    <t>Polonia Bytom</t>
-  </si>
-  <si>
-    <t>Kerry</t>
-  </si>
-  <si>
-    <t>Hassania Agadir</t>
-  </si>
-  <si>
-    <t>Al Ahli</t>
-  </si>
-  <si>
-    <t>Treaty United</t>
-  </si>
-  <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
-    <t>Al Jazeera</t>
-  </si>
-  <si>
-    <t>Cobh Ramblers</t>
-  </si>
-  <si>
-    <t>Bohemians</t>
-  </si>
-  <si>
     <t>Al Feiha</t>
   </si>
   <si>
     <t>Al Shabab</t>
   </si>
   <si>
+    <t>Cremonese</t>
+  </si>
+  <si>
     <t>Rheindorf Altach</t>
   </si>
   <si>
-    <t>Cremonese</t>
+    <t>Hearts</t>
   </si>
   <si>
     <t>Arsenal Tula</t>
   </si>
   <si>
-    <t>Hearts</t>
-  </si>
-  <si>
     <t>CR Belouizdad</t>
   </si>
   <si>
+    <t>Halmstad</t>
+  </si>
+  <si>
+    <t>Wadi Degla</t>
+  </si>
+  <si>
+    <t>Djurgården</t>
+  </si>
+  <si>
+    <t>Midtjylland</t>
+  </si>
+  <si>
+    <t>Bnei Sakhnin</t>
+  </si>
+  <si>
+    <t>Porto II</t>
+  </si>
+  <si>
     <t>Maccabi Netanya</t>
   </si>
   <si>
-    <t>Wadi Degla</t>
-  </si>
-  <si>
-    <t>Bnei Sakhnin</t>
+    <t>Radomiak Radom</t>
   </si>
   <si>
     <t>Torreense</t>
   </si>
   <si>
-    <t>Radomiak Radom</t>
-  </si>
-  <si>
-    <t>Djurgården</t>
-  </si>
-  <si>
     <t>Al Ittihad</t>
   </si>
   <si>
-    <t>Halmstad</t>
-  </si>
-  <si>
     <t>FK Bodo - Glimt</t>
   </si>
   <si>
-    <t>Midtjylland</t>
-  </si>
-  <si>
     <t>Čukarički</t>
   </si>
   <si>
-    <t>Porto II</t>
-  </si>
-  <si>
     <t>Landskrona</t>
   </si>
   <si>
+    <t>B36</t>
+  </si>
+  <si>
+    <t>Víkingur</t>
+  </si>
+  <si>
     <t>Rapid Bucureşti</t>
   </si>
   <si>
-    <t>Víkingur</t>
-  </si>
-  <si>
-    <t>B36</t>
+    <t>Yacoub El Mansour</t>
+  </si>
+  <si>
+    <t>Vasas</t>
   </si>
   <si>
     <t>Al Ittifaq</t>
   </si>
   <si>
-    <t>Yacoub El Mansour</t>
-  </si>
-  <si>
-    <t>Vasas</t>
-  </si>
-  <si>
     <t>LASK Linz</t>
   </si>
   <si>
@@ -640,15 +640,15 @@
     <t>Roma</t>
   </si>
   <si>
+    <t>Everton</t>
+  </si>
+  <si>
     <t>USM Alger</t>
   </si>
   <si>
     <t>Sevilla FC</t>
   </si>
   <si>
-    <t>Everton</t>
-  </si>
-  <si>
     <t>Sporting CP</t>
   </si>
   <si>
@@ -661,45 +661,45 @@
     <t>Vila Nova</t>
   </si>
   <si>
+    <t>Floresta</t>
+  </si>
+  <si>
+    <t>Figueirense</t>
+  </si>
+  <si>
+    <t>Ypiranga Erechim</t>
+  </si>
+  <si>
     <t>Quilmes</t>
   </si>
   <si>
-    <t>Ypiranga Erechim</t>
-  </si>
-  <si>
-    <t>Figueirense</t>
-  </si>
-  <si>
-    <t>Floresta</t>
-  </si>
-  <si>
     <t>Universitario de Vinto</t>
   </si>
   <si>
+    <t>Gimnasia y Tiro</t>
+  </si>
+  <si>
     <t>San Marcos</t>
   </si>
   <si>
-    <t>Gimnasia y Tiro</t>
+    <t>PSIM Yogyakarta</t>
   </si>
   <si>
     <t>Bhayangkara</t>
   </si>
   <si>
-    <t>PSIM Yogyakarta</t>
-  </si>
-  <si>
     <t>Hadiya Hosaena</t>
   </si>
   <si>
     <t>Young Lions</t>
   </si>
   <si>
+    <t>Persija</t>
+  </si>
+  <si>
     <t>West Ham United Women</t>
   </si>
   <si>
-    <t>Persija</t>
-  </si>
-  <si>
     <t>Adama Kenema</t>
   </si>
   <si>
@@ -709,186 +709,186 @@
     <t>Cibalia</t>
   </si>
   <si>
+    <t>Qizilqum</t>
+  </si>
+  <si>
+    <t>Saham</t>
+  </si>
+  <si>
+    <t>Shinnik</t>
+  </si>
+  <si>
+    <t>Andijan</t>
+  </si>
+  <si>
+    <t>Bengaluru</t>
+  </si>
+  <si>
+    <t>Kabel Novi Sad</t>
+  </si>
+  <si>
     <t>Jedinstvo Ub</t>
   </si>
   <si>
     <t>Nottingham Forest</t>
   </si>
   <si>
-    <t>Bengaluru</t>
-  </si>
-  <si>
-    <t>Saham</t>
-  </si>
-  <si>
-    <t>Shinnik</t>
-  </si>
-  <si>
-    <t>Qizilqum</t>
-  </si>
-  <si>
     <t>Al Mokawloon</t>
   </si>
   <si>
-    <t>Kabel Novi Sad</t>
-  </si>
-  <si>
-    <t>Andijan</t>
-  </si>
-  <si>
     <t>Hermannstadt</t>
   </si>
   <si>
+    <t>Etoile du Sahel</t>
+  </si>
+  <si>
     <t>Métlaoui</t>
   </si>
   <si>
+    <t>Navbahor</t>
+  </si>
+  <si>
+    <t>Vojvodina</t>
+  </si>
+  <si>
+    <t>ES Tunis</t>
+  </si>
+  <si>
     <t>Marsa</t>
   </si>
   <si>
-    <t>Etoile du Sahel</t>
-  </si>
-  <si>
-    <t>ES Tunis</t>
-  </si>
-  <si>
-    <t>Vojvodina</t>
-  </si>
-  <si>
-    <t>Navbahor</t>
-  </si>
-  <si>
     <t>Al-Nahda</t>
   </si>
   <si>
     <t>Turan</t>
   </si>
   <si>
+    <t>Cork City</t>
+  </si>
+  <si>
+    <t>Wexford</t>
+  </si>
+  <si>
+    <t>Dundalk</t>
+  </si>
+  <si>
+    <t>Olympic Safi</t>
+  </si>
+  <si>
+    <t>UCD</t>
+  </si>
+  <si>
+    <t>St Patrick's Athl.</t>
+  </si>
+  <si>
+    <t>Athlone Town</t>
+  </si>
+  <si>
+    <t>Al Buqa'a</t>
+  </si>
+  <si>
+    <t>Bray Wanderers</t>
+  </si>
+  <si>
+    <t>Shabab Al Ordon</t>
+  </si>
+  <si>
+    <t>Shelbourne</t>
+  </si>
+  <si>
+    <t>Drogheda United</t>
+  </si>
+  <si>
+    <t>Slaven Koprivnica</t>
+  </si>
+  <si>
+    <t>Polonia Warszawa</t>
+  </si>
+  <si>
     <t>Galway United</t>
   </si>
   <si>
-    <t>Dundalk</t>
-  </si>
-  <si>
-    <t>St Patrick's Athl.</t>
-  </si>
-  <si>
-    <t>Drogheda United</t>
-  </si>
-  <si>
-    <t>Athlone Town</t>
-  </si>
-  <si>
-    <t>Slaven Koprivnica</t>
-  </si>
-  <si>
-    <t>Polonia Warszawa</t>
-  </si>
-  <si>
-    <t>Cork City</t>
-  </si>
-  <si>
-    <t>Olympic Safi</t>
-  </si>
-  <si>
-    <t>Al Buqa'a</t>
-  </si>
-  <si>
-    <t>Wexford</t>
-  </si>
-  <si>
-    <t>Bray Wanderers</t>
-  </si>
-  <si>
-    <t>Shabab Al Ordon</t>
-  </si>
-  <si>
-    <t>UCD</t>
-  </si>
-  <si>
-    <t>Shelbourne</t>
-  </si>
-  <si>
     <t>Al Riyadh</t>
   </si>
   <si>
     <t>Al-Rustaq</t>
   </si>
   <si>
+    <t>Lazio</t>
+  </si>
+  <si>
     <t>Wolfsberger AC</t>
   </si>
   <si>
-    <t>Lazio</t>
+    <t>Rangers</t>
   </si>
   <si>
     <t>Rotor Volgograd</t>
   </si>
   <si>
-    <t>Rangers</t>
-  </si>
-  <si>
     <t>USM Khenchela</t>
   </si>
   <si>
+    <t>Brommapojkarna</t>
+  </si>
+  <si>
+    <t>Kahraba Ismailia</t>
+  </si>
+  <si>
+    <t>IFK Göteborg</t>
+  </si>
+  <si>
+    <t>Viborg</t>
+  </si>
+  <si>
+    <t>Maccabi Bnei Raina</t>
+  </si>
+  <si>
+    <t>Felgueiras 1932</t>
+  </si>
+  <si>
     <t>Hapoel Katamon</t>
   </si>
   <si>
-    <t>Kahraba Ismailia</t>
-  </si>
-  <si>
-    <t>Maccabi Bnei Raina</t>
+    <t>Lechia Gdańsk</t>
   </si>
   <si>
     <t>FC Penafiel</t>
   </si>
   <si>
-    <t>Lechia Gdańsk</t>
-  </si>
-  <si>
-    <t>IFK Göteborg</t>
-  </si>
-  <si>
     <t>Petrojet</t>
   </si>
   <si>
-    <t>Brommapojkarna</t>
-  </si>
-  <si>
     <t>Molde</t>
   </si>
   <si>
-    <t>Viborg</t>
-  </si>
-  <si>
     <t>Red Star Belgrade</t>
   </si>
   <si>
-    <t>Felgueiras 1932</t>
-  </si>
-  <si>
     <t>Öster</t>
   </si>
   <si>
+    <t>NSÍ</t>
+  </si>
+  <si>
+    <t>07 Vestur</t>
+  </si>
+  <si>
     <t>CFR Cluj</t>
   </si>
   <si>
-    <t>07 Vestur</t>
-  </si>
-  <si>
-    <t>NSÍ</t>
+    <t>RSB Berkane</t>
   </si>
   <si>
     <t>Al Kholood</t>
   </si>
   <si>
+    <t>Budafoki MTE</t>
+  </si>
+  <si>
     <t>Al Najma</t>
   </si>
   <si>
-    <t>RSB Berkane</t>
-  </si>
-  <si>
-    <t>Budafoki MTE</t>
-  </si>
-  <si>
     <t>Rapid Wien</t>
   </si>
   <si>
@@ -898,15 +898,15 @@
     <t>Fiorentina</t>
   </si>
   <si>
+    <t>Manchester City</t>
+  </si>
+  <si>
     <t>Paradou AC</t>
   </si>
   <si>
     <t>Real Sociedad</t>
   </si>
   <si>
-    <t>Manchester City</t>
-  </si>
-  <si>
     <t>Vitória Guimarães</t>
   </si>
   <si>
@@ -919,25 +919,25 @@
     <t>Athletic Club</t>
   </si>
   <si>
+    <t>Maranhão</t>
+  </si>
+  <si>
+    <t>Barra do Garcas</t>
+  </si>
+  <si>
+    <t>Ituano</t>
+  </si>
+  <si>
     <t>Chacarita Juniors</t>
   </si>
   <si>
-    <t>Ituano</t>
-  </si>
-  <si>
-    <t>Barra do Garcas</t>
-  </si>
-  <si>
-    <t>Maranhão</t>
-  </si>
-  <si>
     <t>Blooming</t>
   </si>
   <si>
+    <t>Agropecuario</t>
+  </si>
+  <si>
     <t>Recoleta</t>
-  </si>
-  <si>
-    <t>Agropecuario</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -1539,133 +1539,133 @@
         <v>308</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>5.09</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S2">
-        <v>2.63</v>
+        <v>1.72</v>
       </c>
       <c r="T2">
-        <v>2.03</v>
+        <v>2.42</v>
       </c>
       <c r="U2">
-        <v>4.23</v>
+        <v>8.65</v>
       </c>
       <c r="V2">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="W2">
-        <v>2.71</v>
+        <v>3.04</v>
       </c>
       <c r="X2">
-        <v>2.71</v>
+        <v>2.39</v>
       </c>
       <c r="Y2">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="Z2">
-        <v>6.7</v>
+        <v>5.8</v>
       </c>
       <c r="AA2">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AB2">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC2">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AD2">
-        <v>3.34</v>
+        <v>3.94</v>
       </c>
       <c r="AE2">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AF2">
+        <v>2.1</v>
+      </c>
+      <c r="AG2">
+        <v>2.49</v>
+      </c>
+      <c r="AH2">
+        <v>1.42</v>
+      </c>
+      <c r="AI2">
+        <v>4.51</v>
+      </c>
+      <c r="AJ2">
+        <v>1.14</v>
+      </c>
+      <c r="AK2">
+        <v>2.09</v>
+      </c>
+      <c r="AL2">
+        <v>1.63</v>
+      </c>
+      <c r="AM2">
+        <v>1.1</v>
+      </c>
+      <c r="AN2">
+        <v>3.28</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>1.23</v>
+      </c>
+      <c r="AQ2">
+        <v>1.47</v>
+      </c>
+      <c r="AR2">
+        <v>2.06</v>
+      </c>
+      <c r="AS2">
+        <v>2.29</v>
+      </c>
+      <c r="AT2">
+        <v>3.06</v>
+      </c>
+      <c r="AU2">
+        <v>3.42</v>
+      </c>
+      <c r="AV2">
+        <v>2.43</v>
+      </c>
+      <c r="AW2">
+        <v>1.88</v>
+      </c>
+      <c r="AX2">
+        <v>1.53</v>
+      </c>
+      <c r="AY2">
+        <v>1.29</v>
+      </c>
+      <c r="AZ2">
+        <v>1.22</v>
+      </c>
+      <c r="BA2">
+        <v>6.22</v>
+      </c>
+      <c r="BB2">
+        <v>1.15</v>
+      </c>
+      <c r="BC2">
         <v>1.84</v>
       </c>
-      <c r="AG2">
-        <v>3.04</v>
-      </c>
-      <c r="AH2">
-        <v>1.29</v>
-      </c>
-      <c r="AI2">
-        <v>5.88</v>
-      </c>
-      <c r="AJ2">
-        <v>1.12</v>
-      </c>
-      <c r="AK2">
-        <v>1.68</v>
-      </c>
-      <c r="AL2">
-        <v>2.02</v>
-      </c>
-      <c r="AM2">
-        <v>1.25</v>
-      </c>
-      <c r="AN2">
-        <v>1.65</v>
-      </c>
-      <c r="AO2">
-        <v>0</v>
-      </c>
-      <c r="AP2">
-        <v>1.21</v>
-      </c>
-      <c r="AQ2">
-        <v>1.45</v>
-      </c>
-      <c r="AR2">
-        <v>1.78</v>
-      </c>
-      <c r="AS2">
-        <v>2.24</v>
-      </c>
-      <c r="AT2">
-        <v>2.97</v>
-      </c>
-      <c r="AU2">
-        <v>3.53</v>
-      </c>
-      <c r="AV2">
-        <v>2.48</v>
-      </c>
-      <c r="AW2">
-        <v>1.92</v>
-      </c>
-      <c r="AX2">
-        <v>1.56</v>
-      </c>
-      <c r="AY2">
-        <v>1.31</v>
-      </c>
-      <c r="AZ2">
-        <v>1.6</v>
-      </c>
-      <c r="BA2">
-        <v>3.13</v>
-      </c>
-      <c r="BB2">
-        <v>1.19</v>
-      </c>
-      <c r="BC2">
-        <v>2.03</v>
-      </c>
       <c r="BD2">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="BE2">
-        <v>1.68</v>
+        <v>1.84</v>
       </c>
       <c r="BF2">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="BG2">
         <v>0</v>
@@ -1724,133 +1724,133 @@
         <v>308</v>
       </c>
       <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>2.63</v>
+      </c>
+      <c r="T3">
+        <v>2.03</v>
+      </c>
+      <c r="U3">
+        <v>4.23</v>
+      </c>
+      <c r="V3">
+        <v>1.37</v>
+      </c>
+      <c r="W3">
+        <v>2.71</v>
+      </c>
+      <c r="X3">
+        <v>2.71</v>
+      </c>
+      <c r="Y3">
+        <v>1.37</v>
+      </c>
+      <c r="Z3">
+        <v>6.7</v>
+      </c>
+      <c r="AA3">
+        <v>1.05</v>
+      </c>
+      <c r="AB3">
+        <v>1.01</v>
+      </c>
+      <c r="AC3">
+        <v>1.24</v>
+      </c>
+      <c r="AD3">
+        <v>3.34</v>
+      </c>
+      <c r="AE3">
+        <v>1.85</v>
+      </c>
+      <c r="AF3">
+        <v>1.84</v>
+      </c>
+      <c r="AG3">
+        <v>3.04</v>
+      </c>
+      <c r="AH3">
+        <v>1.29</v>
+      </c>
+      <c r="AI3">
+        <v>5.88</v>
+      </c>
+      <c r="AJ3">
+        <v>1.12</v>
+      </c>
+      <c r="AK3">
+        <v>1.68</v>
+      </c>
+      <c r="AL3">
+        <v>2.02</v>
+      </c>
+      <c r="AM3">
         <v>1.25</v>
       </c>
-      <c r="Q3">
-        <v>5.09</v>
-      </c>
-      <c r="R3">
-        <v>10</v>
-      </c>
-      <c r="S3">
-        <v>1.72</v>
-      </c>
-      <c r="T3">
-        <v>2.42</v>
-      </c>
-      <c r="U3">
-        <v>8.65</v>
-      </c>
-      <c r="V3">
-        <v>1.3</v>
-      </c>
-      <c r="W3">
-        <v>3.04</v>
-      </c>
-      <c r="X3">
-        <v>2.39</v>
-      </c>
-      <c r="Y3">
-        <v>1.47</v>
-      </c>
-      <c r="Z3">
-        <v>5.8</v>
-      </c>
-      <c r="AA3">
-        <v>1.09</v>
-      </c>
-      <c r="AB3">
-        <v>1</v>
-      </c>
-      <c r="AC3">
-        <v>1.17</v>
-      </c>
-      <c r="AD3">
-        <v>3.94</v>
-      </c>
-      <c r="AE3">
-        <v>1.67</v>
-      </c>
-      <c r="AF3">
-        <v>2.1</v>
-      </c>
-      <c r="AG3">
-        <v>2.49</v>
-      </c>
-      <c r="AH3">
-        <v>1.42</v>
-      </c>
-      <c r="AI3">
-        <v>4.51</v>
-      </c>
-      <c r="AJ3">
-        <v>1.14</v>
-      </c>
-      <c r="AK3">
-        <v>2.09</v>
-      </c>
-      <c r="AL3">
-        <v>1.63</v>
-      </c>
-      <c r="AM3">
-        <v>1.1</v>
-      </c>
       <c r="AN3">
-        <v>3.28</v>
+        <v>1.65</v>
       </c>
       <c r="AO3">
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ3">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AR3">
-        <v>2.06</v>
+        <v>1.78</v>
       </c>
       <c r="AS3">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="AT3">
-        <v>3.06</v>
+        <v>2.97</v>
       </c>
       <c r="AU3">
-        <v>3.42</v>
+        <v>3.53</v>
       </c>
       <c r="AV3">
-        <v>2.43</v>
+        <v>2.48</v>
       </c>
       <c r="AW3">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AX3">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AY3">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AZ3">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="BA3">
-        <v>6.22</v>
+        <v>3.13</v>
       </c>
       <c r="BB3">
+        <v>1.19</v>
+      </c>
+      <c r="BC3">
+        <v>2.03</v>
+      </c>
+      <c r="BD3">
+        <v>3.8</v>
+      </c>
+      <c r="BE3">
+        <v>1.68</v>
+      </c>
+      <c r="BF3">
         <v>1.15</v>
-      </c>
-      <c r="BC3">
-        <v>1.84</v>
-      </c>
-      <c r="BD3">
-        <v>4.3</v>
-      </c>
-      <c r="BE3">
-        <v>1.84</v>
-      </c>
-      <c r="BF3">
-        <v>1.22</v>
       </c>
       <c r="BG3">
         <v>0</v>
@@ -2240,7 +2240,7 @@
         <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
         <v>134</v>
@@ -2279,13 +2279,13 @@
         <v>308</v>
       </c>
       <c r="P6">
-        <v>2.17</v>
+        <v>5.2</v>
       </c>
       <c r="Q6">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="R6">
-        <v>2.83</v>
+        <v>1.57</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
         <v>134</v>
@@ -2464,13 +2464,13 @@
         <v>308</v>
       </c>
       <c r="P7">
-        <v>5.2</v>
+        <v>2.17</v>
       </c>
       <c r="Q7">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R7">
-        <v>1.57</v>
+        <v>2.83</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -3168,7 +3168,7 @@
         <v>95</v>
       </c>
       <c r="D11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E11" t="s">
         <v>146</v>
@@ -3389,133 +3389,133 @@
         <v>308</v>
       </c>
       <c r="P12">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R12">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="T12">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>5.18</v>
+        <v>0</v>
       </c>
       <c r="V12">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W12">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X12">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Y12">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z12">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="AA12">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC12">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD12">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AE12">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF12">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AG12">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH12">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AI12">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AJ12">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK12">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL12">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM12">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN12">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AO12">
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ12">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR12">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AS12">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AT12">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AU12">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="AV12">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="AW12">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AX12">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AY12">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AZ12">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BA12">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BB12">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC12">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BD12">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE12">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF12">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG12">
         <v>0</v>
@@ -3574,79 +3574,79 @@
         <v>308</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI13">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL13">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM13">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN13">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AO13">
         <v>0</v>
@@ -3688,19 +3688,19 @@
         <v>0</v>
       </c>
       <c r="BB13">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC13">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BD13">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE13">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF13">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG13">
         <v>0</v>
@@ -3720,10 +3720,10 @@
         <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D14" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E14" t="s">
         <v>149</v>
@@ -3905,7 +3905,7 @@
         <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D15" t="s">
         <v>134</v>
@@ -3944,79 +3944,79 @@
         <v>308</v>
       </c>
       <c r="P15">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q15">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R15">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="S15">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="T15">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U15">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="V15">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W15">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="X15">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y15">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z15">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AA15">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB15">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC15">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD15">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AE15">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AF15">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG15">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AH15">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI15">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AJ15">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK15">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL15">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AM15">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN15">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AO15">
         <v>0</v>
@@ -4058,19 +4058,19 @@
         <v>0</v>
       </c>
       <c r="BB15">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BC15">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="BD15">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE15">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF15">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG15">
         <v>0</v>
@@ -4090,10 +4090,10 @@
         <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D16" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E16" t="s">
         <v>151</v>
@@ -4275,7 +4275,7 @@
         <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D17" t="s">
         <v>134</v>
@@ -4314,133 +4314,133 @@
         <v>308</v>
       </c>
       <c r="P17">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q17">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="R17">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S17">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="T17">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="V17">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="W17">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="X17">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="Y17">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z17">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AA17">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC17">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD17">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE17">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AF17">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG17">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="AH17">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AI17">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AJ17">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK17">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AL17">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AM17">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AN17">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AO17">
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AQ17">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR17">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AS17">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AT17">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AU17">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AV17">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AW17">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX17">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AY17">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ17">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="BA17">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BB17">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC17">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="BD17">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BE17">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BF17">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BG17">
         <v>0</v>
@@ -4460,7 +4460,7 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D18" t="s">
         <v>134</v>
@@ -4499,133 +4499,133 @@
         <v>308</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>5.18</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH18">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AI18">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL18">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM18">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN18">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AO18">
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AU18">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="AV18">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AW18">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AX18">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AY18">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AZ18">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BA18">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BB18">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC18">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BD18">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE18">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF18">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG18">
         <v>0</v>
@@ -4645,10 +4645,10 @@
         <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D19" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E19" t="s">
         <v>154</v>
@@ -4684,133 +4684,133 @@
         <v>308</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AH19">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI19">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL19">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AM19">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AN19">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AO19">
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AU19">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AV19">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AW19">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX19">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AY19">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ19">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BA19">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BB19">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC19">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="BD19">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BE19">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BF19">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BG19">
         <v>0</v>
@@ -5385,10 +5385,10 @@
         <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D23" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E23" t="s">
         <v>158</v>
@@ -5570,7 +5570,7 @@
         <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D24" t="s">
         <v>134</v>
@@ -5609,61 +5609,61 @@
         <v>308</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB24">
         <v>0</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH24">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI24">
         <v>0</v>
@@ -5672,16 +5672,16 @@
         <v>0</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL24">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM24">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN24">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO24">
         <v>0</v>
@@ -5726,13 +5726,13 @@
         <v>0</v>
       </c>
       <c r="BC24">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BD24">
         <v>0</v>
       </c>
       <c r="BE24">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BF24">
         <v>0</v>
@@ -5755,7 +5755,7 @@
         <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D25" t="s">
         <v>134</v>
@@ -5794,61 +5794,61 @@
         <v>308</v>
       </c>
       <c r="P25">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q25">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R25">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S25">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="T25">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="U25">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="V25">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W25">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="X25">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Y25">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z25">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AA25">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB25">
         <v>0</v>
       </c>
       <c r="AC25">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD25">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="AE25">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AF25">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG25">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH25">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AI25">
         <v>0</v>
@@ -5857,16 +5857,16 @@
         <v>0</v>
       </c>
       <c r="AK25">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AL25">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AM25">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN25">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO25">
         <v>0</v>
@@ -5911,13 +5911,13 @@
         <v>0</v>
       </c>
       <c r="BC25">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="BD25">
         <v>0</v>
       </c>
       <c r="BE25">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="BF25">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D26" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E26" t="s">
         <v>161</v>
@@ -6125,7 +6125,7 @@
         <v>70</v>
       </c>
       <c r="C27" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D27" t="s">
         <v>134</v>
@@ -6534,13 +6534,13 @@
         <v>308</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S29">
         <v>0</v>
@@ -6719,22 +6719,22 @@
         <v>308</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V30">
         <v>0</v>
@@ -6743,10 +6743,10 @@
         <v>0</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -6758,40 +6758,40 @@
         <v>0</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH30">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI30">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL30">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM30">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN30">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AO30">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0</v>
       </c>
       <c r="BC30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD30">
         <v>0</v>
       </c>
       <c r="BE30">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BF30">
         <v>0</v>
@@ -6865,7 +6865,7 @@
         <v>72</v>
       </c>
       <c r="C31" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D31" t="s">
         <v>136</v>
@@ -7050,10 +7050,10 @@
         <v>72</v>
       </c>
       <c r="C32" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D32" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E32" t="s">
         <v>167</v>
@@ -7235,7 +7235,7 @@
         <v>72</v>
       </c>
       <c r="C33" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D33" t="s">
         <v>136</v>
@@ -7274,22 +7274,22 @@
         <v>308</v>
       </c>
       <c r="P33">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="Q33">
         <v>3.3</v>
       </c>
       <c r="R33">
-        <v>3.24</v>
+        <v>3.14</v>
       </c>
       <c r="S33">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="T33">
         <v>2.2</v>
       </c>
       <c r="U33">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="V33">
         <v>0</v>
@@ -7331,73 +7331,73 @@
         <v>1.3</v>
       </c>
       <c r="AI33">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AJ33">
         <v>1.09</v>
       </c>
       <c r="AK33">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AL33">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AM33">
         <v>1.23</v>
       </c>
       <c r="AN33">
+        <v>1.58</v>
+      </c>
+      <c r="AO33">
+        <v>0</v>
+      </c>
+      <c r="AP33">
+        <v>0</v>
+      </c>
+      <c r="AQ33">
+        <v>0</v>
+      </c>
+      <c r="AR33">
+        <v>0</v>
+      </c>
+      <c r="AS33">
+        <v>0</v>
+      </c>
+      <c r="AT33">
+        <v>0</v>
+      </c>
+      <c r="AU33">
+        <v>0</v>
+      </c>
+      <c r="AV33">
+        <v>0</v>
+      </c>
+      <c r="AW33">
+        <v>0</v>
+      </c>
+      <c r="AX33">
+        <v>0</v>
+      </c>
+      <c r="AY33">
+        <v>0</v>
+      </c>
+      <c r="AZ33">
+        <v>0</v>
+      </c>
+      <c r="BA33">
+        <v>0</v>
+      </c>
+      <c r="BB33">
+        <v>0</v>
+      </c>
+      <c r="BC33">
+        <v>2.02</v>
+      </c>
+      <c r="BD33">
+        <v>0</v>
+      </c>
+      <c r="BE33">
         <v>1.62</v>
-      </c>
-      <c r="AO33">
-        <v>0</v>
-      </c>
-      <c r="AP33">
-        <v>0</v>
-      </c>
-      <c r="AQ33">
-        <v>0</v>
-      </c>
-      <c r="AR33">
-        <v>0</v>
-      </c>
-      <c r="AS33">
-        <v>0</v>
-      </c>
-      <c r="AT33">
-        <v>0</v>
-      </c>
-      <c r="AU33">
-        <v>0</v>
-      </c>
-      <c r="AV33">
-        <v>0</v>
-      </c>
-      <c r="AW33">
-        <v>0</v>
-      </c>
-      <c r="AX33">
-        <v>0</v>
-      </c>
-      <c r="AY33">
-        <v>0</v>
-      </c>
-      <c r="AZ33">
-        <v>0</v>
-      </c>
-      <c r="BA33">
-        <v>0</v>
-      </c>
-      <c r="BB33">
-        <v>0</v>
-      </c>
-      <c r="BC33">
-        <v>2</v>
-      </c>
-      <c r="BD33">
-        <v>0</v>
-      </c>
-      <c r="BE33">
-        <v>1.64</v>
       </c>
       <c r="BF33">
         <v>0</v>
@@ -7420,10 +7420,10 @@
         <v>72</v>
       </c>
       <c r="C34" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D34" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E34" t="s">
         <v>169</v>
@@ -7459,133 +7459,133 @@
         <v>308</v>
       </c>
       <c r="P34">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q34">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R34">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S34">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T34">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U34">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="V34">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W34">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="X34">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Y34">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z34">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AA34">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB34">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC34">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD34">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE34">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF34">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG34">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AH34">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI34">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AJ34">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK34">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AL34">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM34">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN34">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AO34">
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AQ34">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AR34">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AS34">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AT34">
-        <v>5.44</v>
+        <v>0</v>
       </c>
       <c r="AU34">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AV34">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AW34">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AX34">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AY34">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AZ34">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BA34">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BB34">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC34">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="BD34">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE34">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BF34">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG34">
         <v>0</v>
@@ -7605,10 +7605,10 @@
         <v>72</v>
       </c>
       <c r="C35" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D35" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E35" t="s">
         <v>170</v>
@@ -7644,79 +7644,79 @@
         <v>308</v>
       </c>
       <c r="P35">
-        <v>2.27</v>
+        <v>2.09</v>
       </c>
       <c r="Q35">
-        <v>3.43</v>
+        <v>3.3</v>
       </c>
       <c r="R35">
-        <v>2.73</v>
+        <v>3.24</v>
       </c>
       <c r="S35">
-        <v>2.82</v>
+        <v>2.55</v>
       </c>
       <c r="T35">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="U35">
-        <v>3.28</v>
+        <v>3.75</v>
       </c>
       <c r="V35">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W35">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="X35">
-        <v>2.31</v>
+        <v>2.55</v>
       </c>
       <c r="Y35">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="Z35">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA35">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB35">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC35">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AD35">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="AE35">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="AF35">
-        <v>2.19</v>
+        <v>1.82</v>
       </c>
       <c r="AG35">
-        <v>2.53</v>
+        <v>3</v>
       </c>
       <c r="AH35">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AI35">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="AJ35">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AK35">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AL35">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="AM35">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AN35">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="AO35">
         <v>0</v>
@@ -7758,19 +7758,19 @@
         <v>0</v>
       </c>
       <c r="BB35">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC35">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="BD35">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE35">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="BF35">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BG35">
         <v>0</v>
@@ -7790,10 +7790,10 @@
         <v>72</v>
       </c>
       <c r="C36" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D36" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E36" t="s">
         <v>171</v>
@@ -7829,13 +7829,13 @@
         <v>308</v>
       </c>
       <c r="P36">
-        <v>5.6</v>
+        <v>2.35</v>
       </c>
       <c r="Q36">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="R36">
-        <v>1.56</v>
+        <v>2.62</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -7975,10 +7975,10 @@
         <v>72</v>
       </c>
       <c r="C37" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D37" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E37" t="s">
         <v>172</v>
@@ -8014,22 +8014,22 @@
         <v>308</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V37">
         <v>0</v>
@@ -8038,10 +8038,10 @@
         <v>0</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -8053,40 +8053,40 @@
         <v>0</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AH37">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI37">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL37">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AM37">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN37">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO37">
         <v>0</v>
@@ -8131,13 +8131,13 @@
         <v>0</v>
       </c>
       <c r="BC37">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BD37">
         <v>0</v>
       </c>
       <c r="BE37">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF37">
         <v>0</v>
@@ -8160,7 +8160,7 @@
         <v>72</v>
       </c>
       <c r="C38" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D38" t="s">
         <v>134</v>
@@ -8199,13 +8199,13 @@
         <v>308</v>
       </c>
       <c r="P38">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R38">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -8244,10 +8244,10 @@
         <v>0</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG38">
         <v>0</v>
@@ -8262,10 +8262,10 @@
         <v>0</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL38">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AM38">
         <v>0</v>
@@ -8384,22 +8384,22 @@
         <v>308</v>
       </c>
       <c r="P39">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q39">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R39">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S39">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T39">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U39">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V39">
         <v>0</v>
@@ -8408,10 +8408,10 @@
         <v>0</v>
       </c>
       <c r="X39">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Y39">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -8423,40 +8423,40 @@
         <v>0</v>
       </c>
       <c r="AC39">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD39">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AE39">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF39">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG39">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH39">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI39">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AJ39">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK39">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AL39">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM39">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN39">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AO39">
         <v>0</v>
@@ -8501,13 +8501,13 @@
         <v>0</v>
       </c>
       <c r="BC39">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD39">
         <v>0</v>
       </c>
       <c r="BE39">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BF39">
         <v>0</v>
@@ -8569,22 +8569,22 @@
         <v>308</v>
       </c>
       <c r="P40">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q40">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R40">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S40">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T40">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U40">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="V40">
         <v>0</v>
@@ -8593,10 +8593,10 @@
         <v>0</v>
       </c>
       <c r="X40">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y40">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -8608,40 +8608,40 @@
         <v>0</v>
       </c>
       <c r="AC40">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AD40">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE40">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF40">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG40">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AH40">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI40">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ40">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK40">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL40">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AM40">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN40">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO40">
         <v>0</v>
@@ -8686,13 +8686,13 @@
         <v>0</v>
       </c>
       <c r="BC40">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="BD40">
         <v>0</v>
       </c>
       <c r="BE40">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BF40">
         <v>0</v>
@@ -8715,7 +8715,7 @@
         <v>72</v>
       </c>
       <c r="C41" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D41" t="s">
         <v>134</v>
@@ -8754,133 +8754,133 @@
         <v>308</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE41">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AF41">
         <v>1.8</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AH41">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI41">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK41">
-        <v>1.84</v>
+        <v>1.69</v>
       </c>
       <c r="AL41">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AM41">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN41">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AO41">
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AQ41">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AR41">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AS41">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AT41">
-        <v>0</v>
+        <v>5.44</v>
       </c>
       <c r="AU41">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AV41">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AW41">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AX41">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AY41">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AZ41">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BA41">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BB41">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC41">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BD41">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE41">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BF41">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG41">
         <v>0</v>
@@ -8900,10 +8900,10 @@
         <v>72</v>
       </c>
       <c r="C42" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D42" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E42" t="s">
         <v>177</v>
@@ -8939,79 +8939,79 @@
         <v>308</v>
       </c>
       <c r="P42">
-        <v>2.14</v>
+        <v>2.27</v>
       </c>
       <c r="Q42">
-        <v>3.3</v>
+        <v>3.43</v>
       </c>
       <c r="R42">
-        <v>3.14</v>
+        <v>2.73</v>
       </c>
       <c r="S42">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="T42">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="U42">
-        <v>3.65</v>
+        <v>3.28</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="X42">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="Y42">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC42">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AD42">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="AE42">
-        <v>1.82</v>
+        <v>1.63</v>
       </c>
       <c r="AF42">
-        <v>1.82</v>
+        <v>2.19</v>
       </c>
       <c r="AG42">
-        <v>3</v>
+        <v>2.53</v>
       </c>
       <c r="AH42">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AI42">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="AJ42">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AK42">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AL42">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="AM42">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AN42">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AO42">
         <v>0</v>
@@ -9053,19 +9053,19 @@
         <v>0</v>
       </c>
       <c r="BB42">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC42">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="BD42">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE42">
-        <v>1.62</v>
+        <v>1.86</v>
       </c>
       <c r="BF42">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG42">
         <v>0</v>
@@ -9085,7 +9085,7 @@
         <v>72</v>
       </c>
       <c r="C43" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D43" t="s">
         <v>136</v>
@@ -9455,7 +9455,7 @@
         <v>74</v>
       </c>
       <c r="C45" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D45" t="s">
         <v>134</v>
@@ -9679,130 +9679,130 @@
         <v>308</v>
       </c>
       <c r="P46">
-        <v>2.32</v>
+        <v>2.95</v>
       </c>
       <c r="Q46">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="R46">
-        <v>2.92</v>
+        <v>2.4</v>
       </c>
       <c r="S46">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="T46">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="U46">
+        <v>2.9</v>
+      </c>
+      <c r="V46">
+        <v>1.44</v>
+      </c>
+      <c r="W46">
+        <v>2.65</v>
+      </c>
+      <c r="X46">
+        <v>2.9</v>
+      </c>
+      <c r="Y46">
+        <v>1.34</v>
+      </c>
+      <c r="Z46">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AA46">
+        <v>1.03</v>
+      </c>
+      <c r="AB46">
+        <v>1.06</v>
+      </c>
+      <c r="AC46">
+        <v>1.34</v>
+      </c>
+      <c r="AD46">
+        <v>3</v>
+      </c>
+      <c r="AE46">
+        <v>2.21</v>
+      </c>
+      <c r="AF46">
+        <v>1.7</v>
+      </c>
+      <c r="AG46">
+        <v>3.58</v>
+      </c>
+      <c r="AH46">
+        <v>1.29</v>
+      </c>
+      <c r="AI46">
+        <v>7.8</v>
+      </c>
+      <c r="AJ46">
+        <v>1.02</v>
+      </c>
+      <c r="AK46">
+        <v>1.83</v>
+      </c>
+      <c r="AL46">
+        <v>1.92</v>
+      </c>
+      <c r="AM46">
+        <v>1.33</v>
+      </c>
+      <c r="AN46">
+        <v>1.36</v>
+      </c>
+      <c r="AO46">
+        <v>0</v>
+      </c>
+      <c r="AP46">
+        <v>1.38</v>
+      </c>
+      <c r="AQ46">
+        <v>1.68</v>
+      </c>
+      <c r="AR46">
+        <v>2.1</v>
+      </c>
+      <c r="AS46">
+        <v>2.38</v>
+      </c>
+      <c r="AT46">
+        <v>3.15</v>
+      </c>
+      <c r="AU46">
+        <v>3.1</v>
+      </c>
+      <c r="AV46">
+        <v>2.06</v>
+      </c>
+      <c r="AW46">
+        <v>1.6</v>
+      </c>
+      <c r="AX46">
+        <v>1.5</v>
+      </c>
+      <c r="AY46">
+        <v>1.3</v>
+      </c>
+      <c r="AZ46">
+        <v>2.5</v>
+      </c>
+      <c r="BA46">
+        <v>1.8</v>
+      </c>
+      <c r="BB46">
+        <v>1.27</v>
+      </c>
+      <c r="BC46">
+        <v>2.38</v>
+      </c>
+      <c r="BD46">
         <v>3.55</v>
       </c>
-      <c r="V46">
-        <v>1.4</v>
-      </c>
-      <c r="W46">
-        <v>2.73</v>
-      </c>
-      <c r="X46">
-        <v>2.85</v>
-      </c>
-      <c r="Y46">
-        <v>1.37</v>
-      </c>
-      <c r="Z46">
-        <v>7</v>
-      </c>
-      <c r="AA46">
-        <v>1.04</v>
-      </c>
-      <c r="AB46">
-        <v>1.01</v>
-      </c>
-      <c r="AC46">
-        <v>1.28</v>
-      </c>
-      <c r="AD46">
-        <v>3.12</v>
-      </c>
-      <c r="AE46">
-        <v>2</v>
-      </c>
-      <c r="AF46">
-        <v>1.78</v>
-      </c>
-      <c r="AG46">
-        <v>3.3</v>
-      </c>
-      <c r="AH46">
-        <v>1.25</v>
-      </c>
-      <c r="AI46">
-        <v>6.5</v>
-      </c>
-      <c r="AJ46">
-        <v>1.05</v>
-      </c>
-      <c r="AK46">
-        <v>1.75</v>
-      </c>
-      <c r="AL46">
-        <v>2</v>
-      </c>
-      <c r="AM46">
-        <v>1.35</v>
-      </c>
-      <c r="AN46">
-        <v>1.54</v>
-      </c>
-      <c r="AO46">
-        <v>0</v>
-      </c>
-      <c r="AP46">
-        <v>1.33</v>
-      </c>
-      <c r="AQ46">
-        <v>1.61</v>
-      </c>
-      <c r="AR46">
-        <v>2.06</v>
-      </c>
-      <c r="AS46">
-        <v>2.75</v>
-      </c>
-      <c r="AT46">
-        <v>3.8</v>
-      </c>
-      <c r="AU46">
-        <v>2.83</v>
-      </c>
-      <c r="AV46">
-        <v>2.09</v>
-      </c>
-      <c r="AW46">
-        <v>1.66</v>
-      </c>
-      <c r="AX46">
-        <v>1.36</v>
-      </c>
-      <c r="AY46">
-        <v>1.19</v>
-      </c>
-      <c r="AZ46">
-        <v>1.65</v>
-      </c>
-      <c r="BA46">
-        <v>2.85</v>
-      </c>
-      <c r="BB46">
-        <v>1.25</v>
-      </c>
-      <c r="BC46">
-        <v>2.2</v>
-      </c>
-      <c r="BD46">
-        <v>3.58</v>
-      </c>
       <c r="BE46">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="BF46">
         <v>1.13</v>
@@ -9864,130 +9864,130 @@
         <v>308</v>
       </c>
       <c r="P47">
-        <v>2.95</v>
+        <v>2.32</v>
       </c>
       <c r="Q47">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="R47">
-        <v>2.4</v>
+        <v>2.92</v>
       </c>
       <c r="S47">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="T47">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="U47">
-        <v>2.9</v>
+        <v>3.55</v>
       </c>
       <c r="V47">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W47">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="X47">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="Y47">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="Z47">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="AA47">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AB47">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AC47">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AD47">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="AE47">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="AF47">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AG47">
+        <v>3.3</v>
+      </c>
+      <c r="AH47">
+        <v>1.25</v>
+      </c>
+      <c r="AI47">
+        <v>6.5</v>
+      </c>
+      <c r="AJ47">
+        <v>1.05</v>
+      </c>
+      <c r="AK47">
+        <v>1.75</v>
+      </c>
+      <c r="AL47">
+        <v>2</v>
+      </c>
+      <c r="AM47">
+        <v>1.35</v>
+      </c>
+      <c r="AN47">
+        <v>1.54</v>
+      </c>
+      <c r="AO47">
+        <v>0</v>
+      </c>
+      <c r="AP47">
+        <v>1.33</v>
+      </c>
+      <c r="AQ47">
+        <v>1.61</v>
+      </c>
+      <c r="AR47">
+        <v>2.06</v>
+      </c>
+      <c r="AS47">
+        <v>2.75</v>
+      </c>
+      <c r="AT47">
+        <v>3.8</v>
+      </c>
+      <c r="AU47">
+        <v>2.83</v>
+      </c>
+      <c r="AV47">
+        <v>2.09</v>
+      </c>
+      <c r="AW47">
+        <v>1.66</v>
+      </c>
+      <c r="AX47">
+        <v>1.36</v>
+      </c>
+      <c r="AY47">
+        <v>1.19</v>
+      </c>
+      <c r="AZ47">
+        <v>1.65</v>
+      </c>
+      <c r="BA47">
+        <v>2.85</v>
+      </c>
+      <c r="BB47">
+        <v>1.25</v>
+      </c>
+      <c r="BC47">
+        <v>2.2</v>
+      </c>
+      <c r="BD47">
         <v>3.58</v>
       </c>
-      <c r="AH47">
-        <v>1.29</v>
-      </c>
-      <c r="AI47">
-        <v>7.8</v>
-      </c>
-      <c r="AJ47">
-        <v>1.02</v>
-      </c>
-      <c r="AK47">
-        <v>1.83</v>
-      </c>
-      <c r="AL47">
-        <v>1.92</v>
-      </c>
-      <c r="AM47">
-        <v>1.33</v>
-      </c>
-      <c r="AN47">
-        <v>1.36</v>
-      </c>
-      <c r="AO47">
-        <v>0</v>
-      </c>
-      <c r="AP47">
-        <v>1.38</v>
-      </c>
-      <c r="AQ47">
-        <v>1.68</v>
-      </c>
-      <c r="AR47">
-        <v>2.1</v>
-      </c>
-      <c r="AS47">
-        <v>2.38</v>
-      </c>
-      <c r="AT47">
-        <v>3.15</v>
-      </c>
-      <c r="AU47">
-        <v>3.1</v>
-      </c>
-      <c r="AV47">
-        <v>2.06</v>
-      </c>
-      <c r="AW47">
-        <v>1.6</v>
-      </c>
-      <c r="AX47">
-        <v>1.5</v>
-      </c>
-      <c r="AY47">
-        <v>1.3</v>
-      </c>
-      <c r="AZ47">
-        <v>2.5</v>
-      </c>
-      <c r="BA47">
-        <v>1.8</v>
-      </c>
-      <c r="BB47">
-        <v>1.27</v>
-      </c>
-      <c r="BC47">
-        <v>2.38</v>
-      </c>
-      <c r="BD47">
-        <v>3.55</v>
-      </c>
       <c r="BE47">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="BF47">
         <v>1.13</v>
@@ -10010,7 +10010,7 @@
         <v>75</v>
       </c>
       <c r="C48" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="D48" t="s">
         <v>134</v>
@@ -10049,79 +10049,79 @@
         <v>308</v>
       </c>
       <c r="P48">
-        <v>3.22</v>
+        <v>2.73</v>
       </c>
       <c r="Q48">
-        <v>2.93</v>
+        <v>3.5</v>
       </c>
       <c r="R48">
-        <v>2.84</v>
+        <v>2.4</v>
       </c>
       <c r="S48">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="T48">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="U48">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="V48">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W48">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="X48">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="Y48">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z48">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB48">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC48">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AD48">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AE48">
-        <v>2.52</v>
+        <v>1.72</v>
       </c>
       <c r="AF48">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="AG48">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AH48">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI48">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="AJ48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK48">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AL48">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AM48">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AN48">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AO48">
         <v>0</v>
@@ -10163,19 +10163,19 @@
         <v>0</v>
       </c>
       <c r="BB48">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC48">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="BD48">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="BE48">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BF48">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BG48">
         <v>0</v>
@@ -10195,7 +10195,7 @@
         <v>75</v>
       </c>
       <c r="C49" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="D49" t="s">
         <v>134</v>
@@ -10234,79 +10234,79 @@
         <v>308</v>
       </c>
       <c r="P49">
-        <v>2.73</v>
+        <v>3.22</v>
       </c>
       <c r="Q49">
-        <v>3.5</v>
+        <v>2.93</v>
       </c>
       <c r="R49">
-        <v>2.4</v>
+        <v>2.84</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AE49">
-        <v>1.72</v>
+        <v>2.52</v>
       </c>
       <c r="AF49">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AH49">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI49">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL49">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AM49">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AN49">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AO49">
         <v>0</v>
@@ -10348,19 +10348,19 @@
         <v>0</v>
       </c>
       <c r="BB49">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC49">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BD49">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="BE49">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF49">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BG49">
         <v>0</v>
@@ -10568,7 +10568,7 @@
         <v>117</v>
       </c>
       <c r="D51" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E51" t="s">
         <v>186</v>
@@ -10604,133 +10604,133 @@
         <v>308</v>
       </c>
       <c r="P51">
-        <v>1.7</v>
+        <v>2.81</v>
       </c>
       <c r="Q51">
-        <v>4.35</v>
+        <v>3.3</v>
       </c>
       <c r="R51">
-        <v>3.47</v>
+        <v>2.41</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AH51">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI51">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL51">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AM51">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN51">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AO51">
         <v>0</v>
       </c>
       <c r="AP51">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AQ51">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR51">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS51">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AT51">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU51">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AV51">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AW51">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AX51">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY51">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AZ51">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BA51">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BB51">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC51">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BD51">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="BE51">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BF51">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG51">
         <v>0</v>
@@ -10938,7 +10938,7 @@
         <v>117</v>
       </c>
       <c r="D53" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E53" t="s">
         <v>188</v>
@@ -10974,133 +10974,133 @@
         <v>308</v>
       </c>
       <c r="P53">
-        <v>2.13</v>
+        <v>1.71</v>
       </c>
       <c r="Q53">
-        <v>3.41</v>
+        <v>3.67</v>
       </c>
       <c r="R53">
+        <v>4.35</v>
+      </c>
+      <c r="S53">
+        <v>2.25</v>
+      </c>
+      <c r="T53">
+        <v>2.17</v>
+      </c>
+      <c r="U53">
+        <v>5.23</v>
+      </c>
+      <c r="V53">
+        <v>1.36</v>
+      </c>
+      <c r="W53">
+        <v>2.89</v>
+      </c>
+      <c r="X53">
+        <v>2.69</v>
+      </c>
+      <c r="Y53">
+        <v>1.41</v>
+      </c>
+      <c r="Z53">
+        <v>6.45</v>
+      </c>
+      <c r="AA53">
+        <v>1.09</v>
+      </c>
+      <c r="AB53">
+        <v>1.06</v>
+      </c>
+      <c r="AC53">
+        <v>1.21</v>
+      </c>
+      <c r="AD53">
+        <v>3.44</v>
+      </c>
+      <c r="AE53">
+        <v>1.84</v>
+      </c>
+      <c r="AF53">
+        <v>1.94</v>
+      </c>
+      <c r="AG53">
         <v>3.07</v>
       </c>
-      <c r="S53">
-        <v>2.75</v>
-      </c>
-      <c r="T53">
-        <v>2.07</v>
-      </c>
-      <c r="U53">
-        <v>3.85</v>
-      </c>
-      <c r="V53">
-        <v>1.42</v>
-      </c>
-      <c r="W53">
-        <v>2.69</v>
-      </c>
-      <c r="X53">
-        <v>3</v>
-      </c>
-      <c r="Y53">
-        <v>1.32</v>
-      </c>
-      <c r="Z53">
-        <v>7</v>
-      </c>
-      <c r="AA53">
-        <v>1.02</v>
-      </c>
-      <c r="AB53">
-        <v>1.01</v>
-      </c>
-      <c r="AC53">
-        <v>1.32</v>
-      </c>
-      <c r="AD53">
-        <v>2.88</v>
-      </c>
-      <c r="AE53">
-        <v>2.05</v>
-      </c>
-      <c r="AF53">
-        <v>1.69</v>
-      </c>
-      <c r="AG53">
-        <v>3.84</v>
-      </c>
       <c r="AH53">
+        <v>1.36</v>
+      </c>
+      <c r="AI53">
+        <v>5.84</v>
+      </c>
+      <c r="AJ53">
+        <v>1.13</v>
+      </c>
+      <c r="AK53">
+        <v>1.75</v>
+      </c>
+      <c r="AL53">
+        <v>1.95</v>
+      </c>
+      <c r="AM53">
+        <v>1.25</v>
+      </c>
+      <c r="AN53">
+        <v>2.09</v>
+      </c>
+      <c r="AO53">
+        <v>0</v>
+      </c>
+      <c r="AP53">
+        <v>0</v>
+      </c>
+      <c r="AQ53">
+        <v>1.28</v>
+      </c>
+      <c r="AR53">
+        <v>1.48</v>
+      </c>
+      <c r="AS53">
+        <v>1.75</v>
+      </c>
+      <c r="AT53">
+        <v>2.12</v>
+      </c>
+      <c r="AU53">
+        <v>0</v>
+      </c>
+      <c r="AV53">
+        <v>3.25</v>
+      </c>
+      <c r="AW53">
+        <v>2.43</v>
+      </c>
+      <c r="AX53">
+        <v>1.94</v>
+      </c>
+      <c r="AY53">
+        <v>1.62</v>
+      </c>
+      <c r="AZ53">
+        <v>1.4</v>
+      </c>
+      <c r="BA53">
+        <v>3.3</v>
+      </c>
+      <c r="BB53">
         <v>1.19</v>
       </c>
-      <c r="AI53">
-        <v>7.5</v>
-      </c>
-      <c r="AJ53">
-        <v>1.03</v>
-      </c>
-      <c r="AK53">
-        <v>1.91</v>
-      </c>
-      <c r="AL53">
-        <v>1.85</v>
-      </c>
-      <c r="AM53">
-        <v>1.28</v>
-      </c>
-      <c r="AN53">
-        <v>1.66</v>
-      </c>
-      <c r="AO53">
-        <v>0</v>
-      </c>
-      <c r="AP53">
-        <v>0</v>
-      </c>
-      <c r="AQ53">
-        <v>0</v>
-      </c>
-      <c r="AR53">
-        <v>0</v>
-      </c>
-      <c r="AS53">
-        <v>0</v>
-      </c>
-      <c r="AT53">
-        <v>0</v>
-      </c>
-      <c r="AU53">
-        <v>0</v>
-      </c>
-      <c r="AV53">
-        <v>0</v>
-      </c>
-      <c r="AW53">
-        <v>0</v>
-      </c>
-      <c r="AX53">
-        <v>0</v>
-      </c>
-      <c r="AY53">
-        <v>0</v>
-      </c>
-      <c r="AZ53">
-        <v>0</v>
-      </c>
-      <c r="BA53">
-        <v>0</v>
-      </c>
-      <c r="BB53">
-        <v>1.26</v>
-      </c>
       <c r="BC53">
-        <v>2.31</v>
+        <v>2.04</v>
       </c>
       <c r="BD53">
-        <v>3.42</v>
+        <v>3.98</v>
       </c>
       <c r="BE53">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="BF53">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="BG53">
         <v>0</v>
@@ -11159,133 +11159,133 @@
         <v>308</v>
       </c>
       <c r="P54">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="Q54">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="R54">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="S54">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="T54">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="U54">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="V54">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="W54">
-        <v>2.69</v>
+        <v>3.5</v>
       </c>
       <c r="X54">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="Y54">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="Z54">
-        <v>7.3</v>
+        <v>5</v>
       </c>
       <c r="AA54">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AB54">
         <v>1.01</v>
       </c>
       <c r="AC54">
+        <v>1.13</v>
+      </c>
+      <c r="AD54">
+        <v>4.95</v>
+      </c>
+      <c r="AE54">
+        <v>1.48</v>
+      </c>
+      <c r="AF54">
+        <v>2.4</v>
+      </c>
+      <c r="AG54">
+        <v>2.35</v>
+      </c>
+      <c r="AH54">
+        <v>1.59</v>
+      </c>
+      <c r="AI54">
+        <v>3.88</v>
+      </c>
+      <c r="AJ54">
+        <v>1.18</v>
+      </c>
+      <c r="AK54">
+        <v>1.57</v>
+      </c>
+      <c r="AL54">
+        <v>2.2</v>
+      </c>
+      <c r="AM54">
+        <v>1.17</v>
+      </c>
+      <c r="AN54">
+        <v>2.25</v>
+      </c>
+      <c r="AO54">
+        <v>0</v>
+      </c>
+      <c r="AP54">
+        <v>1.17</v>
+      </c>
+      <c r="AQ54">
+        <v>1.34</v>
+      </c>
+      <c r="AR54">
+        <v>1.85</v>
+      </c>
+      <c r="AS54">
+        <v>2.05</v>
+      </c>
+      <c r="AT54">
+        <v>2.67</v>
+      </c>
+      <c r="AU54">
+        <v>4</v>
+      </c>
+      <c r="AV54">
+        <v>2.78</v>
+      </c>
+      <c r="AW54">
+        <v>2.08</v>
+      </c>
+      <c r="AX54">
+        <v>1.67</v>
+      </c>
+      <c r="AY54">
+        <v>1.38</v>
+      </c>
+      <c r="AZ54">
+        <v>1.36</v>
+      </c>
+      <c r="BA54">
+        <v>3.55</v>
+      </c>
+      <c r="BB54">
+        <v>1.11</v>
+      </c>
+      <c r="BC54">
+        <v>1.74</v>
+      </c>
+      <c r="BD54">
+        <v>5.4</v>
+      </c>
+      <c r="BE54">
+        <v>2.02</v>
+      </c>
+      <c r="BF54">
         <v>1.32</v>
-      </c>
-      <c r="AD54">
-        <v>3.1</v>
-      </c>
-      <c r="AE54">
-        <v>1.77</v>
-      </c>
-      <c r="AF54">
-        <v>1.75</v>
-      </c>
-      <c r="AG54">
-        <v>3.34</v>
-      </c>
-      <c r="AH54">
-        <v>1.24</v>
-      </c>
-      <c r="AI54">
-        <v>6.65</v>
-      </c>
-      <c r="AJ54">
-        <v>1.05</v>
-      </c>
-      <c r="AK54">
-        <v>1.8</v>
-      </c>
-      <c r="AL54">
-        <v>1.85</v>
-      </c>
-      <c r="AM54">
-        <v>1.26</v>
-      </c>
-      <c r="AN54">
-        <v>1.94</v>
-      </c>
-      <c r="AO54">
-        <v>0</v>
-      </c>
-      <c r="AP54">
-        <v>1.13</v>
-      </c>
-      <c r="AQ54">
-        <v>1.31</v>
-      </c>
-      <c r="AR54">
-        <v>1.74</v>
-      </c>
-      <c r="AS54">
-        <v>1.95</v>
-      </c>
-      <c r="AT54">
-        <v>2.48</v>
-      </c>
-      <c r="AU54">
-        <v>4.38</v>
-      </c>
-      <c r="AV54">
-        <v>2.95</v>
-      </c>
-      <c r="AW54">
-        <v>2.2</v>
-      </c>
-      <c r="AX54">
-        <v>1.76</v>
-      </c>
-      <c r="AY54">
-        <v>1.45</v>
-      </c>
-      <c r="AZ54">
-        <v>1.49</v>
-      </c>
-      <c r="BA54">
-        <v>3.04</v>
-      </c>
-      <c r="BB54">
-        <v>1.22</v>
-      </c>
-      <c r="BC54">
-        <v>2.2</v>
-      </c>
-      <c r="BD54">
-        <v>3.58</v>
-      </c>
-      <c r="BE54">
-        <v>1.62</v>
-      </c>
-      <c r="BF54">
-        <v>1.13</v>
       </c>
       <c r="BG54">
         <v>0</v>
@@ -11344,133 +11344,133 @@
         <v>308</v>
       </c>
       <c r="P55">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="Q55">
-        <v>3.52</v>
+        <v>3.41</v>
       </c>
       <c r="R55">
-        <v>2.96</v>
+        <v>3.07</v>
       </c>
       <c r="S55">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="T55">
-        <v>2.19</v>
+        <v>2.07</v>
       </c>
       <c r="U55">
-        <v>3.58</v>
+        <v>3.85</v>
       </c>
       <c r="V55">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="W55">
-        <v>3.16</v>
+        <v>2.69</v>
       </c>
       <c r="X55">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="Y55">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="Z55">
-        <v>5.55</v>
+        <v>7</v>
       </c>
       <c r="AA55">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AB55">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC55">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="AD55">
-        <v>4.1</v>
+        <v>2.88</v>
       </c>
       <c r="AE55">
+        <v>2.05</v>
+      </c>
+      <c r="AF55">
+        <v>1.69</v>
+      </c>
+      <c r="AG55">
+        <v>3.84</v>
+      </c>
+      <c r="AH55">
+        <v>1.19</v>
+      </c>
+      <c r="AI55">
+        <v>7.5</v>
+      </c>
+      <c r="AJ55">
+        <v>1.03</v>
+      </c>
+      <c r="AK55">
+        <v>1.91</v>
+      </c>
+      <c r="AL55">
+        <v>1.85</v>
+      </c>
+      <c r="AM55">
+        <v>1.28</v>
+      </c>
+      <c r="AN55">
         <v>1.66</v>
       </c>
-      <c r="AF55">
-        <v>2.16</v>
-      </c>
-      <c r="AG55">
-        <v>2.63</v>
-      </c>
-      <c r="AH55">
-        <v>1.41</v>
-      </c>
-      <c r="AI55">
-        <v>4.55</v>
-      </c>
-      <c r="AJ55">
-        <v>1.13</v>
-      </c>
-      <c r="AK55">
-        <v>1.55</v>
-      </c>
-      <c r="AL55">
-        <v>2.35</v>
-      </c>
-      <c r="AM55">
+      <c r="AO55">
+        <v>0</v>
+      </c>
+      <c r="AP55">
+        <v>0</v>
+      </c>
+      <c r="AQ55">
+        <v>0</v>
+      </c>
+      <c r="AR55">
+        <v>0</v>
+      </c>
+      <c r="AS55">
+        <v>0</v>
+      </c>
+      <c r="AT55">
+        <v>0</v>
+      </c>
+      <c r="AU55">
+        <v>0</v>
+      </c>
+      <c r="AV55">
+        <v>0</v>
+      </c>
+      <c r="AW55">
+        <v>0</v>
+      </c>
+      <c r="AX55">
+        <v>0</v>
+      </c>
+      <c r="AY55">
+        <v>0</v>
+      </c>
+      <c r="AZ55">
+        <v>0</v>
+      </c>
+      <c r="BA55">
+        <v>0</v>
+      </c>
+      <c r="BB55">
         <v>1.26</v>
       </c>
-      <c r="AN55">
-        <v>1.61</v>
-      </c>
-      <c r="AO55">
-        <v>0</v>
-      </c>
-      <c r="AP55">
-        <v>1.18</v>
-      </c>
-      <c r="AQ55">
-        <v>1.34</v>
-      </c>
-      <c r="AR55">
-        <v>1.58</v>
-      </c>
-      <c r="AS55">
-        <v>2.05</v>
-      </c>
-      <c r="AT55">
-        <v>2.45</v>
-      </c>
-      <c r="AU55">
-        <v>3.95</v>
-      </c>
-      <c r="AV55">
-        <v>2.85</v>
-      </c>
-      <c r="AW55">
-        <v>2.14</v>
-      </c>
-      <c r="AX55">
-        <v>1.7</v>
-      </c>
-      <c r="AY55">
-        <v>1.45</v>
-      </c>
-      <c r="AZ55">
-        <v>1.76</v>
-      </c>
-      <c r="BA55">
-        <v>2.33</v>
-      </c>
-      <c r="BB55">
-        <v>1.14</v>
-      </c>
       <c r="BC55">
-        <v>1.87</v>
+        <v>2.31</v>
       </c>
       <c r="BD55">
-        <v>4.45</v>
+        <v>3.42</v>
       </c>
       <c r="BE55">
-        <v>1.87</v>
+        <v>1.53</v>
       </c>
       <c r="BF55">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="BG55">
         <v>0</v>
@@ -11493,7 +11493,7 @@
         <v>120</v>
       </c>
       <c r="D56" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E56" t="s">
         <v>191</v>
@@ -11529,133 +11529,133 @@
         <v>308</v>
       </c>
       <c r="P56">
-        <v>1.71</v>
+        <v>2.61</v>
       </c>
       <c r="Q56">
-        <v>3.67</v>
+        <v>3.34</v>
       </c>
       <c r="R56">
-        <v>4.35</v>
+        <v>2.52</v>
       </c>
       <c r="S56">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
       <c r="T56">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="U56">
-        <v>5.23</v>
+        <v>3.01</v>
       </c>
       <c r="V56">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W56">
-        <v>2.89</v>
+        <v>2.66</v>
       </c>
       <c r="X56">
-        <v>2.69</v>
+        <v>3.16</v>
       </c>
       <c r="Y56">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="Z56">
-        <v>6.45</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA56">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="AB56">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AC56">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AD56">
-        <v>3.44</v>
+        <v>2.81</v>
       </c>
       <c r="AE56">
-        <v>1.84</v>
+        <v>2.19</v>
       </c>
       <c r="AF56">
-        <v>1.94</v>
+        <v>1.64</v>
       </c>
       <c r="AG56">
-        <v>3.07</v>
+        <v>4</v>
       </c>
       <c r="AH56">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AI56">
-        <v>5.84</v>
+        <v>8.5</v>
       </c>
       <c r="AJ56">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="AK56">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AL56">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AM56">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AN56">
-        <v>2.09</v>
+        <v>1.37</v>
       </c>
       <c r="AO56">
         <v>0</v>
       </c>
       <c r="AP56">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ56">
-        <v>1.28</v>
+        <v>1.54</v>
       </c>
       <c r="AR56">
-        <v>1.48</v>
+        <v>2.2</v>
       </c>
       <c r="AS56">
-        <v>1.75</v>
+        <v>2.46</v>
       </c>
       <c r="AT56">
-        <v>2.12</v>
+        <v>3.35</v>
       </c>
       <c r="AU56">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AV56">
-        <v>3.25</v>
+        <v>2.27</v>
       </c>
       <c r="AW56">
-        <v>2.43</v>
+        <v>1.79</v>
       </c>
       <c r="AX56">
-        <v>1.94</v>
+        <v>1.46</v>
       </c>
       <c r="AY56">
-        <v>1.62</v>
+        <v>1.24</v>
       </c>
       <c r="AZ56">
-        <v>1.4</v>
+        <v>2.92</v>
       </c>
       <c r="BA56">
-        <v>3.3</v>
+        <v>1.66</v>
       </c>
       <c r="BB56">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="BC56">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="BD56">
-        <v>3.98</v>
+        <v>3.35</v>
       </c>
       <c r="BE56">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="BF56">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="BG56">
         <v>0</v>
@@ -11675,7 +11675,7 @@
         <v>77</v>
       </c>
       <c r="C57" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="D57" t="s">
         <v>134</v>
@@ -11714,133 +11714,133 @@
         <v>308</v>
       </c>
       <c r="P57">
-        <v>2.13</v>
+        <v>1.7</v>
       </c>
       <c r="Q57">
-        <v>2.99</v>
+        <v>4.35</v>
       </c>
       <c r="R57">
-        <v>3.3</v>
+        <v>3.47</v>
       </c>
       <c r="S57">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T57">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="U57">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V57">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W57">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="X57">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Y57">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z57">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA57">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB57">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC57">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AD57">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AE57">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AF57">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AG57">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AH57">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI57">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="AJ57">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK57">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL57">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AM57">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AN57">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AO57">
         <v>0</v>
       </c>
       <c r="AP57">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AQ57">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AR57">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AS57">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AT57">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AU57">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AV57">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AW57">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AX57">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AY57">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ57">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BA57">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BB57">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BC57">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="BD57">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="BE57">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="BF57">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BG57">
         <v>0</v>
@@ -11860,10 +11860,10 @@
         <v>77</v>
       </c>
       <c r="C58" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D58" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E58" t="s">
         <v>193</v>
@@ -11899,133 +11899,133 @@
         <v>308</v>
       </c>
       <c r="P58">
-        <v>2.81</v>
+        <v>2.21</v>
       </c>
       <c r="Q58">
-        <v>3.3</v>
+        <v>3.52</v>
       </c>
       <c r="R58">
-        <v>2.41</v>
+        <v>2.96</v>
       </c>
       <c r="S58">
-        <v>3.23</v>
+        <v>2.5</v>
       </c>
       <c r="T58">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="U58">
-        <v>2.83</v>
+        <v>3.58</v>
       </c>
       <c r="V58">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="W58">
-        <v>2.95</v>
+        <v>3.16</v>
       </c>
       <c r="X58">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="Y58">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="Z58">
-        <v>7.1</v>
+        <v>5.55</v>
       </c>
       <c r="AA58">
+        <v>1.08</v>
+      </c>
+      <c r="AB58">
         <v>1.04</v>
       </c>
-      <c r="AB58">
-        <v>1.01</v>
-      </c>
       <c r="AC58">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AD58">
-        <v>3.18</v>
+        <v>4.1</v>
       </c>
       <c r="AE58">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AF58">
-        <v>1.84</v>
+        <v>2.16</v>
       </c>
       <c r="AG58">
-        <v>3.41</v>
+        <v>2.63</v>
       </c>
       <c r="AH58">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AI58">
-        <v>5.75</v>
+        <v>4.55</v>
       </c>
       <c r="AJ58">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AK58">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AL58">
-        <v>1.97</v>
+        <v>2.35</v>
       </c>
       <c r="AM58">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AN58">
-        <v>1.37</v>
+        <v>1.61</v>
       </c>
       <c r="AO58">
         <v>0</v>
       </c>
       <c r="AP58">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AQ58">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
       <c r="AR58">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="AS58">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="AT58">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="AU58">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="AV58">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="AW58">
-        <v>1.93</v>
+        <v>2.14</v>
       </c>
       <c r="AX58">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AY58">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="AZ58">
-        <v>2.12</v>
+        <v>1.76</v>
       </c>
       <c r="BA58">
-        <v>1.91</v>
+        <v>2.33</v>
       </c>
       <c r="BB58">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="BC58">
-        <v>2.14</v>
+        <v>1.87</v>
       </c>
       <c r="BD58">
-        <v>3.66</v>
+        <v>4.45</v>
       </c>
       <c r="BE58">
-        <v>1.66</v>
+        <v>1.87</v>
       </c>
       <c r="BF58">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="BG58">
         <v>0</v>
@@ -12045,10 +12045,10 @@
         <v>77</v>
       </c>
       <c r="C59" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D59" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E59" t="s">
         <v>194</v>
@@ -12084,133 +12084,133 @@
         <v>308</v>
       </c>
       <c r="P59">
+        <v>1.75</v>
+      </c>
+      <c r="Q59">
+        <v>3.4</v>
+      </c>
+      <c r="R59">
+        <v>4</v>
+      </c>
+      <c r="S59">
+        <v>2.45</v>
+      </c>
+      <c r="T59">
+        <v>2.05</v>
+      </c>
+      <c r="U59">
+        <v>4.9</v>
+      </c>
+      <c r="V59">
+        <v>1.4</v>
+      </c>
+      <c r="W59">
+        <v>2.69</v>
+      </c>
+      <c r="X59">
+        <v>2.9</v>
+      </c>
+      <c r="Y59">
         <v>1.35</v>
       </c>
-      <c r="Q59">
-        <v>5</v>
-      </c>
-      <c r="R59">
-        <v>7.2</v>
-      </c>
-      <c r="S59">
-        <v>1.67</v>
-      </c>
-      <c r="T59">
-        <v>2.8</v>
-      </c>
-      <c r="U59">
-        <v>5.9</v>
-      </c>
-      <c r="V59">
-        <v>1.17</v>
-      </c>
-      <c r="W59">
-        <v>4.25</v>
-      </c>
-      <c r="X59">
-        <v>1.9</v>
-      </c>
-      <c r="Y59">
-        <v>1.84</v>
-      </c>
       <c r="Z59">
-        <v>3.66</v>
+        <v>7.3</v>
       </c>
       <c r="AA59">
-        <v>1.22</v>
+        <v>1.03</v>
       </c>
       <c r="AB59">
         <v>1.01</v>
       </c>
       <c r="AC59">
-        <v>1.06</v>
+        <v>1.32</v>
       </c>
       <c r="AD59">
-        <v>7</v>
+        <v>3.1</v>
       </c>
       <c r="AE59">
-        <v>1.28</v>
+        <v>1.77</v>
       </c>
       <c r="AF59">
-        <v>3.5</v>
+        <v>1.75</v>
       </c>
       <c r="AG59">
+        <v>3.34</v>
+      </c>
+      <c r="AH59">
+        <v>1.24</v>
+      </c>
+      <c r="AI59">
+        <v>6.65</v>
+      </c>
+      <c r="AJ59">
+        <v>1.05</v>
+      </c>
+      <c r="AK59">
+        <v>1.8</v>
+      </c>
+      <c r="AL59">
         <v>1.85</v>
       </c>
-      <c r="AH59">
-        <v>1.98</v>
-      </c>
-      <c r="AI59">
-        <v>2.64</v>
-      </c>
-      <c r="AJ59">
-        <v>1.38</v>
-      </c>
-      <c r="AK59">
-        <v>1.48</v>
-      </c>
-      <c r="AL59">
-        <v>2.43</v>
-      </c>
       <c r="AM59">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="AN59">
-        <v>3.08</v>
+        <v>1.94</v>
       </c>
       <c r="AO59">
         <v>0</v>
       </c>
       <c r="AP59">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AQ59">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AR59">
+        <v>1.74</v>
+      </c>
+      <c r="AS59">
+        <v>1.95</v>
+      </c>
+      <c r="AT59">
+        <v>2.48</v>
+      </c>
+      <c r="AU59">
+        <v>4.38</v>
+      </c>
+      <c r="AV59">
+        <v>2.95</v>
+      </c>
+      <c r="AW59">
+        <v>2.2</v>
+      </c>
+      <c r="AX59">
+        <v>1.76</v>
+      </c>
+      <c r="AY59">
+        <v>1.45</v>
+      </c>
+      <c r="AZ59">
         <v>1.49</v>
       </c>
-      <c r="AS59">
-        <v>1.78</v>
-      </c>
-      <c r="AT59">
+      <c r="BA59">
+        <v>3.04</v>
+      </c>
+      <c r="BB59">
+        <v>1.22</v>
+      </c>
+      <c r="BC59">
         <v>2.2</v>
       </c>
-      <c r="AU59">
-        <v>0</v>
-      </c>
-      <c r="AV59">
-        <v>3.2</v>
-      </c>
-      <c r="AW59">
-        <v>2.38</v>
-      </c>
-      <c r="AX59">
-        <v>1.9</v>
-      </c>
-      <c r="AY59">
-        <v>1.58</v>
-      </c>
-      <c r="AZ59">
-        <v>1.22</v>
-      </c>
-      <c r="BA59">
-        <v>4.35</v>
-      </c>
-      <c r="BB59">
-        <v>1.07</v>
-      </c>
-      <c r="BC59">
-        <v>1.55</v>
-      </c>
       <c r="BD59">
-        <v>6</v>
+        <v>3.58</v>
       </c>
       <c r="BE59">
-        <v>2.41</v>
+        <v>1.62</v>
       </c>
       <c r="BF59">
-        <v>1.46</v>
+        <v>1.13</v>
       </c>
       <c r="BG59">
         <v>0</v>
@@ -12230,7 +12230,7 @@
         <v>77</v>
       </c>
       <c r="C60" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="D60" t="s">
         <v>134</v>
@@ -12269,133 +12269,133 @@
         <v>308</v>
       </c>
       <c r="P60">
-        <v>1.57</v>
+        <v>2.13</v>
       </c>
       <c r="Q60">
-        <v>4.2</v>
+        <v>2.99</v>
       </c>
       <c r="R60">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="S60">
-        <v>1.91</v>
+        <v>3</v>
       </c>
       <c r="T60">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="U60">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V60">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="W60">
-        <v>3.5</v>
+        <v>2.22</v>
       </c>
       <c r="X60">
-        <v>2.25</v>
+        <v>3.48</v>
       </c>
       <c r="Y60">
-        <v>1.6</v>
+        <v>1.22</v>
       </c>
       <c r="Z60">
-        <v>5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA60">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="AB60">
+        <v>1.06</v>
+      </c>
+      <c r="AC60">
+        <v>1.49</v>
+      </c>
+      <c r="AD60">
+        <v>2.49</v>
+      </c>
+      <c r="AE60">
+        <v>2.6</v>
+      </c>
+      <c r="AF60">
+        <v>1.45</v>
+      </c>
+      <c r="AG60">
+        <v>4.7</v>
+      </c>
+      <c r="AH60">
+        <v>1.13</v>
+      </c>
+      <c r="AI60">
+        <v>9.5</v>
+      </c>
+      <c r="AJ60">
         <v>1.01</v>
       </c>
-      <c r="AC60">
-        <v>1.13</v>
-      </c>
-      <c r="AD60">
-        <v>4.95</v>
-      </c>
-      <c r="AE60">
-        <v>1.48</v>
-      </c>
-      <c r="AF60">
-        <v>2.4</v>
-      </c>
-      <c r="AG60">
-        <v>2.35</v>
-      </c>
-      <c r="AH60">
-        <v>1.59</v>
-      </c>
-      <c r="AI60">
-        <v>3.88</v>
-      </c>
-      <c r="AJ60">
-        <v>1.18</v>
-      </c>
       <c r="AK60">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="AL60">
-        <v>2.2</v>
+        <v>1.66</v>
       </c>
       <c r="AM60">
-        <v>1.17</v>
+        <v>1.34</v>
       </c>
       <c r="AN60">
-        <v>2.25</v>
+        <v>1.52</v>
       </c>
       <c r="AO60">
         <v>0</v>
       </c>
       <c r="AP60">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="AQ60">
-        <v>1.34</v>
+        <v>1.68</v>
       </c>
       <c r="AR60">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AS60">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="AT60">
-        <v>2.67</v>
+        <v>3.65</v>
       </c>
       <c r="AU60">
-        <v>4</v>
+        <v>2.65</v>
       </c>
       <c r="AV60">
-        <v>2.78</v>
+        <v>2.04</v>
       </c>
       <c r="AW60">
-        <v>2.08</v>
+        <v>1.64</v>
       </c>
       <c r="AX60">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="AY60">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="AZ60">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="BA60">
-        <v>3.55</v>
+        <v>2.14</v>
       </c>
       <c r="BB60">
-        <v>1.11</v>
+        <v>1.32</v>
       </c>
       <c r="BC60">
-        <v>1.74</v>
+        <v>2.63</v>
       </c>
       <c r="BD60">
-        <v>5.4</v>
+        <v>2.96</v>
       </c>
       <c r="BE60">
-        <v>2.02</v>
+        <v>1.43</v>
       </c>
       <c r="BF60">
-        <v>1.32</v>
+        <v>1.06</v>
       </c>
       <c r="BG60">
         <v>0</v>
@@ -12415,10 +12415,10 @@
         <v>77</v>
       </c>
       <c r="C61" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="D61" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E61" t="s">
         <v>196</v>
@@ -12454,133 +12454,133 @@
         <v>308</v>
       </c>
       <c r="P61">
-        <v>7.95</v>
+        <v>1.35</v>
       </c>
       <c r="Q61">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="R61">
-        <v>1.33</v>
+        <v>7.2</v>
       </c>
       <c r="S61">
-        <v>7.13</v>
+        <v>1.67</v>
       </c>
       <c r="T61">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="U61">
-        <v>1.81</v>
+        <v>5.9</v>
       </c>
       <c r="V61">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W61">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="X61">
-        <v>2.18</v>
+        <v>1.9</v>
       </c>
       <c r="Y61">
-        <v>1.6</v>
+        <v>1.84</v>
       </c>
       <c r="Z61">
-        <v>4.55</v>
+        <v>3.66</v>
       </c>
       <c r="AA61">
+        <v>1.22</v>
+      </c>
+      <c r="AB61">
+        <v>1.01</v>
+      </c>
+      <c r="AC61">
+        <v>1.06</v>
+      </c>
+      <c r="AD61">
+        <v>7</v>
+      </c>
+      <c r="AE61">
+        <v>1.28</v>
+      </c>
+      <c r="AF61">
+        <v>3.5</v>
+      </c>
+      <c r="AG61">
+        <v>1.85</v>
+      </c>
+      <c r="AH61">
+        <v>1.98</v>
+      </c>
+      <c r="AI61">
+        <v>2.64</v>
+      </c>
+      <c r="AJ61">
+        <v>1.38</v>
+      </c>
+      <c r="AK61">
+        <v>1.48</v>
+      </c>
+      <c r="AL61">
+        <v>2.43</v>
+      </c>
+      <c r="AM61">
         <v>1.15</v>
       </c>
-      <c r="AB61">
-        <v>0</v>
-      </c>
-      <c r="AC61">
-        <v>1.16</v>
-      </c>
-      <c r="AD61">
-        <v>4.2</v>
-      </c>
-      <c r="AE61">
-        <v>1.52</v>
-      </c>
-      <c r="AF61">
-        <v>2.3</v>
-      </c>
-      <c r="AG61">
-        <v>2.29</v>
-      </c>
-      <c r="AH61">
-        <v>1.53</v>
-      </c>
-      <c r="AI61">
-        <v>4</v>
-      </c>
-      <c r="AJ61">
-        <v>1.21</v>
-      </c>
-      <c r="AK61">
+      <c r="AN61">
+        <v>3.08</v>
+      </c>
+      <c r="AO61">
+        <v>0</v>
+      </c>
+      <c r="AP61">
+        <v>0</v>
+      </c>
+      <c r="AQ61">
+        <v>1.29</v>
+      </c>
+      <c r="AR61">
+        <v>1.49</v>
+      </c>
+      <c r="AS61">
+        <v>1.78</v>
+      </c>
+      <c r="AT61">
+        <v>2.2</v>
+      </c>
+      <c r="AU61">
+        <v>0</v>
+      </c>
+      <c r="AV61">
+        <v>3.2</v>
+      </c>
+      <c r="AW61">
+        <v>2.38</v>
+      </c>
+      <c r="AX61">
         <v>1.9</v>
       </c>
-      <c r="AL61">
-        <v>1.9</v>
-      </c>
-      <c r="AM61">
-        <v>1.13</v>
-      </c>
-      <c r="AN61">
-        <v>1.05</v>
-      </c>
-      <c r="AO61">
-        <v>0</v>
-      </c>
-      <c r="AP61">
-        <v>0</v>
-      </c>
-      <c r="AQ61">
-        <v>0</v>
-      </c>
-      <c r="AR61">
-        <v>0</v>
-      </c>
-      <c r="AS61">
-        <v>0</v>
-      </c>
-      <c r="AT61">
-        <v>0</v>
-      </c>
-      <c r="AU61">
-        <v>0</v>
-      </c>
-      <c r="AV61">
-        <v>0</v>
-      </c>
-      <c r="AW61">
-        <v>0</v>
-      </c>
-      <c r="AX61">
-        <v>0</v>
-      </c>
       <c r="AY61">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AZ61">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BA61">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="BB61">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BC61">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="BD61">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BE61">
-        <v>1.85</v>
+        <v>2.41</v>
       </c>
       <c r="BF61">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BG61">
         <v>0</v>
@@ -12600,7 +12600,7 @@
         <v>77</v>
       </c>
       <c r="C62" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="D62" t="s">
         <v>134</v>
@@ -12639,133 +12639,133 @@
         <v>308</v>
       </c>
       <c r="P62">
-        <v>2.61</v>
+        <v>7.95</v>
       </c>
       <c r="Q62">
-        <v>3.34</v>
+        <v>4.7</v>
       </c>
       <c r="R62">
-        <v>2.52</v>
+        <v>1.33</v>
       </c>
       <c r="S62">
-        <v>3.25</v>
+        <v>7.13</v>
       </c>
       <c r="T62">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="U62">
-        <v>3.01</v>
+        <v>1.81</v>
       </c>
       <c r="V62">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W62">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="X62">
-        <v>3.16</v>
+        <v>2.18</v>
       </c>
       <c r="Y62">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="Z62">
-        <v>8.699999999999999</v>
+        <v>4.55</v>
       </c>
       <c r="AA62">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AB62">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC62">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="AD62">
-        <v>2.81</v>
+        <v>4.2</v>
       </c>
       <c r="AE62">
-        <v>2.19</v>
+        <v>1.52</v>
       </c>
       <c r="AF62">
-        <v>1.64</v>
+        <v>2.3</v>
       </c>
       <c r="AG62">
+        <v>2.29</v>
+      </c>
+      <c r="AH62">
+        <v>1.53</v>
+      </c>
+      <c r="AI62">
         <v>4</v>
       </c>
-      <c r="AH62">
-        <v>1.17</v>
-      </c>
-      <c r="AI62">
-        <v>8.5</v>
-      </c>
       <c r="AJ62">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AK62">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AL62">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AM62">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AN62">
-        <v>1.37</v>
+        <v>1.05</v>
       </c>
       <c r="AO62">
         <v>0</v>
       </c>
       <c r="AP62">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ62">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AR62">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AS62">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AT62">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AU62">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AV62">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AW62">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AX62">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AY62">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AZ62">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="BA62">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BB62">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BC62">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="BD62">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BE62">
-        <v>1.51</v>
+        <v>1.85</v>
       </c>
       <c r="BF62">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG62">
         <v>0</v>
@@ -12970,10 +12970,10 @@
         <v>79</v>
       </c>
       <c r="C64" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="D64" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E64" t="s">
         <v>199</v>
@@ -13009,133 +13009,133 @@
         <v>308</v>
       </c>
       <c r="P64">
-        <v>2.3</v>
+        <v>2.94</v>
       </c>
       <c r="Q64">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R64">
-        <v>3</v>
+        <v>2.21</v>
       </c>
       <c r="S64">
-        <v>2.96</v>
+        <v>3.35</v>
       </c>
       <c r="T64">
-        <v>2.04</v>
+        <v>2.23</v>
       </c>
       <c r="U64">
-        <v>3.69</v>
+        <v>2.75</v>
       </c>
       <c r="V64">
+        <v>0</v>
+      </c>
+      <c r="W64">
+        <v>0</v>
+      </c>
+      <c r="X64">
+        <v>2.48</v>
+      </c>
+      <c r="Y64">
         <v>1.41</v>
       </c>
-      <c r="W64">
-        <v>2.66</v>
-      </c>
-      <c r="X64">
-        <v>2.99</v>
-      </c>
-      <c r="Y64">
+      <c r="Z64">
+        <v>0</v>
+      </c>
+      <c r="AA64">
+        <v>0</v>
+      </c>
+      <c r="AB64">
+        <v>0</v>
+      </c>
+      <c r="AC64">
+        <v>1.23</v>
+      </c>
+      <c r="AD64">
+        <v>3.5</v>
+      </c>
+      <c r="AE64">
+        <v>1.77</v>
+      </c>
+      <c r="AF64">
+        <v>1.87</v>
+      </c>
+      <c r="AG64">
+        <v>2.9</v>
+      </c>
+      <c r="AH64">
         <v>1.33</v>
       </c>
-      <c r="Z64">
-        <v>8</v>
-      </c>
-      <c r="AA64">
-        <v>1.02</v>
-      </c>
-      <c r="AB64">
-        <v>1.01</v>
-      </c>
-      <c r="AC64">
-        <v>1.31</v>
-      </c>
-      <c r="AD64">
-        <v>2.92</v>
-      </c>
-      <c r="AE64">
-        <v>2.09</v>
-      </c>
-      <c r="AF64">
-        <v>1.7</v>
-      </c>
-      <c r="AG64">
-        <v>3.7</v>
-      </c>
-      <c r="AH64">
-        <v>1.24</v>
-      </c>
       <c r="AI64">
-        <v>7.3</v>
+        <v>5.2</v>
       </c>
       <c r="AJ64">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AK64">
-        <v>1.82</v>
+        <v>1.64</v>
       </c>
       <c r="AL64">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="AM64">
+        <v>1.23</v>
+      </c>
+      <c r="AN64">
         <v>1.29</v>
       </c>
-      <c r="AN64">
-        <v>1.54</v>
-      </c>
       <c r="AO64">
         <v>0</v>
       </c>
       <c r="AP64">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AQ64">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AR64">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AS64">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="AT64">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="AU64">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AV64">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW64">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AX64">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY64">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AZ64">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BA64">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BB64">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC64">
-        <v>2.29</v>
+        <v>1.97</v>
       </c>
       <c r="BD64">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="BE64">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="BF64">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG64">
         <v>0</v>
@@ -13340,10 +13340,10 @@
         <v>79</v>
       </c>
       <c r="C66" t="s">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="D66" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E66" t="s">
         <v>201</v>
@@ -13379,133 +13379,133 @@
         <v>308</v>
       </c>
       <c r="P66">
-        <v>2.94</v>
+        <v>2.3</v>
       </c>
       <c r="Q66">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R66">
-        <v>2.21</v>
+        <v>3</v>
       </c>
       <c r="S66">
-        <v>3.35</v>
+        <v>2.96</v>
       </c>
       <c r="T66">
-        <v>2.23</v>
+        <v>2.04</v>
       </c>
       <c r="U66">
+        <v>3.69</v>
+      </c>
+      <c r="V66">
+        <v>1.41</v>
+      </c>
+      <c r="W66">
+        <v>2.66</v>
+      </c>
+      <c r="X66">
+        <v>2.99</v>
+      </c>
+      <c r="Y66">
+        <v>1.33</v>
+      </c>
+      <c r="Z66">
+        <v>8</v>
+      </c>
+      <c r="AA66">
+        <v>1.02</v>
+      </c>
+      <c r="AB66">
+        <v>1.01</v>
+      </c>
+      <c r="AC66">
+        <v>1.31</v>
+      </c>
+      <c r="AD66">
+        <v>2.92</v>
+      </c>
+      <c r="AE66">
+        <v>2.09</v>
+      </c>
+      <c r="AF66">
+        <v>1.7</v>
+      </c>
+      <c r="AG66">
+        <v>3.7</v>
+      </c>
+      <c r="AH66">
+        <v>1.24</v>
+      </c>
+      <c r="AI66">
+        <v>7.3</v>
+      </c>
+      <c r="AJ66">
+        <v>1.03</v>
+      </c>
+      <c r="AK66">
+        <v>1.82</v>
+      </c>
+      <c r="AL66">
+        <v>1.86</v>
+      </c>
+      <c r="AM66">
+        <v>1.29</v>
+      </c>
+      <c r="AN66">
+        <v>1.54</v>
+      </c>
+      <c r="AO66">
+        <v>0</v>
+      </c>
+      <c r="AP66">
+        <v>1.31</v>
+      </c>
+      <c r="AQ66">
+        <v>1.47</v>
+      </c>
+      <c r="AR66">
+        <v>2.31</v>
+      </c>
+      <c r="AS66">
+        <v>2.58</v>
+      </c>
+      <c r="AT66">
+        <v>3.57</v>
+      </c>
+      <c r="AU66">
+        <v>2.98</v>
+      </c>
+      <c r="AV66">
+        <v>2.18</v>
+      </c>
+      <c r="AW66">
+        <v>1.73</v>
+      </c>
+      <c r="AX66">
+        <v>1.42</v>
+      </c>
+      <c r="AY66">
+        <v>1.21</v>
+      </c>
+      <c r="AZ66">
+        <v>1.68</v>
+      </c>
+      <c r="BA66">
         <v>2.75</v>
       </c>
-      <c r="V66">
-        <v>0</v>
-      </c>
-      <c r="W66">
-        <v>0</v>
-      </c>
-      <c r="X66">
-        <v>2.48</v>
-      </c>
-      <c r="Y66">
-        <v>1.41</v>
-      </c>
-      <c r="Z66">
-        <v>0</v>
-      </c>
-      <c r="AA66">
-        <v>0</v>
-      </c>
-      <c r="AB66">
-        <v>0</v>
-      </c>
-      <c r="AC66">
-        <v>1.23</v>
-      </c>
-      <c r="AD66">
-        <v>3.5</v>
-      </c>
-      <c r="AE66">
-        <v>1.77</v>
-      </c>
-      <c r="AF66">
-        <v>1.87</v>
-      </c>
-      <c r="AG66">
-        <v>2.9</v>
-      </c>
-      <c r="AH66">
-        <v>1.33</v>
-      </c>
-      <c r="AI66">
-        <v>5.2</v>
-      </c>
-      <c r="AJ66">
-        <v>1.1</v>
-      </c>
-      <c r="AK66">
-        <v>1.64</v>
-      </c>
-      <c r="AL66">
-        <v>2.1</v>
-      </c>
-      <c r="AM66">
-        <v>1.23</v>
-      </c>
-      <c r="AN66">
-        <v>1.29</v>
-      </c>
-      <c r="AO66">
-        <v>0</v>
-      </c>
-      <c r="AP66">
-        <v>0</v>
-      </c>
-      <c r="AQ66">
-        <v>0</v>
-      </c>
-      <c r="AR66">
-        <v>0</v>
-      </c>
-      <c r="AS66">
-        <v>0</v>
-      </c>
-      <c r="AT66">
-        <v>0</v>
-      </c>
-      <c r="AU66">
-        <v>0</v>
-      </c>
-      <c r="AV66">
-        <v>0</v>
-      </c>
-      <c r="AW66">
-        <v>0</v>
-      </c>
-      <c r="AX66">
-        <v>0</v>
-      </c>
-      <c r="AY66">
-        <v>0</v>
-      </c>
-      <c r="AZ66">
-        <v>0</v>
-      </c>
-      <c r="BA66">
-        <v>0</v>
-      </c>
       <c r="BB66">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC66">
-        <v>1.97</v>
+        <v>2.29</v>
       </c>
       <c r="BD66">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="BE66">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="BF66">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG66">
         <v>0</v>
@@ -13525,13 +13525,13 @@
         <v>80</v>
       </c>
       <c r="C67" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D67" t="s">
         <v>134</v>
       </c>
       <c r="E67" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="F67" t="s">
         <v>287</v>
@@ -13564,133 +13564,133 @@
         <v>308</v>
       </c>
       <c r="P67">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Q67">
-        <v>5.97</v>
+        <v>0</v>
       </c>
       <c r="R67">
-        <v>8.449999999999999</v>
+        <v>0</v>
       </c>
       <c r="S67">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="T67">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U67">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="V67">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W67">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="X67">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Y67">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Z67">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="AA67">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AB67">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC67">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AD67">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="AE67">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF67">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AG67">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AH67">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI67">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AJ67">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK67">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL67">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AM67">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AN67">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AO67">
         <v>0</v>
       </c>
       <c r="AP67">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AQ67">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AR67">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AS67">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AT67">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AU67">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AV67">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AW67">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AX67">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AY67">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ67">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BA67">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BB67">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BC67">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BD67">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="BE67">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="BF67">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BG67">
         <v>0</v>
@@ -13716,7 +13716,7 @@
         <v>134</v>
       </c>
       <c r="E68" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="F68" t="s">
         <v>288</v>
@@ -13749,133 +13749,133 @@
         <v>308</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>5.97</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="S68">
-        <v>2.08</v>
+        <v>1.65</v>
       </c>
       <c r="T68">
-        <v>2.42</v>
+        <v>2.8</v>
       </c>
       <c r="U68">
-        <v>4.5</v>
+        <v>6.45</v>
       </c>
       <c r="V68">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="W68">
-        <v>3.42</v>
+        <v>4.15</v>
       </c>
       <c r="X68">
-        <v>2.18</v>
+        <v>1.97</v>
       </c>
       <c r="Y68">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="Z68">
-        <v>4.7</v>
+        <v>3.98</v>
       </c>
       <c r="AA68">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AB68">
         <v>1.01</v>
       </c>
       <c r="AC68">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AD68">
-        <v>4.65</v>
+        <v>5.95</v>
       </c>
       <c r="AE68">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="AF68">
-        <v>2.33</v>
+        <v>2.81</v>
       </c>
       <c r="AG68">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="AH68">
+        <v>1.78</v>
+      </c>
+      <c r="AI68">
+        <v>3.05</v>
+      </c>
+      <c r="AJ68">
+        <v>1.28</v>
+      </c>
+      <c r="AK68">
+        <v>1.63</v>
+      </c>
+      <c r="AL68">
+        <v>2.12</v>
+      </c>
+      <c r="AM68">
+        <v>1.1</v>
+      </c>
+      <c r="AN68">
+        <v>3.42</v>
+      </c>
+      <c r="AO68">
+        <v>0</v>
+      </c>
+      <c r="AP68">
+        <v>1.19</v>
+      </c>
+      <c r="AQ68">
+        <v>1.35</v>
+      </c>
+      <c r="AR68">
+        <v>1.57</v>
+      </c>
+      <c r="AS68">
+        <v>1.92</v>
+      </c>
+      <c r="AT68">
+        <v>2.43</v>
+      </c>
+      <c r="AU68">
+        <v>3.9</v>
+      </c>
+      <c r="AV68">
+        <v>2.8</v>
+      </c>
+      <c r="AW68">
+        <v>2.15</v>
+      </c>
+      <c r="AX68">
+        <v>1.73</v>
+      </c>
+      <c r="AY68">
+        <v>1.45</v>
+      </c>
+      <c r="AZ68">
+        <v>1.3</v>
+      </c>
+      <c r="BA68">
+        <v>3.95</v>
+      </c>
+      <c r="BB68">
+        <v>1.09</v>
+      </c>
+      <c r="BC68">
         <v>1.58</v>
       </c>
-      <c r="AI68">
-        <v>3.75</v>
-      </c>
-      <c r="AJ68">
-        <v>1.19</v>
-      </c>
-      <c r="AK68">
-        <v>1.55</v>
-      </c>
-      <c r="AL68">
-        <v>2.27</v>
-      </c>
-      <c r="AM68">
-        <v>1.2</v>
-      </c>
-      <c r="AN68">
-        <v>2.17</v>
-      </c>
-      <c r="AO68">
-        <v>0</v>
-      </c>
-      <c r="AP68">
-        <v>1.2</v>
-      </c>
-      <c r="AQ68">
+      <c r="BD68">
+        <v>6.1</v>
+      </c>
+      <c r="BE68">
+        <v>2.16</v>
+      </c>
+      <c r="BF68">
         <v>1.36</v>
-      </c>
-      <c r="AR68">
-        <v>1.61</v>
-      </c>
-      <c r="AS68">
-        <v>1.97</v>
-      </c>
-      <c r="AT68">
-        <v>2.5</v>
-      </c>
-      <c r="AU68">
-        <v>3.8</v>
-      </c>
-      <c r="AV68">
-        <v>2.75</v>
-      </c>
-      <c r="AW68">
-        <v>2.1</v>
-      </c>
-      <c r="AX68">
-        <v>1.68</v>
-      </c>
-      <c r="AY68">
-        <v>1.43</v>
-      </c>
-      <c r="AZ68">
-        <v>1.55</v>
-      </c>
-      <c r="BA68">
-        <v>2.8</v>
-      </c>
-      <c r="BB68">
-        <v>1.12</v>
-      </c>
-      <c r="BC68">
-        <v>1.75</v>
-      </c>
-      <c r="BD68">
-        <v>4.7</v>
-      </c>
-      <c r="BE68">
-        <v>1.95</v>
-      </c>
-      <c r="BF68">
-        <v>1.26</v>
       </c>
       <c r="BG68">
         <v>0</v>
@@ -13895,7 +13895,7 @@
         <v>80</v>
       </c>
       <c r="C69" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="D69" t="s">
         <v>134</v>
@@ -14080,7 +14080,7 @@
         <v>80</v>
       </c>
       <c r="C70" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="D70" t="s">
         <v>134</v>
@@ -14128,124 +14128,124 @@
         <v>0</v>
       </c>
       <c r="S70">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T70">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U70">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V70">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W70">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="X70">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Y70">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z70">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA70">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC70">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD70">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AE70">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF70">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AG70">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH70">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI70">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AJ70">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK70">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL70">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AM70">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN70">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AO70">
         <v>0</v>
       </c>
       <c r="AP70">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AQ70">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR70">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS70">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AT70">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AU70">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AV70">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AW70">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AX70">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY70">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AZ70">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BA70">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BB70">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC70">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BD70">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE70">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF70">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BG70">
         <v>0</v>
@@ -14265,7 +14265,7 @@
         <v>81</v>
       </c>
       <c r="C71" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D71" t="s">
         <v>134</v>
@@ -14635,7 +14635,7 @@
         <v>82</v>
       </c>
       <c r="C73" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D73" t="s">
         <v>134</v>
@@ -14820,7 +14820,7 @@
         <v>83</v>
       </c>
       <c r="C74" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="D74" t="s">
         <v>134</v>
@@ -14859,133 +14859,133 @@
         <v>308</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="Q74">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S74">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="T74">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U74">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V74">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W74">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="X74">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Y74">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z74">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA74">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC74">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD74">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AE74">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF74">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG74">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AH74">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI74">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AJ74">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK74">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL74">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AM74">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN74">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AO74">
         <v>0</v>
       </c>
       <c r="AP74">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AQ74">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR74">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AS74">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AT74">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU74">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV74">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AW74">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AX74">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY74">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ74">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BA74">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BB74">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC74">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD74">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE74">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF74">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG74">
         <v>0</v>
@@ -15005,7 +15005,7 @@
         <v>83</v>
       </c>
       <c r="C75" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="D75" t="s">
         <v>134</v>
@@ -15044,133 +15044,133 @@
         <v>308</v>
       </c>
       <c r="P75">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q75">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R75">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S75">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T75">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U75">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V75">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W75">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="X75">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y75">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z75">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA75">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB75">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC75">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AD75">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AE75">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF75">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG75">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AH75">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI75">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AJ75">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK75">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL75">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM75">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AN75">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AO75">
         <v>0</v>
       </c>
       <c r="AP75">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AQ75">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AR75">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AS75">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AT75">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AU75">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AV75">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AW75">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AX75">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AY75">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ75">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BA75">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BB75">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC75">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="BD75">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="BE75">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BF75">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG75">
         <v>0</v>
@@ -15190,7 +15190,7 @@
         <v>83</v>
       </c>
       <c r="C76" t="s">
-        <v>96</v>
+        <v>127</v>
       </c>
       <c r="D76" t="s">
         <v>134</v>
@@ -15229,133 +15229,133 @@
         <v>308</v>
       </c>
       <c r="P76">
-        <v>6.3</v>
+        <v>2.45</v>
       </c>
       <c r="Q76">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="R76">
-        <v>1.45</v>
+        <v>2.88</v>
       </c>
       <c r="S76">
-        <v>5.75</v>
+        <v>3</v>
       </c>
       <c r="T76">
-        <v>2.45</v>
+        <v>2.14</v>
       </c>
       <c r="U76">
-        <v>1.99</v>
+        <v>3.3</v>
       </c>
       <c r="V76">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="W76">
-        <v>3.45</v>
+        <v>2.85</v>
       </c>
       <c r="X76">
-        <v>2.33</v>
+        <v>2.8</v>
       </c>
       <c r="Y76">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="Z76">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="AA76">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AB76">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC76">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AD76">
-        <v>4.45</v>
+        <v>3.34</v>
       </c>
       <c r="AE76">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AF76">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AG76">
-        <v>2.43</v>
+        <v>3.55</v>
       </c>
       <c r="AH76">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="AI76">
-        <v>4.15</v>
+        <v>6.1</v>
       </c>
       <c r="AJ76">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AK76">
         <v>1.75</v>
       </c>
       <c r="AL76">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AM76">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AN76">
-        <v>1.13</v>
+        <v>1.62</v>
       </c>
       <c r="AO76">
         <v>0</v>
       </c>
       <c r="AP76">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ76">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AR76">
+        <v>1.78</v>
+      </c>
+      <c r="AS76">
+        <v>2.19</v>
+      </c>
+      <c r="AT76">
+        <v>2.88</v>
+      </c>
+      <c r="AU76">
+        <v>3.58</v>
+      </c>
+      <c r="AV76">
+        <v>2.57</v>
+      </c>
+      <c r="AW76">
+        <v>1.96</v>
+      </c>
+      <c r="AX76">
+        <v>1.57</v>
+      </c>
+      <c r="AY76">
+        <v>1.32</v>
+      </c>
+      <c r="AZ76">
+        <v>1.65</v>
+      </c>
+      <c r="BA76">
+        <v>2.15</v>
+      </c>
+      <c r="BB76">
+        <v>1.24</v>
+      </c>
+      <c r="BC76">
+        <v>2.08</v>
+      </c>
+      <c r="BD76">
+        <v>3.84</v>
+      </c>
+      <c r="BE76">
         <v>1.71</v>
       </c>
-      <c r="AS76">
-        <v>2.15</v>
-      </c>
-      <c r="AT76">
-        <v>2.8</v>
-      </c>
-      <c r="AU76">
-        <v>3.6</v>
-      </c>
-      <c r="AV76">
-        <v>2.65</v>
-      </c>
-      <c r="AW76">
-        <v>2.01</v>
-      </c>
-      <c r="AX76">
-        <v>1.62</v>
-      </c>
-      <c r="AY76">
-        <v>1.38</v>
-      </c>
-      <c r="AZ76">
-        <v>3.7</v>
-      </c>
-      <c r="BA76">
-        <v>1.31</v>
-      </c>
-      <c r="BB76">
-        <v>1.2</v>
-      </c>
-      <c r="BC76">
-        <v>1.91</v>
-      </c>
-      <c r="BD76">
-        <v>4.8</v>
-      </c>
-      <c r="BE76">
-        <v>1.85</v>
-      </c>
       <c r="BF76">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="BG76">
         <v>0</v>
@@ -15560,7 +15560,7 @@
         <v>85</v>
       </c>
       <c r="C78" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D78" t="s">
         <v>134</v>
@@ -16154,79 +16154,79 @@
         <v>308</v>
       </c>
       <c r="P81">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="Q81">
-        <v>2.78</v>
+        <v>3.25</v>
       </c>
       <c r="R81">
-        <v>3.72</v>
+        <v>5</v>
       </c>
       <c r="S81">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="T81">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U81">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="V81">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W81">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="X81">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y81">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z81">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AA81">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB81">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC81">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD81">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AE81">
-        <v>2.87</v>
+        <v>2.43</v>
       </c>
       <c r="AF81">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG81">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AH81">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI81">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AJ81">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK81">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AL81">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AM81">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN81">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AO81">
         <v>0</v>
@@ -16268,19 +16268,19 @@
         <v>0</v>
       </c>
       <c r="BB81">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BC81">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BD81">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="BE81">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BF81">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BG81">
         <v>0</v>
@@ -16300,7 +16300,7 @@
         <v>87</v>
       </c>
       <c r="C82" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D82" t="s">
         <v>136</v>
@@ -16339,79 +16339,79 @@
         <v>308</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="S82">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T82">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="U82">
-        <v>5.16</v>
+        <v>0</v>
       </c>
       <c r="V82">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W82">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="X82">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Y82">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z82">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA82">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB82">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC82">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD82">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AE82">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AF82">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG82">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AH82">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI82">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="AJ82">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK82">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AL82">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AM82">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN82">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AO82">
         <v>0</v>
@@ -16453,19 +16453,19 @@
         <v>0</v>
       </c>
       <c r="BB82">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC82">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="BD82">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="BE82">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BF82">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="BG82">
         <v>0</v>
@@ -16485,7 +16485,7 @@
         <v>87</v>
       </c>
       <c r="C83" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D83" t="s">
         <v>136</v>
@@ -16524,79 +16524,79 @@
         <v>308</v>
       </c>
       <c r="P83">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q83">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="R83">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="S83">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T83">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="U83">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="V83">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W83">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="X83">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Y83">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z83">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB83">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC83">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD83">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG83">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AH83">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI83">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AJ83">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK83">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AL83">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AM83">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN83">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AO83">
         <v>0</v>
@@ -16638,19 +16638,19 @@
         <v>0</v>
       </c>
       <c r="BB83">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC83">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="BD83">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="BE83">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF83">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG83">
         <v>0</v>
@@ -16709,79 +16709,79 @@
         <v>308</v>
       </c>
       <c r="P84">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="Q84">
-        <v>3.25</v>
+        <v>2.78</v>
       </c>
       <c r="R84">
-        <v>5</v>
+        <v>3.72</v>
       </c>
       <c r="S84">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="T84">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U84">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="V84">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W84">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="X84">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y84">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z84">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA84">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB84">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC84">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AD84">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AE84">
-        <v>2.43</v>
+        <v>2.87</v>
       </c>
       <c r="AF84">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG84">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AH84">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AI84">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AJ84">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK84">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AL84">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AM84">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN84">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AO84">
         <v>0</v>
@@ -16823,19 +16823,19 @@
         <v>0</v>
       </c>
       <c r="BB84">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BC84">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="BD84">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="BE84">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BF84">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BG84">
         <v>0</v>
@@ -17040,7 +17040,7 @@
         <v>89</v>
       </c>
       <c r="C86" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D86" t="s">
         <v>136</v>
@@ -17079,133 +17079,133 @@
         <v>308</v>
       </c>
       <c r="P86">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="Q86">
-        <v>3.38</v>
+        <v>3</v>
       </c>
       <c r="R86">
-        <v>4.01</v>
+        <v>3.8</v>
       </c>
       <c r="S86">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T86">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="U86">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="V86">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W86">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="X86">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Y86">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z86">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA86">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD86">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG86">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="AH86">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI86">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AJ86">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK86">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL86">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AM86">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN86">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AO86">
         <v>0</v>
       </c>
       <c r="AP86">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AQ86">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AR86">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AS86">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AT86">
         <v>0</v>
       </c>
       <c r="AU86">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AV86">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AW86">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AX86">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AY86">
         <v>0</v>
       </c>
       <c r="AZ86">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BA86">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="BB86">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BC86">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="BD86">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BE86">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BF86">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG86">
         <v>0</v>
@@ -17225,7 +17225,7 @@
         <v>89</v>
       </c>
       <c r="C87" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D87" t="s">
         <v>136</v>
@@ -17264,133 +17264,133 @@
         <v>308</v>
       </c>
       <c r="P87">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="Q87">
-        <v>3</v>
+        <v>3.38</v>
       </c>
       <c r="R87">
-        <v>3.8</v>
+        <v>4.01</v>
       </c>
       <c r="S87">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T87">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="U87">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="V87">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="W87">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="X87">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Y87">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z87">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA87">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB87">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC87">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD87">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AE87">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AF87">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AG87">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="AH87">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AI87">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AJ87">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK87">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AL87">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AM87">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN87">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AO87">
         <v>0</v>
       </c>
       <c r="AP87">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AQ87">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AR87">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AS87">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AT87">
         <v>0</v>
       </c>
       <c r="AU87">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AV87">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AW87">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AX87">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AY87">
         <v>0</v>
       </c>
       <c r="AZ87">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="BA87">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="BB87">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BC87">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="BD87">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BE87">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BF87">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BG87">
         <v>0</v>

--- a/jogos_2026-05-04.xlsx
+++ b/jogos_2026-05-04.xlsx
@@ -301,27 +301,27 @@
     <t>Croatia Druga HNL</t>
   </si>
   <si>
+    <t>India Indian Super League</t>
+  </si>
+  <si>
     <t>Uzbekistan Uzbekistan Super League</t>
   </si>
   <si>
     <t>Oman Professional League</t>
   </si>
   <si>
+    <t>Egypt Egyptian Premier League</t>
+  </si>
+  <si>
+    <t>Serbia Prva Liga</t>
+  </si>
+  <si>
+    <t>England Premier League</t>
+  </si>
+  <si>
     <t>Russia FNL</t>
   </si>
   <si>
-    <t>India Indian Super League</t>
-  </si>
-  <si>
-    <t>Serbia Prva Liga</t>
-  </si>
-  <si>
-    <t>England Premier League</t>
-  </si>
-  <si>
-    <t>Egypt Egyptian Premier League</t>
-  </si>
-  <si>
     <t>Romania Liga I</t>
   </si>
   <si>
@@ -334,36 +334,36 @@
     <t>Azerbaijan Premyer Liqası</t>
   </si>
   <si>
+    <t>Republic of Ireland Premier Division</t>
+  </si>
+  <si>
+    <t>Poland 1. Liga</t>
+  </si>
+  <si>
+    <t>Jordan Jordanian Pro League</t>
+  </si>
+  <si>
     <t>Republic of Ireland First Division</t>
   </si>
   <si>
-    <t>Republic of Ireland Premier Division</t>
-  </si>
-  <si>
     <t>Morocco Botola Pro</t>
   </si>
   <si>
-    <t>Jordan Jordanian Pro League</t>
-  </si>
-  <si>
     <t>Croatia Prva HNL</t>
   </si>
   <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
     <t>Italy Serie A</t>
   </si>
   <si>
+    <t>Scotland Premiership</t>
+  </si>
+  <si>
     <t>Austria Bundesliga</t>
   </si>
   <si>
-    <t>Scotland Premiership</t>
-  </si>
-  <si>
     <t>Algeria Ligue 1</t>
   </si>
   <si>
@@ -373,12 +373,12 @@
     <t>Denmark Superliga</t>
   </si>
   <si>
+    <t>Portugal LigaPro</t>
+  </si>
+  <si>
     <t>Israel Israeli Premier League</t>
   </si>
   <si>
-    <t>Portugal LigaPro</t>
-  </si>
-  <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
@@ -403,12 +403,12 @@
     <t>Portugal Liga NOS</t>
   </si>
   <si>
+    <t>Brazil Serie B</t>
+  </si>
+  <si>
     <t>Chile Primera B</t>
   </si>
   <si>
-    <t>Brazil Serie B</t>
-  </si>
-  <si>
     <t>Brazil Serie C</t>
   </si>
   <si>
@@ -439,12 +439,12 @@
     <t>Albirex Niigata S</t>
   </si>
   <si>
+    <t>Aston Villa Ladies</t>
+  </si>
+  <si>
     <t>Persijap</t>
   </si>
   <si>
-    <t>Aston Villa Ladies</t>
-  </si>
-  <si>
     <t>Mekelakeya</t>
   </si>
   <si>
@@ -454,213 +454,213 @@
     <t>Dugopolje</t>
   </si>
   <si>
+    <t>Odisha FC</t>
+  </si>
+  <si>
+    <t>Xorazm</t>
+  </si>
+  <si>
+    <t>Al Khabourah</t>
+  </si>
+  <si>
+    <t>Pharco</t>
+  </si>
+  <si>
+    <t>Stepojevac Vaga</t>
+  </si>
+  <si>
     <t>Lokomotiv</t>
   </si>
   <si>
-    <t>Al Khabourah</t>
+    <t>OFK Vršac</t>
+  </si>
+  <si>
+    <t>Chelsea</t>
   </si>
   <si>
     <t>Ural</t>
   </si>
   <si>
-    <t>Xorazm</t>
-  </si>
-  <si>
-    <t>Odisha FC</t>
-  </si>
-  <si>
-    <t>Stepojevac Vaga</t>
-  </si>
-  <si>
-    <t>OFK Vršac</t>
-  </si>
-  <si>
-    <t>Chelsea</t>
-  </si>
-  <si>
-    <t>Pharco</t>
-  </si>
-  <si>
     <t>Unirea Slobozia</t>
   </si>
   <si>
+    <t>CA Bizertin</t>
+  </si>
+  <si>
+    <t>Monastir</t>
+  </si>
+  <si>
+    <t>Radnik Surdulica</t>
+  </si>
+  <si>
     <t>Zarzis</t>
   </si>
   <si>
-    <t>Monastir</t>
-  </si>
-  <si>
     <t>Nasaf</t>
   </si>
   <si>
-    <t>Radnik Surdulica</t>
-  </si>
-  <si>
     <t>Jeunesse Sportive Omrane</t>
   </si>
   <si>
-    <t>CA Bizertin</t>
-  </si>
-  <si>
     <t>Al Nasr</t>
   </si>
   <si>
     <t>Qarabağ</t>
   </si>
   <si>
+    <t>Sligo Rovers</t>
+  </si>
+  <si>
+    <t>Polonia Bytom</t>
+  </si>
+  <si>
+    <t>Waterford</t>
+  </si>
+  <si>
+    <t>Derry City</t>
+  </si>
+  <si>
+    <t>Bohemians</t>
+  </si>
+  <si>
+    <t>Al Ahli</t>
+  </si>
+  <si>
+    <t>Shamrock Rovers</t>
+  </si>
+  <si>
     <t>Kerry</t>
   </si>
   <si>
+    <t>Hassania Agadir</t>
+  </si>
+  <si>
+    <t>Longford Town</t>
+  </si>
+  <si>
+    <t>Finn Harps</t>
+  </si>
+  <si>
     <t>Treaty United</t>
   </si>
   <si>
-    <t>Waterford</t>
-  </si>
-  <si>
-    <t>Hassania Agadir</t>
+    <t>Istra 1961</t>
   </si>
   <si>
     <t>Cobh Ramblers</t>
   </si>
   <si>
-    <t>Sligo Rovers</t>
-  </si>
-  <si>
-    <t>Longford Town</t>
-  </si>
-  <si>
-    <t>Al Ahli</t>
-  </si>
-  <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
     <t>Al Jazeera</t>
   </si>
   <si>
-    <t>Bohemians</t>
-  </si>
-  <si>
-    <t>Shamrock Rovers</t>
-  </si>
-  <si>
-    <t>Istra 1961</t>
-  </si>
-  <si>
-    <t>Polonia Bytom</t>
-  </si>
-  <si>
-    <t>Derry City</t>
-  </si>
-  <si>
     <t>Al Feiha</t>
   </si>
   <si>
     <t>Al Shabab</t>
   </si>
   <si>
+    <t>Arsenal Tula</t>
+  </si>
+  <si>
     <t>Cremonese</t>
   </si>
   <si>
+    <t>Hearts</t>
+  </si>
+  <si>
     <t>Rheindorf Altach</t>
   </si>
   <si>
-    <t>Hearts</t>
-  </si>
-  <si>
-    <t>Arsenal Tula</t>
-  </si>
-  <si>
     <t>CR Belouizdad</t>
   </si>
   <si>
     <t>Halmstad</t>
   </si>
   <si>
+    <t>Midtjylland</t>
+  </si>
+  <si>
+    <t>Al Ittihad</t>
+  </si>
+  <si>
     <t>Wadi Degla</t>
   </si>
   <si>
     <t>Djurgården</t>
   </si>
   <si>
-    <t>Midtjylland</t>
+    <t>Torreense</t>
   </si>
   <si>
     <t>Bnei Sakhnin</t>
   </si>
   <si>
+    <t>Čukarički</t>
+  </si>
+  <si>
+    <t>Maccabi Netanya</t>
+  </si>
+  <si>
+    <t>Radomiak Radom</t>
+  </si>
+  <si>
+    <t>FK Bodo - Glimt</t>
+  </si>
+  <si>
     <t>Porto II</t>
   </si>
   <si>
-    <t>Maccabi Netanya</t>
-  </si>
-  <si>
-    <t>Radomiak Radom</t>
-  </si>
-  <si>
-    <t>Torreense</t>
-  </si>
-  <si>
-    <t>Al Ittihad</t>
-  </si>
-  <si>
-    <t>FK Bodo - Glimt</t>
-  </si>
-  <si>
-    <t>Čukarički</t>
-  </si>
-  <si>
     <t>Landskrona</t>
   </si>
   <si>
+    <t>Rapid Bucureşti</t>
+  </si>
+  <si>
     <t>B36</t>
   </si>
   <si>
     <t>Víkingur</t>
   </si>
   <si>
-    <t>Rapid Bucureşti</t>
-  </si>
-  <si>
     <t>Yacoub El Mansour</t>
   </si>
   <si>
+    <t>Al Ittifaq</t>
+  </si>
+  <si>
     <t>Vasas</t>
   </si>
   <si>
-    <t>Al Ittifaq</t>
+    <t>Almería</t>
   </si>
   <si>
     <t>LASK Linz</t>
   </si>
   <si>
-    <t>Almería</t>
-  </si>
-  <si>
     <t>Roma</t>
   </si>
   <si>
+    <t>Sevilla FC</t>
+  </si>
+  <si>
     <t>Everton</t>
   </si>
   <si>
     <t>USM Alger</t>
   </si>
   <si>
-    <t>Sevilla FC</t>
-  </si>
-  <si>
     <t>Sporting CP</t>
   </si>
   <si>
     <t>Kawkab Marrakech</t>
   </si>
   <si>
+    <t>Vila Nova</t>
+  </si>
+  <si>
     <t>San Luis</t>
   </si>
   <si>
-    <t>Vila Nova</t>
-  </si>
-  <si>
     <t>Floresta</t>
   </si>
   <si>
@@ -694,12 +694,12 @@
     <t>Young Lions</t>
   </si>
   <si>
+    <t>West Ham United Women</t>
+  </si>
+  <si>
     <t>Persija</t>
   </si>
   <si>
-    <t>West Ham United Women</t>
-  </si>
-  <si>
     <t>Adama Kenema</t>
   </si>
   <si>
@@ -709,214 +709,214 @@
     <t>Cibalia</t>
   </si>
   <si>
+    <t>Bengaluru</t>
+  </si>
+  <si>
+    <t>Andijan</t>
+  </si>
+  <si>
+    <t>Saham</t>
+  </si>
+  <si>
+    <t>Al Mokawloon</t>
+  </si>
+  <si>
+    <t>Kabel Novi Sad</t>
+  </si>
+  <si>
     <t>Qizilqum</t>
   </si>
   <si>
-    <t>Saham</t>
+    <t>Jedinstvo Ub</t>
+  </si>
+  <si>
+    <t>Nottingham Forest</t>
   </si>
   <si>
     <t>Shinnik</t>
   </si>
   <si>
-    <t>Andijan</t>
-  </si>
-  <si>
-    <t>Bengaluru</t>
-  </si>
-  <si>
-    <t>Kabel Novi Sad</t>
-  </si>
-  <si>
-    <t>Jedinstvo Ub</t>
-  </si>
-  <si>
-    <t>Nottingham Forest</t>
-  </si>
-  <si>
-    <t>Al Mokawloon</t>
-  </si>
-  <si>
     <t>Hermannstadt</t>
   </si>
   <si>
+    <t>Marsa</t>
+  </si>
+  <si>
+    <t>Métlaoui</t>
+  </si>
+  <si>
+    <t>Vojvodina</t>
+  </si>
+  <si>
     <t>Etoile du Sahel</t>
   </si>
   <si>
-    <t>Métlaoui</t>
-  </si>
-  <si>
     <t>Navbahor</t>
   </si>
   <si>
-    <t>Vojvodina</t>
-  </si>
-  <si>
     <t>ES Tunis</t>
   </si>
   <si>
-    <t>Marsa</t>
-  </si>
-  <si>
     <t>Al-Nahda</t>
   </si>
   <si>
     <t>Turan</t>
   </si>
   <si>
+    <t>St Patrick's Athl.</t>
+  </si>
+  <si>
+    <t>Polonia Warszawa</t>
+  </si>
+  <si>
+    <t>Dundalk</t>
+  </si>
+  <si>
+    <t>Galway United</t>
+  </si>
+  <si>
+    <t>Shelbourne</t>
+  </si>
+  <si>
+    <t>Al Buqa'a</t>
+  </si>
+  <si>
+    <t>Drogheda United</t>
+  </si>
+  <si>
     <t>Cork City</t>
   </si>
   <si>
+    <t>Olympic Safi</t>
+  </si>
+  <si>
+    <t>Athlone Town</t>
+  </si>
+  <si>
+    <t>Bray Wanderers</t>
+  </si>
+  <si>
     <t>Wexford</t>
   </si>
   <si>
-    <t>Dundalk</t>
-  </si>
-  <si>
-    <t>Olympic Safi</t>
+    <t>Slaven Koprivnica</t>
   </si>
   <si>
     <t>UCD</t>
   </si>
   <si>
-    <t>St Patrick's Athl.</t>
-  </si>
-  <si>
-    <t>Athlone Town</t>
-  </si>
-  <si>
-    <t>Al Buqa'a</t>
-  </si>
-  <si>
-    <t>Bray Wanderers</t>
-  </si>
-  <si>
     <t>Shabab Al Ordon</t>
   </si>
   <si>
-    <t>Shelbourne</t>
-  </si>
-  <si>
-    <t>Drogheda United</t>
-  </si>
-  <si>
-    <t>Slaven Koprivnica</t>
-  </si>
-  <si>
-    <t>Polonia Warszawa</t>
-  </si>
-  <si>
-    <t>Galway United</t>
-  </si>
-  <si>
     <t>Al Riyadh</t>
   </si>
   <si>
     <t>Al-Rustaq</t>
   </si>
   <si>
+    <t>Rotor Volgograd</t>
+  </si>
+  <si>
     <t>Lazio</t>
   </si>
   <si>
+    <t>Rangers</t>
+  </si>
+  <si>
     <t>Wolfsberger AC</t>
   </si>
   <si>
-    <t>Rangers</t>
-  </si>
-  <si>
-    <t>Rotor Volgograd</t>
-  </si>
-  <si>
     <t>USM Khenchela</t>
   </si>
   <si>
     <t>Brommapojkarna</t>
   </si>
   <si>
+    <t>Viborg</t>
+  </si>
+  <si>
+    <t>Petrojet</t>
+  </si>
+  <si>
     <t>Kahraba Ismailia</t>
   </si>
   <si>
     <t>IFK Göteborg</t>
   </si>
   <si>
-    <t>Viborg</t>
+    <t>FC Penafiel</t>
   </si>
   <si>
     <t>Maccabi Bnei Raina</t>
   </si>
   <si>
+    <t>Red Star Belgrade</t>
+  </si>
+  <si>
+    <t>Hapoel Katamon</t>
+  </si>
+  <si>
+    <t>Lechia Gdańsk</t>
+  </si>
+  <si>
+    <t>Molde</t>
+  </si>
+  <si>
     <t>Felgueiras 1932</t>
   </si>
   <si>
-    <t>Hapoel Katamon</t>
-  </si>
-  <si>
-    <t>Lechia Gdańsk</t>
-  </si>
-  <si>
-    <t>FC Penafiel</t>
-  </si>
-  <si>
-    <t>Petrojet</t>
-  </si>
-  <si>
-    <t>Molde</t>
-  </si>
-  <si>
-    <t>Red Star Belgrade</t>
-  </si>
-  <si>
     <t>Öster</t>
   </si>
   <si>
+    <t>CFR Cluj</t>
+  </si>
+  <si>
     <t>NSÍ</t>
   </si>
   <si>
     <t>07 Vestur</t>
   </si>
   <si>
-    <t>CFR Cluj</t>
-  </si>
-  <si>
     <t>RSB Berkane</t>
   </si>
   <si>
+    <t>Al Najma</t>
+  </si>
+  <si>
+    <t>Budafoki MTE</t>
+  </si>
+  <si>
     <t>Al Kholood</t>
   </si>
   <si>
-    <t>Budafoki MTE</t>
-  </si>
-  <si>
-    <t>Al Najma</t>
+    <t>Mirandés</t>
   </si>
   <si>
     <t>Rapid Wien</t>
   </si>
   <si>
-    <t>Mirandés</t>
-  </si>
-  <si>
     <t>Fiorentina</t>
   </si>
   <si>
+    <t>Real Sociedad</t>
+  </si>
+  <si>
     <t>Manchester City</t>
   </si>
   <si>
     <t>Paradou AC</t>
   </si>
   <si>
-    <t>Real Sociedad</t>
-  </si>
-  <si>
     <t>Vitória Guimarães</t>
   </si>
   <si>
     <t>Olympique Dcheïra</t>
   </si>
   <si>
+    <t>Athletic Club</t>
+  </si>
+  <si>
     <t>Unión San Felipe</t>
-  </si>
-  <si>
-    <t>Athletic Club</t>
   </si>
   <si>
     <t>Maranhão</t>
@@ -1539,13 +1539,13 @@
         <v>308</v>
       </c>
       <c r="P2">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q2">
-        <v>5.09</v>
+        <v>5.2</v>
       </c>
       <c r="R2">
-        <v>10</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S2">
         <v>1.72</v>
@@ -1578,10 +1578,10 @@
         <v>1</v>
       </c>
       <c r="AC2">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AD2">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="AE2">
         <v>1.67</v>
@@ -1596,7 +1596,7 @@
         <v>1.42</v>
       </c>
       <c r="AI2">
-        <v>4.51</v>
+        <v>4.4</v>
       </c>
       <c r="AJ2">
         <v>1.14</v>
@@ -1754,7 +1754,7 @@
         <v>1.37</v>
       </c>
       <c r="Z3">
-        <v>6.7</v>
+        <v>6.65</v>
       </c>
       <c r="AA3">
         <v>1.05</v>
@@ -1784,7 +1784,7 @@
         <v>5.88</v>
       </c>
       <c r="AJ3">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AK3">
         <v>1.68</v>
@@ -1793,7 +1793,7 @@
         <v>2.02</v>
       </c>
       <c r="AM3">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AN3">
         <v>1.65</v>
@@ -1808,7 +1808,7 @@
         <v>1.45</v>
       </c>
       <c r="AR3">
-        <v>1.78</v>
+        <v>2.01</v>
       </c>
       <c r="AS3">
         <v>2.24</v>
@@ -1844,7 +1844,7 @@
         <v>2.03</v>
       </c>
       <c r="BD3">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="BE3">
         <v>1.68</v>
@@ -2240,7 +2240,7 @@
         <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D6" t="s">
         <v>134</v>
@@ -2279,13 +2279,13 @@
         <v>308</v>
       </c>
       <c r="P6">
-        <v>5.2</v>
+        <v>2.17</v>
       </c>
       <c r="Q6">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R6">
-        <v>1.57</v>
+        <v>2.83</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D7" t="s">
         <v>134</v>
@@ -2464,13 +2464,13 @@
         <v>308</v>
       </c>
       <c r="P7">
-        <v>2.17</v>
+        <v>4.4</v>
       </c>
       <c r="Q7">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="R7">
-        <v>2.83</v>
+        <v>1.54</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -3168,7 +3168,7 @@
         <v>95</v>
       </c>
       <c r="D11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E11" t="s">
         <v>146</v>
@@ -3353,7 +3353,7 @@
         <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E12" t="s">
         <v>147</v>
@@ -3574,79 +3574,79 @@
         <v>308</v>
       </c>
       <c r="P13">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q13">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R13">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="S13">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="T13">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U13">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="V13">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W13">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="X13">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y13">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z13">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AA13">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB13">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC13">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD13">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AE13">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AF13">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG13">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AH13">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI13">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AJ13">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK13">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL13">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AM13">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN13">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AO13">
         <v>0</v>
@@ -3688,19 +3688,19 @@
         <v>0</v>
       </c>
       <c r="BB13">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BC13">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="BD13">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE13">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF13">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG13">
         <v>0</v>
@@ -3720,10 +3720,10 @@
         <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D14" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E14" t="s">
         <v>149</v>
@@ -3759,133 +3759,133 @@
         <v>308</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AN14">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AO14">
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AU14">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV14">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AW14">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AX14">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AY14">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ14">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BA14">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BB14">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BC14">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="BD14">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BE14">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BF14">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BG14">
         <v>0</v>
@@ -3905,7 +3905,7 @@
         <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D15" t="s">
         <v>134</v>
@@ -4090,10 +4090,10 @@
         <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D16" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E16" t="s">
         <v>151</v>
@@ -4684,133 +4684,133 @@
         <v>308</v>
       </c>
       <c r="P19">
-        <v>3.2</v>
+        <v>1.77</v>
       </c>
       <c r="Q19">
-        <v>2.78</v>
+        <v>3.42</v>
       </c>
       <c r="R19">
-        <v>2.42</v>
+        <v>4.48</v>
       </c>
       <c r="S19">
-        <v>4.25</v>
+        <v>2.44</v>
       </c>
       <c r="T19">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="U19">
-        <v>3.41</v>
+        <v>4.9</v>
       </c>
       <c r="V19">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="W19">
-        <v>2.07</v>
+        <v>2.53</v>
       </c>
       <c r="X19">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="Y19">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="Z19">
-        <v>12</v>
+        <v>7.6</v>
       </c>
       <c r="AA19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AB19">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AC19">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="AD19">
-        <v>2.3</v>
+        <v>2.74</v>
       </c>
       <c r="AE19">
-        <v>2.7</v>
+        <v>2.17</v>
       </c>
       <c r="AF19">
-        <v>1.36</v>
+        <v>1.68</v>
       </c>
       <c r="AG19">
-        <v>5.35</v>
+        <v>3.78</v>
       </c>
       <c r="AH19">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="AI19">
-        <v>12.5</v>
+        <v>7.3</v>
       </c>
       <c r="AJ19">
         <v>1.03</v>
       </c>
       <c r="AK19">
-        <v>2.15</v>
+        <v>1.97</v>
       </c>
       <c r="AL19">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AM19">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AN19">
-        <v>1.27</v>
+        <v>1.91</v>
       </c>
       <c r="AO19">
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AQ19">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AR19">
-        <v>1.97</v>
+        <v>2.49</v>
       </c>
       <c r="AS19">
-        <v>2.55</v>
+        <v>2.78</v>
       </c>
       <c r="AT19">
-        <v>3.3</v>
+        <v>3.94</v>
       </c>
       <c r="AU19">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="AV19">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="AW19">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="AX19">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AY19">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AZ19">
-        <v>2.48</v>
+        <v>1.46</v>
       </c>
       <c r="BA19">
-        <v>1.62</v>
+        <v>3.75</v>
       </c>
       <c r="BB19">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="BC19">
-        <v>2.78</v>
+        <v>2.32</v>
       </c>
       <c r="BD19">
-        <v>2.7</v>
+        <v>3.28</v>
       </c>
       <c r="BE19">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="BF19">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="BG19">
         <v>0</v>
@@ -5385,10 +5385,10 @@
         <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="D23" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E23" t="s">
         <v>158</v>
@@ -5424,61 +5424,61 @@
         <v>308</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB23">
         <v>0</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH23">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI23">
         <v>0</v>
@@ -5487,16 +5487,16 @@
         <v>0</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL23">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM23">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN23">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO23">
         <v>0</v>
@@ -5541,13 +5541,13 @@
         <v>0</v>
       </c>
       <c r="BC23">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BD23">
         <v>0</v>
       </c>
       <c r="BE23">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BF23">
         <v>0</v>
@@ -5570,7 +5570,7 @@
         <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D24" t="s">
         <v>134</v>
@@ -5609,61 +5609,61 @@
         <v>308</v>
       </c>
       <c r="P24">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q24">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R24">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S24">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="T24">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="U24">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="V24">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W24">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="X24">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Y24">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z24">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AA24">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB24">
         <v>0</v>
       </c>
       <c r="AC24">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD24">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="AE24">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AF24">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG24">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH24">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AI24">
         <v>0</v>
@@ -5672,16 +5672,16 @@
         <v>0</v>
       </c>
       <c r="AK24">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AL24">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AM24">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN24">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO24">
         <v>0</v>
@@ -5726,13 +5726,13 @@
         <v>0</v>
       </c>
       <c r="BC24">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="BD24">
         <v>0</v>
       </c>
       <c r="BE24">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="BF24">
         <v>0</v>
@@ -5755,10 +5755,10 @@
         <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D25" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E25" t="s">
         <v>160</v>
@@ -6125,7 +6125,7 @@
         <v>70</v>
       </c>
       <c r="C27" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D27" t="s">
         <v>134</v>
@@ -6349,13 +6349,13 @@
         <v>308</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>5.96</v>
       </c>
       <c r="S28">
         <v>0</v>
@@ -6534,13 +6534,13 @@
         <v>308</v>
       </c>
       <c r="P29">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="Q29">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R29">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S29">
         <v>0</v>
@@ -6680,10 +6680,10 @@
         <v>72</v>
       </c>
       <c r="C30" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D30" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E30" t="s">
         <v>165</v>
@@ -6719,79 +6719,79 @@
         <v>308</v>
       </c>
       <c r="P30">
-        <v>2.6</v>
+        <v>2.27</v>
       </c>
       <c r="Q30">
-        <v>3.3</v>
+        <v>3.43</v>
       </c>
       <c r="R30">
-        <v>2.43</v>
+        <v>2.73</v>
       </c>
       <c r="S30">
-        <v>3.25</v>
+        <v>2.82</v>
       </c>
       <c r="T30">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="U30">
-        <v>2.9</v>
+        <v>3.28</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="X30">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="Y30">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC30">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AD30">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="AE30">
-        <v>1.82</v>
+        <v>1.63</v>
       </c>
       <c r="AF30">
-        <v>1.82</v>
+        <v>2.19</v>
       </c>
       <c r="AG30">
-        <v>3</v>
+        <v>2.53</v>
       </c>
       <c r="AH30">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AI30">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="AJ30">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AK30">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AL30">
-        <v>2.05</v>
+        <v>2.32</v>
       </c>
       <c r="AM30">
         <v>1.24</v>
       </c>
       <c r="AN30">
-        <v>1.32</v>
+        <v>1.49</v>
       </c>
       <c r="AO30">
         <v>0</v>
@@ -6833,19 +6833,19 @@
         <v>0</v>
       </c>
       <c r="BB30">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC30">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="BD30">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE30">
-        <v>1.64</v>
+        <v>1.86</v>
       </c>
       <c r="BF30">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG30">
         <v>0</v>
@@ -6865,7 +6865,7 @@
         <v>72</v>
       </c>
       <c r="C31" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D31" t="s">
         <v>136</v>
@@ -7050,10 +7050,10 @@
         <v>72</v>
       </c>
       <c r="C32" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D32" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E32" t="s">
         <v>167</v>
@@ -7274,22 +7274,22 @@
         <v>308</v>
       </c>
       <c r="P33">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q33">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R33">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S33">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T33">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U33">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="V33">
         <v>0</v>
@@ -7298,10 +7298,10 @@
         <v>0</v>
       </c>
       <c r="X33">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Y33">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -7313,40 +7313,40 @@
         <v>0</v>
       </c>
       <c r="AC33">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD33">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AE33">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF33">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG33">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH33">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI33">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ33">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK33">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL33">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AM33">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN33">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AO33">
         <v>0</v>
@@ -7391,13 +7391,13 @@
         <v>0</v>
       </c>
       <c r="BC33">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="BD33">
         <v>0</v>
       </c>
       <c r="BE33">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF33">
         <v>0</v>
@@ -7420,10 +7420,10 @@
         <v>72</v>
       </c>
       <c r="C34" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D34" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E34" t="s">
         <v>169</v>
@@ -7459,13 +7459,13 @@
         <v>308</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S34">
         <v>0</v>
@@ -7644,22 +7644,22 @@
         <v>308</v>
       </c>
       <c r="P35">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q35">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R35">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="S35">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T35">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U35">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="V35">
         <v>0</v>
@@ -7668,10 +7668,10 @@
         <v>0</v>
       </c>
       <c r="X35">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Y35">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -7683,40 +7683,40 @@
         <v>0</v>
       </c>
       <c r="AC35">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD35">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AE35">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF35">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG35">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH35">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI35">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AJ35">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK35">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM35">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN35">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AO35">
         <v>0</v>
@@ -7761,13 +7761,13 @@
         <v>0</v>
       </c>
       <c r="BC35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD35">
         <v>0</v>
       </c>
       <c r="BE35">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BF35">
         <v>0</v>
@@ -7793,7 +7793,7 @@
         <v>109</v>
       </c>
       <c r="D36" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E36" t="s">
         <v>171</v>
@@ -7829,13 +7829,13 @@
         <v>308</v>
       </c>
       <c r="P36">
-        <v>2.35</v>
+        <v>5.42</v>
       </c>
       <c r="Q36">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="R36">
-        <v>2.62</v>
+        <v>1.56</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -7975,10 +7975,10 @@
         <v>72</v>
       </c>
       <c r="C37" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D37" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E37" t="s">
         <v>172</v>
@@ -8014,22 +8014,22 @@
         <v>308</v>
       </c>
       <c r="P37">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q37">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R37">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S37">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T37">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U37">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="V37">
         <v>0</v>
@@ -8038,10 +8038,10 @@
         <v>0</v>
       </c>
       <c r="X37">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y37">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -8053,40 +8053,40 @@
         <v>0</v>
       </c>
       <c r="AC37">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AD37">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE37">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF37">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG37">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AH37">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI37">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ37">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK37">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL37">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AM37">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN37">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO37">
         <v>0</v>
@@ -8131,13 +8131,13 @@
         <v>0</v>
       </c>
       <c r="BC37">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="BD37">
         <v>0</v>
       </c>
       <c r="BE37">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BF37">
         <v>0</v>
@@ -8163,7 +8163,7 @@
         <v>109</v>
       </c>
       <c r="D38" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E38" t="s">
         <v>173</v>
@@ -8199,22 +8199,22 @@
         <v>308</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V38">
         <v>0</v>
@@ -8223,10 +8223,10 @@
         <v>0</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -8238,40 +8238,40 @@
         <v>0</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE38">
+        <v>1.82</v>
+      </c>
+      <c r="AF38">
+        <v>1.82</v>
+      </c>
+      <c r="AG38">
+        <v>3</v>
+      </c>
+      <c r="AH38">
+        <v>1.3</v>
+      </c>
+      <c r="AI38">
+        <v>5.4</v>
+      </c>
+      <c r="AJ38">
+        <v>1.09</v>
+      </c>
+      <c r="AK38">
+        <v>1.67</v>
+      </c>
+      <c r="AL38">
         <v>2</v>
       </c>
-      <c r="AF38">
-        <v>1.8</v>
-      </c>
-      <c r="AG38">
-        <v>0</v>
-      </c>
-      <c r="AH38">
-        <v>0</v>
-      </c>
-      <c r="AI38">
-        <v>0</v>
-      </c>
-      <c r="AJ38">
-        <v>0</v>
-      </c>
-      <c r="AK38">
-        <v>1.84</v>
-      </c>
-      <c r="AL38">
-        <v>1.97</v>
-      </c>
       <c r="AM38">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN38">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AO38">
         <v>0</v>
@@ -8316,13 +8316,13 @@
         <v>0</v>
       </c>
       <c r="BC38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD38">
         <v>0</v>
       </c>
       <c r="BE38">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BF38">
         <v>0</v>
@@ -8345,7 +8345,7 @@
         <v>72</v>
       </c>
       <c r="C39" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D39" t="s">
         <v>136</v>
@@ -8384,22 +8384,22 @@
         <v>308</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V39">
         <v>0</v>
@@ -8408,10 +8408,10 @@
         <v>0</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -8423,40 +8423,40 @@
         <v>0</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AH39">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI39">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL39">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AM39">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN39">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO39">
         <v>0</v>
@@ -8501,13 +8501,13 @@
         <v>0</v>
       </c>
       <c r="BC39">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BD39">
         <v>0</v>
       </c>
       <c r="BE39">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF39">
         <v>0</v>
@@ -8530,7 +8530,7 @@
         <v>72</v>
       </c>
       <c r="C40" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D40" t="s">
         <v>136</v>
@@ -8569,22 +8569,22 @@
         <v>308</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V40">
         <v>0</v>
@@ -8593,10 +8593,10 @@
         <v>0</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -8608,40 +8608,40 @@
         <v>0</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH40">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI40">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL40">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM40">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN40">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AO40">
         <v>0</v>
@@ -8686,13 +8686,13 @@
         <v>0</v>
       </c>
       <c r="BC40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD40">
         <v>0</v>
       </c>
       <c r="BE40">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BF40">
         <v>0</v>
@@ -8715,7 +8715,7 @@
         <v>72</v>
       </c>
       <c r="C41" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D41" t="s">
         <v>134</v>
@@ -8900,10 +8900,10 @@
         <v>72</v>
       </c>
       <c r="C42" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D42" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E42" t="s">
         <v>177</v>
@@ -8939,79 +8939,79 @@
         <v>308</v>
       </c>
       <c r="P42">
-        <v>2.27</v>
+        <v>2.14</v>
       </c>
       <c r="Q42">
-        <v>3.43</v>
+        <v>3.3</v>
       </c>
       <c r="R42">
-        <v>2.73</v>
+        <v>3.14</v>
       </c>
       <c r="S42">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
       <c r="T42">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="U42">
-        <v>3.28</v>
+        <v>3.65</v>
       </c>
       <c r="V42">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W42">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="X42">
-        <v>2.31</v>
+        <v>2.55</v>
       </c>
       <c r="Y42">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="Z42">
+        <v>0</v>
+      </c>
+      <c r="AA42">
+        <v>0</v>
+      </c>
+      <c r="AB42">
+        <v>0</v>
+      </c>
+      <c r="AC42">
+        <v>1.25</v>
+      </c>
+      <c r="AD42">
+        <v>3.35</v>
+      </c>
+      <c r="AE42">
+        <v>1.82</v>
+      </c>
+      <c r="AF42">
+        <v>1.82</v>
+      </c>
+      <c r="AG42">
+        <v>3</v>
+      </c>
+      <c r="AH42">
+        <v>1.3</v>
+      </c>
+      <c r="AI42">
         <v>5.5</v>
       </c>
-      <c r="AA42">
-        <v>1.11</v>
-      </c>
-      <c r="AB42">
-        <v>1.03</v>
-      </c>
-      <c r="AC42">
-        <v>1.18</v>
-      </c>
-      <c r="AD42">
-        <v>4</v>
-      </c>
-      <c r="AE42">
-        <v>1.63</v>
-      </c>
-      <c r="AF42">
-        <v>2.19</v>
-      </c>
-      <c r="AG42">
-        <v>2.53</v>
-      </c>
-      <c r="AH42">
-        <v>1.44</v>
-      </c>
-      <c r="AI42">
-        <v>4.3</v>
-      </c>
       <c r="AJ42">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AK42">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AL42">
-        <v>2.32</v>
+        <v>2.02</v>
       </c>
       <c r="AM42">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AN42">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AO42">
         <v>0</v>
@@ -9053,19 +9053,19 @@
         <v>0</v>
       </c>
       <c r="BB42">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC42">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="BD42">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE42">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="BF42">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BG42">
         <v>0</v>
@@ -9085,10 +9085,10 @@
         <v>72</v>
       </c>
       <c r="C43" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D43" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E43" t="s">
         <v>178</v>
@@ -9169,10 +9169,10 @@
         <v>0</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG43">
         <v>0</v>
@@ -9187,10 +9187,10 @@
         <v>0</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL43">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AM43">
         <v>0</v>
@@ -9318,28 +9318,28 @@
         <v>0</v>
       </c>
       <c r="S44">
-        <v>2.68</v>
+        <v>2.91</v>
       </c>
       <c r="T44">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="U44">
-        <v>4.1</v>
+        <v>3.62</v>
       </c>
       <c r="V44">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="W44">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="X44">
-        <v>3.17</v>
+        <v>2.96</v>
       </c>
       <c r="Y44">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z44">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="AA44">
         <v>1.02</v>
@@ -9348,94 +9348,94 @@
         <v>1.01</v>
       </c>
       <c r="AC44">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AD44">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AE44">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="AF44">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AG44">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="AH44">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AI44">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AJ44">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK44">
+        <v>1.79</v>
+      </c>
+      <c r="AL44">
+        <v>1.9</v>
+      </c>
+      <c r="AM44">
+        <v>1.3</v>
+      </c>
+      <c r="AN44">
+        <v>1.55</v>
+      </c>
+      <c r="AO44">
+        <v>0</v>
+      </c>
+      <c r="AP44">
+        <v>1.24</v>
+      </c>
+      <c r="AQ44">
+        <v>1.46</v>
+      </c>
+      <c r="AR44">
+        <v>1.82</v>
+      </c>
+      <c r="AS44">
+        <v>2.3</v>
+      </c>
+      <c r="AT44">
+        <v>3.14</v>
+      </c>
+      <c r="AU44">
+        <v>3.34</v>
+      </c>
+      <c r="AV44">
+        <v>2.38</v>
+      </c>
+      <c r="AW44">
         <v>1.84</v>
       </c>
-      <c r="AL44">
+      <c r="AX44">
+        <v>1.49</v>
+      </c>
+      <c r="AY44">
+        <v>1.27</v>
+      </c>
+      <c r="AZ44">
         <v>1.85</v>
       </c>
-      <c r="AM44">
-        <v>1.29</v>
-      </c>
-      <c r="AN44">
-        <v>1.61</v>
-      </c>
-      <c r="AO44">
-        <v>0</v>
-      </c>
-      <c r="AP44">
-        <v>1.2</v>
-      </c>
-      <c r="AQ44">
-        <v>1.37</v>
-      </c>
-      <c r="AR44">
-        <v>1.62</v>
-      </c>
-      <c r="AS44">
-        <v>1.98</v>
-      </c>
-      <c r="AT44">
-        <v>2.5</v>
-      </c>
-      <c r="AU44">
-        <v>3.75</v>
-      </c>
-      <c r="AV44">
-        <v>2.7</v>
-      </c>
-      <c r="AW44">
-        <v>2.08</v>
-      </c>
-      <c r="AX44">
-        <v>1.68</v>
-      </c>
-      <c r="AY44">
-        <v>1.42</v>
-      </c>
-      <c r="AZ44">
-        <v>1.68</v>
-      </c>
       <c r="BA44">
-        <v>2.48</v>
+        <v>2.39</v>
       </c>
       <c r="BB44">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="BC44">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="BD44">
-        <v>3.75</v>
+        <v>3.42</v>
       </c>
       <c r="BE44">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="BF44">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="BG44">
         <v>0</v>
@@ -9455,7 +9455,7 @@
         <v>74</v>
       </c>
       <c r="C45" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D45" t="s">
         <v>134</v>
@@ -9640,7 +9640,7 @@
         <v>75</v>
       </c>
       <c r="C46" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="D46" t="s">
         <v>134</v>
@@ -9679,133 +9679,133 @@
         <v>308</v>
       </c>
       <c r="P46">
-        <v>2.95</v>
+        <v>3.22</v>
       </c>
       <c r="Q46">
-        <v>3.22</v>
+        <v>2.93</v>
       </c>
       <c r="R46">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="S46">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="T46">
+        <v>1.85</v>
+      </c>
+      <c r="U46">
+        <v>3.82</v>
+      </c>
+      <c r="V46">
+        <v>1.55</v>
+      </c>
+      <c r="W46">
+        <v>2.33</v>
+      </c>
+      <c r="X46">
+        <v>3.44</v>
+      </c>
+      <c r="Y46">
+        <v>1.24</v>
+      </c>
+      <c r="Z46">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AA46">
+        <v>1</v>
+      </c>
+      <c r="AB46">
+        <v>1.05</v>
+      </c>
+      <c r="AC46">
+        <v>1.48</v>
+      </c>
+      <c r="AD46">
+        <v>2.56</v>
+      </c>
+      <c r="AE46">
+        <v>2.48</v>
+      </c>
+      <c r="AF46">
+        <v>1.55</v>
+      </c>
+      <c r="AG46">
+        <v>4.55</v>
+      </c>
+      <c r="AH46">
+        <v>1.13</v>
+      </c>
+      <c r="AI46">
+        <v>9.5</v>
+      </c>
+      <c r="AJ46">
+        <v>1</v>
+      </c>
+      <c r="AK46">
+        <v>2.02</v>
+      </c>
+      <c r="AL46">
+        <v>1.71</v>
+      </c>
+      <c r="AM46">
+        <v>1.38</v>
+      </c>
+      <c r="AN46">
+        <v>1.52</v>
+      </c>
+      <c r="AO46">
+        <v>0</v>
+      </c>
+      <c r="AP46">
+        <v>1.5</v>
+      </c>
+      <c r="AQ46">
+        <v>1.88</v>
+      </c>
+      <c r="AR46">
+        <v>3.02</v>
+      </c>
+      <c r="AS46">
+        <v>3.35</v>
+      </c>
+      <c r="AT46">
+        <v>4.99</v>
+      </c>
+      <c r="AU46">
+        <v>2.37</v>
+      </c>
+      <c r="AV46">
+        <v>1.83</v>
+      </c>
+      <c r="AW46">
+        <v>1.47</v>
+      </c>
+      <c r="AX46">
+        <v>1.24</v>
+      </c>
+      <c r="AY46">
+        <v>1.09</v>
+      </c>
+      <c r="AZ46">
         <v>2.1</v>
       </c>
-      <c r="U46">
-        <v>2.9</v>
-      </c>
-      <c r="V46">
+      <c r="BA46">
+        <v>2.19</v>
+      </c>
+      <c r="BB46">
+        <v>1.33</v>
+      </c>
+      <c r="BC46">
+        <v>2.56</v>
+      </c>
+      <c r="BD46">
+        <v>2.99</v>
+      </c>
+      <c r="BE46">
         <v>1.44</v>
       </c>
-      <c r="W46">
-        <v>2.65</v>
-      </c>
-      <c r="X46">
-        <v>2.9</v>
-      </c>
-      <c r="Y46">
-        <v>1.34</v>
-      </c>
-      <c r="Z46">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AA46">
-        <v>1.03</v>
-      </c>
-      <c r="AB46">
+      <c r="BF46">
         <v>1.06</v>
-      </c>
-      <c r="AC46">
-        <v>1.34</v>
-      </c>
-      <c r="AD46">
-        <v>3</v>
-      </c>
-      <c r="AE46">
-        <v>2.21</v>
-      </c>
-      <c r="AF46">
-        <v>1.7</v>
-      </c>
-      <c r="AG46">
-        <v>3.58</v>
-      </c>
-      <c r="AH46">
-        <v>1.29</v>
-      </c>
-      <c r="AI46">
-        <v>7.8</v>
-      </c>
-      <c r="AJ46">
-        <v>1.02</v>
-      </c>
-      <c r="AK46">
-        <v>1.83</v>
-      </c>
-      <c r="AL46">
-        <v>1.92</v>
-      </c>
-      <c r="AM46">
-        <v>1.33</v>
-      </c>
-      <c r="AN46">
-        <v>1.36</v>
-      </c>
-      <c r="AO46">
-        <v>0</v>
-      </c>
-      <c r="AP46">
-        <v>1.38</v>
-      </c>
-      <c r="AQ46">
-        <v>1.68</v>
-      </c>
-      <c r="AR46">
-        <v>2.1</v>
-      </c>
-      <c r="AS46">
-        <v>2.38</v>
-      </c>
-      <c r="AT46">
-        <v>3.15</v>
-      </c>
-      <c r="AU46">
-        <v>3.1</v>
-      </c>
-      <c r="AV46">
-        <v>2.06</v>
-      </c>
-      <c r="AW46">
-        <v>1.6</v>
-      </c>
-      <c r="AX46">
-        <v>1.5</v>
-      </c>
-      <c r="AY46">
-        <v>1.3</v>
-      </c>
-      <c r="AZ46">
-        <v>2.5</v>
-      </c>
-      <c r="BA46">
-        <v>1.8</v>
-      </c>
-      <c r="BB46">
-        <v>1.27</v>
-      </c>
-      <c r="BC46">
-        <v>2.38</v>
-      </c>
-      <c r="BD46">
-        <v>3.55</v>
-      </c>
-      <c r="BE46">
-        <v>1.6</v>
-      </c>
-      <c r="BF46">
-        <v>1.13</v>
       </c>
       <c r="BG46">
         <v>0</v>
@@ -9825,7 +9825,7 @@
         <v>75</v>
       </c>
       <c r="C47" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D47" t="s">
         <v>134</v>
@@ -9864,133 +9864,133 @@
         <v>308</v>
       </c>
       <c r="P47">
-        <v>2.32</v>
+        <v>2.9</v>
       </c>
       <c r="Q47">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="R47">
-        <v>2.92</v>
+        <v>2.5</v>
       </c>
       <c r="S47">
+        <v>3.5</v>
+      </c>
+      <c r="T47">
+        <v>2.1</v>
+      </c>
+      <c r="U47">
+        <v>2.9</v>
+      </c>
+      <c r="V47">
+        <v>1.47</v>
+      </c>
+      <c r="W47">
+        <v>2.65</v>
+      </c>
+      <c r="X47">
+        <v>3.22</v>
+      </c>
+      <c r="Y47">
+        <v>1.34</v>
+      </c>
+      <c r="Z47">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AA47">
+        <v>1.03</v>
+      </c>
+      <c r="AB47">
+        <v>1.06</v>
+      </c>
+      <c r="AC47">
+        <v>1.36</v>
+      </c>
+      <c r="AD47">
+        <v>3</v>
+      </c>
+      <c r="AE47">
+        <v>2.15</v>
+      </c>
+      <c r="AF47">
+        <v>1.7</v>
+      </c>
+      <c r="AG47">
+        <v>3.9</v>
+      </c>
+      <c r="AH47">
+        <v>1.22</v>
+      </c>
+      <c r="AI47">
+        <v>8</v>
+      </c>
+      <c r="AJ47">
+        <v>1.06</v>
+      </c>
+      <c r="AK47">
+        <v>1.85</v>
+      </c>
+      <c r="AL47">
+        <v>1.89</v>
+      </c>
+      <c r="AM47">
+        <v>1.33</v>
+      </c>
+      <c r="AN47">
+        <v>1.36</v>
+      </c>
+      <c r="AO47">
+        <v>0</v>
+      </c>
+      <c r="AP47">
+        <v>1.38</v>
+      </c>
+      <c r="AQ47">
+        <v>1.66</v>
+      </c>
+      <c r="AR47">
+        <v>2.48</v>
+      </c>
+      <c r="AS47">
+        <v>2.77</v>
+      </c>
+      <c r="AT47">
+        <v>3.66</v>
+      </c>
+      <c r="AU47">
         <v>2.8</v>
       </c>
-      <c r="T47">
-        <v>2.05</v>
-      </c>
-      <c r="U47">
-        <v>3.55</v>
-      </c>
-      <c r="V47">
-        <v>1.4</v>
-      </c>
-      <c r="W47">
-        <v>2.73</v>
-      </c>
-      <c r="X47">
-        <v>2.85</v>
-      </c>
-      <c r="Y47">
-        <v>1.37</v>
-      </c>
-      <c r="Z47">
-        <v>7</v>
-      </c>
-      <c r="AA47">
-        <v>1.04</v>
-      </c>
-      <c r="AB47">
-        <v>1.01</v>
-      </c>
-      <c r="AC47">
-        <v>1.28</v>
-      </c>
-      <c r="AD47">
-        <v>3.12</v>
-      </c>
-      <c r="AE47">
-        <v>2</v>
-      </c>
-      <c r="AF47">
-        <v>1.78</v>
-      </c>
-      <c r="AG47">
+      <c r="AV47">
+        <v>2.08</v>
+      </c>
+      <c r="AW47">
+        <v>1.65</v>
+      </c>
+      <c r="AX47">
+        <v>1.39</v>
+      </c>
+      <c r="AY47">
+        <v>1.22</v>
+      </c>
+      <c r="AZ47">
+        <v>2.25</v>
+      </c>
+      <c r="BA47">
+        <v>1.83</v>
+      </c>
+      <c r="BB47">
+        <v>1.3</v>
+      </c>
+      <c r="BC47">
+        <v>2.3</v>
+      </c>
+      <c r="BD47">
         <v>3.3</v>
       </c>
-      <c r="AH47">
-        <v>1.25</v>
-      </c>
-      <c r="AI47">
-        <v>6.5</v>
-      </c>
-      <c r="AJ47">
-        <v>1.05</v>
-      </c>
-      <c r="AK47">
-        <v>1.75</v>
-      </c>
-      <c r="AL47">
-        <v>2</v>
-      </c>
-      <c r="AM47">
-        <v>1.35</v>
-      </c>
-      <c r="AN47">
-        <v>1.54</v>
-      </c>
-      <c r="AO47">
-        <v>0</v>
-      </c>
-      <c r="AP47">
-        <v>1.33</v>
-      </c>
-      <c r="AQ47">
-        <v>1.61</v>
-      </c>
-      <c r="AR47">
-        <v>2.06</v>
-      </c>
-      <c r="AS47">
-        <v>2.75</v>
-      </c>
-      <c r="AT47">
-        <v>3.8</v>
-      </c>
-      <c r="AU47">
-        <v>2.83</v>
-      </c>
-      <c r="AV47">
-        <v>2.09</v>
-      </c>
-      <c r="AW47">
-        <v>1.66</v>
-      </c>
-      <c r="AX47">
-        <v>1.36</v>
-      </c>
-      <c r="AY47">
-        <v>1.19</v>
-      </c>
-      <c r="AZ47">
-        <v>1.65</v>
-      </c>
-      <c r="BA47">
-        <v>2.85</v>
-      </c>
-      <c r="BB47">
-        <v>1.25</v>
-      </c>
-      <c r="BC47">
-        <v>2.2</v>
-      </c>
-      <c r="BD47">
-        <v>3.58</v>
-      </c>
       <c r="BE47">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="BF47">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="BG47">
         <v>0</v>
@@ -10010,7 +10010,7 @@
         <v>75</v>
       </c>
       <c r="C48" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D48" t="s">
         <v>134</v>
@@ -10195,7 +10195,7 @@
         <v>75</v>
       </c>
       <c r="C49" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="D49" t="s">
         <v>134</v>
@@ -10234,133 +10234,133 @@
         <v>308</v>
       </c>
       <c r="P49">
-        <v>3.22</v>
+        <v>2.32</v>
       </c>
       <c r="Q49">
-        <v>2.93</v>
+        <v>3.25</v>
       </c>
       <c r="R49">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="S49">
-        <v>3.24</v>
+        <v>2.8</v>
       </c>
       <c r="T49">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="U49">
-        <v>3.82</v>
+        <v>3.55</v>
       </c>
       <c r="V49">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="W49">
-        <v>2.44</v>
+        <v>2.73</v>
       </c>
       <c r="X49">
-        <v>3.44</v>
+        <v>2.85</v>
       </c>
       <c r="Y49">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="Z49">
-        <v>9.300000000000001</v>
+        <v>7</v>
       </c>
       <c r="AA49">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AB49">
+        <v>1.01</v>
+      </c>
+      <c r="AC49">
+        <v>1.28</v>
+      </c>
+      <c r="AD49">
+        <v>3.12</v>
+      </c>
+      <c r="AE49">
+        <v>2</v>
+      </c>
+      <c r="AF49">
+        <v>1.78</v>
+      </c>
+      <c r="AG49">
+        <v>3.3</v>
+      </c>
+      <c r="AH49">
+        <v>1.25</v>
+      </c>
+      <c r="AI49">
+        <v>6.5</v>
+      </c>
+      <c r="AJ49">
         <v>1.05</v>
       </c>
-      <c r="AC49">
-        <v>1.48</v>
-      </c>
-      <c r="AD49">
-        <v>2.56</v>
-      </c>
-      <c r="AE49">
-        <v>2.52</v>
-      </c>
-      <c r="AF49">
-        <v>1.55</v>
-      </c>
-      <c r="AG49">
-        <v>4.55</v>
-      </c>
-      <c r="AH49">
+      <c r="AK49">
+        <v>1.75</v>
+      </c>
+      <c r="AL49">
+        <v>2</v>
+      </c>
+      <c r="AM49">
+        <v>1.35</v>
+      </c>
+      <c r="AN49">
+        <v>1.54</v>
+      </c>
+      <c r="AO49">
+        <v>0</v>
+      </c>
+      <c r="AP49">
+        <v>1.33</v>
+      </c>
+      <c r="AQ49">
+        <v>1.61</v>
+      </c>
+      <c r="AR49">
+        <v>2.06</v>
+      </c>
+      <c r="AS49">
+        <v>2.75</v>
+      </c>
+      <c r="AT49">
+        <v>3.8</v>
+      </c>
+      <c r="AU49">
+        <v>2.83</v>
+      </c>
+      <c r="AV49">
+        <v>2.09</v>
+      </c>
+      <c r="AW49">
+        <v>1.66</v>
+      </c>
+      <c r="AX49">
+        <v>1.36</v>
+      </c>
+      <c r="AY49">
+        <v>1.19</v>
+      </c>
+      <c r="AZ49">
+        <v>1.65</v>
+      </c>
+      <c r="BA49">
+        <v>2.85</v>
+      </c>
+      <c r="BB49">
+        <v>1.25</v>
+      </c>
+      <c r="BC49">
+        <v>2.2</v>
+      </c>
+      <c r="BD49">
+        <v>3.58</v>
+      </c>
+      <c r="BE49">
+        <v>1.62</v>
+      </c>
+      <c r="BF49">
         <v>1.13</v>
-      </c>
-      <c r="AI49">
-        <v>9.5</v>
-      </c>
-      <c r="AJ49">
-        <v>1</v>
-      </c>
-      <c r="AK49">
-        <v>2.02</v>
-      </c>
-      <c r="AL49">
-        <v>1.69</v>
-      </c>
-      <c r="AM49">
-        <v>1.38</v>
-      </c>
-      <c r="AN49">
-        <v>1.52</v>
-      </c>
-      <c r="AO49">
-        <v>0</v>
-      </c>
-      <c r="AP49">
-        <v>0</v>
-      </c>
-      <c r="AQ49">
-        <v>0</v>
-      </c>
-      <c r="AR49">
-        <v>0</v>
-      </c>
-      <c r="AS49">
-        <v>0</v>
-      </c>
-      <c r="AT49">
-        <v>0</v>
-      </c>
-      <c r="AU49">
-        <v>0</v>
-      </c>
-      <c r="AV49">
-        <v>0</v>
-      </c>
-      <c r="AW49">
-        <v>0</v>
-      </c>
-      <c r="AX49">
-        <v>0</v>
-      </c>
-      <c r="AY49">
-        <v>0</v>
-      </c>
-      <c r="AZ49">
-        <v>0</v>
-      </c>
-      <c r="BA49">
-        <v>0</v>
-      </c>
-      <c r="BB49">
-        <v>1.33</v>
-      </c>
-      <c r="BC49">
-        <v>2.56</v>
-      </c>
-      <c r="BD49">
-        <v>2.99</v>
-      </c>
-      <c r="BE49">
-        <v>1.44</v>
-      </c>
-      <c r="BF49">
-        <v>1.06</v>
       </c>
       <c r="BG49">
         <v>0</v>
@@ -10604,19 +10604,19 @@
         <v>308</v>
       </c>
       <c r="P51">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="Q51">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R51">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="S51">
-        <v>3.23</v>
+        <v>3.74</v>
       </c>
       <c r="T51">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="U51">
         <v>2.83</v>
@@ -10625,7 +10625,7 @@
         <v>1.42</v>
       </c>
       <c r="W51">
-        <v>2.95</v>
+        <v>2.65</v>
       </c>
       <c r="X51">
         <v>2.75</v>
@@ -10649,31 +10649,31 @@
         <v>3.18</v>
       </c>
       <c r="AE51">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AF51">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AG51">
         <v>3.41</v>
       </c>
       <c r="AH51">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AI51">
-        <v>5.75</v>
+        <v>6.3</v>
       </c>
       <c r="AJ51">
         <v>1.06</v>
       </c>
       <c r="AK51">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AL51">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AM51">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AN51">
         <v>1.37</v>
@@ -10682,43 +10682,43 @@
         <v>0</v>
       </c>
       <c r="AP51">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AQ51">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AR51">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AS51">
-        <v>2.18</v>
+        <v>2.27</v>
       </c>
       <c r="AT51">
-        <v>2.8</v>
+        <v>3.04</v>
       </c>
       <c r="AU51">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AV51">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="AW51">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AX51">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="AY51">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="AZ51">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="BA51">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="BB51">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BC51">
         <v>2.14</v>
@@ -10750,7 +10750,7 @@
         <v>77</v>
       </c>
       <c r="C52" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="D52" t="s">
         <v>134</v>
@@ -10789,133 +10789,133 @@
         <v>308</v>
       </c>
       <c r="P52">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="Q52">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="R52">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="S52">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="T52">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="U52">
+        <v>5.13</v>
+      </c>
+      <c r="V52">
+        <v>1.24</v>
+      </c>
+      <c r="W52">
+        <v>3.5</v>
+      </c>
+      <c r="X52">
+        <v>2.25</v>
+      </c>
+      <c r="Y52">
+        <v>1.6</v>
+      </c>
+      <c r="Z52">
         <v>5</v>
       </c>
-      <c r="V52">
-        <v>1.5</v>
-      </c>
-      <c r="W52">
-        <v>2.5</v>
-      </c>
-      <c r="X52">
-        <v>2.95</v>
-      </c>
-      <c r="Y52">
-        <v>1.3</v>
-      </c>
-      <c r="Z52">
-        <v>8</v>
-      </c>
       <c r="AA52">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="AB52">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC52">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="AD52">
-        <v>2.83</v>
+        <v>4.95</v>
       </c>
       <c r="AE52">
-        <v>2.15</v>
+        <v>1.47</v>
       </c>
       <c r="AF52">
-        <v>1.67</v>
+        <v>2.38</v>
       </c>
       <c r="AG52">
-        <v>3.82</v>
+        <v>2.35</v>
       </c>
       <c r="AH52">
-        <v>1.2</v>
+        <v>1.59</v>
       </c>
       <c r="AI52">
-        <v>7</v>
+        <v>3.88</v>
       </c>
       <c r="AJ52">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AK52">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AL52">
-        <v>1.73</v>
+        <v>2.26</v>
       </c>
       <c r="AM52">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AN52">
-        <v>1.94</v>
+        <v>2.35</v>
       </c>
       <c r="AO52">
         <v>0</v>
       </c>
       <c r="AP52">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="AQ52">
-        <v>1.62</v>
+        <v>1.32</v>
       </c>
       <c r="AR52">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AS52">
-        <v>2.55</v>
+        <v>2.01</v>
       </c>
       <c r="AT52">
-        <v>3.3</v>
+        <v>2.56</v>
       </c>
       <c r="AU52">
-        <v>2.85</v>
+        <v>4.15</v>
       </c>
       <c r="AV52">
-        <v>2.14</v>
+        <v>2.88</v>
       </c>
       <c r="AW52">
-        <v>1.71</v>
+        <v>2.13</v>
       </c>
       <c r="AX52">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AY52">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="AZ52">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="BA52">
-        <v>2.85</v>
+        <v>3.62</v>
       </c>
       <c r="BB52">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="BC52">
-        <v>2.25</v>
+        <v>1.74</v>
       </c>
       <c r="BD52">
-        <v>3.34</v>
+        <v>5.2</v>
       </c>
       <c r="BE52">
-        <v>1.55</v>
+        <v>2.02</v>
       </c>
       <c r="BF52">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="BG52">
         <v>0</v>
@@ -10935,10 +10935,10 @@
         <v>77</v>
       </c>
       <c r="C53" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="D53" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E53" t="s">
         <v>188</v>
@@ -10974,133 +10974,133 @@
         <v>308</v>
       </c>
       <c r="P53">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="Q53">
-        <v>3.67</v>
+        <v>2.9</v>
       </c>
       <c r="R53">
-        <v>4.35</v>
+        <v>3.1</v>
       </c>
       <c r="S53">
-        <v>2.25</v>
+        <v>3.04</v>
       </c>
       <c r="T53">
-        <v>2.17</v>
+        <v>1.8</v>
       </c>
       <c r="U53">
-        <v>5.23</v>
+        <v>4.53</v>
       </c>
       <c r="V53">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="W53">
-        <v>2.89</v>
+        <v>2.22</v>
       </c>
       <c r="X53">
-        <v>2.69</v>
+        <v>3.48</v>
       </c>
       <c r="Y53">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="Z53">
-        <v>6.45</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA53">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="AB53">
         <v>1.06</v>
       </c>
       <c r="AC53">
-        <v>1.21</v>
+        <v>1.47</v>
       </c>
       <c r="AD53">
-        <v>3.44</v>
+        <v>2.49</v>
       </c>
       <c r="AE53">
-        <v>1.84</v>
+        <v>2.58</v>
       </c>
       <c r="AF53">
-        <v>1.94</v>
+        <v>1.45</v>
       </c>
       <c r="AG53">
-        <v>3.07</v>
+        <v>4.6</v>
       </c>
       <c r="AH53">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AI53">
-        <v>5.84</v>
+        <v>10.5</v>
       </c>
       <c r="AJ53">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="AK53">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="AL53">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="AM53">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AN53">
-        <v>2.09</v>
+        <v>1.52</v>
       </c>
       <c r="AO53">
         <v>0</v>
       </c>
       <c r="AP53">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AQ53">
+        <v>1.76</v>
+      </c>
+      <c r="AR53">
+        <v>2.26</v>
+      </c>
+      <c r="AS53">
+        <v>3.08</v>
+      </c>
+      <c r="AT53">
+        <v>3.65</v>
+      </c>
+      <c r="AU53">
+        <v>2.52</v>
+      </c>
+      <c r="AV53">
+        <v>1.91</v>
+      </c>
+      <c r="AW53">
+        <v>1.51</v>
+      </c>
+      <c r="AX53">
         <v>1.28</v>
       </c>
-      <c r="AR53">
-        <v>1.48</v>
-      </c>
-      <c r="AS53">
-        <v>1.75</v>
-      </c>
-      <c r="AT53">
-        <v>2.12</v>
-      </c>
-      <c r="AU53">
-        <v>0</v>
-      </c>
-      <c r="AV53">
-        <v>3.25</v>
-      </c>
-      <c r="AW53">
-        <v>2.43</v>
-      </c>
-      <c r="AX53">
-        <v>1.94</v>
-      </c>
       <c r="AY53">
-        <v>1.62</v>
+        <v>1.23</v>
       </c>
       <c r="AZ53">
-        <v>1.4</v>
+        <v>1.87</v>
       </c>
       <c r="BA53">
-        <v>3.3</v>
+        <v>2.47</v>
       </c>
       <c r="BB53">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="BC53">
-        <v>2.04</v>
+        <v>2.53</v>
       </c>
       <c r="BD53">
-        <v>3.98</v>
+        <v>2.96</v>
       </c>
       <c r="BE53">
-        <v>1.73</v>
+        <v>1.43</v>
       </c>
       <c r="BF53">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="BG53">
         <v>0</v>
@@ -11120,7 +11120,7 @@
         <v>77</v>
       </c>
       <c r="C54" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="D54" t="s">
         <v>134</v>
@@ -11159,133 +11159,133 @@
         <v>308</v>
       </c>
       <c r="P54">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="Q54">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="R54">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="S54">
-        <v>1.91</v>
+        <v>2.36</v>
       </c>
       <c r="T54">
-        <v>2.4</v>
+        <v>1.99</v>
       </c>
       <c r="U54">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="V54">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="W54">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="X54">
-        <v>2.25</v>
+        <v>3.08</v>
       </c>
       <c r="Y54">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="Z54">
-        <v>5</v>
+        <v>7.9</v>
       </c>
       <c r="AA54">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="AB54">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC54">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AD54">
-        <v>4.95</v>
+        <v>2.83</v>
       </c>
       <c r="AE54">
-        <v>1.48</v>
+        <v>2.11</v>
       </c>
       <c r="AF54">
-        <v>2.4</v>
+        <v>1.65</v>
       </c>
       <c r="AG54">
-        <v>2.35</v>
+        <v>3.72</v>
       </c>
       <c r="AH54">
-        <v>1.59</v>
+        <v>1.2</v>
       </c>
       <c r="AI54">
-        <v>3.88</v>
+        <v>7.4</v>
       </c>
       <c r="AJ54">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="AK54">
-        <v>1.57</v>
+        <v>1.97</v>
       </c>
       <c r="AL54">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="AM54">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AN54">
-        <v>2.25</v>
+        <v>1.94</v>
       </c>
       <c r="AO54">
         <v>0</v>
       </c>
       <c r="AP54">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AQ54">
-        <v>1.34</v>
+        <v>1.67</v>
       </c>
       <c r="AR54">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="AS54">
-        <v>2.05</v>
+        <v>2.83</v>
       </c>
       <c r="AT54">
-        <v>2.67</v>
+        <v>3.3</v>
       </c>
       <c r="AU54">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="AV54">
-        <v>2.78</v>
+        <v>2.02</v>
       </c>
       <c r="AW54">
-        <v>2.08</v>
+        <v>1.58</v>
       </c>
       <c r="AX54">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AY54">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AZ54">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="BA54">
-        <v>3.55</v>
+        <v>3.72</v>
       </c>
       <c r="BB54">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="BC54">
-        <v>1.74</v>
+        <v>2.28</v>
       </c>
       <c r="BD54">
-        <v>5.4</v>
+        <v>3.34</v>
       </c>
       <c r="BE54">
-        <v>2.02</v>
+        <v>1.55</v>
       </c>
       <c r="BF54">
-        <v>1.32</v>
+        <v>1.1</v>
       </c>
       <c r="BG54">
         <v>0</v>
@@ -11305,10 +11305,10 @@
         <v>77</v>
       </c>
       <c r="C55" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D55" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E55" t="s">
         <v>190</v>
@@ -11344,133 +11344,133 @@
         <v>308</v>
       </c>
       <c r="P55">
-        <v>2.13</v>
+        <v>1.67</v>
       </c>
       <c r="Q55">
-        <v>3.41</v>
+        <v>3.5</v>
       </c>
       <c r="R55">
-        <v>3.07</v>
+        <v>4.4</v>
       </c>
       <c r="S55">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="T55">
-        <v>2.07</v>
+        <v>2.17</v>
       </c>
       <c r="U55">
-        <v>3.85</v>
+        <v>5.3</v>
       </c>
       <c r="V55">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W55">
+        <v>2.89</v>
+      </c>
+      <c r="X55">
         <v>2.69</v>
       </c>
-      <c r="X55">
-        <v>3</v>
-      </c>
       <c r="Y55">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="Z55">
-        <v>7</v>
+        <v>6.45</v>
       </c>
       <c r="AA55">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AB55">
         <v>1.01</v>
       </c>
       <c r="AC55">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AD55">
-        <v>2.88</v>
+        <v>3.44</v>
       </c>
       <c r="AE55">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AF55">
-        <v>1.69</v>
+        <v>1.93</v>
       </c>
       <c r="AG55">
-        <v>3.84</v>
+        <v>2.94</v>
       </c>
       <c r="AH55">
+        <v>1.31</v>
+      </c>
+      <c r="AI55">
+        <v>5.55</v>
+      </c>
+      <c r="AJ55">
+        <v>1.08</v>
+      </c>
+      <c r="AK55">
+        <v>1.78</v>
+      </c>
+      <c r="AL55">
+        <v>1.95</v>
+      </c>
+      <c r="AM55">
+        <v>1.25</v>
+      </c>
+      <c r="AN55">
+        <v>2.09</v>
+      </c>
+      <c r="AO55">
+        <v>0</v>
+      </c>
+      <c r="AP55">
+        <v>1.11</v>
+      </c>
+      <c r="AQ55">
+        <v>1.25</v>
+      </c>
+      <c r="AR55">
+        <v>1.61</v>
+      </c>
+      <c r="AS55">
+        <v>1.81</v>
+      </c>
+      <c r="AT55">
+        <v>2.27</v>
+      </c>
+      <c r="AU55">
+        <v>4.9</v>
+      </c>
+      <c r="AV55">
+        <v>3.28</v>
+      </c>
+      <c r="AW55">
+        <v>2.41</v>
+      </c>
+      <c r="AX55">
+        <v>1.87</v>
+      </c>
+      <c r="AY55">
+        <v>1.52</v>
+      </c>
+      <c r="AZ55">
+        <v>1.4</v>
+      </c>
+      <c r="BA55">
+        <v>3.58</v>
+      </c>
+      <c r="BB55">
         <v>1.19</v>
       </c>
-      <c r="AI55">
-        <v>7.5</v>
-      </c>
-      <c r="AJ55">
-        <v>1.03</v>
-      </c>
-      <c r="AK55">
-        <v>1.91</v>
-      </c>
-      <c r="AL55">
-        <v>1.85</v>
-      </c>
-      <c r="AM55">
-        <v>1.28</v>
-      </c>
-      <c r="AN55">
-        <v>1.66</v>
-      </c>
-      <c r="AO55">
-        <v>0</v>
-      </c>
-      <c r="AP55">
-        <v>0</v>
-      </c>
-      <c r="AQ55">
-        <v>0</v>
-      </c>
-      <c r="AR55">
-        <v>0</v>
-      </c>
-      <c r="AS55">
-        <v>0</v>
-      </c>
-      <c r="AT55">
-        <v>0</v>
-      </c>
-      <c r="AU55">
-        <v>0</v>
-      </c>
-      <c r="AV55">
-        <v>0</v>
-      </c>
-      <c r="AW55">
-        <v>0</v>
-      </c>
-      <c r="AX55">
-        <v>0</v>
-      </c>
-      <c r="AY55">
-        <v>0</v>
-      </c>
-      <c r="AZ55">
-        <v>0</v>
-      </c>
-      <c r="BA55">
-        <v>0</v>
-      </c>
-      <c r="BB55">
-        <v>1.26</v>
-      </c>
       <c r="BC55">
-        <v>2.31</v>
+        <v>2.04</v>
       </c>
       <c r="BD55">
-        <v>3.42</v>
+        <v>3.98</v>
       </c>
       <c r="BE55">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="BF55">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="BG55">
         <v>0</v>
@@ -11490,7 +11490,7 @@
         <v>77</v>
       </c>
       <c r="C56" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D56" t="s">
         <v>134</v>
@@ -11529,133 +11529,133 @@
         <v>308</v>
       </c>
       <c r="P56">
-        <v>2.61</v>
+        <v>1.75</v>
       </c>
       <c r="Q56">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="R56">
-        <v>2.52</v>
+        <v>4.2</v>
       </c>
       <c r="S56">
-        <v>3.25</v>
+        <v>2.38</v>
       </c>
       <c r="T56">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="U56">
-        <v>3.01</v>
+        <v>5.08</v>
       </c>
       <c r="V56">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W56">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="X56">
-        <v>3.16</v>
+        <v>2.9</v>
       </c>
       <c r="Y56">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="Z56">
-        <v>8.699999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="AA56">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AB56">
         <v>1.01</v>
       </c>
       <c r="AC56">
+        <v>1.28</v>
+      </c>
+      <c r="AD56">
+        <v>3.08</v>
+      </c>
+      <c r="AE56">
+        <v>2.01</v>
+      </c>
+      <c r="AF56">
+        <v>1.76</v>
+      </c>
+      <c r="AG56">
+        <v>3.34</v>
+      </c>
+      <c r="AH56">
+        <v>1.24</v>
+      </c>
+      <c r="AI56">
+        <v>6.65</v>
+      </c>
+      <c r="AJ56">
+        <v>1.05</v>
+      </c>
+      <c r="AK56">
+        <v>1.86</v>
+      </c>
+      <c r="AL56">
+        <v>1.84</v>
+      </c>
+      <c r="AM56">
+        <v>1.26</v>
+      </c>
+      <c r="AN56">
+        <v>1.94</v>
+      </c>
+      <c r="AO56">
+        <v>0</v>
+      </c>
+      <c r="AP56">
+        <v>1.2</v>
+      </c>
+      <c r="AQ56">
+        <v>1.42</v>
+      </c>
+      <c r="AR56">
+        <v>1.96</v>
+      </c>
+      <c r="AS56">
+        <v>2.18</v>
+      </c>
+      <c r="AT56">
+        <v>2.87</v>
+      </c>
+      <c r="AU56">
+        <v>3.66</v>
+      </c>
+      <c r="AV56">
+        <v>2.56</v>
+      </c>
+      <c r="AW56">
+        <v>1.97</v>
+      </c>
+      <c r="AX56">
+        <v>1.6</v>
+      </c>
+      <c r="AY56">
         <v>1.33</v>
       </c>
-      <c r="AD56">
-        <v>2.81</v>
-      </c>
-      <c r="AE56">
-        <v>2.19</v>
-      </c>
-      <c r="AF56">
-        <v>1.64</v>
-      </c>
-      <c r="AG56">
-        <v>4</v>
-      </c>
-      <c r="AH56">
-        <v>1.17</v>
-      </c>
-      <c r="AI56">
-        <v>8.5</v>
-      </c>
-      <c r="AJ56">
-        <v>1.01</v>
-      </c>
-      <c r="AK56">
-        <v>1.8</v>
-      </c>
-      <c r="AL56">
-        <v>1.83</v>
-      </c>
-      <c r="AM56">
-        <v>1.3</v>
-      </c>
-      <c r="AN56">
-        <v>1.37</v>
-      </c>
-      <c r="AO56">
-        <v>0</v>
-      </c>
-      <c r="AP56">
-        <v>1.27</v>
-      </c>
-      <c r="AQ56">
-        <v>1.54</v>
-      </c>
-      <c r="AR56">
-        <v>2.2</v>
-      </c>
-      <c r="AS56">
-        <v>2.46</v>
-      </c>
-      <c r="AT56">
-        <v>3.35</v>
-      </c>
-      <c r="AU56">
-        <v>3.14</v>
-      </c>
-      <c r="AV56">
-        <v>2.27</v>
-      </c>
-      <c r="AW56">
-        <v>1.79</v>
-      </c>
-      <c r="AX56">
-        <v>1.46</v>
-      </c>
-      <c r="AY56">
-        <v>1.24</v>
-      </c>
       <c r="AZ56">
-        <v>2.92</v>
+        <v>1.48</v>
       </c>
       <c r="BA56">
-        <v>1.66</v>
+        <v>3.6</v>
       </c>
       <c r="BB56">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="BC56">
         <v>2.2</v>
       </c>
       <c r="BD56">
-        <v>3.35</v>
+        <v>3.58</v>
       </c>
       <c r="BE56">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="BF56">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="BG56">
         <v>0</v>
@@ -11675,7 +11675,7 @@
         <v>77</v>
       </c>
       <c r="C57" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D57" t="s">
         <v>134</v>
@@ -11714,133 +11714,133 @@
         <v>308</v>
       </c>
       <c r="P57">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="Q57">
-        <v>4.35</v>
+        <v>3.2</v>
       </c>
       <c r="R57">
-        <v>3.47</v>
+        <v>3</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="T57">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U57">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="V57">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W57">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="X57">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Y57">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z57">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC57">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE57">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AF57">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG57">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AH57">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI57">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AJ57">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK57">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL57">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM57">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN57">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AO57">
         <v>0</v>
       </c>
       <c r="AP57">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AQ57">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AR57">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AS57">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="AT57">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="AU57">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AV57">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AW57">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AX57">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AY57">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AZ57">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BA57">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="BB57">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC57">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BD57">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="BE57">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF57">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG57">
         <v>0</v>
@@ -11860,7 +11860,7 @@
         <v>77</v>
       </c>
       <c r="C58" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="D58" t="s">
         <v>134</v>
@@ -11899,133 +11899,133 @@
         <v>308</v>
       </c>
       <c r="P58">
-        <v>2.21</v>
+        <v>7.95</v>
       </c>
       <c r="Q58">
-        <v>3.52</v>
+        <v>4.7</v>
       </c>
       <c r="R58">
-        <v>2.96</v>
+        <v>1.33</v>
       </c>
       <c r="S58">
-        <v>2.5</v>
+        <v>7.13</v>
       </c>
       <c r="T58">
-        <v>2.19</v>
+        <v>2.55</v>
       </c>
       <c r="U58">
-        <v>3.58</v>
+        <v>1.81</v>
       </c>
       <c r="V58">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W58">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="X58">
+        <v>2.18</v>
+      </c>
+      <c r="Y58">
+        <v>1.6</v>
+      </c>
+      <c r="Z58">
+        <v>4.55</v>
+      </c>
+      <c r="AA58">
+        <v>1.15</v>
+      </c>
+      <c r="AB58">
+        <v>0</v>
+      </c>
+      <c r="AC58">
+        <v>1.16</v>
+      </c>
+      <c r="AD58">
+        <v>4.2</v>
+      </c>
+      <c r="AE58">
+        <v>1.52</v>
+      </c>
+      <c r="AF58">
         <v>2.3</v>
       </c>
-      <c r="Y58">
-        <v>1.5</v>
-      </c>
-      <c r="Z58">
-        <v>5.55</v>
-      </c>
-      <c r="AA58">
-        <v>1.08</v>
-      </c>
-      <c r="AB58">
-        <v>1.04</v>
-      </c>
-      <c r="AC58">
-        <v>1.2</v>
-      </c>
-      <c r="AD58">
-        <v>4.1</v>
-      </c>
-      <c r="AE58">
-        <v>1.66</v>
-      </c>
-      <c r="AF58">
-        <v>2.16</v>
-      </c>
       <c r="AG58">
-        <v>2.63</v>
+        <v>2.29</v>
       </c>
       <c r="AH58">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AI58">
-        <v>4.55</v>
+        <v>4</v>
       </c>
       <c r="AJ58">
+        <v>1.21</v>
+      </c>
+      <c r="AK58">
+        <v>1.9</v>
+      </c>
+      <c r="AL58">
+        <v>1.9</v>
+      </c>
+      <c r="AM58">
         <v>1.13</v>
       </c>
-      <c r="AK58">
-        <v>1.55</v>
-      </c>
-      <c r="AL58">
-        <v>2.35</v>
-      </c>
-      <c r="AM58">
-        <v>1.26</v>
-      </c>
       <c r="AN58">
-        <v>1.61</v>
+        <v>1.05</v>
       </c>
       <c r="AO58">
         <v>0</v>
       </c>
       <c r="AP58">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ58">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AR58">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AS58">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AT58">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AU58">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AV58">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AW58">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AX58">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AY58">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ58">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="BA58">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="BB58">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC58">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="BD58">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="BE58">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="BF58">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG58">
         <v>0</v>
@@ -12087,130 +12087,130 @@
         <v>1.75</v>
       </c>
       <c r="Q59">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="R59">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="S59">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T59">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U59">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="V59">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W59">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="X59">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y59">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z59">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA59">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB59">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC59">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD59">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AE59">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF59">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG59">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AH59">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI59">
-        <v>6.65</v>
+        <v>0</v>
       </c>
       <c r="AJ59">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK59">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL59">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM59">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN59">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AO59">
         <v>0</v>
       </c>
       <c r="AP59">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AQ59">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AR59">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AS59">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AT59">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AU59">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="AV59">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AW59">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AX59">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AY59">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ59">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="BA59">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="BB59">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC59">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD59">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BE59">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF59">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG59">
         <v>0</v>
@@ -12230,7 +12230,7 @@
         <v>77</v>
       </c>
       <c r="C60" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="D60" t="s">
         <v>134</v>
@@ -12269,133 +12269,133 @@
         <v>308</v>
       </c>
       <c r="P60">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="Q60">
-        <v>2.99</v>
+        <v>3.4</v>
       </c>
       <c r="R60">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="S60">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="T60">
-        <v>1.85</v>
+        <v>2.19</v>
       </c>
       <c r="U60">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="V60">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="W60">
-        <v>2.22</v>
+        <v>3.16</v>
       </c>
       <c r="X60">
-        <v>3.48</v>
+        <v>2.41</v>
       </c>
       <c r="Y60">
+        <v>1.49</v>
+      </c>
+      <c r="Z60">
+        <v>5.55</v>
+      </c>
+      <c r="AA60">
+        <v>1.08</v>
+      </c>
+      <c r="AB60">
+        <v>1.01</v>
+      </c>
+      <c r="AC60">
+        <v>1.16</v>
+      </c>
+      <c r="AD60">
+        <v>4.1</v>
+      </c>
+      <c r="AE60">
+        <v>1.66</v>
+      </c>
+      <c r="AF60">
+        <v>2.16</v>
+      </c>
+      <c r="AG60">
+        <v>2.52</v>
+      </c>
+      <c r="AH60">
+        <v>1.41</v>
+      </c>
+      <c r="AI60">
+        <v>4.55</v>
+      </c>
+      <c r="AJ60">
+        <v>1.13</v>
+      </c>
+      <c r="AK60">
+        <v>1.53</v>
+      </c>
+      <c r="AL60">
+        <v>2.34</v>
+      </c>
+      <c r="AM60">
+        <v>1.26</v>
+      </c>
+      <c r="AN60">
+        <v>1.61</v>
+      </c>
+      <c r="AO60">
+        <v>0</v>
+      </c>
+      <c r="AP60">
+        <v>1.16</v>
+      </c>
+      <c r="AQ60">
+        <v>1.35</v>
+      </c>
+      <c r="AR60">
+        <v>1.63</v>
+      </c>
+      <c r="AS60">
+        <v>2.03</v>
+      </c>
+      <c r="AT60">
+        <v>2.62</v>
+      </c>
+      <c r="AU60">
+        <v>4.05</v>
+      </c>
+      <c r="AV60">
+        <v>2.79</v>
+      </c>
+      <c r="AW60">
+        <v>2.11</v>
+      </c>
+      <c r="AX60">
+        <v>1.65</v>
+      </c>
+      <c r="AY60">
+        <v>1.38</v>
+      </c>
+      <c r="AZ60">
+        <v>1.78</v>
+      </c>
+      <c r="BA60">
+        <v>2.58</v>
+      </c>
+      <c r="BB60">
+        <v>1.14</v>
+      </c>
+      <c r="BC60">
+        <v>1.87</v>
+      </c>
+      <c r="BD60">
+        <v>4.45</v>
+      </c>
+      <c r="BE60">
+        <v>1.87</v>
+      </c>
+      <c r="BF60">
         <v>1.22</v>
-      </c>
-      <c r="Z60">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AA60">
-        <v>1.02</v>
-      </c>
-      <c r="AB60">
-        <v>1.06</v>
-      </c>
-      <c r="AC60">
-        <v>1.49</v>
-      </c>
-      <c r="AD60">
-        <v>2.49</v>
-      </c>
-      <c r="AE60">
-        <v>2.6</v>
-      </c>
-      <c r="AF60">
-        <v>1.45</v>
-      </c>
-      <c r="AG60">
-        <v>4.7</v>
-      </c>
-      <c r="AH60">
-        <v>1.13</v>
-      </c>
-      <c r="AI60">
-        <v>9.5</v>
-      </c>
-      <c r="AJ60">
-        <v>1.01</v>
-      </c>
-      <c r="AK60">
-        <v>2.1</v>
-      </c>
-      <c r="AL60">
-        <v>1.66</v>
-      </c>
-      <c r="AM60">
-        <v>1.34</v>
-      </c>
-      <c r="AN60">
-        <v>1.52</v>
-      </c>
-      <c r="AO60">
-        <v>0</v>
-      </c>
-      <c r="AP60">
-        <v>1.4</v>
-      </c>
-      <c r="AQ60">
-        <v>1.68</v>
-      </c>
-      <c r="AR60">
-        <v>2.1</v>
-      </c>
-      <c r="AS60">
-        <v>2.75</v>
-      </c>
-      <c r="AT60">
-        <v>3.65</v>
-      </c>
-      <c r="AU60">
-        <v>2.65</v>
-      </c>
-      <c r="AV60">
-        <v>2.04</v>
-      </c>
-      <c r="AW60">
-        <v>1.64</v>
-      </c>
-      <c r="AX60">
-        <v>1.38</v>
-      </c>
-      <c r="AY60">
-        <v>1.23</v>
-      </c>
-      <c r="AZ60">
-        <v>1.83</v>
-      </c>
-      <c r="BA60">
-        <v>2.14</v>
-      </c>
-      <c r="BB60">
-        <v>1.32</v>
-      </c>
-      <c r="BC60">
-        <v>2.63</v>
-      </c>
-      <c r="BD60">
-        <v>2.96</v>
-      </c>
-      <c r="BE60">
-        <v>1.43</v>
-      </c>
-      <c r="BF60">
-        <v>1.06</v>
       </c>
       <c r="BG60">
         <v>0</v>
@@ -12460,16 +12460,16 @@
         <v>5</v>
       </c>
       <c r="R61">
-        <v>7.2</v>
+        <v>5.75</v>
       </c>
       <c r="S61">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="T61">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="U61">
-        <v>5.9</v>
+        <v>5.95</v>
       </c>
       <c r="V61">
         <v>1.17</v>
@@ -12493,7 +12493,7 @@
         <v>1.01</v>
       </c>
       <c r="AC61">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AD61">
         <v>7</v>
@@ -12502,7 +12502,7 @@
         <v>1.28</v>
       </c>
       <c r="AF61">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="AG61">
         <v>1.85</v>
@@ -12517,10 +12517,10 @@
         <v>1.38</v>
       </c>
       <c r="AK61">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="AL61">
-        <v>2.43</v>
+        <v>2.39</v>
       </c>
       <c r="AM61">
         <v>1.15</v>
@@ -12532,49 +12532,49 @@
         <v>0</v>
       </c>
       <c r="AP61">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AQ61">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AR61">
-        <v>1.49</v>
+        <v>1.69</v>
       </c>
       <c r="AS61">
+        <v>1.9</v>
+      </c>
+      <c r="AT61">
+        <v>2.41</v>
+      </c>
+      <c r="AU61">
+        <v>4.45</v>
+      </c>
+      <c r="AV61">
+        <v>3.05</v>
+      </c>
+      <c r="AW61">
+        <v>2.24</v>
+      </c>
+      <c r="AX61">
         <v>1.78</v>
       </c>
-      <c r="AT61">
-        <v>2.2</v>
-      </c>
-      <c r="AU61">
-        <v>0</v>
-      </c>
-      <c r="AV61">
-        <v>3.2</v>
-      </c>
-      <c r="AW61">
-        <v>2.38</v>
-      </c>
-      <c r="AX61">
-        <v>1.9</v>
-      </c>
       <c r="AY61">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AZ61">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="BA61">
-        <v>4.35</v>
+        <v>4.95</v>
       </c>
       <c r="BB61">
         <v>1.07</v>
       </c>
       <c r="BC61">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="BD61">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BE61">
         <v>2.41</v>
@@ -12600,7 +12600,7 @@
         <v>77</v>
       </c>
       <c r="C62" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="D62" t="s">
         <v>134</v>
@@ -12639,133 +12639,133 @@
         <v>308</v>
       </c>
       <c r="P62">
-        <v>7.95</v>
+        <v>2.61</v>
       </c>
       <c r="Q62">
-        <v>4.7</v>
+        <v>3.34</v>
       </c>
       <c r="R62">
+        <v>2.52</v>
+      </c>
+      <c r="S62">
+        <v>3.7</v>
+      </c>
+      <c r="T62">
+        <v>2.01</v>
+      </c>
+      <c r="U62">
+        <v>3.01</v>
+      </c>
+      <c r="V62">
+        <v>1.42</v>
+      </c>
+      <c r="W62">
+        <v>2.62</v>
+      </c>
+      <c r="X62">
+        <v>3.16</v>
+      </c>
+      <c r="Y62">
+        <v>1.3</v>
+      </c>
+      <c r="Z62">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AA62">
+        <v>1.01</v>
+      </c>
+      <c r="AB62">
+        <v>1.01</v>
+      </c>
+      <c r="AC62">
         <v>1.33</v>
       </c>
-      <c r="S62">
-        <v>7.13</v>
-      </c>
-      <c r="T62">
-        <v>2.55</v>
-      </c>
-      <c r="U62">
-        <v>1.81</v>
-      </c>
-      <c r="V62">
-        <v>0</v>
-      </c>
-      <c r="W62">
-        <v>0</v>
-      </c>
-      <c r="X62">
-        <v>2.18</v>
-      </c>
-      <c r="Y62">
-        <v>1.6</v>
-      </c>
-      <c r="Z62">
-        <v>4.55</v>
-      </c>
-      <c r="AA62">
-        <v>1.15</v>
-      </c>
-      <c r="AB62">
-        <v>0</v>
-      </c>
-      <c r="AC62">
-        <v>1.16</v>
-      </c>
       <c r="AD62">
-        <v>4.2</v>
+        <v>2.81</v>
       </c>
       <c r="AE62">
-        <v>1.52</v>
+        <v>2.19</v>
       </c>
       <c r="AF62">
-        <v>2.3</v>
+        <v>1.64</v>
       </c>
       <c r="AG62">
-        <v>2.29</v>
+        <v>4.02</v>
       </c>
       <c r="AH62">
-        <v>1.53</v>
+        <v>1.17</v>
       </c>
       <c r="AI62">
-        <v>4</v>
+        <v>8.5</v>
       </c>
       <c r="AJ62">
+        <v>1.01</v>
+      </c>
+      <c r="AK62">
+        <v>1.87</v>
+      </c>
+      <c r="AL62">
+        <v>1.83</v>
+      </c>
+      <c r="AM62">
+        <v>1.3</v>
+      </c>
+      <c r="AN62">
+        <v>1.37</v>
+      </c>
+      <c r="AO62">
+        <v>0</v>
+      </c>
+      <c r="AP62">
+        <v>1.3</v>
+      </c>
+      <c r="AQ62">
+        <v>1.59</v>
+      </c>
+      <c r="AR62">
+        <v>1.98</v>
+      </c>
+      <c r="AS62">
+        <v>2.56</v>
+      </c>
+      <c r="AT62">
+        <v>3.54</v>
+      </c>
+      <c r="AU62">
+        <v>3</v>
+      </c>
+      <c r="AV62">
+        <v>2.19</v>
+      </c>
+      <c r="AW62">
+        <v>1.74</v>
+      </c>
+      <c r="AX62">
+        <v>1.42</v>
+      </c>
+      <c r="AY62">
         <v>1.21</v>
       </c>
-      <c r="AK62">
-        <v>1.9</v>
-      </c>
-      <c r="AL62">
-        <v>1.9</v>
-      </c>
-      <c r="AM62">
-        <v>1.13</v>
-      </c>
-      <c r="AN62">
-        <v>1.05</v>
-      </c>
-      <c r="AO62">
-        <v>0</v>
-      </c>
-      <c r="AP62">
-        <v>0</v>
-      </c>
-      <c r="AQ62">
-        <v>0</v>
-      </c>
-      <c r="AR62">
-        <v>0</v>
-      </c>
-      <c r="AS62">
-        <v>0</v>
-      </c>
-      <c r="AT62">
-        <v>0</v>
-      </c>
-      <c r="AU62">
-        <v>0</v>
-      </c>
-      <c r="AV62">
-        <v>0</v>
-      </c>
-      <c r="AW62">
-        <v>0</v>
-      </c>
-      <c r="AX62">
-        <v>0</v>
-      </c>
-      <c r="AY62">
-        <v>0</v>
-      </c>
       <c r="AZ62">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BA62">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BB62">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC62">
-        <v>1.75</v>
+        <v>2.36</v>
       </c>
       <c r="BD62">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BE62">
-        <v>1.85</v>
+        <v>1.51</v>
       </c>
       <c r="BF62">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG62">
         <v>0</v>
@@ -12824,13 +12824,13 @@
         <v>308</v>
       </c>
       <c r="P63">
-        <v>2.42</v>
+        <v>2.91</v>
       </c>
       <c r="Q63">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="R63">
-        <v>2.65</v>
+        <v>2.28</v>
       </c>
       <c r="S63">
         <v>3.02</v>
@@ -12839,13 +12839,13 @@
         <v>2.07</v>
       </c>
       <c r="U63">
-        <v>3.1</v>
+        <v>3.36</v>
       </c>
       <c r="V63">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W63">
-        <v>3.07</v>
+        <v>2.84</v>
       </c>
       <c r="X63">
         <v>2.69</v>
@@ -12854,13 +12854,13 @@
         <v>1.4</v>
       </c>
       <c r="Z63">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="AA63">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AB63">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AC63">
         <v>1.23</v>
@@ -12872,7 +12872,7 @@
         <v>1.85</v>
       </c>
       <c r="AF63">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="AG63">
         <v>2.92</v>
@@ -12884,19 +12884,19 @@
         <v>5.55</v>
       </c>
       <c r="AJ63">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AK63">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="AL63">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="AM63">
         <v>1.3</v>
       </c>
       <c r="AN63">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AO63">
         <v>0</v>
@@ -12905,10 +12905,10 @@
         <v>0</v>
       </c>
       <c r="AQ63">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AR63">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AS63">
         <v>1.84</v>
@@ -12920,10 +12920,10 @@
         <v>0</v>
       </c>
       <c r="AV63">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AW63">
-        <v>2.48</v>
+        <v>2.34</v>
       </c>
       <c r="AX63">
         <v>1.84</v>
@@ -12970,10 +12970,10 @@
         <v>79</v>
       </c>
       <c r="C64" t="s">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="D64" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E64" t="s">
         <v>199</v>
@@ -13009,133 +13009,133 @@
         <v>308</v>
       </c>
       <c r="P64">
-        <v>2.94</v>
+        <v>2.3</v>
       </c>
       <c r="Q64">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R64">
-        <v>2.21</v>
+        <v>3</v>
       </c>
       <c r="S64">
-        <v>3.35</v>
+        <v>2.96</v>
       </c>
       <c r="T64">
-        <v>2.23</v>
+        <v>2.04</v>
       </c>
       <c r="U64">
+        <v>3.69</v>
+      </c>
+      <c r="V64">
+        <v>1.41</v>
+      </c>
+      <c r="W64">
+        <v>2.66</v>
+      </c>
+      <c r="X64">
+        <v>2.99</v>
+      </c>
+      <c r="Y64">
+        <v>1.33</v>
+      </c>
+      <c r="Z64">
+        <v>8</v>
+      </c>
+      <c r="AA64">
+        <v>1.02</v>
+      </c>
+      <c r="AB64">
+        <v>1.01</v>
+      </c>
+      <c r="AC64">
+        <v>1.31</v>
+      </c>
+      <c r="AD64">
+        <v>2.92</v>
+      </c>
+      <c r="AE64">
+        <v>2.09</v>
+      </c>
+      <c r="AF64">
+        <v>1.7</v>
+      </c>
+      <c r="AG64">
+        <v>3.7</v>
+      </c>
+      <c r="AH64">
+        <v>1.24</v>
+      </c>
+      <c r="AI64">
+        <v>7.3</v>
+      </c>
+      <c r="AJ64">
+        <v>1.03</v>
+      </c>
+      <c r="AK64">
+        <v>1.82</v>
+      </c>
+      <c r="AL64">
+        <v>1.86</v>
+      </c>
+      <c r="AM64">
+        <v>1.29</v>
+      </c>
+      <c r="AN64">
+        <v>1.54</v>
+      </c>
+      <c r="AO64">
+        <v>0</v>
+      </c>
+      <c r="AP64">
+        <v>1.31</v>
+      </c>
+      <c r="AQ64">
+        <v>1.47</v>
+      </c>
+      <c r="AR64">
+        <v>2.31</v>
+      </c>
+      <c r="AS64">
+        <v>2.58</v>
+      </c>
+      <c r="AT64">
+        <v>3.57</v>
+      </c>
+      <c r="AU64">
+        <v>2.98</v>
+      </c>
+      <c r="AV64">
+        <v>2.18</v>
+      </c>
+      <c r="AW64">
+        <v>1.73</v>
+      </c>
+      <c r="AX64">
+        <v>1.42</v>
+      </c>
+      <c r="AY64">
+        <v>1.21</v>
+      </c>
+      <c r="AZ64">
+        <v>1.68</v>
+      </c>
+      <c r="BA64">
         <v>2.75</v>
       </c>
-      <c r="V64">
-        <v>0</v>
-      </c>
-      <c r="W64">
-        <v>0</v>
-      </c>
-      <c r="X64">
-        <v>2.48</v>
-      </c>
-      <c r="Y64">
-        <v>1.41</v>
-      </c>
-      <c r="Z64">
-        <v>0</v>
-      </c>
-      <c r="AA64">
-        <v>0</v>
-      </c>
-      <c r="AB64">
-        <v>0</v>
-      </c>
-      <c r="AC64">
-        <v>1.23</v>
-      </c>
-      <c r="AD64">
-        <v>3.5</v>
-      </c>
-      <c r="AE64">
-        <v>1.77</v>
-      </c>
-      <c r="AF64">
-        <v>1.87</v>
-      </c>
-      <c r="AG64">
-        <v>2.9</v>
-      </c>
-      <c r="AH64">
-        <v>1.33</v>
-      </c>
-      <c r="AI64">
-        <v>5.2</v>
-      </c>
-      <c r="AJ64">
-        <v>1.1</v>
-      </c>
-      <c r="AK64">
-        <v>1.64</v>
-      </c>
-      <c r="AL64">
-        <v>2.1</v>
-      </c>
-      <c r="AM64">
-        <v>1.23</v>
-      </c>
-      <c r="AN64">
-        <v>1.29</v>
-      </c>
-      <c r="AO64">
-        <v>0</v>
-      </c>
-      <c r="AP64">
-        <v>0</v>
-      </c>
-      <c r="AQ64">
-        <v>0</v>
-      </c>
-      <c r="AR64">
-        <v>0</v>
-      </c>
-      <c r="AS64">
-        <v>0</v>
-      </c>
-      <c r="AT64">
-        <v>0</v>
-      </c>
-      <c r="AU64">
-        <v>0</v>
-      </c>
-      <c r="AV64">
-        <v>0</v>
-      </c>
-      <c r="AW64">
-        <v>0</v>
-      </c>
-      <c r="AX64">
-        <v>0</v>
-      </c>
-      <c r="AY64">
-        <v>0</v>
-      </c>
-      <c r="AZ64">
-        <v>0</v>
-      </c>
-      <c r="BA64">
-        <v>0</v>
-      </c>
       <c r="BB64">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC64">
-        <v>1.97</v>
+        <v>2.29</v>
       </c>
       <c r="BD64">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="BE64">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="BF64">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG64">
         <v>0</v>
@@ -13194,22 +13194,22 @@
         <v>308</v>
       </c>
       <c r="P65">
-        <v>1.34</v>
+        <v>2.94</v>
       </c>
       <c r="Q65">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="R65">
-        <v>7.55</v>
+        <v>2.21</v>
       </c>
       <c r="S65">
-        <v>1.81</v>
+        <v>3.35</v>
       </c>
       <c r="T65">
-        <v>2.65</v>
+        <v>2.23</v>
       </c>
       <c r="U65">
-        <v>5.6</v>
+        <v>2.75</v>
       </c>
       <c r="V65">
         <v>0</v>
@@ -13218,10 +13218,10 @@
         <v>0</v>
       </c>
       <c r="X65">
-        <v>2.07</v>
+        <v>2.48</v>
       </c>
       <c r="Y65">
-        <v>1.58</v>
+        <v>1.41</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -13233,40 +13233,40 @@
         <v>0</v>
       </c>
       <c r="AC65">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AD65">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="AE65">
-        <v>1.46</v>
+        <v>1.77</v>
       </c>
       <c r="AF65">
-        <v>2.4</v>
+        <v>1.87</v>
       </c>
       <c r="AG65">
-        <v>2.17</v>
+        <v>2.9</v>
       </c>
       <c r="AH65">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AI65">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="AJ65">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AK65">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AL65">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AM65">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AN65">
-        <v>2.5</v>
+        <v>1.29</v>
       </c>
       <c r="AO65">
         <v>0</v>
@@ -13311,13 +13311,13 @@
         <v>0</v>
       </c>
       <c r="BC65">
-        <v>1.66</v>
+        <v>1.97</v>
       </c>
       <c r="BD65">
         <v>0</v>
       </c>
       <c r="BE65">
-        <v>1.96</v>
+        <v>1.65</v>
       </c>
       <c r="BF65">
         <v>0</v>
@@ -13340,10 +13340,10 @@
         <v>79</v>
       </c>
       <c r="C66" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="D66" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E66" t="s">
         <v>201</v>
@@ -13379,133 +13379,133 @@
         <v>308</v>
       </c>
       <c r="P66">
-        <v>2.3</v>
+        <v>1.34</v>
       </c>
       <c r="Q66">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="R66">
-        <v>3</v>
+        <v>7.55</v>
       </c>
       <c r="S66">
-        <v>2.96</v>
+        <v>1.81</v>
       </c>
       <c r="T66">
-        <v>2.04</v>
+        <v>2.65</v>
       </c>
       <c r="U66">
-        <v>3.69</v>
+        <v>5.6</v>
       </c>
       <c r="V66">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W66">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="X66">
-        <v>2.99</v>
+        <v>2.07</v>
       </c>
       <c r="Y66">
-        <v>1.33</v>
+        <v>1.58</v>
       </c>
       <c r="Z66">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA66">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB66">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC66">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="AD66">
-        <v>2.92</v>
+        <v>4.7</v>
       </c>
       <c r="AE66">
-        <v>2.09</v>
+        <v>1.46</v>
       </c>
       <c r="AF66">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="AG66">
-        <v>3.7</v>
+        <v>2.17</v>
       </c>
       <c r="AH66">
-        <v>1.24</v>
+        <v>1.57</v>
       </c>
       <c r="AI66">
-        <v>7.3</v>
+        <v>3.6</v>
       </c>
       <c r="AJ66">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="AK66">
-        <v>1.82</v>
+        <v>1.66</v>
       </c>
       <c r="AL66">
-        <v>1.86</v>
+        <v>2.07</v>
       </c>
       <c r="AM66">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AN66">
-        <v>1.54</v>
+        <v>2.5</v>
       </c>
       <c r="AO66">
         <v>0</v>
       </c>
       <c r="AP66">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AQ66">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AR66">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AS66">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="AT66">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="AU66">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AV66">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW66">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AX66">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY66">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AZ66">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BA66">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BB66">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC66">
-        <v>2.29</v>
+        <v>1.66</v>
       </c>
       <c r="BD66">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="BE66">
-        <v>1.57</v>
+        <v>1.96</v>
       </c>
       <c r="BF66">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG66">
         <v>0</v>
@@ -13525,7 +13525,7 @@
         <v>80</v>
       </c>
       <c r="C67" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D67" t="s">
         <v>134</v>
@@ -13716,7 +13716,7 @@
         <v>134</v>
       </c>
       <c r="E68" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="F68" t="s">
         <v>288</v>
@@ -13749,133 +13749,133 @@
         <v>308</v>
       </c>
       <c r="P68">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Q68">
-        <v>5.97</v>
+        <v>0</v>
       </c>
       <c r="R68">
-        <v>8.449999999999999</v>
+        <v>0</v>
       </c>
       <c r="S68">
-        <v>1.65</v>
+        <v>2.07</v>
       </c>
       <c r="T68">
-        <v>2.8</v>
+        <v>2.42</v>
       </c>
       <c r="U68">
-        <v>6.45</v>
+        <v>4.5</v>
       </c>
       <c r="V68">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="W68">
-        <v>4.15</v>
+        <v>3.42</v>
       </c>
       <c r="X68">
-        <v>1.97</v>
+        <v>2.18</v>
       </c>
       <c r="Y68">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="Z68">
-        <v>3.98</v>
+        <v>4.65</v>
       </c>
       <c r="AA68">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AB68">
         <v>1.01</v>
       </c>
       <c r="AC68">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AD68">
-        <v>5.95</v>
+        <v>4.65</v>
       </c>
       <c r="AE68">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="AF68">
-        <v>2.81</v>
+        <v>2.33</v>
       </c>
       <c r="AG68">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="AH68">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="AI68">
+        <v>3.76</v>
+      </c>
+      <c r="AJ68">
+        <v>1.19</v>
+      </c>
+      <c r="AK68">
+        <v>1.55</v>
+      </c>
+      <c r="AL68">
+        <v>2.27</v>
+      </c>
+      <c r="AM68">
+        <v>1.2</v>
+      </c>
+      <c r="AN68">
+        <v>2.17</v>
+      </c>
+      <c r="AO68">
+        <v>0</v>
+      </c>
+      <c r="AP68">
+        <v>1.23</v>
+      </c>
+      <c r="AQ68">
+        <v>1.44</v>
+      </c>
+      <c r="AR68">
+        <v>1.79</v>
+      </c>
+      <c r="AS68">
+        <v>2.26</v>
+      </c>
+      <c r="AT68">
         <v>3.05</v>
       </c>
-      <c r="AJ68">
+      <c r="AU68">
+        <v>3.42</v>
+      </c>
+      <c r="AV68">
+        <v>2.43</v>
+      </c>
+      <c r="AW68">
+        <v>1.87</v>
+      </c>
+      <c r="AX68">
+        <v>1.51</v>
+      </c>
+      <c r="AY68">
         <v>1.28</v>
       </c>
-      <c r="AK68">
-        <v>1.63</v>
-      </c>
-      <c r="AL68">
-        <v>2.12</v>
-      </c>
-      <c r="AM68">
-        <v>1.1</v>
-      </c>
-      <c r="AN68">
-        <v>3.42</v>
-      </c>
-      <c r="AO68">
-        <v>0</v>
-      </c>
-      <c r="AP68">
-        <v>1.19</v>
-      </c>
-      <c r="AQ68">
-        <v>1.35</v>
-      </c>
-      <c r="AR68">
-        <v>1.57</v>
-      </c>
-      <c r="AS68">
-        <v>1.92</v>
-      </c>
-      <c r="AT68">
-        <v>2.43</v>
-      </c>
-      <c r="AU68">
-        <v>3.9</v>
-      </c>
-      <c r="AV68">
-        <v>2.8</v>
-      </c>
-      <c r="AW68">
-        <v>2.15</v>
-      </c>
-      <c r="AX68">
-        <v>1.73</v>
-      </c>
-      <c r="AY68">
-        <v>1.45</v>
-      </c>
       <c r="AZ68">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="BA68">
-        <v>3.95</v>
+        <v>2.96</v>
       </c>
       <c r="BB68">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="BC68">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="BD68">
-        <v>6.1</v>
+        <v>4.7</v>
       </c>
       <c r="BE68">
-        <v>2.16</v>
+        <v>1.95</v>
       </c>
       <c r="BF68">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="BG68">
         <v>0</v>
@@ -13901,7 +13901,7 @@
         <v>134</v>
       </c>
       <c r="E69" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F69" t="s">
         <v>289</v>
@@ -14086,7 +14086,7 @@
         <v>134</v>
       </c>
       <c r="E70" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="F70" t="s">
         <v>290</v>
@@ -14119,133 +14119,133 @@
         <v>308</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S70">
-        <v>2.08</v>
+        <v>1.77</v>
       </c>
       <c r="T70">
-        <v>2.42</v>
+        <v>2.66</v>
       </c>
       <c r="U70">
-        <v>4.5</v>
+        <v>5.65</v>
       </c>
       <c r="V70">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="W70">
-        <v>3.42</v>
+        <v>3.95</v>
       </c>
       <c r="X70">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="Y70">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="Z70">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="AA70">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AB70">
         <v>1.01</v>
       </c>
       <c r="AC70">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AD70">
-        <v>4.65</v>
+        <v>5.6</v>
       </c>
       <c r="AE70">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AF70">
-        <v>2.33</v>
+        <v>2.62</v>
       </c>
       <c r="AG70">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AH70">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="AI70">
-        <v>3.75</v>
+        <v>3.28</v>
       </c>
       <c r="AJ70">
+        <v>1.25</v>
+      </c>
+      <c r="AK70">
+        <v>1.57</v>
+      </c>
+      <c r="AL70">
+        <v>2.23</v>
+      </c>
+      <c r="AM70">
+        <v>1.13</v>
+      </c>
+      <c r="AN70">
+        <v>2.88</v>
+      </c>
+      <c r="AO70">
+        <v>0</v>
+      </c>
+      <c r="AP70">
         <v>1.19</v>
       </c>
-      <c r="AK70">
-        <v>1.55</v>
-      </c>
-      <c r="AL70">
-        <v>2.27</v>
-      </c>
-      <c r="AM70">
-        <v>1.2</v>
-      </c>
-      <c r="AN70">
-        <v>2.17</v>
-      </c>
-      <c r="AO70">
-        <v>0</v>
-      </c>
-      <c r="AP70">
-        <v>1.2</v>
-      </c>
       <c r="AQ70">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AR70">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AS70">
-        <v>1.97</v>
+        <v>2.14</v>
       </c>
       <c r="AT70">
-        <v>2.5</v>
+        <v>2.83</v>
       </c>
       <c r="AU70">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="AV70">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="AW70">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AX70">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AY70">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AZ70">
-        <v>1.55</v>
+        <v>1.29</v>
       </c>
       <c r="BA70">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="BB70">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="BC70">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="BD70">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BE70">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="BF70">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="BG70">
         <v>0</v>
@@ -14265,7 +14265,7 @@
         <v>81</v>
       </c>
       <c r="C71" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="D71" t="s">
         <v>134</v>
@@ -14304,133 +14304,133 @@
         <v>308</v>
       </c>
       <c r="P71">
-        <v>1.91</v>
+        <v>1.44</v>
       </c>
       <c r="Q71">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="R71">
-        <v>3.55</v>
+        <v>5.5</v>
       </c>
       <c r="S71">
-        <v>2.45</v>
+        <v>1.88</v>
       </c>
       <c r="T71">
-        <v>2.16</v>
+        <v>2.5</v>
       </c>
       <c r="U71">
-        <v>3.6</v>
+        <v>5.45</v>
       </c>
       <c r="V71">
+        <v>1.22</v>
+      </c>
+      <c r="W71">
+        <v>3.66</v>
+      </c>
+      <c r="X71">
+        <v>2.11</v>
+      </c>
+      <c r="Y71">
+        <v>1.68</v>
+      </c>
+      <c r="Z71">
+        <v>4.4</v>
+      </c>
+      <c r="AA71">
+        <v>1.16</v>
+      </c>
+      <c r="AB71">
+        <v>1.02</v>
+      </c>
+      <c r="AC71">
+        <v>1.1</v>
+      </c>
+      <c r="AD71">
+        <v>5.2</v>
+      </c>
+      <c r="AE71">
+        <v>1.41</v>
+      </c>
+      <c r="AF71">
+        <v>2.54</v>
+      </c>
+      <c r="AG71">
+        <v>2.15</v>
+      </c>
+      <c r="AH71">
+        <v>1.73</v>
+      </c>
+      <c r="AI71">
+        <v>3.78</v>
+      </c>
+      <c r="AJ71">
+        <v>1.25</v>
+      </c>
+      <c r="AK71">
+        <v>1.57</v>
+      </c>
+      <c r="AL71">
+        <v>2.26</v>
+      </c>
+      <c r="AM71">
+        <v>1.19</v>
+      </c>
+      <c r="AN71">
+        <v>2.68</v>
+      </c>
+      <c r="AO71">
+        <v>0</v>
+      </c>
+      <c r="AP71">
+        <v>1.25</v>
+      </c>
+      <c r="AQ71">
+        <v>1.48</v>
+      </c>
+      <c r="AR71">
+        <v>1.85</v>
+      </c>
+      <c r="AS71">
+        <v>2.39</v>
+      </c>
+      <c r="AT71">
+        <v>3.2</v>
+      </c>
+      <c r="AU71">
+        <v>3.28</v>
+      </c>
+      <c r="AV71">
+        <v>2.36</v>
+      </c>
+      <c r="AW71">
+        <v>1.83</v>
+      </c>
+      <c r="AX71">
+        <v>1.47</v>
+      </c>
+      <c r="AY71">
+        <v>1.26</v>
+      </c>
+      <c r="AZ71">
+        <v>1.31</v>
+      </c>
+      <c r="BA71">
+        <v>4.2</v>
+      </c>
+      <c r="BB71">
+        <v>1.1</v>
+      </c>
+      <c r="BC71">
+        <v>1.66</v>
+      </c>
+      <c r="BD71">
+        <v>5.35</v>
+      </c>
+      <c r="BE71">
+        <v>2.14</v>
+      </c>
+      <c r="BF71">
         <v>1.33</v>
-      </c>
-      <c r="W71">
-        <v>3.04</v>
-      </c>
-      <c r="X71">
-        <v>2.32</v>
-      </c>
-      <c r="Y71">
-        <v>1.46</v>
-      </c>
-      <c r="Z71">
-        <v>5.85</v>
-      </c>
-      <c r="AA71">
-        <v>1.07</v>
-      </c>
-      <c r="AB71">
-        <v>1</v>
-      </c>
-      <c r="AC71">
-        <v>1.24</v>
-      </c>
-      <c r="AD71">
-        <v>3.75</v>
-      </c>
-      <c r="AE71">
-        <v>1.76</v>
-      </c>
-      <c r="AF71">
-        <v>2</v>
-      </c>
-      <c r="AG71">
-        <v>2.95</v>
-      </c>
-      <c r="AH71">
-        <v>1.36</v>
-      </c>
-      <c r="AI71">
-        <v>5.05</v>
-      </c>
-      <c r="AJ71">
-        <v>1.1</v>
-      </c>
-      <c r="AK71">
-        <v>1.62</v>
-      </c>
-      <c r="AL71">
-        <v>2.1</v>
-      </c>
-      <c r="AM71">
-        <v>1.28</v>
-      </c>
-      <c r="AN71">
-        <v>1.77</v>
-      </c>
-      <c r="AO71">
-        <v>0</v>
-      </c>
-      <c r="AP71">
-        <v>1.2</v>
-      </c>
-      <c r="AQ71">
-        <v>1.4</v>
-      </c>
-      <c r="AR71">
-        <v>1.96</v>
-      </c>
-      <c r="AS71">
-        <v>2.16</v>
-      </c>
-      <c r="AT71">
-        <v>2.88</v>
-      </c>
-      <c r="AU71">
-        <v>3.72</v>
-      </c>
-      <c r="AV71">
-        <v>2.6</v>
-      </c>
-      <c r="AW71">
-        <v>1.98</v>
-      </c>
-      <c r="AX71">
-        <v>1.57</v>
-      </c>
-      <c r="AY71">
-        <v>1.32</v>
-      </c>
-      <c r="AZ71">
-        <v>2.03</v>
-      </c>
-      <c r="BA71">
-        <v>2.19</v>
-      </c>
-      <c r="BB71">
-        <v>1.18</v>
-      </c>
-      <c r="BC71">
-        <v>1.97</v>
-      </c>
-      <c r="BD71">
-        <v>4.15</v>
-      </c>
-      <c r="BE71">
-        <v>1.85</v>
-      </c>
-      <c r="BF71">
-        <v>1.19</v>
       </c>
       <c r="BG71">
         <v>0</v>
@@ -14450,7 +14450,7 @@
         <v>81</v>
       </c>
       <c r="C72" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="D72" t="s">
         <v>134</v>
@@ -14489,79 +14489,79 @@
         <v>308</v>
       </c>
       <c r="P72">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="Q72">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="R72">
-        <v>5.5</v>
+        <v>3.55</v>
       </c>
       <c r="S72">
-        <v>1.88</v>
+        <v>2.45</v>
       </c>
       <c r="T72">
-        <v>2.5</v>
+        <v>2.16</v>
       </c>
       <c r="U72">
-        <v>5.45</v>
+        <v>3.6</v>
       </c>
       <c r="V72">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="W72">
-        <v>3.66</v>
+        <v>3.04</v>
       </c>
       <c r="X72">
-        <v>2.11</v>
+        <v>2.32</v>
       </c>
       <c r="Y72">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="Z72">
-        <v>4.4</v>
+        <v>5.85</v>
       </c>
       <c r="AA72">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="AB72">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AC72">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AD72">
-        <v>5.35</v>
+        <v>3.75</v>
       </c>
       <c r="AE72">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AF72">
-        <v>2.59</v>
+        <v>2</v>
       </c>
       <c r="AG72">
-        <v>2.24</v>
+        <v>2.95</v>
       </c>
       <c r="AH72">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="AI72">
-        <v>3.78</v>
+        <v>5.05</v>
       </c>
       <c r="AJ72">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AK72">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL72">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AM72">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AN72">
-        <v>2.68</v>
+        <v>1.77</v>
       </c>
       <c r="AO72">
         <v>0</v>
@@ -14570,52 +14570,52 @@
         <v>1.2</v>
       </c>
       <c r="AQ72">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AR72">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AS72">
-        <v>1.96</v>
+        <v>2.16</v>
       </c>
       <c r="AT72">
-        <v>3.42</v>
+        <v>2.88</v>
       </c>
       <c r="AU72">
-        <v>3.85</v>
+        <v>3.72</v>
       </c>
       <c r="AV72">
-        <v>2.24</v>
+        <v>2.6</v>
       </c>
       <c r="AW72">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="AX72">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="AY72">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AZ72">
-        <v>1.22</v>
+        <v>2.03</v>
       </c>
       <c r="BA72">
-        <v>5.25</v>
+        <v>2.19</v>
       </c>
       <c r="BB72">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="BC72">
-        <v>1.66</v>
+        <v>1.97</v>
       </c>
       <c r="BD72">
-        <v>5.3</v>
+        <v>4.15</v>
       </c>
       <c r="BE72">
-        <v>2.14</v>
+        <v>1.85</v>
       </c>
       <c r="BF72">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="BG72">
         <v>0</v>
@@ -14674,19 +14674,19 @@
         <v>308</v>
       </c>
       <c r="P73">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Q73">
-        <v>4.08</v>
+        <v>4</v>
       </c>
       <c r="R73">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="S73">
         <v>2.25</v>
       </c>
       <c r="T73">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="U73">
         <v>4.6</v>
@@ -14704,7 +14704,7 @@
         <v>1.44</v>
       </c>
       <c r="Z73">
-        <v>6.75</v>
+        <v>6.8</v>
       </c>
       <c r="AA73">
         <v>1.07</v>
@@ -14713,13 +14713,13 @@
         <v>1.02</v>
       </c>
       <c r="AC73">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AD73">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AE73">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AF73">
         <v>1.91</v>
@@ -14728,22 +14728,22 @@
         <v>3.1</v>
       </c>
       <c r="AH73">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AI73">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AJ73">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AK73">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AL73">
         <v>1.95</v>
       </c>
       <c r="AM73">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AN73">
         <v>2.25</v>
@@ -14779,10 +14779,10 @@
         <v>1.41</v>
       </c>
       <c r="AY73">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AZ73">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="BA73">
         <v>3.8</v>
@@ -14791,7 +14791,7 @@
         <v>1.25</v>
       </c>
       <c r="BC73">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="BD73">
         <v>3.6</v>
@@ -14800,7 +14800,7 @@
         <v>1.67</v>
       </c>
       <c r="BF73">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BG73">
         <v>0</v>
@@ -14820,7 +14820,7 @@
         <v>83</v>
       </c>
       <c r="C74" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="D74" t="s">
         <v>134</v>
@@ -14859,133 +14859,133 @@
         <v>308</v>
       </c>
       <c r="P74">
-        <v>6.3</v>
+        <v>2.45</v>
       </c>
       <c r="Q74">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="R74">
-        <v>1.45</v>
+        <v>2.88</v>
       </c>
       <c r="S74">
-        <v>5.75</v>
+        <v>3</v>
       </c>
       <c r="T74">
-        <v>2.45</v>
+        <v>2.14</v>
       </c>
       <c r="U74">
-        <v>1.99</v>
+        <v>3.3</v>
       </c>
       <c r="V74">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="W74">
-        <v>3.45</v>
+        <v>2.85</v>
       </c>
       <c r="X74">
-        <v>2.33</v>
+        <v>2.8</v>
       </c>
       <c r="Y74">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="Z74">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="AA74">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AB74">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC74">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AD74">
-        <v>4.45</v>
+        <v>3.34</v>
       </c>
       <c r="AE74">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AF74">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AG74">
-        <v>2.43</v>
+        <v>3.55</v>
       </c>
       <c r="AH74">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="AI74">
-        <v>4.15</v>
+        <v>6.1</v>
       </c>
       <c r="AJ74">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AK74">
         <v>1.75</v>
       </c>
       <c r="AL74">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AM74">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AN74">
-        <v>1.13</v>
+        <v>1.62</v>
       </c>
       <c r="AO74">
         <v>0</v>
       </c>
       <c r="AP74">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ74">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AR74">
+        <v>1.78</v>
+      </c>
+      <c r="AS74">
+        <v>2.19</v>
+      </c>
+      <c r="AT74">
+        <v>2.88</v>
+      </c>
+      <c r="AU74">
+        <v>3.58</v>
+      </c>
+      <c r="AV74">
+        <v>2.57</v>
+      </c>
+      <c r="AW74">
+        <v>1.96</v>
+      </c>
+      <c r="AX74">
+        <v>1.57</v>
+      </c>
+      <c r="AY74">
+        <v>1.32</v>
+      </c>
+      <c r="AZ74">
+        <v>1.65</v>
+      </c>
+      <c r="BA74">
+        <v>2.15</v>
+      </c>
+      <c r="BB74">
+        <v>1.24</v>
+      </c>
+      <c r="BC74">
+        <v>2.08</v>
+      </c>
+      <c r="BD74">
+        <v>3.84</v>
+      </c>
+      <c r="BE74">
         <v>1.71</v>
       </c>
-      <c r="AS74">
-        <v>2.15</v>
-      </c>
-      <c r="AT74">
-        <v>2.8</v>
-      </c>
-      <c r="AU74">
-        <v>3.6</v>
-      </c>
-      <c r="AV74">
-        <v>2.65</v>
-      </c>
-      <c r="AW74">
-        <v>2.01</v>
-      </c>
-      <c r="AX74">
-        <v>1.62</v>
-      </c>
-      <c r="AY74">
-        <v>1.38</v>
-      </c>
-      <c r="AZ74">
-        <v>3.7</v>
-      </c>
-      <c r="BA74">
-        <v>1.31</v>
-      </c>
-      <c r="BB74">
-        <v>1.2</v>
-      </c>
-      <c r="BC74">
-        <v>1.91</v>
-      </c>
-      <c r="BD74">
-        <v>4.8</v>
-      </c>
-      <c r="BE74">
-        <v>1.85</v>
-      </c>
       <c r="BF74">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="BG74">
         <v>0</v>
@@ -15005,7 +15005,7 @@
         <v>83</v>
       </c>
       <c r="C75" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="D75" t="s">
         <v>134</v>
@@ -15044,133 +15044,133 @@
         <v>308</v>
       </c>
       <c r="P75">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="Q75">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R75">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S75">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="T75">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U75">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V75">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W75">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="X75">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Y75">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z75">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA75">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB75">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC75">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD75">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AE75">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF75">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG75">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AH75">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI75">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AJ75">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK75">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL75">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AM75">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN75">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AO75">
         <v>0</v>
       </c>
       <c r="AP75">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AQ75">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR75">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AS75">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AT75">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU75">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV75">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AW75">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AX75">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY75">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ75">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BA75">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BB75">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC75">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD75">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE75">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF75">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG75">
         <v>0</v>
@@ -15190,7 +15190,7 @@
         <v>83</v>
       </c>
       <c r="C76" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="D76" t="s">
         <v>134</v>
@@ -15229,133 +15229,133 @@
         <v>308</v>
       </c>
       <c r="P76">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q76">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R76">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S76">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T76">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U76">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V76">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W76">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="X76">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y76">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z76">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA76">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB76">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC76">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AD76">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AE76">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF76">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG76">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AH76">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI76">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AJ76">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK76">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL76">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM76">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AN76">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AO76">
         <v>0</v>
       </c>
       <c r="AP76">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AQ76">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AR76">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AS76">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AT76">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AU76">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AV76">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AW76">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AX76">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AY76">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ76">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BA76">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BB76">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC76">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="BD76">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="BE76">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BF76">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG76">
         <v>0</v>
@@ -15560,7 +15560,7 @@
         <v>85</v>
       </c>
       <c r="C78" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D78" t="s">
         <v>134</v>
@@ -15784,133 +15784,133 @@
         <v>308</v>
       </c>
       <c r="P79">
+        <v>1.75</v>
+      </c>
+      <c r="Q79">
+        <v>3.3</v>
+      </c>
+      <c r="R79">
+        <v>4.2</v>
+      </c>
+      <c r="S79">
+        <v>2.4</v>
+      </c>
+      <c r="T79">
+        <v>1.99</v>
+      </c>
+      <c r="U79">
+        <v>5.61</v>
+      </c>
+      <c r="V79">
+        <v>1.46</v>
+      </c>
+      <c r="W79">
+        <v>2.61</v>
+      </c>
+      <c r="X79">
+        <v>3.16</v>
+      </c>
+      <c r="Y79">
+        <v>1.3</v>
+      </c>
+      <c r="Z79">
+        <v>8.1</v>
+      </c>
+      <c r="AA79">
+        <v>1.02</v>
+      </c>
+      <c r="AB79">
+        <v>1.08</v>
+      </c>
+      <c r="AC79">
+        <v>1.36</v>
+      </c>
+      <c r="AD79">
+        <v>2.7</v>
+      </c>
+      <c r="AE79">
+        <v>2.23</v>
+      </c>
+      <c r="AF79">
+        <v>1.62</v>
+      </c>
+      <c r="AG79">
+        <v>3.95</v>
+      </c>
+      <c r="AH79">
+        <v>1.17</v>
+      </c>
+      <c r="AI79">
+        <v>7.9</v>
+      </c>
+      <c r="AJ79">
+        <v>1.02</v>
+      </c>
+      <c r="AK79">
+        <v>2.03</v>
+      </c>
+      <c r="AL79">
+        <v>1.7</v>
+      </c>
+      <c r="AM79">
+        <v>1.28</v>
+      </c>
+      <c r="AN79">
+        <v>1.98</v>
+      </c>
+      <c r="AO79">
+        <v>0</v>
+      </c>
+      <c r="AP79">
+        <v>1.18</v>
+      </c>
+      <c r="AQ79">
+        <v>1.36</v>
+      </c>
+      <c r="AR79">
+        <v>1.91</v>
+      </c>
+      <c r="AS79">
         <v>2.08</v>
       </c>
-      <c r="Q79">
-        <v>3.15</v>
-      </c>
-      <c r="R79">
-        <v>3.41</v>
-      </c>
-      <c r="S79">
-        <v>0</v>
-      </c>
-      <c r="T79">
-        <v>0</v>
-      </c>
-      <c r="U79">
-        <v>0</v>
-      </c>
-      <c r="V79">
-        <v>0</v>
-      </c>
-      <c r="W79">
-        <v>0</v>
-      </c>
-      <c r="X79">
-        <v>0</v>
-      </c>
-      <c r="Y79">
-        <v>0</v>
-      </c>
-      <c r="Z79">
-        <v>0</v>
-      </c>
-      <c r="AA79">
-        <v>0</v>
-      </c>
-      <c r="AB79">
-        <v>0</v>
-      </c>
-      <c r="AC79">
-        <v>0</v>
-      </c>
-      <c r="AD79">
-        <v>0</v>
-      </c>
-      <c r="AE79">
-        <v>0</v>
-      </c>
-      <c r="AF79">
-        <v>0</v>
-      </c>
-      <c r="AG79">
-        <v>0</v>
-      </c>
-      <c r="AH79">
-        <v>0</v>
-      </c>
-      <c r="AI79">
-        <v>0</v>
-      </c>
-      <c r="AJ79">
-        <v>0</v>
-      </c>
-      <c r="AK79">
-        <v>0</v>
-      </c>
-      <c r="AL79">
-        <v>0</v>
-      </c>
-      <c r="AM79">
-        <v>0</v>
-      </c>
-      <c r="AN79">
-        <v>0</v>
-      </c>
-      <c r="AO79">
-        <v>0</v>
-      </c>
-      <c r="AP79">
-        <v>0</v>
-      </c>
-      <c r="AQ79">
-        <v>0</v>
-      </c>
-      <c r="AR79">
-        <v>0</v>
-      </c>
-      <c r="AS79">
-        <v>0</v>
-      </c>
       <c r="AT79">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU79">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AV79">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AW79">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AX79">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY79">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ79">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BA79">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="BB79">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC79">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="BD79">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BE79">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF79">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG79">
         <v>0</v>
@@ -15969,133 +15969,133 @@
         <v>308</v>
       </c>
       <c r="P80">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="Q80">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="R80">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="S80">
-        <v>2.38</v>
+        <v>2.67</v>
       </c>
       <c r="T80">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="U80">
-        <v>5.57</v>
+        <v>4.21</v>
       </c>
       <c r="V80">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="W80">
-        <v>2.61</v>
+        <v>2.66</v>
       </c>
       <c r="X80">
-        <v>3.16</v>
+        <v>2.96</v>
       </c>
       <c r="Y80">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z80">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="AA80">
         <v>1.02</v>
       </c>
       <c r="AB80">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AC80">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AD80">
-        <v>2.7</v>
+        <v>3.04</v>
       </c>
       <c r="AE80">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AF80">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AG80">
-        <v>4.2</v>
+        <v>3.58</v>
       </c>
       <c r="AH80">
         <v>1.21</v>
       </c>
       <c r="AI80">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
       <c r="AJ80">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AK80">
-        <v>2.03</v>
+        <v>1.81</v>
       </c>
       <c r="AL80">
-        <v>1.74</v>
+        <v>1.88</v>
       </c>
       <c r="AM80">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AN80">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="AO80">
         <v>0</v>
       </c>
       <c r="AP80">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AQ80">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AR80">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AS80">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AT80">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AU80">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AV80">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AW80">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AX80">
+        <v>0</v>
+      </c>
+      <c r="AY80">
+        <v>0</v>
+      </c>
+      <c r="AZ80">
+        <v>0</v>
+      </c>
+      <c r="BA80">
+        <v>0</v>
+      </c>
+      <c r="BB80">
+        <v>1.22</v>
+      </c>
+      <c r="BC80">
+        <v>2.24</v>
+      </c>
+      <c r="BD80">
+        <v>3.5</v>
+      </c>
+      <c r="BE80">
         <v>1.57</v>
       </c>
-      <c r="AY80">
-        <v>1.32</v>
-      </c>
-      <c r="AZ80">
-        <v>1.51</v>
-      </c>
-      <c r="BA80">
-        <v>2.85</v>
-      </c>
-      <c r="BB80">
-        <v>1.28</v>
-      </c>
-      <c r="BC80">
-        <v>2.39</v>
-      </c>
-      <c r="BD80">
-        <v>3.4</v>
-      </c>
-      <c r="BE80">
-        <v>1.5</v>
-      </c>
       <c r="BF80">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="BG80">
         <v>0</v>
@@ -16154,22 +16154,22 @@
         <v>308</v>
       </c>
       <c r="P81">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="Q81">
         <v>3.25</v>
       </c>
       <c r="R81">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="S81">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="T81">
         <v>1.87</v>
       </c>
       <c r="U81">
-        <v>6.5</v>
+        <v>6.37</v>
       </c>
       <c r="V81">
         <v>1.55</v>
@@ -16193,13 +16193,13 @@
         <v>1.06</v>
       </c>
       <c r="AC81">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AD81">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="AE81">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="AF81">
         <v>1.44</v>
@@ -16211,22 +16211,22 @@
         <v>1.12</v>
       </c>
       <c r="AI81">
-        <v>10.5</v>
+        <v>8.9</v>
       </c>
       <c r="AJ81">
         <v>1.01</v>
       </c>
       <c r="AK81">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="AL81">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AM81">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AN81">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AO81">
         <v>0</v>
@@ -16235,37 +16235,37 @@
         <v>0</v>
       </c>
       <c r="AQ81">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR81">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS81">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AT81">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU81">
         <v>0</v>
       </c>
       <c r="AV81">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AW81">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AX81">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY81">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AZ81">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BA81">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BB81">
         <v>1.32</v>
@@ -16339,13 +16339,13 @@
         <v>308</v>
       </c>
       <c r="P82">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="Q82">
         <v>2.87</v>
       </c>
       <c r="R82">
-        <v>3.54</v>
+        <v>3.58</v>
       </c>
       <c r="S82">
         <v>0</v>
@@ -16533,13 +16533,13 @@
         <v>0</v>
       </c>
       <c r="S83">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="T83">
         <v>1.92</v>
       </c>
       <c r="U83">
-        <v>5.16</v>
+        <v>4.25</v>
       </c>
       <c r="V83">
         <v>1.48</v>
@@ -16563,7 +16563,7 @@
         <v>1.04</v>
       </c>
       <c r="AC83">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AD83">
         <v>2.56</v>
@@ -16575,7 +16575,7 @@
         <v>1.53</v>
       </c>
       <c r="AG83">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="AH83">
         <v>1.14</v>
@@ -16593,10 +16593,10 @@
         <v>1.65</v>
       </c>
       <c r="AM83">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AN83">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AO83">
         <v>0</v>
@@ -16605,37 +16605,37 @@
         <v>0</v>
       </c>
       <c r="AQ83">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AR83">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AS83">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AT83">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AU83">
         <v>0</v>
       </c>
       <c r="AV83">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AW83">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AX83">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY83">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AZ83">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BA83">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BB83">
         <v>1.29</v>
@@ -16712,10 +16712,10 @@
         <v>2</v>
       </c>
       <c r="Q84">
-        <v>2.78</v>
+        <v>2.87</v>
       </c>
       <c r="R84">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="S84">
         <v>0</v>
@@ -16906,7 +16906,7 @@
         <v>2.32</v>
       </c>
       <c r="T85">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="U85">
         <v>3.5</v>
@@ -16918,10 +16918,10 @@
         <v>3.5</v>
       </c>
       <c r="X85">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="Y85">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Z85">
         <v>4.5</v>
@@ -16930,7 +16930,7 @@
         <v>1.13</v>
       </c>
       <c r="AB85">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC85">
         <v>1.09</v>
@@ -16939,7 +16939,7 @@
         <v>5.25</v>
       </c>
       <c r="AE85">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AF85">
         <v>2.49</v>
@@ -16957,10 +16957,10 @@
         <v>1.23</v>
       </c>
       <c r="AK85">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AL85">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AM85">
         <v>1.19</v>
@@ -16972,40 +16972,40 @@
         <v>0</v>
       </c>
       <c r="AP85">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AQ85">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AR85">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AS85">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AT85">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="AU85">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="AV85">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="AW85">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AX85">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AY85">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AZ85">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BA85">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="BB85">
         <v>1.09</v>
@@ -17079,13 +17079,13 @@
         <v>308</v>
       </c>
       <c r="P86">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q86">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="R86">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="S86">
         <v>2.81</v>
@@ -17094,7 +17094,7 @@
         <v>1.78</v>
       </c>
       <c r="U86">
-        <v>5.04</v>
+        <v>5.31</v>
       </c>
       <c r="V86">
         <v>1.63</v>
@@ -17121,10 +17121,10 @@
         <v>1.57</v>
       </c>
       <c r="AD86">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AE86">
-        <v>2.45</v>
+        <v>2.66</v>
       </c>
       <c r="AF86">
         <v>1.38</v>
@@ -17142,13 +17142,13 @@
         <v>1.03</v>
       </c>
       <c r="AK86">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AL86">
         <v>1.55</v>
       </c>
       <c r="AM86">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AN86">
         <v>1.65</v>
@@ -17225,7 +17225,7 @@
         <v>89</v>
       </c>
       <c r="C87" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D87" t="s">
         <v>136</v>
@@ -17264,79 +17264,79 @@
         <v>308</v>
       </c>
       <c r="P87">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="Q87">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="R87">
-        <v>4.01</v>
+        <v>4</v>
       </c>
       <c r="S87">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T87">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U87">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="V87">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W87">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="X87">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="Y87">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z87">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AA87">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB87">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC87">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD87">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AE87">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF87">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG87">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH87">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI87">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ87">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK87">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL87">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM87">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN87">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AO87">
         <v>0</v>
@@ -17378,19 +17378,19 @@
         <v>0</v>
       </c>
       <c r="BB87">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC87">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BD87">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="BE87">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BF87">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG87">
         <v>0</v>

--- a/jogos_2026-05-04.xlsx
+++ b/jogos_2026-05-04.xlsx
@@ -307,81 +307,81 @@
     <t>Uzbekistan Uzbekistan Super League</t>
   </si>
   <si>
+    <t>Serbia Prva Liga</t>
+  </si>
+  <si>
+    <t>England Premier League</t>
+  </si>
+  <si>
     <t>Oman Professional League</t>
   </si>
   <si>
     <t>Egypt Egyptian Premier League</t>
   </si>
   <si>
-    <t>Serbia Prva Liga</t>
-  </si>
-  <si>
-    <t>England Premier League</t>
-  </si>
-  <si>
     <t>Russia FNL</t>
   </si>
   <si>
     <t>Romania Liga I</t>
   </si>
   <si>
+    <t>Serbia SuperLiga</t>
+  </si>
+  <si>
     <t>Tunisia Ligue 1</t>
   </si>
   <si>
-    <t>Serbia SuperLiga</t>
-  </si>
-  <si>
     <t>Azerbaijan Premyer Liqası</t>
   </si>
   <si>
+    <t>Poland 1. Liga</t>
+  </si>
+  <si>
+    <t>Republic of Ireland First Division</t>
+  </si>
+  <si>
     <t>Republic of Ireland Premier Division</t>
   </si>
   <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
     <t>Jordan Jordanian Pro League</t>
   </si>
   <si>
-    <t>Republic of Ireland First Division</t>
+    <t>Croatia Prva HNL</t>
   </si>
   <si>
     <t>Morocco Botola Pro</t>
   </si>
   <si>
-    <t>Croatia Prva HNL</t>
-  </si>
-  <si>
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
+    <t>Austria Bundesliga</t>
+  </si>
+  <si>
     <t>Italy Serie A</t>
   </si>
   <si>
     <t>Scotland Premiership</t>
   </si>
   <si>
-    <t>Austria Bundesliga</t>
-  </si>
-  <si>
     <t>Algeria Ligue 1</t>
   </si>
   <si>
+    <t>Denmark Superliga</t>
+  </si>
+  <si>
+    <t>Israel Israeli Premier League</t>
+  </si>
+  <si>
+    <t>Poland Ekstraklasa</t>
+  </si>
+  <si>
+    <t>Portugal LigaPro</t>
+  </si>
+  <si>
     <t>Sweden Allsvenskan</t>
   </si>
   <si>
-    <t>Denmark Superliga</t>
-  </si>
-  <si>
-    <t>Portugal LigaPro</t>
-  </si>
-  <si>
-    <t>Israel Israeli Premier League</t>
-  </si>
-  <si>
-    <t>Poland Ekstraklasa</t>
-  </si>
-  <si>
     <t>Norway Eliteserien</t>
   </si>
   <si>
@@ -439,12 +439,12 @@
     <t>Albirex Niigata S</t>
   </si>
   <si>
+    <t>Persijap</t>
+  </si>
+  <si>
     <t>Aston Villa Ladies</t>
   </si>
   <si>
-    <t>Persijap</t>
-  </si>
-  <si>
     <t>Mekelakeya</t>
   </si>
   <si>
@@ -457,102 +457,102 @@
     <t>Odisha FC</t>
   </si>
   <si>
+    <t>Lokomotiv</t>
+  </si>
+  <si>
+    <t>Stepojevac Vaga</t>
+  </si>
+  <si>
+    <t>Chelsea</t>
+  </si>
+  <si>
+    <t>Al Khabourah</t>
+  </si>
+  <si>
+    <t>Pharco</t>
+  </si>
+  <si>
+    <t>Ural</t>
+  </si>
+  <si>
+    <t>OFK Vršac</t>
+  </si>
+  <si>
     <t>Xorazm</t>
   </si>
   <si>
-    <t>Al Khabourah</t>
-  </si>
-  <si>
-    <t>Pharco</t>
-  </si>
-  <si>
-    <t>Stepojevac Vaga</t>
-  </si>
-  <si>
-    <t>Lokomotiv</t>
-  </si>
-  <si>
-    <t>OFK Vršac</t>
-  </si>
-  <si>
-    <t>Chelsea</t>
-  </si>
-  <si>
-    <t>Ural</t>
-  </si>
-  <si>
     <t>Unirea Slobozia</t>
   </si>
   <si>
+    <t>Radnik Surdulica</t>
+  </si>
+  <si>
     <t>CA Bizertin</t>
   </si>
   <si>
     <t>Monastir</t>
   </si>
   <si>
-    <t>Radnik Surdulica</t>
-  </si>
-  <si>
     <t>Zarzis</t>
   </si>
   <si>
+    <t>Jeunesse Sportive Omrane</t>
+  </si>
+  <si>
     <t>Nasaf</t>
   </si>
   <si>
-    <t>Jeunesse Sportive Omrane</t>
-  </si>
-  <si>
     <t>Al Nasr</t>
   </si>
   <si>
     <t>Qarabağ</t>
   </si>
   <si>
+    <t>Polonia Bytom</t>
+  </si>
+  <si>
+    <t>Finn Harps</t>
+  </si>
+  <si>
+    <t>Cobh Ramblers</t>
+  </si>
+  <si>
+    <t>Longford Town</t>
+  </si>
+  <si>
+    <t>Waterford</t>
+  </si>
+  <si>
+    <t>Treaty United</t>
+  </si>
+  <si>
+    <t>Bohemians</t>
+  </si>
+  <si>
     <t>Sligo Rovers</t>
   </si>
   <si>
-    <t>Polonia Bytom</t>
-  </si>
-  <si>
-    <t>Waterford</t>
+    <t>Al Jazeera</t>
+  </si>
+  <si>
+    <t>Shamrock Rovers</t>
+  </si>
+  <si>
+    <t>Kerry</t>
+  </si>
+  <si>
+    <t>Istra 1961</t>
   </si>
   <si>
     <t>Derry City</t>
   </si>
   <si>
-    <t>Bohemians</t>
+    <t>Hassania Agadir</t>
   </si>
   <si>
     <t>Al Ahli</t>
   </si>
   <si>
-    <t>Shamrock Rovers</t>
-  </si>
-  <si>
-    <t>Kerry</t>
-  </si>
-  <si>
-    <t>Hassania Agadir</t>
-  </si>
-  <si>
-    <t>Longford Town</t>
-  </si>
-  <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
-    <t>Treaty United</t>
-  </si>
-  <si>
-    <t>Istra 1961</t>
-  </si>
-  <si>
-    <t>Cobh Ramblers</t>
-  </si>
-  <si>
-    <t>Al Jazeera</t>
-  </si>
-  <si>
     <t>Al Feiha</t>
   </si>
   <si>
@@ -562,66 +562,66 @@
     <t>Arsenal Tula</t>
   </si>
   <si>
+    <t>Rheindorf Altach</t>
+  </si>
+  <si>
     <t>Cremonese</t>
   </si>
   <si>
     <t>Hearts</t>
   </si>
   <si>
-    <t>Rheindorf Altach</t>
-  </si>
-  <si>
     <t>CR Belouizdad</t>
   </si>
   <si>
+    <t>Midtjylland</t>
+  </si>
+  <si>
+    <t>Maccabi Netanya</t>
+  </si>
+  <si>
+    <t>Wadi Degla</t>
+  </si>
+  <si>
+    <t>Čukarički</t>
+  </si>
+  <si>
+    <t>Radomiak Radom</t>
+  </si>
+  <si>
+    <t>Bnei Sakhnin</t>
+  </si>
+  <si>
+    <t>Torreense</t>
+  </si>
+  <si>
+    <t>Djurgården</t>
+  </si>
+  <si>
+    <t>FK Bodo - Glimt</t>
+  </si>
+  <si>
     <t>Halmstad</t>
   </si>
   <si>
-    <t>Midtjylland</t>
+    <t>Porto II</t>
   </si>
   <si>
     <t>Al Ittihad</t>
   </si>
   <si>
-    <t>Wadi Degla</t>
-  </si>
-  <si>
-    <t>Djurgården</t>
-  </si>
-  <si>
-    <t>Torreense</t>
-  </si>
-  <si>
-    <t>Bnei Sakhnin</t>
-  </si>
-  <si>
-    <t>Čukarički</t>
-  </si>
-  <si>
-    <t>Maccabi Netanya</t>
-  </si>
-  <si>
-    <t>Radomiak Radom</t>
-  </si>
-  <si>
-    <t>FK Bodo - Glimt</t>
-  </si>
-  <si>
-    <t>Porto II</t>
-  </si>
-  <si>
     <t>Landskrona</t>
   </si>
   <si>
+    <t>Víkingur</t>
+  </si>
+  <si>
+    <t>B36</t>
+  </si>
+  <si>
     <t>Rapid Bucureşti</t>
   </si>
   <si>
-    <t>B36</t>
-  </si>
-  <si>
-    <t>Víkingur</t>
-  </si>
-  <si>
     <t>Yacoub El Mansour</t>
   </si>
   <si>
@@ -631,12 +631,12 @@
     <t>Vasas</t>
   </si>
   <si>
+    <t>LASK Linz</t>
+  </si>
+  <si>
     <t>Almería</t>
   </si>
   <si>
-    <t>LASK Linz</t>
-  </si>
-  <si>
     <t>Roma</t>
   </si>
   <si>
@@ -661,15 +661,15 @@
     <t>San Luis</t>
   </si>
   <si>
+    <t>Figueirense</t>
+  </si>
+  <si>
+    <t>Ypiranga Erechim</t>
+  </si>
+  <si>
     <t>Floresta</t>
   </si>
   <si>
-    <t>Figueirense</t>
-  </si>
-  <si>
-    <t>Ypiranga Erechim</t>
-  </si>
-  <si>
     <t>Quilmes</t>
   </si>
   <si>
@@ -694,12 +694,12 @@
     <t>Young Lions</t>
   </si>
   <si>
+    <t>Persija</t>
+  </si>
+  <si>
     <t>West Ham United Women</t>
   </si>
   <si>
-    <t>Persija</t>
-  </si>
-  <si>
     <t>Adama Kenema</t>
   </si>
   <si>
@@ -712,102 +712,102 @@
     <t>Bengaluru</t>
   </si>
   <si>
+    <t>Qizilqum</t>
+  </si>
+  <si>
+    <t>Kabel Novi Sad</t>
+  </si>
+  <si>
+    <t>Nottingham Forest</t>
+  </si>
+  <si>
+    <t>Saham</t>
+  </si>
+  <si>
+    <t>Al Mokawloon</t>
+  </si>
+  <si>
+    <t>Shinnik</t>
+  </si>
+  <si>
+    <t>Jedinstvo Ub</t>
+  </si>
+  <si>
     <t>Andijan</t>
   </si>
   <si>
-    <t>Saham</t>
-  </si>
-  <si>
-    <t>Al Mokawloon</t>
-  </si>
-  <si>
-    <t>Kabel Novi Sad</t>
-  </si>
-  <si>
-    <t>Qizilqum</t>
-  </si>
-  <si>
-    <t>Jedinstvo Ub</t>
-  </si>
-  <si>
-    <t>Nottingham Forest</t>
-  </si>
-  <si>
-    <t>Shinnik</t>
-  </si>
-  <si>
     <t>Hermannstadt</t>
   </si>
   <si>
+    <t>Vojvodina</t>
+  </si>
+  <si>
     <t>Marsa</t>
   </si>
   <si>
     <t>Métlaoui</t>
   </si>
   <si>
-    <t>Vojvodina</t>
-  </si>
-  <si>
     <t>Etoile du Sahel</t>
   </si>
   <si>
+    <t>ES Tunis</t>
+  </si>
+  <si>
     <t>Navbahor</t>
   </si>
   <si>
-    <t>ES Tunis</t>
-  </si>
-  <si>
     <t>Al-Nahda</t>
   </si>
   <si>
     <t>Turan</t>
   </si>
   <si>
+    <t>Polonia Warszawa</t>
+  </si>
+  <si>
+    <t>Bray Wanderers</t>
+  </si>
+  <si>
+    <t>UCD</t>
+  </si>
+  <si>
+    <t>Athlone Town</t>
+  </si>
+  <si>
+    <t>Dundalk</t>
+  </si>
+  <si>
+    <t>Wexford</t>
+  </si>
+  <si>
+    <t>Shelbourne</t>
+  </si>
+  <si>
     <t>St Patrick's Athl.</t>
   </si>
   <si>
-    <t>Polonia Warszawa</t>
-  </si>
-  <si>
-    <t>Dundalk</t>
+    <t>Shabab Al Ordon</t>
+  </si>
+  <si>
+    <t>Drogheda United</t>
+  </si>
+  <si>
+    <t>Cork City</t>
+  </si>
+  <si>
+    <t>Slaven Koprivnica</t>
   </si>
   <si>
     <t>Galway United</t>
   </si>
   <si>
-    <t>Shelbourne</t>
+    <t>Olympic Safi</t>
   </si>
   <si>
     <t>Al Buqa'a</t>
   </si>
   <si>
-    <t>Drogheda United</t>
-  </si>
-  <si>
-    <t>Cork City</t>
-  </si>
-  <si>
-    <t>Olympic Safi</t>
-  </si>
-  <si>
-    <t>Athlone Town</t>
-  </si>
-  <si>
-    <t>Bray Wanderers</t>
-  </si>
-  <si>
-    <t>Wexford</t>
-  </si>
-  <si>
-    <t>Slaven Koprivnica</t>
-  </si>
-  <si>
-    <t>UCD</t>
-  </si>
-  <si>
-    <t>Shabab Al Ordon</t>
-  </si>
-  <si>
     <t>Al Riyadh</t>
   </si>
   <si>
@@ -817,84 +817,84 @@
     <t>Rotor Volgograd</t>
   </si>
   <si>
+    <t>Wolfsberger AC</t>
+  </si>
+  <si>
     <t>Lazio</t>
   </si>
   <si>
     <t>Rangers</t>
   </si>
   <si>
-    <t>Wolfsberger AC</t>
-  </si>
-  <si>
     <t>USM Khenchela</t>
   </si>
   <si>
+    <t>Viborg</t>
+  </si>
+  <si>
+    <t>Hapoel Katamon</t>
+  </si>
+  <si>
+    <t>Kahraba Ismailia</t>
+  </si>
+  <si>
+    <t>Red Star Belgrade</t>
+  </si>
+  <si>
+    <t>Lechia Gdańsk</t>
+  </si>
+  <si>
+    <t>Maccabi Bnei Raina</t>
+  </si>
+  <si>
+    <t>FC Penafiel</t>
+  </si>
+  <si>
+    <t>IFK Göteborg</t>
+  </si>
+  <si>
+    <t>Molde</t>
+  </si>
+  <si>
     <t>Brommapojkarna</t>
   </si>
   <si>
-    <t>Viborg</t>
+    <t>Felgueiras 1932</t>
   </si>
   <si>
     <t>Petrojet</t>
   </si>
   <si>
-    <t>Kahraba Ismailia</t>
-  </si>
-  <si>
-    <t>IFK Göteborg</t>
-  </si>
-  <si>
-    <t>FC Penafiel</t>
-  </si>
-  <si>
-    <t>Maccabi Bnei Raina</t>
-  </si>
-  <si>
-    <t>Red Star Belgrade</t>
-  </si>
-  <si>
-    <t>Hapoel Katamon</t>
-  </si>
-  <si>
-    <t>Lechia Gdańsk</t>
-  </si>
-  <si>
-    <t>Molde</t>
-  </si>
-  <si>
-    <t>Felgueiras 1932</t>
-  </si>
-  <si>
     <t>Öster</t>
   </si>
   <si>
+    <t>07 Vestur</t>
+  </si>
+  <si>
+    <t>NSÍ</t>
+  </si>
+  <si>
     <t>CFR Cluj</t>
   </si>
   <si>
-    <t>NSÍ</t>
-  </si>
-  <si>
-    <t>07 Vestur</t>
-  </si>
-  <si>
     <t>RSB Berkane</t>
   </si>
   <si>
+    <t>Al Kholood</t>
+  </si>
+  <si>
     <t>Al Najma</t>
   </si>
   <si>
     <t>Budafoki MTE</t>
   </si>
   <si>
-    <t>Al Kholood</t>
+    <t>Rapid Wien</t>
   </si>
   <si>
     <t>Mirandés</t>
   </si>
   <si>
-    <t>Rapid Wien</t>
-  </si>
-  <si>
     <t>Fiorentina</t>
   </si>
   <si>
@@ -919,13 +919,13 @@
     <t>Unión San Felipe</t>
   </si>
   <si>
+    <t>Barra do Garcas</t>
+  </si>
+  <si>
+    <t>Ituano</t>
+  </si>
+  <si>
     <t>Maranhão</t>
-  </si>
-  <si>
-    <t>Barra do Garcas</t>
-  </si>
-  <si>
-    <t>Ituano</t>
   </si>
   <si>
     <t>Chacarita Juniors</t>
@@ -1539,13 +1539,13 @@
         <v>308</v>
       </c>
       <c r="P2">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Q2">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="R2">
-        <v>8.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S2">
         <v>1.72</v>
@@ -1569,7 +1569,7 @@
         <v>1.47</v>
       </c>
       <c r="Z2">
-        <v>5.8</v>
+        <v>5.35</v>
       </c>
       <c r="AA2">
         <v>1.09</v>
@@ -1578,13 +1578,13 @@
         <v>1</v>
       </c>
       <c r="AC2">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AD2">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="AE2">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AF2">
         <v>2.1</v>
@@ -1754,7 +1754,7 @@
         <v>1.37</v>
       </c>
       <c r="Z3">
-        <v>6.65</v>
+        <v>6.7</v>
       </c>
       <c r="AA3">
         <v>1.05</v>
@@ -1769,7 +1769,7 @@
         <v>3.34</v>
       </c>
       <c r="AE3">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AF3">
         <v>1.84</v>
@@ -1781,7 +1781,7 @@
         <v>1.29</v>
       </c>
       <c r="AI3">
-        <v>5.88</v>
+        <v>5.75</v>
       </c>
       <c r="AJ3">
         <v>1.07</v>
@@ -1793,7 +1793,7 @@
         <v>2.02</v>
       </c>
       <c r="AM3">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AN3">
         <v>1.65</v>
@@ -1832,7 +1832,7 @@
         <v>1.31</v>
       </c>
       <c r="AZ3">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="BA3">
         <v>3.13</v>
@@ -1844,7 +1844,7 @@
         <v>2.03</v>
       </c>
       <c r="BD3">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="BE3">
         <v>1.68</v>
@@ -2240,7 +2240,7 @@
         <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
         <v>134</v>
@@ -2279,13 +2279,13 @@
         <v>308</v>
       </c>
       <c r="P6">
-        <v>2.17</v>
+        <v>4.2</v>
       </c>
       <c r="Q6">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="R6">
-        <v>2.83</v>
+        <v>1.6</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
         <v>134</v>
@@ -2464,13 +2464,13 @@
         <v>308</v>
       </c>
       <c r="P7">
-        <v>4.4</v>
+        <v>2.17</v>
       </c>
       <c r="Q7">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="R7">
-        <v>1.54</v>
+        <v>2.83</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -3759,133 +3759,133 @@
         <v>308</v>
       </c>
       <c r="P14">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="Q14">
-        <v>2.75</v>
+        <v>3.9</v>
       </c>
       <c r="R14">
+        <v>4.6</v>
+      </c>
+      <c r="S14">
+        <v>2.1</v>
+      </c>
+      <c r="T14">
+        <v>2.4</v>
+      </c>
+      <c r="U14">
+        <v>4.75</v>
+      </c>
+      <c r="V14">
+        <v>1.33</v>
+      </c>
+      <c r="W14">
+        <v>3.3</v>
+      </c>
+      <c r="X14">
+        <v>2.49</v>
+      </c>
+      <c r="Y14">
+        <v>1.53</v>
+      </c>
+      <c r="Z14">
+        <v>5.8</v>
+      </c>
+      <c r="AA14">
+        <v>1.1</v>
+      </c>
+      <c r="AB14">
+        <v>1.03</v>
+      </c>
+      <c r="AC14">
+        <v>1.17</v>
+      </c>
+      <c r="AD14">
+        <v>4.25</v>
+      </c>
+      <c r="AE14">
+        <v>1.67</v>
+      </c>
+      <c r="AF14">
+        <v>2.2</v>
+      </c>
+      <c r="AG14">
+        <v>2.65</v>
+      </c>
+      <c r="AH14">
+        <v>1.44</v>
+      </c>
+      <c r="AI14">
+        <v>4.75</v>
+      </c>
+      <c r="AJ14">
+        <v>1.13</v>
+      </c>
+      <c r="AK14">
+        <v>1.67</v>
+      </c>
+      <c r="AL14">
+        <v>2.15</v>
+      </c>
+      <c r="AM14">
+        <v>1.25</v>
+      </c>
+      <c r="AN14">
+        <v>2.15</v>
+      </c>
+      <c r="AO14">
+        <v>0</v>
+      </c>
+      <c r="AP14">
+        <v>1.16</v>
+      </c>
+      <c r="AQ14">
+        <v>1.3</v>
+      </c>
+      <c r="AR14">
+        <v>1.67</v>
+      </c>
+      <c r="AS14">
+        <v>1.89</v>
+      </c>
+      <c r="AT14">
         <v>2.37</v>
       </c>
-      <c r="S14">
-        <v>4.39</v>
-      </c>
-      <c r="T14">
-        <v>1.73</v>
-      </c>
-      <c r="U14">
-        <v>3.36</v>
-      </c>
-      <c r="V14">
-        <v>1.66</v>
-      </c>
-      <c r="